--- a/eBus_Functions/Post_Processing/Root_Cause_Analysis_Work/info/eBus_Model_Info.xlsx
+++ b/eBus_Functions/Post_Processing/Root_Cause_Analysis_Work/info/eBus_Model_Info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\TempData\Github\eBus_Tool\eBus_Functions\Post_Processing\Root_Cause_Analysis_Work\info\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6131672D-4ED9-4F7D-A61C-7B21708AF24E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F51235E-357C-439C-9754-B52EC84886CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="254">
   <si>
     <t>Driver</t>
   </si>
@@ -254,9 +254,6 @@
     <t>logout.mec_veh_FWheelTraaction_info</t>
   </si>
   <si>
-    <t>logout.pne_brk_Axle1_BrakingPower</t>
-  </si>
-  <si>
     <t>Battery Current</t>
   </si>
   <si>
@@ -791,7 +788,7 @@
     <t>aux_volt</t>
   </si>
   <si>
-    <t>aux_pwr</t>
+    <t>logout.pne_brk_Axle1_BrakingPower+logout.pne_brk_Axle2_BrakingPower+logout.pne_brk_Axle3_BrakingPower+logout.pne_brk_Axle4_BrakingPower</t>
   </si>
 </sst>
 </file>
@@ -1040,7 +1037,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1067,12 +1064,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1082,107 +1073,52 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="5">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1568,19 +1504,19 @@
   <sheetData>
     <row r="27" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="28" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G28" s="20" t="s">
+      <c r="G28" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="H28" s="21" t="s">
-        <v>97</v>
-      </c>
-      <c r="I28" s="22" t="s">
+      <c r="H28" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="I28" s="20" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="29" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G29" s="7"/>
-      <c r="H29" s="18" t="s">
+      <c r="H29" s="30" t="s">
         <v>6</v>
       </c>
       <c r="I29" s="8" t="s">
@@ -1589,14 +1525,14 @@
     </row>
     <row r="30" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G30" s="9"/>
-      <c r="H30" s="19"/>
+      <c r="H30" s="31"/>
       <c r="I30" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="31" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G31" s="10"/>
-      <c r="H31" s="26"/>
+      <c r="H31" s="32"/>
       <c r="I31" s="2" t="s">
         <v>33</v>
       </c>
@@ -1605,7 +1541,7 @@
       <c r="G32" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="H32" s="27" t="s">
+      <c r="H32" s="33" t="s">
         <v>0</v>
       </c>
       <c r="I32" s="8" t="s">
@@ -1616,7 +1552,7 @@
       <c r="G33" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H33" s="24"/>
+      <c r="H33" s="34"/>
       <c r="I33" s="1" t="s">
         <v>13</v>
       </c>
@@ -1625,56 +1561,56 @@
       <c r="G34" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="H34" s="24"/>
+      <c r="H34" s="34"/>
       <c r="I34" s="1"/>
     </row>
     <row r="35" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G35" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="H35" s="24"/>
+      <c r="H35" s="34"/>
       <c r="I35" s="1"/>
     </row>
     <row r="36" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G36" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="H36" s="24"/>
+        <v>199</v>
+      </c>
+      <c r="H36" s="34"/>
       <c r="I36" s="1"/>
     </row>
     <row r="37" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G37" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="H37" s="28"/>
+      <c r="H37" s="35"/>
       <c r="I37" s="2"/>
     </row>
     <row r="38" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G38" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="H38" s="18" t="s">
+      <c r="H38" s="30" t="s">
         <v>2</v>
       </c>
       <c r="I38" s="8" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="39" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G39" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="H39" s="26"/>
+      <c r="H39" s="32"/>
       <c r="I39" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="40" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G40" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="H40" s="27" t="s">
-        <v>117</v>
+        <v>191</v>
+      </c>
+      <c r="H40" s="33" t="s">
+        <v>116</v>
       </c>
       <c r="I40" s="8" t="s">
         <v>38</v>
@@ -1682,132 +1618,132 @@
     </row>
     <row r="41" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G41" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="H41" s="24"/>
+        <v>192</v>
+      </c>
+      <c r="H41" s="34"/>
       <c r="I41" s="1" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="42" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G42" s="9"/>
-      <c r="H42" s="24"/>
+      <c r="H42" s="34"/>
       <c r="I42" s="1" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="43" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G43" s="9"/>
-      <c r="H43" s="24"/>
+      <c r="H43" s="34"/>
       <c r="I43" s="1" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="44" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G44" s="9"/>
-      <c r="H44" s="24"/>
+      <c r="H44" s="34"/>
       <c r="I44" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="45" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G45" s="9"/>
-      <c r="H45" s="24"/>
+      <c r="H45" s="34"/>
       <c r="I45" s="1" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="46" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G46" s="9"/>
-      <c r="H46" s="24"/>
+      <c r="H46" s="34"/>
       <c r="I46" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="47" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G47" s="9"/>
-      <c r="H47" s="24"/>
+      <c r="H47" s="34"/>
       <c r="I47" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="48" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G48" s="9"/>
-      <c r="H48" s="24"/>
+      <c r="H48" s="34"/>
       <c r="I48" s="1" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="49" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G49" s="9"/>
-      <c r="H49" s="24"/>
+      <c r="H49" s="34"/>
       <c r="I49" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="50" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G50" s="9"/>
-      <c r="H50" s="24"/>
+      <c r="H50" s="34"/>
       <c r="I50" s="1" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="51" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G51" s="10"/>
-      <c r="H51" s="28"/>
+      <c r="H51" s="35"/>
       <c r="I51" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="52" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G52" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="H52" s="18" t="s">
-        <v>118</v>
+      <c r="H52" s="30" t="s">
+        <v>117</v>
       </c>
       <c r="I52" s="8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="53" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G53" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="H53" s="19"/>
+      <c r="H53" s="31"/>
       <c r="I53" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="54" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G54" s="9"/>
-      <c r="H54" s="19"/>
+      <c r="H54" s="31"/>
       <c r="I54" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="55" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G55" s="9"/>
-      <c r="H55" s="19"/>
+      <c r="H55" s="31"/>
       <c r="I55" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="56" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G56" s="9"/>
-      <c r="H56" s="19"/>
+      <c r="H56" s="31"/>
       <c r="I56" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="57" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G57" s="29" t="s">
-        <v>198</v>
-      </c>
-      <c r="H57" s="30" t="s">
+      <c r="G57" s="21" t="s">
+        <v>197</v>
+      </c>
+      <c r="H57" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="I57" s="31" t="s">
+      <c r="I57" s="23" t="s">
         <v>19</v>
       </c>
     </row>
@@ -1815,7 +1751,7 @@
       <c r="G58" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="H58" s="19" t="s">
+      <c r="H58" s="31" t="s">
         <v>20</v>
       </c>
       <c r="I58" s="1" t="s">
@@ -1824,42 +1760,42 @@
     </row>
     <row r="59" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G59" s="9"/>
-      <c r="H59" s="19"/>
+      <c r="H59" s="31"/>
       <c r="I59" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="60" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G60" s="9"/>
-      <c r="H60" s="19"/>
+      <c r="H60" s="31"/>
       <c r="I60" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="61" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G61" s="9"/>
-      <c r="H61" s="19"/>
+      <c r="H61" s="31"/>
       <c r="I61" s="1" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="62" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G62" s="9"/>
-      <c r="H62" s="19"/>
+      <c r="H62" s="31"/>
       <c r="I62" s="1" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="63" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G63" s="9"/>
-      <c r="H63" s="19"/>
+      <c r="H63" s="31"/>
       <c r="I63" s="1" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="64" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G64" s="9"/>
-      <c r="H64" s="19"/>
+      <c r="H64" s="31"/>
       <c r="I64" s="1" t="s">
         <v>73</v>
       </c>
@@ -1868,135 +1804,135 @@
       <c r="G65" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="H65" s="27" t="s">
-        <v>119</v>
+      <c r="H65" s="33" t="s">
+        <v>118</v>
       </c>
       <c r="I65" s="8" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="66" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G66" s="10"/>
-      <c r="H66" s="28"/>
+      <c r="H66" s="35"/>
       <c r="I66" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="67" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G67" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="H67" s="19" t="s">
-        <v>120</v>
+      <c r="H67" s="31" t="s">
+        <v>119</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="68" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G68" s="9"/>
-      <c r="H68" s="19"/>
+      <c r="H68" s="31"/>
       <c r="I68" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="69" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G69" s="9"/>
-      <c r="H69" s="19"/>
+      <c r="H69" s="31"/>
       <c r="I69" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="70" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G70" s="9"/>
-      <c r="H70" s="19"/>
+      <c r="H70" s="31"/>
       <c r="I70" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="71" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G71" s="9"/>
-      <c r="H71" s="19"/>
+      <c r="H71" s="31"/>
       <c r="I71" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="72" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G72" s="9"/>
-      <c r="H72" s="19"/>
+      <c r="H72" s="31"/>
       <c r="I72" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="73" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G73" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="H73" s="27" t="s">
-        <v>121</v>
+      <c r="H73" s="33" t="s">
+        <v>120</v>
       </c>
       <c r="I73" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="74" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G74" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="H74" s="24"/>
+        <v>84</v>
+      </c>
+      <c r="H74" s="34"/>
       <c r="I74" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="75" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G75" s="9"/>
-      <c r="H75" s="24"/>
+      <c r="H75" s="34"/>
       <c r="I75" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="76" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G76" s="10"/>
-      <c r="H76" s="28"/>
+      <c r="H76" s="35"/>
       <c r="I76" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="77" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G77" s="9"/>
-      <c r="H77" s="19" t="s">
-        <v>122</v>
-      </c>
-      <c r="I77" s="32" t="s">
-        <v>204</v>
+      <c r="H77" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="I77" s="1" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="78" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G78" s="9"/>
-      <c r="H78" s="19"/>
-      <c r="I78" s="32" t="s">
-        <v>205</v>
+      <c r="H78" s="31"/>
+      <c r="I78" s="1" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="79" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G79" s="10"/>
-      <c r="H79" s="26"/>
-      <c r="I79" s="33" t="s">
-        <v>206</v>
+      <c r="H79" s="32"/>
+      <c r="I79" s="2" t="s">
+        <v>205</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="H67:H72"/>
+    <mergeCell ref="H73:H76"/>
+    <mergeCell ref="H52:H56"/>
+    <mergeCell ref="H58:H64"/>
+    <mergeCell ref="H77:H79"/>
     <mergeCell ref="H29:H31"/>
     <mergeCell ref="H32:H37"/>
     <mergeCell ref="H38:H39"/>
     <mergeCell ref="H40:H51"/>
     <mergeCell ref="H65:H66"/>
-    <mergeCell ref="H67:H72"/>
-    <mergeCell ref="H73:H76"/>
-    <mergeCell ref="H52:H56"/>
-    <mergeCell ref="H58:H64"/>
-    <mergeCell ref="H77:H79"/>
   </mergeCells>
   <conditionalFormatting sqref="I29:I79 G29:G79">
     <cfRule type="duplicateValues" dxfId="4" priority="1"/>
@@ -2009,1036 +1945,1009 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFA16316-83DB-41C7-8B25-B191695DD108}">
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28" style="40" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19" style="41" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.6640625" style="42" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="46.44140625" style="40" bestFit="1" customWidth="1"/>
-    <col min="6" max="9" width="17.21875" style="23" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28" style="28" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.6640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="46.44140625" style="28" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="17.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="24" t="s">
         <v>97</v>
       </c>
-      <c r="B1" s="34" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="D1" s="35" t="s">
-        <v>98</v>
-      </c>
-      <c r="E1" s="34" t="s">
+      <c r="E1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="F1" s="34" t="s">
+      <c r="F1" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="G1" s="34" t="s">
+      <c r="G1" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="H1" s="34" t="s">
+      <c r="H1" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="I1" s="34" t="s">
+      <c r="I1" s="5" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="B2" s="23" t="s">
+        <v>99</v>
+      </c>
+      <c r="B2" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="36" t="s">
-        <v>109</v>
-      </c>
-      <c r="D2" s="37" t="s">
-        <v>99</v>
-      </c>
-      <c r="E2" s="37" t="s">
+      <c r="C2" s="25" t="s">
+        <v>108</v>
+      </c>
+      <c r="D2" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="E2" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="B3" s="23" t="s">
+        <v>99</v>
+      </c>
+      <c r="B3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="36" t="s">
+      <c r="C3" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="37" t="s">
-        <v>209</v>
-      </c>
-      <c r="E3" s="37" t="s">
+      <c r="D3" s="26" t="s">
+        <v>208</v>
+      </c>
+      <c r="E3" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="B4" s="23" t="s">
+        <v>99</v>
+      </c>
+      <c r="B4" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="36" t="s">
+      <c r="C4" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="D4" s="37" t="s">
-        <v>210</v>
-      </c>
-      <c r="E4" s="37" t="s">
+      <c r="D4" s="26" t="s">
+        <v>209</v>
+      </c>
+      <c r="E4" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="B5" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="B5" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="36" t="s">
+      <c r="C5" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="37" t="s">
-        <v>211</v>
-      </c>
-      <c r="E5" s="37" t="s">
+      <c r="D5" s="26" t="s">
+        <v>210</v>
+      </c>
+      <c r="E5" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="38"/>
-      <c r="G5" s="38"/>
-      <c r="H5" s="38"/>
-      <c r="I5" s="38"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="B6" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="B6" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="36" t="s">
+      <c r="C6" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="37" t="s">
-        <v>212</v>
-      </c>
-      <c r="E6" s="37" t="s">
+      <c r="D6" s="26" t="s">
+        <v>211</v>
+      </c>
+      <c r="E6" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="F6" s="38"/>
-      <c r="G6" s="38"/>
-      <c r="H6" s="38"/>
-      <c r="I6" s="38"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="B7" s="23" t="s">
-        <v>192</v>
-      </c>
-      <c r="C7" s="36" t="s">
+        <v>107</v>
+      </c>
+      <c r="B7" t="s">
+        <v>191</v>
+      </c>
+      <c r="C7" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="D7" s="37" t="s">
-        <v>213</v>
-      </c>
-      <c r="E7" s="37" t="s">
-        <v>207</v>
-      </c>
-      <c r="F7" s="38"/>
-      <c r="G7" s="38"/>
-      <c r="H7" s="38"/>
-      <c r="I7" s="38"/>
+      <c r="D7" s="26" t="s">
+        <v>212</v>
+      </c>
+      <c r="E7" s="26" t="s">
+        <v>206</v>
+      </c>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="B8" s="23" t="s">
-        <v>193</v>
-      </c>
-      <c r="C8" s="36" t="s">
+        <v>107</v>
+      </c>
+      <c r="B8" t="s">
+        <v>192</v>
+      </c>
+      <c r="C8" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="37" t="s">
-        <v>214</v>
-      </c>
-      <c r="E8" s="37" t="s">
-        <v>207</v>
-      </c>
-      <c r="F8" s="38"/>
-      <c r="G8" s="38"/>
-      <c r="H8" s="38"/>
-      <c r="I8" s="38"/>
+      <c r="D8" s="26" t="s">
+        <v>213</v>
+      </c>
+      <c r="E8" s="26" t="s">
+        <v>206</v>
+      </c>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="B9" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="B9" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="36" t="s">
+      <c r="C9" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="D9" s="37" t="s">
-        <v>215</v>
-      </c>
-      <c r="E9" s="37" t="s">
+      <c r="D9" s="26" t="s">
+        <v>214</v>
+      </c>
+      <c r="E9" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="F9" s="38"/>
-      <c r="G9" s="38"/>
-      <c r="H9" s="38"/>
-      <c r="I9" s="38"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="B10" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="B10" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="36" t="s">
+      <c r="C10" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="D10" s="37" t="s">
-        <v>216</v>
-      </c>
-      <c r="E10" s="37" t="s">
+      <c r="D10" s="26" t="s">
+        <v>215</v>
+      </c>
+      <c r="E10" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="F10" s="39"/>
-      <c r="G10" s="38"/>
-      <c r="H10" s="38"/>
-      <c r="I10" s="38"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="B11" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="B11" t="s">
         <v>42</v>
       </c>
-      <c r="C11" s="36" t="s">
+      <c r="C11" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="D11" s="37" t="s">
-        <v>217</v>
-      </c>
-      <c r="E11" s="37" t="s">
+      <c r="D11" s="26" t="s">
+        <v>216</v>
+      </c>
+      <c r="E11" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="F11" s="38"/>
-      <c r="G11" s="38"/>
-      <c r="H11" s="38"/>
-      <c r="I11" s="38"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="B12" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="B12" t="s">
         <v>44</v>
       </c>
-      <c r="C12" s="36" t="s">
+      <c r="C12" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="D12" s="37" t="s">
-        <v>218</v>
-      </c>
-      <c r="E12" s="37" t="s">
+      <c r="D12" s="26" t="s">
+        <v>217</v>
+      </c>
+      <c r="E12" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="F12" s="38"/>
-      <c r="G12" s="38"/>
-      <c r="H12" s="38"/>
-      <c r="I12" s="38"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="B13" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="B13" t="s">
         <v>46</v>
       </c>
-      <c r="C13" s="36" t="s">
+      <c r="C13" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="D13" s="37" t="s">
-        <v>219</v>
-      </c>
-      <c r="E13" s="37" t="s">
+      <c r="D13" s="26" t="s">
+        <v>218</v>
+      </c>
+      <c r="E13" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="F13" s="38"/>
-      <c r="G13" s="38"/>
-      <c r="H13" s="38"/>
-      <c r="I13" s="38"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="B14" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="B14" t="s">
         <v>48</v>
       </c>
-      <c r="C14" s="36" t="s">
+      <c r="C14" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="D14" s="37" t="s">
-        <v>220</v>
-      </c>
-      <c r="E14" s="37" t="s">
+      <c r="D14" s="26" t="s">
+        <v>219</v>
+      </c>
+      <c r="E14" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="F14" s="38"/>
-      <c r="G14" s="38"/>
-      <c r="H14" s="38"/>
-      <c r="I14" s="38"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="B15" s="23" t="s">
-        <v>194</v>
-      </c>
-      <c r="C15" s="36" t="s">
+        <v>105</v>
+      </c>
+      <c r="B15" t="s">
+        <v>193</v>
+      </c>
+      <c r="C15" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="D15" s="37" t="s">
-        <v>221</v>
-      </c>
-      <c r="E15" s="37" t="s">
+      <c r="D15" s="26" t="s">
+        <v>220</v>
+      </c>
+      <c r="E15" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="F15" s="38"/>
-      <c r="G15" s="38"/>
-      <c r="H15" s="38"/>
-      <c r="I15" s="38"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="B16" s="23" t="s">
-        <v>195</v>
-      </c>
-      <c r="C16" s="36" t="s">
+        <v>105</v>
+      </c>
+      <c r="B16" t="s">
+        <v>194</v>
+      </c>
+      <c r="C16" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="D16" s="37" t="s">
-        <v>222</v>
-      </c>
-      <c r="E16" s="37" t="s">
+      <c r="D16" s="26" t="s">
+        <v>221</v>
+      </c>
+      <c r="E16" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="F16" s="38"/>
-      <c r="G16" s="38"/>
-      <c r="H16" s="38"/>
-      <c r="I16" s="38"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="B17" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="B17" t="s">
         <v>52</v>
       </c>
-      <c r="C17" s="36" t="s">
+      <c r="C17" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="D17" s="37" t="s">
-        <v>223</v>
-      </c>
-      <c r="E17" s="37" t="s">
+      <c r="D17" s="26" t="s">
+        <v>222</v>
+      </c>
+      <c r="E17" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="F17" s="38"/>
-      <c r="G17" s="38"/>
-      <c r="H17" s="38"/>
-      <c r="I17" s="38"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="B18" s="23" t="s">
-        <v>196</v>
-      </c>
-      <c r="C18" s="36" t="s">
+        <v>105</v>
+      </c>
+      <c r="B18" t="s">
+        <v>195</v>
+      </c>
+      <c r="C18" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="D18" s="37" t="s">
-        <v>224</v>
-      </c>
-      <c r="E18" s="37" t="s">
+      <c r="D18" s="26" t="s">
+        <v>223</v>
+      </c>
+      <c r="E18" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="F18" s="38"/>
-      <c r="G18" s="38"/>
-      <c r="H18" s="38"/>
-      <c r="I18" s="38"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="B19" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="B19" t="s">
         <v>55</v>
       </c>
-      <c r="C19" s="36" t="s">
+      <c r="C19" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="D19" s="37" t="s">
-        <v>225</v>
-      </c>
-      <c r="E19" s="37" t="s">
+      <c r="D19" s="26" t="s">
+        <v>224</v>
+      </c>
+      <c r="E19" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="F19" s="38"/>
-      <c r="G19" s="38"/>
-      <c r="H19" s="38"/>
-      <c r="I19" s="38"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="6"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="B20" s="23" t="s">
-        <v>197</v>
-      </c>
-      <c r="C20" s="36" t="s">
+        <v>105</v>
+      </c>
+      <c r="B20" t="s">
+        <v>196</v>
+      </c>
+      <c r="C20" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="D20" s="37" t="s">
-        <v>226</v>
-      </c>
-      <c r="E20" s="37" t="s">
+      <c r="D20" s="26" t="s">
+        <v>225</v>
+      </c>
+      <c r="E20" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="F20" s="38"/>
-      <c r="G20" s="38"/>
-      <c r="H20" s="38"/>
-      <c r="I20" s="38"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="6"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="B21" s="23" t="s">
-        <v>198</v>
-      </c>
-      <c r="C21" s="36" t="s">
+        <v>104</v>
+      </c>
+      <c r="B21" t="s">
+        <v>197</v>
+      </c>
+      <c r="C21" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="D21" s="37" t="s">
-        <v>227</v>
-      </c>
-      <c r="E21" s="37" t="s">
-        <v>39</v>
-      </c>
-      <c r="F21" s="38"/>
-      <c r="G21" s="38"/>
-      <c r="H21" s="38"/>
-      <c r="I21" s="38"/>
+      <c r="D21" s="26" t="s">
+        <v>226</v>
+      </c>
+      <c r="E21" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="6"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="B22" s="23" t="s">
-        <v>199</v>
-      </c>
-      <c r="C22" s="36" t="s">
+        <v>104</v>
+      </c>
+      <c r="B22" t="s">
+        <v>198</v>
+      </c>
+      <c r="C22" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="D22" s="37" t="s">
-        <v>228</v>
-      </c>
-      <c r="E22" s="37" t="s">
-        <v>41</v>
-      </c>
-      <c r="F22" s="38"/>
-      <c r="G22" s="38"/>
-      <c r="H22" s="38"/>
-      <c r="I22" s="38"/>
+      <c r="D22" s="26" t="s">
+        <v>227</v>
+      </c>
+      <c r="E22" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="B23" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="B23" t="s">
         <v>16</v>
       </c>
-      <c r="C23" s="36"/>
-      <c r="D23" s="37" t="s">
-        <v>229</v>
-      </c>
-      <c r="E23" s="37" t="s">
-        <v>58</v>
-      </c>
-      <c r="F23" s="38"/>
-      <c r="G23" s="38"/>
-      <c r="H23" s="38"/>
-      <c r="I23" s="38"/>
+      <c r="C23" s="25"/>
+      <c r="D23" s="26" t="s">
+        <v>228</v>
+      </c>
+      <c r="E23" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="6"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="B24" s="23" t="s">
-        <v>200</v>
-      </c>
-      <c r="C24" s="36"/>
-      <c r="D24" s="37" t="s">
-        <v>230</v>
-      </c>
-      <c r="E24" s="37" t="s">
-        <v>59</v>
-      </c>
-      <c r="F24" s="38"/>
-      <c r="G24" s="38"/>
-      <c r="H24" s="38"/>
-      <c r="I24" s="38"/>
+        <v>104</v>
+      </c>
+      <c r="B24" t="s">
+        <v>199</v>
+      </c>
+      <c r="C24" s="25"/>
+      <c r="D24" s="26" t="s">
+        <v>229</v>
+      </c>
+      <c r="E24" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="6"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="B25" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="B25" t="s">
         <v>17</v>
       </c>
-      <c r="C25" s="36" t="s">
+      <c r="C25" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="D25" s="37" t="s">
-        <v>231</v>
-      </c>
-      <c r="E25" s="37" t="s">
-        <v>60</v>
-      </c>
-      <c r="F25" s="38"/>
-      <c r="G25" s="38"/>
-      <c r="H25" s="38"/>
-      <c r="I25" s="38"/>
+      <c r="D25" s="26" t="s">
+        <v>230</v>
+      </c>
+      <c r="E25" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="6"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="B26" s="23" t="s">
+      <c r="B26" t="s">
         <v>19</v>
       </c>
-      <c r="C26" s="36" t="s">
+      <c r="C26" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="D26" s="37" t="s">
-        <v>232</v>
-      </c>
-      <c r="E26" s="37" t="s">
-        <v>36</v>
-      </c>
-      <c r="F26" s="38"/>
-      <c r="G26" s="38"/>
-      <c r="H26" s="38"/>
-      <c r="I26" s="38"/>
+      <c r="D26" s="26" t="s">
+        <v>231</v>
+      </c>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="6"/>
+      <c r="I26" s="6"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="B27" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="B27" t="s">
         <v>21</v>
       </c>
-      <c r="C27" s="36" t="s">
+      <c r="C27" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="D27" s="37" t="s">
-        <v>233</v>
-      </c>
-      <c r="E27" s="37" t="s">
-        <v>61</v>
-      </c>
-      <c r="F27" s="38"/>
-      <c r="G27" s="38"/>
-      <c r="H27" s="38"/>
-      <c r="I27" s="38"/>
+      <c r="D27" s="26" t="s">
+        <v>232</v>
+      </c>
+      <c r="E27" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="F27" s="6"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="6"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="B28" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="B28" t="s">
         <v>22</v>
       </c>
-      <c r="C28" s="36" t="s">
-        <v>109</v>
-      </c>
-      <c r="D28" s="37" t="s">
-        <v>234</v>
-      </c>
-      <c r="E28" s="37"/>
-      <c r="F28" s="38"/>
-      <c r="G28" s="38"/>
-      <c r="H28" s="38"/>
-      <c r="I28" s="38"/>
+      <c r="C28" s="25" t="s">
+        <v>108</v>
+      </c>
+      <c r="D28" s="26" t="s">
+        <v>233</v>
+      </c>
+      <c r="E28" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="F28" s="6"/>
+      <c r="G28" s="6"/>
+      <c r="H28" s="6"/>
+      <c r="I28" s="6"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="B29" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="B29" t="s">
         <v>23</v>
       </c>
-      <c r="C29" s="36" t="s">
-        <v>208</v>
-      </c>
-      <c r="D29" s="37" t="s">
-        <v>235</v>
-      </c>
-      <c r="E29" s="37" t="s">
-        <v>63</v>
-      </c>
-      <c r="F29" s="38"/>
-      <c r="G29" s="38"/>
-      <c r="H29" s="38"/>
-      <c r="I29" s="38"/>
+      <c r="C29" s="25" t="s">
+        <v>207</v>
+      </c>
+      <c r="D29" s="26" t="s">
+        <v>234</v>
+      </c>
+      <c r="E29" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="F29" s="6"/>
+      <c r="G29" s="6"/>
+      <c r="H29" s="6"/>
+      <c r="I29" s="6"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="B30" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="B30" t="s">
         <v>66</v>
       </c>
-      <c r="C30" s="36" t="s">
+      <c r="C30" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="D30" s="37" t="s">
-        <v>236</v>
-      </c>
-      <c r="E30" s="37" t="s">
-        <v>64</v>
-      </c>
-      <c r="F30" s="38"/>
-      <c r="G30" s="38"/>
-      <c r="H30" s="38"/>
-      <c r="I30" s="38"/>
+      <c r="D30" s="26" t="s">
+        <v>235</v>
+      </c>
+      <c r="E30" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="F30" s="6"/>
+      <c r="G30" s="6"/>
+      <c r="H30" s="6"/>
+      <c r="I30" s="6"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="B31" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="B31" t="s">
         <v>68</v>
       </c>
-      <c r="C31" s="36" t="s">
+      <c r="C31" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="D31" s="37" t="s">
-        <v>237</v>
-      </c>
-      <c r="E31" s="37" t="s">
-        <v>65</v>
-      </c>
-      <c r="F31" s="38"/>
-      <c r="G31" s="38"/>
-      <c r="H31" s="38"/>
-      <c r="I31" s="38"/>
+      <c r="D31" s="26" t="s">
+        <v>236</v>
+      </c>
+      <c r="E31" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="F31" s="6"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="6"/>
+      <c r="I31" s="6"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="B32" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="B32" t="s">
         <v>71</v>
       </c>
-      <c r="C32" s="36" t="s">
+      <c r="C32" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="D32" s="37" t="s">
-        <v>238</v>
-      </c>
-      <c r="E32" s="37" t="s">
-        <v>67</v>
-      </c>
-      <c r="F32" s="38"/>
-      <c r="G32" s="38"/>
-      <c r="H32" s="38"/>
-      <c r="I32" s="38"/>
+      <c r="D32" s="26" t="s">
+        <v>237</v>
+      </c>
+      <c r="E32" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="F32" s="6"/>
+      <c r="G32" s="6"/>
+      <c r="H32" s="6"/>
+      <c r="I32" s="6"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="B33" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="B33" t="s">
         <v>73</v>
       </c>
-      <c r="C33" s="36" t="s">
+      <c r="C33" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="D33" s="37" t="s">
-        <v>239</v>
-      </c>
-      <c r="E33" s="37" t="s">
-        <v>70</v>
-      </c>
-      <c r="F33" s="38"/>
-      <c r="G33" s="38"/>
-      <c r="H33" s="38"/>
-      <c r="I33" s="38"/>
+      <c r="D33" s="26" t="s">
+        <v>238</v>
+      </c>
+      <c r="E33" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="F33" s="6"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="6"/>
+      <c r="I33" s="6"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="B34" s="23" t="s">
-        <v>201</v>
-      </c>
-      <c r="C34" s="36" t="s">
+        <v>103</v>
+      </c>
+      <c r="B34" t="s">
+        <v>200</v>
+      </c>
+      <c r="C34" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="D34" s="37" t="s">
-        <v>240</v>
-      </c>
-      <c r="E34" s="37" t="s">
-        <v>72</v>
-      </c>
-      <c r="F34" s="38"/>
-      <c r="G34" s="38"/>
-      <c r="H34" s="38"/>
-      <c r="I34" s="38"/>
+      <c r="D34" s="26" t="s">
+        <v>239</v>
+      </c>
+      <c r="F34" s="6"/>
+      <c r="G34" s="6"/>
+      <c r="H34" s="6"/>
+      <c r="I34" s="6"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="B35" s="23" t="s">
-        <v>202</v>
-      </c>
-      <c r="C35" s="36" t="s">
+        <v>103</v>
+      </c>
+      <c r="B35" t="s">
+        <v>201</v>
+      </c>
+      <c r="C35" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="D35" s="37" t="s">
-        <v>241</v>
-      </c>
-      <c r="E35" s="37" t="s">
-        <v>74</v>
-      </c>
-      <c r="F35" s="38"/>
-      <c r="G35" s="38"/>
-      <c r="H35" s="38"/>
-      <c r="I35" s="38"/>
+      <c r="D35" s="26" t="s">
+        <v>240</v>
+      </c>
+      <c r="E35" s="26" t="s">
+        <v>253</v>
+      </c>
+      <c r="F35" s="6"/>
+      <c r="G35" s="6"/>
+      <c r="H35" s="6"/>
+      <c r="I35" s="6"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="B36" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="B36" t="s">
+        <v>75</v>
+      </c>
+      <c r="C36" s="25" t="s">
         <v>76</v>
       </c>
-      <c r="C36" s="36" t="s">
+      <c r="D36" s="26" t="s">
+        <v>241</v>
+      </c>
+      <c r="E36" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="D36" s="37" t="s">
-        <v>242</v>
-      </c>
-      <c r="E36" s="37" t="s">
-        <v>75</v>
-      </c>
-      <c r="F36" s="38"/>
-      <c r="G36" s="38"/>
-      <c r="H36" s="38"/>
-      <c r="I36" s="38"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
+      <c r="H36" s="6"/>
+      <c r="I36" s="6"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="B37" s="23" t="s">
-        <v>203</v>
-      </c>
-      <c r="C37" s="36" t="s">
+        <v>100</v>
+      </c>
+      <c r="B37" t="s">
+        <v>202</v>
+      </c>
+      <c r="C37" s="25" t="s">
+        <v>78</v>
+      </c>
+      <c r="D37" s="26" t="s">
+        <v>242</v>
+      </c>
+      <c r="E37" s="26" t="s">
         <v>79</v>
       </c>
-      <c r="D37" s="37" t="s">
-        <v>243</v>
-      </c>
-      <c r="E37" s="37" t="s">
-        <v>78</v>
-      </c>
-      <c r="F37" s="38"/>
-      <c r="G37" s="38"/>
-      <c r="H37" s="38"/>
-      <c r="I37" s="38"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="6"/>
+      <c r="H37" s="6"/>
+      <c r="I37" s="6"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="B38" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="B38" t="s">
+        <v>80</v>
+      </c>
+      <c r="C38" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="D38" s="26" t="s">
+        <v>243</v>
+      </c>
+      <c r="E38" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="C38" s="36" t="s">
-        <v>4</v>
-      </c>
-      <c r="D38" s="37" t="s">
-        <v>244</v>
-      </c>
-      <c r="E38" s="37" t="s">
-        <v>80</v>
-      </c>
-      <c r="F38" s="38"/>
-      <c r="G38" s="38"/>
-      <c r="H38" s="38"/>
-      <c r="I38" s="38"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="6"/>
+      <c r="H38" s="6"/>
+      <c r="I38" s="6"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="B39" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="B39" t="s">
+        <v>82</v>
+      </c>
+      <c r="C39" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="D39" s="26" t="s">
+        <v>244</v>
+      </c>
+      <c r="E39" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="C39" s="36" t="s">
-        <v>4</v>
-      </c>
-      <c r="D39" s="37" t="s">
-        <v>245</v>
-      </c>
-      <c r="E39" s="37" t="s">
-        <v>82</v>
-      </c>
-      <c r="F39" s="38"/>
-      <c r="G39" s="38"/>
-      <c r="H39" s="38"/>
-      <c r="I39" s="38"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="6"/>
+      <c r="H39" s="6"/>
+      <c r="I39" s="6"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="B40" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="B40" t="s">
+        <v>84</v>
+      </c>
+      <c r="C40" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="D40" s="26" t="s">
+        <v>245</v>
+      </c>
+      <c r="E40" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="C40" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="D40" s="37" t="s">
-        <v>246</v>
-      </c>
-      <c r="E40" s="37" t="s">
-        <v>84</v>
-      </c>
-      <c r="F40" s="38"/>
-      <c r="G40" s="38"/>
-      <c r="H40" s="38"/>
-      <c r="I40" s="38"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="6"/>
+      <c r="H40" s="6"/>
+      <c r="I40" s="6"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="B41" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="B41" t="s">
+        <v>86</v>
+      </c>
+      <c r="C41" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="D41" s="26" t="s">
+        <v>246</v>
+      </c>
+      <c r="E41" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="C41" s="36" t="s">
-        <v>34</v>
-      </c>
-      <c r="D41" s="37" t="s">
-        <v>247</v>
-      </c>
-      <c r="E41" s="37" t="s">
-        <v>86</v>
-      </c>
-      <c r="F41" s="38"/>
-      <c r="G41" s="38"/>
-      <c r="H41" s="38"/>
-      <c r="I41" s="38"/>
+      <c r="F41" s="6"/>
+      <c r="G41" s="6"/>
+      <c r="H41" s="6"/>
+      <c r="I41" s="6"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="B42" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="B42" t="s">
+        <v>88</v>
+      </c>
+      <c r="C42" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="D42" s="26" t="s">
+        <v>247</v>
+      </c>
+      <c r="E42" s="26" t="s">
         <v>89</v>
       </c>
-      <c r="C42" s="36" t="s">
-        <v>77</v>
-      </c>
-      <c r="D42" s="37" t="s">
-        <v>248</v>
-      </c>
-      <c r="E42" s="37" t="s">
-        <v>88</v>
-      </c>
-      <c r="F42" s="38"/>
-      <c r="G42" s="38"/>
-      <c r="H42" s="38"/>
-      <c r="I42" s="38"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="6"/>
+      <c r="H42" s="6"/>
+      <c r="I42" s="6"/>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="B43" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="B43" t="s">
+        <v>90</v>
+      </c>
+      <c r="C43" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="D43" s="26" t="s">
+        <v>248</v>
+      </c>
+      <c r="E43" s="26" t="s">
         <v>91</v>
       </c>
-      <c r="C43" s="36" t="s">
-        <v>77</v>
-      </c>
-      <c r="D43" s="37" t="s">
-        <v>249</v>
-      </c>
-      <c r="E43" s="37" t="s">
-        <v>90</v>
-      </c>
-      <c r="F43" s="38"/>
-      <c r="G43" s="38"/>
-      <c r="H43" s="38"/>
-      <c r="I43" s="38"/>
+      <c r="F43" s="6"/>
+      <c r="G43" s="6"/>
+      <c r="H43" s="6"/>
+      <c r="I43" s="6"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="B44" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="B44" t="s">
+        <v>92</v>
+      </c>
+      <c r="C44" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="D44" s="26" t="s">
+        <v>249</v>
+      </c>
+      <c r="E44" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="C44" s="36" t="s">
-        <v>4</v>
-      </c>
-      <c r="D44" s="37" t="s">
-        <v>250</v>
-      </c>
-      <c r="E44" s="37" t="s">
-        <v>92</v>
-      </c>
-      <c r="F44" s="38"/>
-      <c r="G44" s="38"/>
-      <c r="H44" s="38"/>
-      <c r="I44" s="38"/>
+      <c r="F44" s="6"/>
+      <c r="G44" s="6"/>
+      <c r="H44" s="6"/>
+      <c r="I44" s="6"/>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="B45" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="B45" t="s">
+        <v>94</v>
+      </c>
+      <c r="C45" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="D45" s="26" t="s">
+        <v>250</v>
+      </c>
+      <c r="E45" s="26" t="s">
         <v>95</v>
       </c>
-      <c r="C45" s="36" t="s">
-        <v>4</v>
-      </c>
-      <c r="D45" s="37" t="s">
-        <v>251</v>
-      </c>
-      <c r="E45" s="37" t="s">
-        <v>94</v>
-      </c>
-      <c r="F45" s="38"/>
-      <c r="G45" s="38"/>
-      <c r="H45" s="38"/>
-      <c r="I45" s="38"/>
+      <c r="F45" s="6"/>
+      <c r="G45" s="6"/>
+      <c r="H45" s="6"/>
+      <c r="I45" s="6"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="B46" s="25" t="s">
-        <v>204</v>
-      </c>
-      <c r="C46" s="36" t="s">
-        <v>77</v>
-      </c>
-      <c r="D46" s="37" t="s">
-        <v>252</v>
-      </c>
-      <c r="E46" s="37" t="s">
-        <v>96</v>
-      </c>
-      <c r="F46" s="38"/>
-      <c r="G46" s="38"/>
-      <c r="H46" s="38"/>
-      <c r="I46" s="38"/>
+        <v>121</v>
+      </c>
+      <c r="B46" t="s">
+        <v>203</v>
+      </c>
+      <c r="C46" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="D46" s="26" t="s">
+        <v>251</v>
+      </c>
+      <c r="F46" s="6"/>
+      <c r="G46" s="6"/>
+      <c r="H46" s="6"/>
+      <c r="I46" s="6"/>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="B47" s="25" t="s">
-        <v>205</v>
-      </c>
-      <c r="C47" s="36" t="s">
-        <v>79</v>
-      </c>
-      <c r="D47" s="37" t="s">
-        <v>253</v>
-      </c>
-      <c r="E47" s="37"/>
-      <c r="F47" s="38"/>
-      <c r="G47" s="38"/>
-      <c r="H47" s="38"/>
-      <c r="I47" s="38"/>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A48" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="B48" s="25" t="s">
-        <v>206</v>
-      </c>
-      <c r="C48" s="36" t="s">
-        <v>4</v>
-      </c>
-      <c r="D48" s="37" t="s">
-        <v>254</v>
-      </c>
-      <c r="E48" s="37"/>
-      <c r="F48" s="38"/>
-      <c r="G48" s="38"/>
-      <c r="H48" s="38"/>
-      <c r="I48" s="38"/>
+        <v>121</v>
+      </c>
+      <c r="B47" t="s">
+        <v>204</v>
+      </c>
+      <c r="C47" s="25" t="s">
+        <v>78</v>
+      </c>
+      <c r="D47" s="26" t="s">
+        <v>252</v>
+      </c>
+      <c r="F47" s="6"/>
+      <c r="G47" s="6"/>
+      <c r="H47" s="6"/>
+      <c r="I47" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="B2:B6">
     <cfRule type="duplicateValues" dxfId="3" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B7:B48">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  <conditionalFormatting sqref="B2:B47">
+    <cfRule type="duplicateValues" dxfId="2" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B48">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  <conditionalFormatting sqref="B7:B47">
+    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D48">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  <conditionalFormatting sqref="D2:D47">
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3059,36 +2968,36 @@
   <sheetData>
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F3" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="G3" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="H3" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="I3" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="J3" s="5" t="s">
         <v>115</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B4" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C4" s="13"/>
       <c r="D4" s="15"/>
@@ -3101,7 +3010,7 @@
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B5" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C5" s="13"/>
       <c r="D5" s="15"/>
@@ -3114,7 +3023,7 @@
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B6" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C6" s="13"/>
       <c r="D6" s="15"/>
@@ -3127,19 +3036,19 @@
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B7" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D7" s="15" t="s">
         <v>3</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G7" s="14"/>
       <c r="H7" s="14"/>
@@ -3148,19 +3057,19 @@
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B8" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D8" s="15" t="s">
         <v>3</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G8" s="14"/>
       <c r="H8" s="14"/>
@@ -3169,19 +3078,19 @@
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B9" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D9" s="15" t="s">
         <v>4</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G9" s="14"/>
       <c r="H9" s="14"/>
@@ -3190,19 +3099,19 @@
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B10" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D10" s="15" t="s">
         <v>4</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G10" s="14"/>
       <c r="H10" s="14"/>
@@ -3211,17 +3120,17 @@
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B11" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E11" s="14"/>
       <c r="F11" s="14" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G11" s="14"/>
       <c r="H11" s="14"/>
@@ -3230,17 +3139,17 @@
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B12" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D12" s="15" t="s">
         <v>3</v>
       </c>
       <c r="E12" s="14"/>
       <c r="F12" s="14" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G12" s="14"/>
       <c r="H12" s="14"/>
@@ -3249,17 +3158,17 @@
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B13" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E13" s="14"/>
       <c r="F13" s="14" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G13" s="14"/>
       <c r="H13" s="14"/>
@@ -3268,17 +3177,17 @@
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B14" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E14" s="14"/>
       <c r="F14" s="14" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G14" s="14"/>
       <c r="H14" s="14"/>
@@ -3287,17 +3196,17 @@
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B15" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D15" s="15" t="s">
         <v>3</v>
       </c>
       <c r="E15" s="14"/>
       <c r="F15" s="14" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G15" s="14"/>
       <c r="H15" s="14"/>
@@ -3306,17 +3215,17 @@
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B16" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E16" s="14"/>
       <c r="F16" s="14" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G16" s="14"/>
       <c r="H16" s="14"/>
@@ -3325,17 +3234,17 @@
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B17" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E17" s="14"/>
       <c r="F17" s="14" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G17" s="14"/>
       <c r="H17" s="14"/>
@@ -3344,17 +3253,17 @@
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B18" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D18" s="15" t="s">
         <v>3</v>
       </c>
       <c r="E18" s="14"/>
       <c r="F18" s="14" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G18" s="14"/>
       <c r="H18" s="14"/>
@@ -3363,7 +3272,7 @@
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B19" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C19" s="13"/>
       <c r="D19" s="15"/>
@@ -3376,15 +3285,15 @@
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B20" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D20" s="15"/>
       <c r="E20" s="14"/>
       <c r="F20" s="14" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G20" s="14"/>
       <c r="H20" s="14"/>
@@ -3393,15 +3302,15 @@
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B21" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D21" s="15"/>
       <c r="E21" s="14"/>
       <c r="F21" s="14" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G21" s="14"/>
       <c r="H21" s="14"/>
@@ -3410,15 +3319,15 @@
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B22" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D22" s="15"/>
       <c r="E22" s="14"/>
       <c r="F22" s="14" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G22" s="14"/>
       <c r="H22" s="14"/>
@@ -3427,15 +3336,15 @@
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B23" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D23" s="15"/>
       <c r="E23" s="14"/>
       <c r="F23" s="14" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G23" s="14"/>
       <c r="H23" s="14"/>
@@ -3444,17 +3353,17 @@
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B24" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C24" s="13" t="s">
         <v>14</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E24" s="14"/>
       <c r="F24" s="14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G24" s="14"/>
       <c r="H24" s="14"/>
@@ -3463,17 +3372,17 @@
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B25" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D25" s="15" t="s">
         <v>4</v>
       </c>
       <c r="E25" s="14"/>
       <c r="F25" s="14" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G25" s="14"/>
       <c r="H25" s="14"/>
@@ -3482,17 +3391,17 @@
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B26" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D26" s="15" t="s">
         <v>3</v>
       </c>
       <c r="E26" s="14"/>
       <c r="F26" s="14" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G26" s="14"/>
       <c r="H26" s="14"/>
@@ -3501,17 +3410,17 @@
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B27" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E27" s="14"/>
       <c r="F27" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G27" s="14"/>
       <c r="H27" s="14"/>
@@ -3520,7 +3429,7 @@
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B28" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C28" s="13"/>
       <c r="D28" s="15"/>
@@ -3533,15 +3442,15 @@
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B29" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D29" s="15"/>
       <c r="E29" s="14"/>
       <c r="F29" s="14" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G29" s="14"/>
       <c r="H29" s="14"/>
@@ -3550,17 +3459,17 @@
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B30" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D30" s="15" t="s">
         <v>1</v>
       </c>
       <c r="E30" s="14"/>
       <c r="F30" s="14" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G30" s="14"/>
       <c r="H30" s="14"/>
@@ -3569,17 +3478,17 @@
     </row>
     <row r="31" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B31" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E31" s="14"/>
       <c r="F31" s="14" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G31" s="14"/>
       <c r="H31" s="14"/>
@@ -3588,17 +3497,17 @@
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B32" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D32" s="15" t="s">
         <v>1</v>
       </c>
       <c r="E32" s="14"/>
       <c r="F32" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G32" s="14"/>
       <c r="H32" s="14"/>
@@ -3607,17 +3516,17 @@
     </row>
     <row r="33" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B33" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E33" s="14"/>
       <c r="F33" s="14" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G33" s="14"/>
       <c r="H33" s="14"/>
@@ -3626,17 +3535,17 @@
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B34" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E34" s="14"/>
       <c r="F34" s="14" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G34" s="14"/>
       <c r="H34" s="14"/>
@@ -3645,17 +3554,17 @@
     </row>
     <row r="35" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B35" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D35" s="15" t="s">
         <v>1</v>
       </c>
       <c r="E35" s="14"/>
       <c r="F35" s="14" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G35" s="14"/>
       <c r="H35" s="14"/>
@@ -3664,17 +3573,17 @@
     </row>
     <row r="36" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B36" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D36" s="15" t="s">
         <v>34</v>
       </c>
       <c r="E36" s="14"/>
       <c r="F36" s="14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G36" s="14"/>
       <c r="H36" s="14"/>
@@ -3683,17 +3592,17 @@
     </row>
     <row r="37" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B37" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E37" s="14"/>
       <c r="F37" s="14" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G37" s="14"/>
       <c r="H37" s="14"/>
@@ -3702,17 +3611,17 @@
     </row>
     <row r="38" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B38" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D38" s="15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E38" s="14"/>
       <c r="F38" s="14" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G38" s="14"/>
       <c r="H38" s="14"/>
@@ -3721,32 +3630,32 @@
     </row>
     <row r="39" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B39" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D39" s="15" t="s">
         <v>1</v>
       </c>
       <c r="E39" s="17"/>
       <c r="F39" s="14" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="40" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B40" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D40" s="15" t="s">
         <v>34</v>
       </c>
       <c r="E40" s="17"/>
       <c r="F40" s="14" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.3">

--- a/eBus_Functions/Post_Processing/Root_Cause_Analysis_Work/info/eBus_Model_Info.xlsx
+++ b/eBus_Functions/Post_Processing/Root_Cause_Analysis_Work/info/eBus_Model_Info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\TempData\Github\eBus_Tool\eBus_Functions\Post_Processing\Root_Cause_Analysis_Work\info\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F51235E-357C-439C-9754-B52EC84886CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3031F610-9564-45F5-899B-1EF1DD6F967B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="261">
   <si>
     <t>Driver</t>
   </si>
@@ -65,9 +65,6 @@
     <t>Accelerator Pedal</t>
   </si>
   <si>
-    <t>logout.drv_AccPdl_pos_in</t>
-  </si>
-  <si>
     <t>Brake Pedal</t>
   </si>
   <si>
@@ -140,9 +137,6 @@
     <t>logout.hvs_zfCetrax_gbx_gearRatio</t>
   </si>
   <si>
-    <t>logout.drv_BrkPdl_pos_in</t>
-  </si>
-  <si>
     <t>Motor 1 Actual Torque</t>
   </si>
   <si>
@@ -230,9 +224,6 @@
     <t>Rolling Resistance Force</t>
   </si>
   <si>
-    <t>logout.mec_brk_Wheel1_TiLossRollRes_info</t>
-  </si>
-  <si>
     <t>Gradient Force</t>
   </si>
   <si>
@@ -272,15 +263,9 @@
     <t>Battery Power</t>
   </si>
   <si>
-    <t>logout.eess_BatHW_P_BatPwr</t>
-  </si>
-  <si>
     <t>Battery Loss Power</t>
   </si>
   <si>
-    <t>logout.eess_BatHW_P_BatLossPwr</t>
-  </si>
-  <si>
     <t>Battery State of Charge</t>
   </si>
   <si>
@@ -789,13 +774,49 @@
   </si>
   <si>
     <t>logout.pne_brk_Axle1_BrakingPower+logout.pne_brk_Axle2_BrakingPower+logout.pne_brk_Axle3_BrakingPower+logout.pne_brk_Axle4_BrakingPower</t>
+  </si>
+  <si>
+    <t>logout.drv_AccPdl_pos</t>
+  </si>
+  <si>
+    <t>logout.drv_BrkPdl_pos</t>
+  </si>
+  <si>
+    <t>logout.hvs_zfCetrax_gbxOut_torque*sMP.global.mec_iDiffAxle/(sMP.global.mec_rWheelDriven*0.001)-(logout.mec_brk_Axle1_TiBrk_info+logout.mec_brk_Axle2_TiBrk_info+logout.mec_brk_Axle3_TiBrk_info+logout.mec_brk_Axle4_TiBrk_info)</t>
+  </si>
+  <si>
+    <t>logout.mec_brk_Axle1_TiBrk_info+logout.mec_brk_Axle2_TiBrk_info+logout.mec_brk_Axle3_TiBrk_info+logout.mec_brk_Axle4_TiBrk_info</t>
+  </si>
+  <si>
+    <t>logout.mec_brk_Wheel1_TiLossRollRes_info+logout.mec_brk_Wheel2_TiLossRollRes_info+logout.mec_brk_Wheel3_TiLossRollRes_info+logout.mec_brk_Wheel4_TiLossRollRes_info</t>
+  </si>
+  <si>
+    <t>logout.eess_BatHW_P_BatPwr/1000</t>
+  </si>
+  <si>
+    <t>logout.eess_BatHW_P_BatLossPwr/1000</t>
+  </si>
+  <si>
+    <t>logout.hvs_dcLink_aux_current</t>
+  </si>
+  <si>
+    <t>logout.hvs_dcLink_ControllableEnergySource_voltage</t>
+  </si>
+  <si>
+    <t>logout.HVB_Pwr_Cval</t>
+  </si>
+  <si>
+    <t>logout.eess_BatHW_P_SysLossPwr/1000</t>
+  </si>
+  <si>
+    <t>logout.eess_average_Temperature</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -857,8 +878,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -904,6 +933,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1037,7 +1072,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1055,8 +1090,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1078,18 +1111,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1113,6 +1134,26 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1504,44 +1545,44 @@
   <sheetData>
     <row r="27" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="28" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G28" s="18" t="s">
+      <c r="G28" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="H28" s="19" t="s">
-        <v>96</v>
-      </c>
-      <c r="I28" s="20" t="s">
+      <c r="H28" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="I28" s="18" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="29" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G29" s="7"/>
-      <c r="H29" s="30" t="s">
+      <c r="H29" s="24" t="s">
         <v>6</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="30" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G30" s="9"/>
-      <c r="H30" s="31"/>
+      <c r="H30" s="25"/>
       <c r="I30" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="31" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G31" s="10"/>
-      <c r="H31" s="32"/>
+      <c r="H31" s="26"/>
       <c r="I31" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="32" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G32" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="H32" s="33" t="s">
+        <v>21</v>
+      </c>
+      <c r="H32" s="27" t="s">
         <v>0</v>
       </c>
       <c r="I32" s="8" t="s">
@@ -1550,375 +1591,375 @@
     </row>
     <row r="33" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G33" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="H33" s="34"/>
+        <v>29</v>
+      </c>
+      <c r="H33" s="28"/>
       <c r="I33" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="34" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G34" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="H34" s="34"/>
+      <c r="H34" s="28"/>
       <c r="I34" s="1"/>
     </row>
     <row r="35" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G35" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="H35" s="34"/>
+        <v>13</v>
+      </c>
+      <c r="H35" s="28"/>
       <c r="I35" s="1"/>
     </row>
     <row r="36" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G36" s="9" t="s">
-        <v>199</v>
-      </c>
-      <c r="H36" s="34"/>
+        <v>194</v>
+      </c>
+      <c r="H36" s="28"/>
       <c r="I36" s="1"/>
     </row>
     <row r="37" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G37" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="H37" s="35"/>
+        <v>14</v>
+      </c>
+      <c r="H37" s="29"/>
       <c r="I37" s="2"/>
     </row>
     <row r="38" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G38" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="H38" s="30" t="s">
+      <c r="H38" s="24" t="s">
         <v>2</v>
       </c>
       <c r="I38" s="8" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="39" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G39" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="H39" s="32"/>
+        <v>12</v>
+      </c>
+      <c r="H39" s="26"/>
       <c r="I39" s="2" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
     </row>
     <row r="40" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G40" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="H40" s="33" t="s">
-        <v>116</v>
+        <v>186</v>
+      </c>
+      <c r="H40" s="27" t="s">
+        <v>111</v>
       </c>
       <c r="I40" s="8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="41" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G41" s="9" t="s">
-        <v>192</v>
-      </c>
-      <c r="H41" s="34"/>
+        <v>187</v>
+      </c>
+      <c r="H41" s="28"/>
       <c r="I41" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="42" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G42" s="9"/>
-      <c r="H42" s="34"/>
+      <c r="H42" s="28"/>
       <c r="I42" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="43" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G43" s="9"/>
-      <c r="H43" s="34"/>
+      <c r="H43" s="28"/>
       <c r="I43" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="44" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G44" s="9"/>
-      <c r="H44" s="34"/>
+      <c r="H44" s="28"/>
       <c r="I44" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="45" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G45" s="9"/>
-      <c r="H45" s="34"/>
+      <c r="H45" s="28"/>
       <c r="I45" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="46" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G46" s="9"/>
-      <c r="H46" s="34"/>
+      <c r="H46" s="28"/>
       <c r="I46" s="1" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
     </row>
     <row r="47" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G47" s="9"/>
-      <c r="H47" s="34"/>
+      <c r="H47" s="28"/>
       <c r="I47" s="1" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
     </row>
     <row r="48" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G48" s="9"/>
-      <c r="H48" s="34"/>
+      <c r="H48" s="28"/>
       <c r="I48" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="49" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G49" s="9"/>
-      <c r="H49" s="34"/>
+      <c r="H49" s="28"/>
       <c r="I49" s="1" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
     </row>
     <row r="50" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G50" s="9"/>
-      <c r="H50" s="34"/>
+      <c r="H50" s="28"/>
       <c r="I50" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="51" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G51" s="10"/>
-      <c r="H51" s="35"/>
+      <c r="H51" s="29"/>
       <c r="I51" s="2" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
     </row>
     <row r="52" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G52" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="H52" s="30" t="s">
-        <v>117</v>
+        <v>36</v>
+      </c>
+      <c r="H52" s="24" t="s">
+        <v>112</v>
       </c>
       <c r="I52" s="8" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
     </row>
     <row r="53" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G53" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="H53" s="31"/>
+        <v>38</v>
+      </c>
+      <c r="H53" s="25"/>
       <c r="I53" s="1" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
     </row>
     <row r="54" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G54" s="9"/>
-      <c r="H54" s="31"/>
+      <c r="H54" s="25"/>
       <c r="I54" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="55" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G55" s="9"/>
-      <c r="H55" s="31"/>
+      <c r="H55" s="25"/>
       <c r="I55" s="1" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
     </row>
     <row r="56" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G56" s="9"/>
-      <c r="H56" s="31"/>
+      <c r="H56" s="25"/>
       <c r="I56" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="57" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G57" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="H57" s="20" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="57" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G57" s="21" t="s">
-        <v>197</v>
-      </c>
-      <c r="H57" s="22" t="s">
+      <c r="I57" s="21" t="s">
         <v>18</v>
-      </c>
-      <c r="I57" s="23" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="58" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G58" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H58" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="H58" s="31" t="s">
+      <c r="I58" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="I58" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="59" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G59" s="9"/>
-      <c r="H59" s="31"/>
+      <c r="H59" s="25"/>
       <c r="I59" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="60" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G60" s="9"/>
-      <c r="H60" s="31"/>
+      <c r="H60" s="25"/>
       <c r="I60" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="61" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G61" s="9"/>
-      <c r="H61" s="31"/>
+      <c r="H61" s="25"/>
       <c r="I61" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="62" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G62" s="9"/>
-      <c r="H62" s="31"/>
+      <c r="H62" s="25"/>
       <c r="I62" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="63" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G63" s="9"/>
-      <c r="H63" s="31"/>
+      <c r="H63" s="25"/>
       <c r="I63" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="64" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G64" s="9"/>
-      <c r="H64" s="31"/>
+      <c r="H64" s="25"/>
       <c r="I64" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="65" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G65" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="H65" s="33" t="s">
-        <v>118</v>
+        <v>12</v>
+      </c>
+      <c r="H65" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="I65" s="8" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
     </row>
     <row r="66" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G66" s="10"/>
-      <c r="H66" s="35"/>
+      <c r="H66" s="29"/>
       <c r="I66" s="2" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
     </row>
     <row r="67" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G67" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="H67" s="31" t="s">
-        <v>119</v>
+        <v>32</v>
+      </c>
+      <c r="H67" s="25" t="s">
+        <v>114</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="68" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G68" s="9"/>
-      <c r="H68" s="31"/>
+      <c r="H68" s="25"/>
       <c r="I68" s="1" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
     </row>
     <row r="69" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G69" s="9"/>
-      <c r="H69" s="31"/>
+      <c r="H69" s="25"/>
       <c r="I69" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="70" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G70" s="9"/>
-      <c r="H70" s="31"/>
+      <c r="H70" s="25"/>
       <c r="I70" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="71" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G71" s="9"/>
-      <c r="H71" s="31"/>
+      <c r="H71" s="25"/>
       <c r="I71" s="1" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="72" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G72" s="9"/>
-      <c r="H72" s="31"/>
+      <c r="H72" s="25"/>
       <c r="I72" s="1" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="73" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G73" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H73" s="33" t="s">
-        <v>120</v>
+        <v>32</v>
+      </c>
+      <c r="H73" s="27" t="s">
+        <v>115</v>
       </c>
       <c r="I73" s="8" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="74" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G74" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="H74" s="34"/>
+        <v>79</v>
+      </c>
+      <c r="H74" s="28"/>
       <c r="I74" s="1" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="75" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G75" s="9"/>
-      <c r="H75" s="34"/>
+      <c r="H75" s="28"/>
       <c r="I75" s="1" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="76" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G76" s="10"/>
-      <c r="H76" s="35"/>
+      <c r="H76" s="29"/>
       <c r="I76" s="2" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="77" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G77" s="9"/>
-      <c r="H77" s="31" t="s">
-        <v>121</v>
+      <c r="H77" s="25" t="s">
+        <v>116</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
     </row>
     <row r="78" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G78" s="9"/>
-      <c r="H78" s="31"/>
+      <c r="H78" s="25"/>
       <c r="I78" s="1" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
     </row>
     <row r="79" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G79" s="10"/>
-      <c r="H79" s="32"/>
+      <c r="H79" s="26"/>
       <c r="I79" s="2" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
     </row>
   </sheetData>
@@ -1945,995 +1986,2072 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFA16316-83DB-41C7-8B25-B191695DD108}">
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:L100"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28" style="28" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28" style="22" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.6640625" style="29" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="46.44140625" style="28" bestFit="1" customWidth="1"/>
-    <col min="6" max="9" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.6640625" style="23" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="46.44140625" style="22" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="39.5546875" customWidth="1"/>
+    <col min="7" max="9" width="17.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="30" t="s">
+        <v>91</v>
+      </c>
+      <c r="B1" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="31" t="s">
+        <v>92</v>
+      </c>
+      <c r="E1" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1" s="30" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="33" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="E2" s="34" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2" s="34" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" s="34" t="s">
+        <v>30</v>
+      </c>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="37" t="s">
+        <v>203</v>
+      </c>
+      <c r="E3" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
+      <c r="L3" s="12"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="37" t="s">
+        <v>204</v>
+      </c>
+      <c r="E4" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="12"/>
+      <c r="L4" s="12"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="35" t="s">
+        <v>101</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="37" t="s">
+        <v>205</v>
+      </c>
+      <c r="E5" s="34" t="s">
+        <v>249</v>
+      </c>
+      <c r="F5" s="34" t="s">
+        <v>249</v>
+      </c>
+      <c r="G5" s="34" t="s">
+        <v>249</v>
+      </c>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="12"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" s="35" t="s">
+        <v>101</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="37" t="s">
+        <v>206</v>
+      </c>
+      <c r="E6" s="34" t="s">
+        <v>250</v>
+      </c>
+      <c r="F6" s="34" t="s">
+        <v>250</v>
+      </c>
+      <c r="G6" s="34" t="s">
+        <v>250</v>
+      </c>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" s="32" t="s">
+        <v>102</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C7" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="37" t="s">
+        <v>207</v>
+      </c>
+      <c r="E7" s="34" t="s">
+        <v>201</v>
+      </c>
+      <c r="F7" s="34" t="s">
+        <v>201</v>
+      </c>
+      <c r="G7" s="34" t="s">
+        <v>201</v>
+      </c>
+      <c r="H7" s="12"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="12"/>
+      <c r="L7" s="12"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="32" t="s">
+        <v>102</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="C8" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="37" t="s">
+        <v>208</v>
+      </c>
+      <c r="E8" s="34" t="s">
+        <v>201</v>
+      </c>
+      <c r="F8" s="34" t="s">
+        <v>201</v>
+      </c>
+      <c r="G8" s="34" t="s">
+        <v>201</v>
+      </c>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="12"/>
+      <c r="L8" s="12"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" s="35" t="s">
+        <v>100</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="37" t="s">
+        <v>209</v>
+      </c>
+      <c r="E9" s="34" t="s">
+        <v>37</v>
+      </c>
+      <c r="F9" s="34" t="s">
+        <v>37</v>
+      </c>
+      <c r="G9" s="34" t="s">
+        <v>37</v>
+      </c>
+      <c r="H9" s="12"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="12"/>
+      <c r="K9" s="12"/>
+      <c r="L9" s="12"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" s="35" t="s">
+        <v>100</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="37" t="s">
+        <v>210</v>
+      </c>
+      <c r="E10" s="34" t="s">
+        <v>39</v>
+      </c>
+      <c r="F10" s="34" t="s">
+        <v>39</v>
+      </c>
+      <c r="G10" s="34" t="s">
+        <v>39</v>
+      </c>
+      <c r="H10" s="12"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="12"/>
+      <c r="K10" s="12"/>
+      <c r="L10" s="12"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" s="35" t="s">
+        <v>100</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" s="37" t="s">
+        <v>211</v>
+      </c>
+      <c r="E11" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="F11" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="G11" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="H11" s="12"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="12"/>
+      <c r="L11" s="12"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" s="35" t="s">
+        <v>100</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="D12" s="37" t="s">
+        <v>212</v>
+      </c>
+      <c r="E12" s="34" t="s">
+        <v>43</v>
+      </c>
+      <c r="F12" s="34" t="s">
+        <v>43</v>
+      </c>
+      <c r="G12" s="34" t="s">
+        <v>43</v>
+      </c>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="12"/>
+      <c r="K12" s="12"/>
+      <c r="L12" s="12"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" s="35" t="s">
+        <v>100</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="D13" s="37" t="s">
+        <v>213</v>
+      </c>
+      <c r="E13" s="34" t="s">
+        <v>45</v>
+      </c>
+      <c r="F13" s="34" t="s">
+        <v>45</v>
+      </c>
+      <c r="G13" s="34" t="s">
+        <v>45</v>
+      </c>
+      <c r="H13" s="12"/>
+      <c r="I13" s="12"/>
+      <c r="J13" s="12"/>
+      <c r="K13" s="12"/>
+      <c r="L13" s="12"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14" s="35" t="s">
+        <v>100</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="D14" s="37" t="s">
+        <v>214</v>
+      </c>
+      <c r="E14" s="34" t="s">
+        <v>47</v>
+      </c>
+      <c r="F14" s="34" t="s">
+        <v>47</v>
+      </c>
+      <c r="G14" s="34" t="s">
+        <v>47</v>
+      </c>
+      <c r="H14" s="12"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="12"/>
+      <c r="L14" s="12"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A15" s="35" t="s">
+        <v>100</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="C15" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="37" t="s">
+        <v>215</v>
+      </c>
+      <c r="E15" s="34" t="s">
+        <v>48</v>
+      </c>
+      <c r="F15" s="34" t="s">
+        <v>48</v>
+      </c>
+      <c r="G15" s="34" t="s">
+        <v>48</v>
+      </c>
+      <c r="H15" s="12"/>
+      <c r="I15" s="12"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="12"/>
+      <c r="L15" s="12"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A16" s="35" t="s">
+        <v>100</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="C16" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="D16" s="37" t="s">
+        <v>216</v>
+      </c>
+      <c r="E16" s="34" t="s">
+        <v>49</v>
+      </c>
+      <c r="F16" s="34" t="s">
+        <v>49</v>
+      </c>
+      <c r="G16" s="34" t="s">
+        <v>49</v>
+      </c>
+      <c r="H16" s="12"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="12"/>
+      <c r="L16" s="12"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A17" s="35" t="s">
+        <v>100</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" s="37" t="s">
+        <v>217</v>
+      </c>
+      <c r="E17" s="34" t="s">
+        <v>51</v>
+      </c>
+      <c r="F17" s="34" t="s">
+        <v>51</v>
+      </c>
+      <c r="G17" s="34" t="s">
+        <v>51</v>
+      </c>
+      <c r="H17" s="12"/>
+      <c r="I17" s="12"/>
+      <c r="J17" s="12"/>
+      <c r="K17" s="12"/>
+      <c r="L17" s="12"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A18" s="35" t="s">
+        <v>100</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="C18" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" s="37" t="s">
+        <v>218</v>
+      </c>
+      <c r="E18" s="34" t="s">
+        <v>52</v>
+      </c>
+      <c r="F18" s="34" t="s">
+        <v>52</v>
+      </c>
+      <c r="G18" s="34" t="s">
+        <v>52</v>
+      </c>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="12"/>
+      <c r="L18" s="12"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A19" s="35" t="s">
+        <v>100</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" s="37" t="s">
+        <v>219</v>
+      </c>
+      <c r="E19" s="34" t="s">
+        <v>54</v>
+      </c>
+      <c r="F19" s="34" t="s">
+        <v>54</v>
+      </c>
+      <c r="G19" s="34" t="s">
+        <v>54</v>
+      </c>
+      <c r="H19" s="12"/>
+      <c r="I19" s="12"/>
+      <c r="J19" s="12"/>
+      <c r="K19" s="12"/>
+      <c r="L19" s="12"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A20" s="35" t="s">
+        <v>100</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="C20" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="D20" s="37" t="s">
+        <v>220</v>
+      </c>
+      <c r="E20" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="F20" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="G20" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="H20" s="12"/>
+      <c r="I20" s="12"/>
+      <c r="J20" s="12"/>
+      <c r="K20" s="12"/>
+      <c r="L20" s="12"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A21" s="32" t="s">
+        <v>99</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="C21" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="D21" s="37" t="s">
+        <v>221</v>
+      </c>
+      <c r="E21" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="F21" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="G21" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="H21" s="12"/>
+      <c r="I21" s="12"/>
+      <c r="J21" s="12"/>
+      <c r="K21" s="12"/>
+      <c r="L21" s="12"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A22" s="32" t="s">
+        <v>99</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="C22" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="D22" s="37" t="s">
+        <v>222</v>
+      </c>
+      <c r="E22" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="F22" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="G22" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="H22" s="12"/>
+      <c r="I22" s="12"/>
+      <c r="J22" s="12"/>
+      <c r="K22" s="12"/>
+      <c r="L22" s="12"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A23" s="32" t="s">
+        <v>99</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" s="33"/>
+      <c r="D23" s="37" t="s">
+        <v>223</v>
+      </c>
+      <c r="E23" s="34" t="s">
+        <v>58</v>
+      </c>
+      <c r="F23" s="34" t="s">
+        <v>58</v>
+      </c>
+      <c r="G23" s="34" t="s">
+        <v>58</v>
+      </c>
+      <c r="H23" s="12"/>
+      <c r="I23" s="12"/>
+      <c r="J23" s="12"/>
+      <c r="K23" s="12"/>
+      <c r="L23" s="12"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A24" s="32" t="s">
+        <v>99</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="C24" s="33"/>
+      <c r="D24" s="37" t="s">
+        <v>224</v>
+      </c>
+      <c r="E24" s="34" t="s">
+        <v>35</v>
+      </c>
+      <c r="F24" s="34" t="s">
+        <v>35</v>
+      </c>
+      <c r="G24" s="34" t="s">
+        <v>35</v>
+      </c>
+      <c r="H24" s="12"/>
+      <c r="I24" s="12"/>
+      <c r="J24" s="12"/>
+      <c r="K24" s="12"/>
+      <c r="L24" s="12"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A25" s="32" t="s">
+        <v>99</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="D25" s="37" t="s">
+        <v>225</v>
+      </c>
+      <c r="E25" s="34" t="s">
+        <v>59</v>
+      </c>
+      <c r="F25" s="34" t="s">
+        <v>59</v>
+      </c>
+      <c r="G25" s="34" t="s">
+        <v>59</v>
+      </c>
+      <c r="H25" s="12"/>
+      <c r="I25" s="12"/>
+      <c r="J25" s="12"/>
+      <c r="K25" s="12"/>
+      <c r="L25" s="12"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A26" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="D26" s="37" t="s">
+        <v>226</v>
+      </c>
+      <c r="E26" s="36" t="s">
+        <v>251</v>
+      </c>
+      <c r="F26" s="36" t="s">
+        <v>251</v>
+      </c>
+      <c r="G26" s="36" t="s">
+        <v>251</v>
+      </c>
+      <c r="H26" s="12"/>
+      <c r="I26" s="12"/>
+      <c r="J26" s="12"/>
+      <c r="K26" s="12"/>
+      <c r="L26" s="12"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A27" s="32" t="s">
+        <v>98</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="C27" s="33" t="s">
+        <v>66</v>
+      </c>
+      <c r="D27" s="37" t="s">
+        <v>234</v>
+      </c>
+      <c r="E27" s="36" t="s">
+        <v>252</v>
+      </c>
+      <c r="F27" s="36" t="s">
+        <v>252</v>
+      </c>
+      <c r="G27" s="36" t="s">
+        <v>252</v>
+      </c>
+      <c r="H27" s="12"/>
+      <c r="I27" s="12"/>
+      <c r="J27" s="12"/>
+      <c r="K27" s="12"/>
+      <c r="L27" s="12"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A28" s="32" t="s">
+        <v>98</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="C28" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="D28" s="37" t="s">
+        <v>235</v>
+      </c>
+      <c r="E28" s="34" t="s">
+        <v>248</v>
+      </c>
+      <c r="F28" s="34" t="s">
+        <v>248</v>
+      </c>
+      <c r="G28" s="34" t="s">
+        <v>248</v>
+      </c>
+      <c r="H28" s="12"/>
+      <c r="I28" s="12"/>
+      <c r="J28" s="12"/>
+      <c r="K28" s="12"/>
+      <c r="L28" s="12"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A29" s="35" t="s">
+        <v>97</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C29" s="33" t="s">
+        <v>60</v>
+      </c>
+      <c r="D29" s="37" t="s">
+        <v>227</v>
+      </c>
+      <c r="E29" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="F29" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="G29" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="H29" s="12"/>
+      <c r="I29" s="12"/>
+      <c r="J29" s="12"/>
+      <c r="K29" s="12"/>
+      <c r="L29" s="12"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A30" s="35" t="s">
+        <v>97</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C30" s="33" t="s">
+        <v>103</v>
+      </c>
+      <c r="D30" s="37" t="s">
+        <v>228</v>
+      </c>
+      <c r="E30" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="F30" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="G30" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="H30" s="12"/>
+      <c r="I30" s="12"/>
+      <c r="J30" s="12"/>
+      <c r="K30" s="12"/>
+      <c r="L30" s="12"/>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A31" s="35" t="s">
+        <v>97</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C31" s="33" t="s">
+        <v>202</v>
+      </c>
+      <c r="D31" s="37" t="s">
+        <v>229</v>
+      </c>
+      <c r="E31" s="34" t="s">
+        <v>63</v>
+      </c>
+      <c r="F31" s="34" t="s">
+        <v>63</v>
+      </c>
+      <c r="G31" s="34" t="s">
+        <v>63</v>
+      </c>
+      <c r="H31" s="12"/>
+      <c r="I31" s="12"/>
+      <c r="J31" s="12"/>
+      <c r="K31" s="12"/>
+      <c r="L31" s="12"/>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A32" s="35" t="s">
+        <v>97</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="C32" s="33" t="s">
+        <v>66</v>
+      </c>
+      <c r="D32" s="37" t="s">
+        <v>230</v>
+      </c>
+      <c r="E32" s="34" t="s">
+        <v>253</v>
+      </c>
+      <c r="F32" s="34" t="s">
+        <v>253</v>
+      </c>
+      <c r="G32" s="34" t="s">
+        <v>253</v>
+      </c>
+      <c r="H32" s="12"/>
+      <c r="I32" s="12"/>
+      <c r="J32" s="12"/>
+      <c r="K32" s="12"/>
+      <c r="L32" s="12"/>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A33" s="35" t="s">
+        <v>97</v>
+      </c>
+      <c r="B33" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="C33" s="33" t="s">
+        <v>66</v>
+      </c>
+      <c r="D33" s="37" t="s">
+        <v>231</v>
+      </c>
+      <c r="E33" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="F33" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="G33" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="H33" s="12"/>
+      <c r="I33" s="12"/>
+      <c r="J33" s="12"/>
+      <c r="K33" s="12"/>
+      <c r="L33" s="12"/>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A34" s="35" t="s">
+        <v>97</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="C34" s="33" t="s">
+        <v>66</v>
+      </c>
+      <c r="D34" s="37" t="s">
+        <v>232</v>
+      </c>
+      <c r="E34" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F34" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="G34" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="H34" s="12"/>
+      <c r="I34" s="12"/>
+      <c r="J34" s="12"/>
+      <c r="K34" s="12"/>
+      <c r="L34" s="12"/>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A35" s="35" t="s">
+        <v>97</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="C35" s="33" t="s">
+        <v>66</v>
+      </c>
+      <c r="D35" s="37" t="s">
+        <v>233</v>
+      </c>
+      <c r="E35" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="F35" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="G35" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="H35" s="12"/>
+      <c r="I35" s="12"/>
+      <c r="J35" s="12"/>
+      <c r="K35" s="12"/>
+      <c r="L35" s="12"/>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A36" s="32" t="s">
+        <v>95</v>
+      </c>
+      <c r="B36" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="C36" s="33" t="s">
+        <v>73</v>
+      </c>
+      <c r="D36" s="37" t="s">
+        <v>236</v>
+      </c>
+      <c r="E36" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="F36" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="G36" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="H36" s="12"/>
+      <c r="I36" s="12"/>
+      <c r="J36" s="12"/>
+      <c r="K36" s="12"/>
+      <c r="L36" s="12"/>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A37" s="32" t="s">
+        <v>95</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="C37" s="33" t="s">
+        <v>75</v>
+      </c>
+      <c r="D37" s="37" t="s">
+        <v>237</v>
+      </c>
+      <c r="E37" s="34" t="s">
+        <v>76</v>
+      </c>
+      <c r="F37" s="34" t="s">
+        <v>76</v>
+      </c>
+      <c r="G37" s="34" t="s">
+        <v>76</v>
+      </c>
+      <c r="H37" s="12"/>
+      <c r="I37" s="12"/>
+      <c r="J37" s="12"/>
+      <c r="K37" s="12"/>
+      <c r="L37" s="12"/>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A38" s="32" t="s">
+        <v>95</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="C38" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="D38" s="37" t="s">
+        <v>238</v>
+      </c>
+      <c r="E38" s="34" t="s">
+        <v>254</v>
+      </c>
+      <c r="F38" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="G38" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="H38" s="12"/>
+      <c r="I38" s="12"/>
+      <c r="J38" s="12"/>
+      <c r="K38" s="12"/>
+      <c r="L38" s="12"/>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A39" s="32" t="s">
+        <v>95</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="C39" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="D39" s="37" t="s">
+        <v>239</v>
+      </c>
+      <c r="E39" s="34" t="s">
+        <v>255</v>
+      </c>
+      <c r="F39" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="G39" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="H39" s="12"/>
+      <c r="I39" s="12"/>
+      <c r="J39" s="12"/>
+      <c r="K39" s="12"/>
+      <c r="L39" s="12"/>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A40" s="32" t="s">
+        <v>95</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C40" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D40" s="37" t="s">
+        <v>240</v>
+      </c>
+      <c r="E40" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="F40" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="G40" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="H40" s="12"/>
+      <c r="I40" s="12"/>
+      <c r="J40" s="12"/>
+      <c r="K40" s="12"/>
+      <c r="L40" s="12"/>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A41" s="32" t="s">
+        <v>95</v>
+      </c>
+      <c r="B41" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="C41" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="D41" s="37" t="s">
+        <v>241</v>
+      </c>
+      <c r="E41" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="F41" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="G41" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="H41" s="12"/>
+      <c r="I41" s="12"/>
+      <c r="J41" s="12"/>
+      <c r="K41" s="12"/>
+      <c r="L41" s="12"/>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A42" s="35" t="s">
         <v>96</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D1" s="24" t="s">
-        <v>97</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="B2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C2" s="25" t="s">
-        <v>108</v>
-      </c>
-      <c r="D2" s="26" t="s">
-        <v>98</v>
-      </c>
-      <c r="E2" s="26" t="s">
-        <v>31</v>
-      </c>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="26" t="s">
-        <v>208</v>
-      </c>
-      <c r="E3" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="B4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C4" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" s="26" t="s">
-        <v>209</v>
-      </c>
-      <c r="E4" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="B5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" s="26" t="s">
-        <v>210</v>
-      </c>
-      <c r="E5" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="B6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="26" t="s">
-        <v>211</v>
-      </c>
-      <c r="E6" s="26" t="s">
-        <v>37</v>
-      </c>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="B7" t="s">
-        <v>191</v>
-      </c>
-      <c r="C7" s="25" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="26" t="s">
-        <v>212</v>
-      </c>
-      <c r="E7" s="26" t="s">
-        <v>206</v>
-      </c>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="B8" t="s">
-        <v>192</v>
-      </c>
-      <c r="C8" s="25" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="26" t="s">
-        <v>213</v>
-      </c>
-      <c r="E8" s="26" t="s">
-        <v>206</v>
-      </c>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="B9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C9" s="25" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="26" t="s">
-        <v>214</v>
-      </c>
-      <c r="E9" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="B10" t="s">
-        <v>40</v>
-      </c>
-      <c r="C10" s="25" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="26" t="s">
-        <v>215</v>
-      </c>
-      <c r="E10" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="F10" s="27"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="B11" t="s">
-        <v>42</v>
-      </c>
-      <c r="C11" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="D11" s="26" t="s">
-        <v>216</v>
-      </c>
-      <c r="E11" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="B12" t="s">
-        <v>44</v>
-      </c>
-      <c r="C12" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="D12" s="26" t="s">
-        <v>217</v>
-      </c>
-      <c r="E12" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="B13" t="s">
-        <v>46</v>
-      </c>
-      <c r="C13" s="25" t="s">
+      <c r="B42" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="C42" s="33" t="s">
+        <v>73</v>
+      </c>
+      <c r="D42" s="37" t="s">
+        <v>242</v>
+      </c>
+      <c r="E42" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="F42" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="G42" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="H42" s="12"/>
+      <c r="I42" s="12"/>
+      <c r="J42" s="12"/>
+      <c r="K42" s="12"/>
+      <c r="L42" s="12"/>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A43" s="35" t="s">
+        <v>96</v>
+      </c>
+      <c r="B43" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="C43" s="33" t="s">
+        <v>73</v>
+      </c>
+      <c r="D43" s="37" t="s">
+        <v>243</v>
+      </c>
+      <c r="E43" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="F43" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="G43" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="H43" s="12"/>
+      <c r="I43" s="12"/>
+      <c r="J43" s="12"/>
+      <c r="K43" s="12"/>
+      <c r="L43" s="12"/>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A44" s="35" t="s">
+        <v>96</v>
+      </c>
+      <c r="B44" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="C44" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="D13" s="26" t="s">
-        <v>218</v>
-      </c>
-      <c r="E13" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="B14" t="s">
-        <v>48</v>
-      </c>
-      <c r="C14" s="25" t="s">
+      <c r="D44" s="37" t="s">
+        <v>244</v>
+      </c>
+      <c r="E44" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="F44" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="G44" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="H44" s="12"/>
+      <c r="I44" s="12"/>
+      <c r="J44" s="12"/>
+      <c r="K44" s="12"/>
+      <c r="L44" s="12"/>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A45" s="35" t="s">
+        <v>96</v>
+      </c>
+      <c r="B45" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C45" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="D14" s="26" t="s">
-        <v>219</v>
-      </c>
-      <c r="E14" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="B15" t="s">
-        <v>193</v>
-      </c>
-      <c r="C15" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="26" t="s">
-        <v>220</v>
-      </c>
-      <c r="E15" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="B16" t="s">
-        <v>194</v>
-      </c>
-      <c r="C16" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="D16" s="26" t="s">
-        <v>221</v>
-      </c>
-      <c r="E16" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="B17" t="s">
-        <v>52</v>
-      </c>
-      <c r="C17" s="25" t="s">
-        <v>3</v>
-      </c>
-      <c r="D17" s="26" t="s">
-        <v>222</v>
-      </c>
-      <c r="E17" s="26" t="s">
-        <v>53</v>
-      </c>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="B18" t="s">
-        <v>195</v>
-      </c>
-      <c r="C18" s="25" t="s">
-        <v>3</v>
-      </c>
-      <c r="D18" s="26" t="s">
-        <v>223</v>
-      </c>
-      <c r="E18" s="26" t="s">
-        <v>54</v>
-      </c>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="B19" t="s">
-        <v>55</v>
-      </c>
-      <c r="C19" s="25" t="s">
-        <v>3</v>
-      </c>
-      <c r="D19" s="26" t="s">
-        <v>224</v>
-      </c>
-      <c r="E19" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="B20" t="s">
-        <v>196</v>
-      </c>
-      <c r="C20" s="25" t="s">
-        <v>3</v>
-      </c>
-      <c r="D20" s="26" t="s">
-        <v>225</v>
-      </c>
-      <c r="E20" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="B21" t="s">
-        <v>197</v>
-      </c>
-      <c r="C21" s="25" t="s">
-        <v>3</v>
-      </c>
-      <c r="D21" s="26" t="s">
-        <v>226</v>
-      </c>
-      <c r="E21" s="26" t="s">
-        <v>58</v>
-      </c>
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="B22" t="s">
+      <c r="D45" s="37" t="s">
+        <v>245</v>
+      </c>
+      <c r="E45" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="F45" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="G45" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="H45" s="12"/>
+      <c r="I45" s="12"/>
+      <c r="J45" s="12"/>
+      <c r="K45" s="12"/>
+      <c r="L45" s="12"/>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A46" s="32" t="s">
+        <v>116</v>
+      </c>
+      <c r="B46" s="12" t="s">
         <v>198</v>
       </c>
-      <c r="C22" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="D22" s="26" t="s">
-        <v>227</v>
-      </c>
-      <c r="E22" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="B23" t="s">
-        <v>16</v>
-      </c>
-      <c r="C23" s="25"/>
-      <c r="D23" s="26" t="s">
-        <v>228</v>
-      </c>
-      <c r="E23" s="26" t="s">
-        <v>60</v>
-      </c>
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="B24" t="s">
+      <c r="C46" s="33" t="s">
+        <v>73</v>
+      </c>
+      <c r="D46" s="37" t="s">
+        <v>246</v>
+      </c>
+      <c r="E46" s="36" t="s">
+        <v>256</v>
+      </c>
+      <c r="F46" s="36" t="s">
+        <v>256</v>
+      </c>
+      <c r="G46" s="36" t="s">
+        <v>256</v>
+      </c>
+      <c r="H46" s="12"/>
+      <c r="I46" s="12"/>
+      <c r="J46" s="12"/>
+      <c r="K46" s="12"/>
+      <c r="L46" s="12"/>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A47" s="32" t="s">
+        <v>116</v>
+      </c>
+      <c r="B47" s="12" t="s">
         <v>199</v>
       </c>
-      <c r="C24" s="25"/>
-      <c r="D24" s="26" t="s">
-        <v>229</v>
-      </c>
-      <c r="E24" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="B25" t="s">
-        <v>17</v>
-      </c>
-      <c r="C25" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="D25" s="26" t="s">
-        <v>230</v>
-      </c>
-      <c r="E25" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="6"/>
-      <c r="I25" s="6"/>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A26" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="B26" t="s">
-        <v>19</v>
-      </c>
-      <c r="C26" s="25" t="s">
-        <v>3</v>
-      </c>
-      <c r="D26" s="26" t="s">
-        <v>231</v>
-      </c>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="6"/>
-      <c r="I26" s="6"/>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A27" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="B27" t="s">
-        <v>21</v>
-      </c>
-      <c r="C27" s="25" t="s">
-        <v>62</v>
-      </c>
-      <c r="D27" s="26" t="s">
-        <v>232</v>
-      </c>
-      <c r="E27" s="26" t="s">
-        <v>63</v>
-      </c>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="6"/>
-      <c r="I27" s="6"/>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="B28" t="s">
-        <v>22</v>
-      </c>
-      <c r="C28" s="25" t="s">
-        <v>108</v>
-      </c>
-      <c r="D28" s="26" t="s">
-        <v>233</v>
-      </c>
-      <c r="E28" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="6"/>
-      <c r="I28" s="6"/>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A29" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="B29" t="s">
-        <v>23</v>
-      </c>
-      <c r="C29" s="25" t="s">
-        <v>207</v>
-      </c>
-      <c r="D29" s="26" t="s">
-        <v>234</v>
-      </c>
-      <c r="E29" s="26" t="s">
-        <v>65</v>
-      </c>
-      <c r="F29" s="6"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="6"/>
-      <c r="I29" s="6"/>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A30" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="B30" t="s">
-        <v>66</v>
-      </c>
-      <c r="C30" s="25" t="s">
-        <v>69</v>
-      </c>
-      <c r="D30" s="26" t="s">
-        <v>235</v>
-      </c>
-      <c r="E30" s="26" t="s">
-        <v>67</v>
-      </c>
-      <c r="F30" s="6"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="6"/>
-      <c r="I30" s="6"/>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A31" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="B31" t="s">
-        <v>68</v>
-      </c>
-      <c r="C31" s="25" t="s">
-        <v>69</v>
-      </c>
-      <c r="D31" s="26" t="s">
-        <v>236</v>
-      </c>
-      <c r="E31" s="26" t="s">
-        <v>70</v>
-      </c>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="6"/>
-      <c r="I31" s="6"/>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A32" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="B32" t="s">
-        <v>71</v>
-      </c>
-      <c r="C32" s="25" t="s">
-        <v>69</v>
-      </c>
-      <c r="D32" s="26" t="s">
-        <v>237</v>
-      </c>
-      <c r="E32" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="6"/>
-      <c r="I32" s="6"/>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A33" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="B33" t="s">
-        <v>73</v>
-      </c>
-      <c r="C33" s="25" t="s">
-        <v>69</v>
-      </c>
-      <c r="D33" s="26" t="s">
-        <v>238</v>
-      </c>
-      <c r="E33" s="26" t="s">
-        <v>74</v>
-      </c>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="6"/>
-      <c r="I33" s="6"/>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A34" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="B34" t="s">
-        <v>200</v>
-      </c>
-      <c r="C34" s="25" t="s">
-        <v>69</v>
-      </c>
-      <c r="D34" s="26" t="s">
-        <v>239</v>
-      </c>
-      <c r="F34" s="6"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="6"/>
-      <c r="I34" s="6"/>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A35" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="B35" t="s">
-        <v>201</v>
-      </c>
-      <c r="C35" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="D35" s="26" t="s">
-        <v>240</v>
-      </c>
-      <c r="E35" s="26" t="s">
-        <v>253</v>
-      </c>
-      <c r="F35" s="6"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="6"/>
-      <c r="I35" s="6"/>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A36" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="B36" t="s">
+      <c r="C47" s="33" t="s">
         <v>75</v>
       </c>
-      <c r="C36" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="D36" s="26" t="s">
-        <v>241</v>
-      </c>
-      <c r="E36" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="F36" s="6"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="6"/>
-      <c r="I36" s="6"/>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A37" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="B37" t="s">
-        <v>202</v>
-      </c>
-      <c r="C37" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="D37" s="26" t="s">
-        <v>242</v>
-      </c>
-      <c r="E37" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="F37" s="6"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="6"/>
-      <c r="I37" s="6"/>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A38" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="B38" t="s">
-        <v>80</v>
-      </c>
-      <c r="C38" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="D38" s="26" t="s">
-        <v>243</v>
-      </c>
-      <c r="E38" s="26" t="s">
-        <v>81</v>
-      </c>
-      <c r="F38" s="6"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="6"/>
-      <c r="I38" s="6"/>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A39" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="B39" t="s">
-        <v>82</v>
-      </c>
-      <c r="C39" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="D39" s="26" t="s">
-        <v>244</v>
-      </c>
-      <c r="E39" s="26" t="s">
-        <v>83</v>
-      </c>
-      <c r="F39" s="6"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="6"/>
-      <c r="I39" s="6"/>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A40" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="B40" t="s">
-        <v>84</v>
-      </c>
-      <c r="C40" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D40" s="26" t="s">
-        <v>245</v>
-      </c>
-      <c r="E40" s="26" t="s">
-        <v>85</v>
-      </c>
-      <c r="F40" s="6"/>
-      <c r="G40" s="6"/>
-      <c r="H40" s="6"/>
-      <c r="I40" s="6"/>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A41" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="B41" t="s">
-        <v>86</v>
-      </c>
-      <c r="C41" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="D41" s="26" t="s">
-        <v>246</v>
-      </c>
-      <c r="E41" s="26" t="s">
-        <v>87</v>
-      </c>
-      <c r="F41" s="6"/>
-      <c r="G41" s="6"/>
-      <c r="H41" s="6"/>
-      <c r="I41" s="6"/>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A42" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="B42" t="s">
-        <v>88</v>
-      </c>
-      <c r="C42" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="D42" s="26" t="s">
+      <c r="D47" s="37" t="s">
         <v>247</v>
       </c>
-      <c r="E42" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="F42" s="6"/>
-      <c r="G42" s="6"/>
-      <c r="H42" s="6"/>
-      <c r="I42" s="6"/>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A43" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="B43" t="s">
-        <v>90</v>
-      </c>
-      <c r="C43" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="D43" s="26" t="s">
-        <v>248</v>
-      </c>
-      <c r="E43" s="26" t="s">
-        <v>91</v>
-      </c>
-      <c r="F43" s="6"/>
-      <c r="G43" s="6"/>
-      <c r="H43" s="6"/>
-      <c r="I43" s="6"/>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A44" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="B44" t="s">
-        <v>92</v>
-      </c>
-      <c r="C44" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="D44" s="26" t="s">
-        <v>249</v>
-      </c>
-      <c r="E44" s="26" t="s">
-        <v>93</v>
-      </c>
-      <c r="F44" s="6"/>
-      <c r="G44" s="6"/>
-      <c r="H44" s="6"/>
-      <c r="I44" s="6"/>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A45" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="B45" t="s">
-        <v>94</v>
-      </c>
-      <c r="C45" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="D45" s="26" t="s">
-        <v>250</v>
-      </c>
-      <c r="E45" s="26" t="s">
-        <v>95</v>
-      </c>
-      <c r="F45" s="6"/>
-      <c r="G45" s="6"/>
-      <c r="H45" s="6"/>
-      <c r="I45" s="6"/>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A46" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="B46" t="s">
-        <v>203</v>
-      </c>
-      <c r="C46" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="D46" s="26" t="s">
-        <v>251</v>
-      </c>
-      <c r="F46" s="6"/>
-      <c r="G46" s="6"/>
-      <c r="H46" s="6"/>
-      <c r="I46" s="6"/>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A47" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="B47" t="s">
-        <v>204</v>
-      </c>
-      <c r="C47" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="D47" s="26" t="s">
-        <v>252</v>
-      </c>
-      <c r="F47" s="6"/>
-      <c r="G47" s="6"/>
-      <c r="H47" s="6"/>
-      <c r="I47" s="6"/>
+      <c r="E47" s="36" t="s">
+        <v>257</v>
+      </c>
+      <c r="F47" s="36" t="s">
+        <v>257</v>
+      </c>
+      <c r="G47" s="36" t="s">
+        <v>257</v>
+      </c>
+      <c r="H47" s="12"/>
+      <c r="I47" s="12"/>
+      <c r="J47" s="12"/>
+      <c r="K47" s="12"/>
+      <c r="L47" s="12"/>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A48" s="12"/>
+      <c r="B48" s="36"/>
+      <c r="C48" s="33"/>
+      <c r="D48" s="34"/>
+      <c r="E48" s="36"/>
+      <c r="F48" s="12"/>
+      <c r="G48" s="12"/>
+      <c r="H48" s="12"/>
+      <c r="I48" s="12"/>
+      <c r="J48" s="12"/>
+      <c r="K48" s="12"/>
+      <c r="L48" s="12"/>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A49" s="12"/>
+      <c r="B49" s="36"/>
+      <c r="C49" s="33"/>
+      <c r="D49" s="34"/>
+      <c r="E49" s="36"/>
+      <c r="F49" s="12"/>
+      <c r="G49" s="12"/>
+      <c r="H49" s="12"/>
+      <c r="I49" s="12"/>
+      <c r="J49" s="12"/>
+      <c r="K49" s="12"/>
+      <c r="L49" s="12"/>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A50" s="12"/>
+      <c r="B50" s="36"/>
+      <c r="C50" s="33"/>
+      <c r="D50" s="34"/>
+      <c r="E50" s="36"/>
+      <c r="F50" s="12"/>
+      <c r="G50" s="12"/>
+      <c r="H50" s="12"/>
+      <c r="I50" s="12"/>
+      <c r="J50" s="12"/>
+      <c r="K50" s="12"/>
+      <c r="L50" s="12"/>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A51" s="12"/>
+      <c r="B51" s="36"/>
+      <c r="C51" s="33"/>
+      <c r="D51" s="34"/>
+      <c r="E51" s="36"/>
+      <c r="F51" s="12"/>
+      <c r="G51" s="12"/>
+      <c r="H51" s="12"/>
+      <c r="I51" s="12"/>
+      <c r="J51" s="12"/>
+      <c r="K51" s="12"/>
+      <c r="L51" s="12"/>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A52" s="12"/>
+      <c r="B52" s="36"/>
+      <c r="C52" s="33"/>
+      <c r="D52" s="34"/>
+      <c r="E52" s="36"/>
+      <c r="F52" s="12"/>
+      <c r="G52" s="12"/>
+      <c r="H52" s="12"/>
+      <c r="I52" s="12"/>
+      <c r="J52" s="12"/>
+      <c r="K52" s="12"/>
+      <c r="L52" s="12"/>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A53" s="12"/>
+      <c r="B53" s="36"/>
+      <c r="C53" s="33"/>
+      <c r="D53" s="34"/>
+      <c r="E53" s="36"/>
+      <c r="F53" s="12"/>
+      <c r="G53" s="12"/>
+      <c r="H53" s="12"/>
+      <c r="I53" s="12"/>
+      <c r="J53" s="12"/>
+      <c r="K53" s="12"/>
+      <c r="L53" s="12"/>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A54" s="12"/>
+      <c r="B54" s="36"/>
+      <c r="C54" s="33"/>
+      <c r="D54" s="34"/>
+      <c r="E54" s="36"/>
+      <c r="F54" s="12"/>
+      <c r="G54" s="12"/>
+      <c r="H54" s="12"/>
+      <c r="I54" s="12"/>
+      <c r="J54" s="12"/>
+      <c r="K54" s="12"/>
+      <c r="L54" s="12"/>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A55" s="12"/>
+      <c r="B55" s="36"/>
+      <c r="C55" s="33"/>
+      <c r="D55" s="34"/>
+      <c r="E55" s="36"/>
+      <c r="F55" s="12"/>
+      <c r="G55" s="12"/>
+      <c r="H55" s="12"/>
+      <c r="I55" s="12"/>
+      <c r="J55" s="12"/>
+      <c r="K55" s="12"/>
+      <c r="L55" s="12"/>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A56" s="12"/>
+      <c r="B56" s="36"/>
+      <c r="C56" s="33"/>
+      <c r="D56" s="34"/>
+      <c r="E56" s="36"/>
+      <c r="F56" s="12"/>
+      <c r="G56" s="12"/>
+      <c r="H56" s="12"/>
+      <c r="I56" s="12"/>
+      <c r="J56" s="12"/>
+      <c r="K56" s="12"/>
+      <c r="L56" s="12"/>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A57" s="12"/>
+      <c r="B57" s="36"/>
+      <c r="C57" s="33"/>
+      <c r="D57" s="34"/>
+      <c r="E57" s="36"/>
+      <c r="F57" s="12"/>
+      <c r="G57" s="12"/>
+      <c r="H57" s="12"/>
+      <c r="I57" s="12"/>
+      <c r="J57" s="12"/>
+      <c r="K57" s="12"/>
+      <c r="L57" s="12"/>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A58" s="12"/>
+      <c r="B58" s="36"/>
+      <c r="C58" s="33"/>
+      <c r="D58" s="34"/>
+      <c r="E58" s="36"/>
+      <c r="F58" s="12"/>
+      <c r="G58" s="12"/>
+      <c r="H58" s="12"/>
+      <c r="I58" s="12"/>
+      <c r="J58" s="12"/>
+      <c r="K58" s="12"/>
+      <c r="L58" s="12"/>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A59" s="12"/>
+      <c r="B59" s="36"/>
+      <c r="C59" s="33"/>
+      <c r="D59" s="34"/>
+      <c r="E59" s="36"/>
+      <c r="F59" s="12"/>
+      <c r="G59" s="12"/>
+      <c r="H59" s="12"/>
+      <c r="I59" s="12"/>
+      <c r="J59" s="12"/>
+      <c r="K59" s="12"/>
+      <c r="L59" s="12"/>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A60" s="12"/>
+      <c r="B60" s="36"/>
+      <c r="C60" s="33"/>
+      <c r="D60" s="34"/>
+      <c r="E60" s="36"/>
+      <c r="F60" s="12"/>
+      <c r="G60" s="12"/>
+      <c r="H60" s="12"/>
+      <c r="I60" s="12"/>
+      <c r="J60" s="12"/>
+      <c r="K60" s="12"/>
+      <c r="L60" s="12"/>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A61" s="12"/>
+      <c r="B61" s="36"/>
+      <c r="C61" s="33"/>
+      <c r="D61" s="34"/>
+      <c r="E61" s="36"/>
+      <c r="F61" s="12"/>
+      <c r="G61" s="12"/>
+      <c r="H61" s="12"/>
+      <c r="I61" s="12"/>
+      <c r="J61" s="12"/>
+      <c r="K61" s="12"/>
+      <c r="L61" s="12"/>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A62" s="12"/>
+      <c r="B62" s="36"/>
+      <c r="C62" s="33"/>
+      <c r="D62" s="34"/>
+      <c r="E62" s="36"/>
+      <c r="F62" s="12"/>
+      <c r="G62" s="12"/>
+      <c r="H62" s="12"/>
+      <c r="I62" s="12"/>
+      <c r="J62" s="12"/>
+      <c r="K62" s="12"/>
+      <c r="L62" s="12"/>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A63" s="12"/>
+      <c r="B63" s="36"/>
+      <c r="C63" s="33"/>
+      <c r="D63" s="34"/>
+      <c r="E63" s="36"/>
+      <c r="F63" s="12"/>
+      <c r="G63" s="12"/>
+      <c r="H63" s="12"/>
+      <c r="I63" s="12"/>
+      <c r="J63" s="12"/>
+      <c r="K63" s="12"/>
+      <c r="L63" s="12"/>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A64" s="12"/>
+      <c r="B64" s="36"/>
+      <c r="C64" s="33"/>
+      <c r="D64" s="34"/>
+      <c r="E64" s="36"/>
+      <c r="F64" s="12"/>
+      <c r="G64" s="12"/>
+      <c r="H64" s="12"/>
+      <c r="I64" s="12"/>
+      <c r="J64" s="12"/>
+      <c r="K64" s="12"/>
+      <c r="L64" s="12"/>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A65" s="12"/>
+      <c r="B65" s="36"/>
+      <c r="C65" s="33"/>
+      <c r="D65" s="34"/>
+      <c r="E65" s="36"/>
+      <c r="F65" s="12"/>
+      <c r="G65" s="12"/>
+      <c r="H65" s="12"/>
+      <c r="I65" s="12"/>
+      <c r="J65" s="12"/>
+      <c r="K65" s="12"/>
+      <c r="L65" s="12"/>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A66" s="12"/>
+      <c r="B66" s="36"/>
+      <c r="C66" s="33"/>
+      <c r="D66" s="34"/>
+      <c r="E66" s="36"/>
+      <c r="F66" s="12"/>
+      <c r="G66" s="12"/>
+      <c r="H66" s="12"/>
+      <c r="I66" s="12"/>
+      <c r="J66" s="12"/>
+      <c r="K66" s="12"/>
+      <c r="L66" s="12"/>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A67" s="12"/>
+      <c r="B67" s="36"/>
+      <c r="C67" s="33"/>
+      <c r="D67" s="34"/>
+      <c r="E67" s="36"/>
+      <c r="F67" s="12"/>
+      <c r="G67" s="12"/>
+      <c r="H67" s="12"/>
+      <c r="I67" s="12"/>
+      <c r="J67" s="12"/>
+      <c r="K67" s="12"/>
+      <c r="L67" s="12"/>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A68" s="12"/>
+      <c r="B68" s="36"/>
+      <c r="C68" s="33"/>
+      <c r="D68" s="34"/>
+      <c r="E68" s="36"/>
+      <c r="F68" s="12"/>
+      <c r="G68" s="12"/>
+      <c r="H68" s="12"/>
+      <c r="I68" s="12"/>
+      <c r="J68" s="12"/>
+      <c r="K68" s="12"/>
+      <c r="L68" s="12"/>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A69" s="12"/>
+      <c r="B69" s="36"/>
+      <c r="C69" s="33"/>
+      <c r="D69" s="34"/>
+      <c r="E69" s="36"/>
+      <c r="F69" s="12"/>
+      <c r="G69" s="12"/>
+      <c r="H69" s="12"/>
+      <c r="I69" s="12"/>
+      <c r="J69" s="12"/>
+      <c r="K69" s="12"/>
+      <c r="L69" s="12"/>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A70" s="12"/>
+      <c r="B70" s="36"/>
+      <c r="C70" s="33"/>
+      <c r="D70" s="34"/>
+      <c r="E70" s="36"/>
+      <c r="F70" s="12"/>
+      <c r="G70" s="12"/>
+      <c r="H70" s="12"/>
+      <c r="I70" s="12"/>
+      <c r="J70" s="12"/>
+      <c r="K70" s="12"/>
+      <c r="L70" s="12"/>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A71" s="12"/>
+      <c r="B71" s="36"/>
+      <c r="C71" s="33"/>
+      <c r="D71" s="34"/>
+      <c r="E71" s="36"/>
+      <c r="F71" s="12"/>
+      <c r="G71" s="12"/>
+      <c r="H71" s="12"/>
+      <c r="I71" s="12"/>
+      <c r="J71" s="12"/>
+      <c r="K71" s="12"/>
+      <c r="L71" s="12"/>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A72" s="12"/>
+      <c r="B72" s="36"/>
+      <c r="C72" s="33"/>
+      <c r="D72" s="34"/>
+      <c r="E72" s="36"/>
+      <c r="F72" s="12"/>
+      <c r="G72" s="12"/>
+      <c r="H72" s="12"/>
+      <c r="I72" s="12"/>
+      <c r="J72" s="12"/>
+      <c r="K72" s="12"/>
+      <c r="L72" s="12"/>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A73" s="12"/>
+      <c r="B73" s="36"/>
+      <c r="C73" s="33"/>
+      <c r="D73" s="34"/>
+      <c r="E73" s="36"/>
+      <c r="F73" s="12"/>
+      <c r="G73" s="12"/>
+      <c r="H73" s="12"/>
+      <c r="I73" s="12"/>
+      <c r="J73" s="12"/>
+      <c r="K73" s="12"/>
+      <c r="L73" s="12"/>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A74" s="12"/>
+      <c r="B74" s="36"/>
+      <c r="C74" s="33"/>
+      <c r="D74" s="34"/>
+      <c r="E74" s="36"/>
+      <c r="F74" s="12"/>
+      <c r="G74" s="12"/>
+      <c r="H74" s="12"/>
+      <c r="I74" s="12"/>
+      <c r="J74" s="12"/>
+      <c r="K74" s="12"/>
+      <c r="L74" s="12"/>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A75" s="12"/>
+      <c r="B75" s="36"/>
+      <c r="C75" s="33"/>
+      <c r="D75" s="34"/>
+      <c r="E75" s="36"/>
+      <c r="F75" s="12"/>
+      <c r="G75" s="12"/>
+      <c r="H75" s="12"/>
+      <c r="I75" s="12"/>
+      <c r="J75" s="12"/>
+      <c r="K75" s="12"/>
+      <c r="L75" s="12"/>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A76" s="12"/>
+      <c r="B76" s="36"/>
+      <c r="C76" s="33"/>
+      <c r="D76" s="34"/>
+      <c r="E76" s="36"/>
+      <c r="F76" s="12"/>
+      <c r="G76" s="12"/>
+      <c r="H76" s="12"/>
+      <c r="I76" s="12"/>
+      <c r="J76" s="12"/>
+      <c r="K76" s="12"/>
+      <c r="L76" s="12"/>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A77" s="12"/>
+      <c r="B77" s="36"/>
+      <c r="C77" s="33"/>
+      <c r="D77" s="34"/>
+      <c r="E77" s="36"/>
+      <c r="F77" s="12"/>
+      <c r="G77" s="12"/>
+      <c r="H77" s="12"/>
+      <c r="I77" s="12"/>
+      <c r="J77" s="12"/>
+      <c r="K77" s="12"/>
+      <c r="L77" s="12"/>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A78" s="12"/>
+      <c r="B78" s="36"/>
+      <c r="C78" s="33"/>
+      <c r="D78" s="34"/>
+      <c r="E78" s="36"/>
+      <c r="F78" s="12"/>
+      <c r="G78" s="12"/>
+      <c r="H78" s="12"/>
+      <c r="I78" s="12"/>
+      <c r="J78" s="12"/>
+      <c r="K78" s="12"/>
+      <c r="L78" s="12"/>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A79" s="12"/>
+      <c r="B79" s="36"/>
+      <c r="C79" s="33"/>
+      <c r="D79" s="34"/>
+      <c r="E79" s="36"/>
+      <c r="F79" s="12"/>
+      <c r="G79" s="12"/>
+      <c r="H79" s="12"/>
+      <c r="I79" s="12"/>
+      <c r="J79" s="12"/>
+      <c r="K79" s="12"/>
+      <c r="L79" s="12"/>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A80" s="12"/>
+      <c r="B80" s="36"/>
+      <c r="C80" s="33"/>
+      <c r="D80" s="34"/>
+      <c r="E80" s="36"/>
+      <c r="F80" s="12"/>
+      <c r="G80" s="12"/>
+      <c r="H80" s="12"/>
+      <c r="I80" s="12"/>
+      <c r="J80" s="12"/>
+      <c r="K80" s="12"/>
+      <c r="L80" s="12"/>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A81" s="12"/>
+      <c r="B81" s="36"/>
+      <c r="C81" s="33"/>
+      <c r="D81" s="34"/>
+      <c r="E81" s="36"/>
+      <c r="F81" s="12"/>
+      <c r="G81" s="12"/>
+      <c r="H81" s="12"/>
+      <c r="I81" s="12"/>
+      <c r="J81" s="12"/>
+      <c r="K81" s="12"/>
+      <c r="L81" s="12"/>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A82" s="12"/>
+      <c r="B82" s="36"/>
+      <c r="C82" s="33"/>
+      <c r="D82" s="34"/>
+      <c r="E82" s="36"/>
+      <c r="F82" s="12"/>
+      <c r="G82" s="12"/>
+      <c r="H82" s="12"/>
+      <c r="I82" s="12"/>
+      <c r="J82" s="12"/>
+      <c r="K82" s="12"/>
+      <c r="L82" s="12"/>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A83" s="12"/>
+      <c r="B83" s="36"/>
+      <c r="C83" s="33"/>
+      <c r="D83" s="34"/>
+      <c r="E83" s="36"/>
+      <c r="F83" s="12"/>
+      <c r="G83" s="12"/>
+      <c r="H83" s="12"/>
+      <c r="I83" s="12"/>
+      <c r="J83" s="12"/>
+      <c r="K83" s="12"/>
+      <c r="L83" s="12"/>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A84" s="12"/>
+      <c r="B84" s="36"/>
+      <c r="C84" s="33"/>
+      <c r="D84" s="34"/>
+      <c r="E84" s="36"/>
+      <c r="F84" s="12"/>
+      <c r="G84" s="12"/>
+      <c r="H84" s="12"/>
+      <c r="I84" s="12"/>
+      <c r="J84" s="12"/>
+      <c r="K84" s="12"/>
+      <c r="L84" s="12"/>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A85" s="12"/>
+      <c r="B85" s="36"/>
+      <c r="C85" s="33"/>
+      <c r="D85" s="34"/>
+      <c r="E85" s="36"/>
+      <c r="F85" s="12"/>
+      <c r="G85" s="12"/>
+      <c r="H85" s="12"/>
+      <c r="I85" s="12"/>
+      <c r="J85" s="12"/>
+      <c r="K85" s="12"/>
+      <c r="L85" s="12"/>
+    </row>
+    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A86" s="12"/>
+      <c r="B86" s="36"/>
+      <c r="C86" s="33"/>
+      <c r="D86" s="34"/>
+      <c r="E86" s="36"/>
+      <c r="F86" s="12"/>
+      <c r="G86" s="12"/>
+      <c r="H86" s="12"/>
+      <c r="I86" s="12"/>
+      <c r="J86" s="12"/>
+      <c r="K86" s="12"/>
+      <c r="L86" s="12"/>
+    </row>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A87" s="12"/>
+      <c r="B87" s="36"/>
+      <c r="C87" s="33"/>
+      <c r="D87" s="34"/>
+      <c r="E87" s="36"/>
+      <c r="F87" s="12"/>
+      <c r="G87" s="12"/>
+      <c r="H87" s="12"/>
+      <c r="I87" s="12"/>
+      <c r="J87" s="12"/>
+      <c r="K87" s="12"/>
+      <c r="L87" s="12"/>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A88" s="12"/>
+      <c r="B88" s="36"/>
+      <c r="C88" s="33"/>
+      <c r="D88" s="34"/>
+      <c r="E88" s="36"/>
+      <c r="F88" s="12"/>
+      <c r="G88" s="12"/>
+      <c r="H88" s="12"/>
+      <c r="I88" s="12"/>
+      <c r="J88" s="12"/>
+      <c r="K88" s="12"/>
+      <c r="L88" s="12"/>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A89" s="12"/>
+      <c r="B89" s="36"/>
+      <c r="C89" s="33"/>
+      <c r="D89" s="34"/>
+      <c r="E89" s="36"/>
+      <c r="F89" s="12"/>
+      <c r="G89" s="12"/>
+      <c r="H89" s="12"/>
+      <c r="I89" s="12"/>
+      <c r="J89" s="12"/>
+      <c r="K89" s="12"/>
+      <c r="L89" s="12"/>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A90" s="12"/>
+      <c r="B90" s="36"/>
+      <c r="C90" s="33"/>
+      <c r="D90" s="34"/>
+      <c r="E90" s="36"/>
+      <c r="F90" s="12"/>
+      <c r="G90" s="12"/>
+      <c r="H90" s="12"/>
+      <c r="I90" s="12"/>
+      <c r="J90" s="12"/>
+      <c r="K90" s="12"/>
+      <c r="L90" s="12"/>
+    </row>
+    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A91" s="12"/>
+      <c r="B91" s="36"/>
+      <c r="C91" s="33"/>
+      <c r="D91" s="34"/>
+      <c r="E91" s="36"/>
+      <c r="F91" s="12"/>
+      <c r="G91" s="12"/>
+      <c r="H91" s="12"/>
+      <c r="I91" s="12"/>
+      <c r="J91" s="12"/>
+      <c r="K91" s="12"/>
+      <c r="L91" s="12"/>
+    </row>
+    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A92" s="12"/>
+      <c r="B92" s="36"/>
+      <c r="C92" s="33"/>
+      <c r="D92" s="34"/>
+      <c r="E92" s="36"/>
+      <c r="F92" s="12"/>
+      <c r="G92" s="12"/>
+      <c r="H92" s="12"/>
+      <c r="I92" s="12"/>
+      <c r="J92" s="12"/>
+      <c r="K92" s="12"/>
+      <c r="L92" s="12"/>
+    </row>
+    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A93" s="12"/>
+      <c r="B93" s="36"/>
+      <c r="C93" s="33"/>
+      <c r="D93" s="34"/>
+      <c r="E93" s="36"/>
+      <c r="F93" s="12"/>
+      <c r="G93" s="12"/>
+      <c r="H93" s="12"/>
+      <c r="I93" s="12"/>
+      <c r="J93" s="12"/>
+      <c r="K93" s="12"/>
+      <c r="L93" s="12"/>
+    </row>
+    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A94" s="12"/>
+      <c r="B94" s="36"/>
+      <c r="C94" s="33"/>
+      <c r="D94" s="34"/>
+      <c r="E94" s="36"/>
+      <c r="F94" s="12"/>
+      <c r="G94" s="12"/>
+      <c r="H94" s="12"/>
+      <c r="I94" s="12"/>
+      <c r="J94" s="12"/>
+      <c r="K94" s="12"/>
+      <c r="L94" s="12"/>
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A95" s="12"/>
+      <c r="B95" s="36"/>
+      <c r="C95" s="33"/>
+      <c r="D95" s="34"/>
+      <c r="E95" s="36"/>
+      <c r="F95" s="12"/>
+      <c r="G95" s="12"/>
+      <c r="H95" s="12"/>
+      <c r="I95" s="12"/>
+      <c r="J95" s="12"/>
+      <c r="K95" s="12"/>
+      <c r="L95" s="12"/>
+    </row>
+    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A96" s="12"/>
+      <c r="B96" s="36"/>
+      <c r="C96" s="33"/>
+      <c r="D96" s="34"/>
+      <c r="E96" s="36"/>
+      <c r="F96" s="12"/>
+      <c r="G96" s="12"/>
+      <c r="H96" s="12"/>
+      <c r="I96" s="12"/>
+      <c r="J96" s="12"/>
+      <c r="K96" s="12"/>
+      <c r="L96" s="12"/>
+    </row>
+    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A97" s="12"/>
+      <c r="B97" s="36"/>
+      <c r="C97" s="33"/>
+      <c r="D97" s="34"/>
+      <c r="E97" s="36"/>
+      <c r="F97" s="12"/>
+      <c r="G97" s="12"/>
+      <c r="H97" s="12"/>
+      <c r="I97" s="12"/>
+      <c r="J97" s="12"/>
+      <c r="K97" s="12"/>
+      <c r="L97" s="12"/>
+    </row>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A98" s="12"/>
+      <c r="B98" s="36"/>
+      <c r="C98" s="33"/>
+      <c r="D98" s="34"/>
+      <c r="E98" s="36"/>
+      <c r="F98" s="12"/>
+      <c r="G98" s="12"/>
+      <c r="H98" s="12"/>
+      <c r="I98" s="12"/>
+      <c r="J98" s="12"/>
+      <c r="K98" s="12"/>
+      <c r="L98" s="12"/>
+    </row>
+    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A99" s="12"/>
+      <c r="B99" s="36"/>
+      <c r="C99" s="33"/>
+      <c r="D99" s="34"/>
+      <c r="E99" s="36"/>
+      <c r="F99" s="12"/>
+      <c r="G99" s="12"/>
+      <c r="H99" s="12"/>
+      <c r="I99" s="12"/>
+      <c r="J99" s="12"/>
+      <c r="K99" s="12"/>
+      <c r="L99" s="12"/>
+    </row>
+    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A100" s="12"/>
+      <c r="B100" s="36"/>
+      <c r="C100" s="33"/>
+      <c r="D100" s="34"/>
+      <c r="E100" s="36"/>
+      <c r="F100" s="12"/>
+      <c r="G100" s="12"/>
+      <c r="H100" s="12"/>
+      <c r="I100" s="12"/>
+      <c r="J100" s="12"/>
+      <c r="K100" s="12"/>
+      <c r="L100" s="12"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -2950,6 +4068,7 @@
     <cfRule type="duplicateValues" dxfId="0" priority="7"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2968,701 +4087,701 @@
   <sheetData>
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="5" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B4" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="C4" s="13"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="14"/>
-      <c r="I4" s="14"/>
-      <c r="J4" s="14"/>
+        <v>94</v>
+      </c>
+      <c r="C4" s="11"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="12"/>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B5" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="C5" s="13"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14"/>
-      <c r="H5" s="14"/>
-      <c r="I5" s="14"/>
-      <c r="J5" s="14"/>
+        <v>101</v>
+      </c>
+      <c r="C5" s="11"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B6" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="C6" s="13"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="14"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="14"/>
+        <v>102</v>
+      </c>
+      <c r="C6" s="11"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B7" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="D7" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="D7" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="14" t="s">
-        <v>123</v>
-      </c>
-      <c r="F7" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="14"/>
-      <c r="J7" s="14"/>
+      <c r="E7" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="12"/>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B8" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>173</v>
-      </c>
-      <c r="D8" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="D8" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="F8" s="14" t="s">
-        <v>126</v>
-      </c>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="14"/>
-      <c r="J8" s="14"/>
+      <c r="E8" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="12"/>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B9" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="D9" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="D9" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="E9" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="F9" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="14"/>
-      <c r="J9" s="14"/>
+      <c r="E9" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="G9" s="12"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="12"/>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B10" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>172</v>
-      </c>
-      <c r="D10" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="D10" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="E10" s="14" t="s">
-        <v>130</v>
-      </c>
-      <c r="F10" s="14" t="s">
-        <v>181</v>
-      </c>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="14"/>
-      <c r="J10" s="14"/>
+      <c r="E10" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="G10" s="12"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="12"/>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B11" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>176</v>
-      </c>
-      <c r="D11" s="15" t="s">
-        <v>129</v>
-      </c>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="14"/>
-      <c r="J11" s="14"/>
+        <v>100</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="12"/>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B12" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>175</v>
-      </c>
-      <c r="D12" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="D12" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14" t="s">
-        <v>186</v>
-      </c>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="14"/>
-      <c r="J12" s="14"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="12"/>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B13" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="D13" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="14"/>
-      <c r="J13" s="14"/>
+        <v>100</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="12"/>
+      <c r="J13" s="12"/>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B14" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="C14" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12" t="s">
         <v>177</v>
       </c>
-      <c r="D14" s="15" t="s">
-        <v>129</v>
-      </c>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14" t="s">
-        <v>182</v>
-      </c>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="14"/>
-      <c r="J14" s="14"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="12"/>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B15" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="C15" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="D15" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14" t="s">
-        <v>183</v>
-      </c>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="14"/>
-      <c r="J15" s="14"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="12"/>
+      <c r="J15" s="12"/>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B16" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="C16" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12" t="s">
         <v>179</v>
       </c>
-      <c r="D16" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14" t="s">
-        <v>184</v>
-      </c>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="14"/>
-      <c r="J16" s="14"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="12"/>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B17" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="C17" s="13" t="s">
-        <v>188</v>
-      </c>
-      <c r="D17" s="15" t="s">
-        <v>129</v>
-      </c>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14" t="s">
-        <v>182</v>
-      </c>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="14"/>
-      <c r="J17" s="14"/>
+        <v>100</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="G17" s="12"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="12"/>
+      <c r="J17" s="12"/>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B18" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="C18" s="13" t="s">
-        <v>189</v>
-      </c>
-      <c r="D18" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="D18" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="14"/>
-      <c r="J18" s="14"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="12"/>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B19" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="C19" s="13"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="14"/>
-      <c r="J19" s="14"/>
+        <v>99</v>
+      </c>
+      <c r="C19" s="11"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="12"/>
+      <c r="I19" s="12"/>
+      <c r="J19" s="12"/>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B20" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="C20" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="D20" s="15"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14" t="s">
-        <v>164</v>
-      </c>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="14"/>
-      <c r="J20" s="14"/>
+        <v>104</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="D20" s="13"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="12"/>
+      <c r="J20" s="12"/>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B21" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="C21" s="13" t="s">
-        <v>162</v>
-      </c>
-      <c r="D21" s="15"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14" t="s">
-        <v>165</v>
-      </c>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="14"/>
-      <c r="J21" s="14"/>
+        <v>97</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="D21" s="13"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="G21" s="12"/>
+      <c r="H21" s="12"/>
+      <c r="I21" s="12"/>
+      <c r="J21" s="12"/>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B22" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="C22" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="D22" s="15"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="14"/>
-      <c r="J22" s="14"/>
+        <v>97</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="D22" s="13"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="G22" s="12"/>
+      <c r="H22" s="12"/>
+      <c r="I22" s="12"/>
+      <c r="J22" s="12"/>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B23" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="C23" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="D23" s="15"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14" t="s">
-        <v>167</v>
-      </c>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="14"/>
-      <c r="J23" s="14"/>
+        <v>97</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="D23" s="13"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="G23" s="12"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="12"/>
+      <c r="J23" s="12"/>
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B24" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="C24" s="13" t="s">
-        <v>14</v>
+        <v>97</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>13</v>
       </c>
       <c r="D24" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14" t="s">
-        <v>168</v>
-      </c>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="14"/>
-      <c r="J24" s="14"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="12"/>
+      <c r="J24" s="12"/>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B25" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="C25" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="D25" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="D25" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="14"/>
-      <c r="J25" s="14"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="G25" s="12"/>
+      <c r="H25" s="12"/>
+      <c r="I25" s="12"/>
+      <c r="J25" s="12"/>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B26" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="C26" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="D26" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="D26" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="14"/>
-      <c r="J26" s="14"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="G26" s="12"/>
+      <c r="H26" s="12"/>
+      <c r="I26" s="12"/>
+      <c r="J26" s="12"/>
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B27" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="C27" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="D27" s="15" t="s">
-        <v>129</v>
-      </c>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14" t="s">
-        <v>171</v>
-      </c>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="14"/>
-      <c r="J27" s="14"/>
+        <v>97</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="G27" s="12"/>
+      <c r="H27" s="12"/>
+      <c r="I27" s="12"/>
+      <c r="J27" s="12"/>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B28" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="C28" s="13"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="14"/>
-      <c r="J28" s="14"/>
+        <v>98</v>
+      </c>
+      <c r="C28" s="11"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="12"/>
+      <c r="H28" s="12"/>
+      <c r="I28" s="12"/>
+      <c r="J28" s="12"/>
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B29" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="C29" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="D29" s="15"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14" t="s">
-        <v>142</v>
-      </c>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="14"/>
-      <c r="J29" s="14"/>
+        <v>95</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="D29" s="13"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="G29" s="12"/>
+      <c r="H29" s="12"/>
+      <c r="I29" s="12"/>
+      <c r="J29" s="12"/>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B30" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="C30" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="D30" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="D30" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14" t="s">
-        <v>143</v>
-      </c>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="14"/>
-      <c r="J30" s="14"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="G30" s="12"/>
+      <c r="H30" s="12"/>
+      <c r="I30" s="12"/>
+      <c r="J30" s="12"/>
     </row>
     <row r="31" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B31" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="C31" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="D31" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14" t="s">
-        <v>144</v>
-      </c>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="14"/>
-      <c r="J31" s="14"/>
+        <v>95</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="D31" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="E31" s="12"/>
+      <c r="F31" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="G31" s="12"/>
+      <c r="H31" s="12"/>
+      <c r="I31" s="12"/>
+      <c r="J31" s="12"/>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B32" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="C32" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="D32" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="D32" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14" t="s">
-        <v>145</v>
-      </c>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="14"/>
-      <c r="J32" s="14"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="G32" s="12"/>
+      <c r="H32" s="12"/>
+      <c r="I32" s="12"/>
+      <c r="J32" s="12"/>
     </row>
     <row r="33" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B33" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C33" s="13" t="s">
-        <v>146</v>
-      </c>
-      <c r="D33" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14" t="s">
-        <v>154</v>
-      </c>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="14"/>
-      <c r="J33" s="14"/>
+        <v>96</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="D33" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="E33" s="12"/>
+      <c r="F33" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="G33" s="12"/>
+      <c r="H33" s="12"/>
+      <c r="I33" s="12"/>
+      <c r="J33" s="12"/>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B34" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C34" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="D34" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="14"/>
-      <c r="J34" s="14"/>
+        <v>96</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="D34" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="E34" s="12"/>
+      <c r="F34" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="G34" s="12"/>
+      <c r="H34" s="12"/>
+      <c r="I34" s="12"/>
+      <c r="J34" s="12"/>
     </row>
     <row r="35" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B35" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C35" s="13" t="s">
-        <v>148</v>
-      </c>
-      <c r="D35" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="D35" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="14"/>
-      <c r="J35" s="14"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="G35" s="12"/>
+      <c r="H35" s="12"/>
+      <c r="I35" s="12"/>
+      <c r="J35" s="12"/>
     </row>
     <row r="36" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B36" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C36" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="D36" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14" t="s">
-        <v>157</v>
-      </c>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="14"/>
-      <c r="J36" s="14"/>
+        <v>96</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="D36" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="E36" s="12"/>
+      <c r="F36" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="G36" s="12"/>
+      <c r="H36" s="12"/>
+      <c r="I36" s="12"/>
+      <c r="J36" s="12"/>
     </row>
     <row r="37" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B37" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C37" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="D37" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14" t="s">
-        <v>158</v>
-      </c>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="14"/>
-      <c r="J37" s="14"/>
+        <v>96</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D37" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="E37" s="12"/>
+      <c r="F37" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="G37" s="12"/>
+      <c r="H37" s="12"/>
+      <c r="I37" s="12"/>
+      <c r="J37" s="12"/>
     </row>
     <row r="38" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B38" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C38" s="13" t="s">
-        <v>152</v>
-      </c>
-      <c r="D38" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14" t="s">
-        <v>159</v>
-      </c>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="14"/>
-      <c r="J38" s="14"/>
+        <v>96</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="D38" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="E38" s="12"/>
+      <c r="F38" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="G38" s="12"/>
+      <c r="H38" s="12"/>
+      <c r="I38" s="12"/>
+      <c r="J38" s="12"/>
     </row>
     <row r="39" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B39" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C39" s="13" t="s">
-        <v>153</v>
-      </c>
-      <c r="D39" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="D39" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="E39" s="17"/>
-      <c r="F39" s="14" t="s">
-        <v>160</v>
+      <c r="E39" s="15"/>
+      <c r="F39" s="12" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="40" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B40" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C40" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="D40" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="E40" s="17"/>
-      <c r="F40" s="14" t="s">
-        <v>161</v>
+        <v>96</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="D40" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="E40" s="15"/>
+      <c r="F40" s="12" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C41" s="16"/>
+      <c r="C41" s="14"/>
     </row>
     <row r="42" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C42" s="16"/>
+      <c r="C42" s="14"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/eBus_Functions/Post_Processing/Root_Cause_Analysis_Work/info/eBus_Model_Info.xlsx
+++ b/eBus_Functions/Post_Processing/Root_Cause_Analysis_Work/info/eBus_Model_Info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\TempData\Github\eBus_Tool\eBus_Functions\Post_Processing\Root_Cause_Analysis_Work\info\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B9EED08-8AC4-4BE9-A123-A42950F4C85F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D52C8A04-4B3B-4C6D-880C-5E9AB026301A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Block Diagram" sheetId="1" r:id="rId1"/>
@@ -203,9 +203,6 @@
     <t>logout.hvs_zfCetrax_gbxOut_rotSpeed</t>
   </si>
   <si>
-    <t>logout.hvs_zfCetrax_gbxAct</t>
-  </si>
-  <si>
     <t>logout.hvs_zfCetrax_gbx_pwrLoss_info</t>
   </si>
   <si>
@@ -242,9 +239,6 @@
     <t>Wheel Force</t>
   </si>
   <si>
-    <t>logout.mec_veh_FWheelTraaction_info</t>
-  </si>
-  <si>
     <t>Battery Current</t>
   </si>
   <si>
@@ -299,9 +293,6 @@
     <t>Battery Discharge Power Limit</t>
   </si>
   <si>
-    <t>logout.HVB_DischrgPwr</t>
-  </si>
-  <si>
     <t>Subsystem</t>
   </si>
   <si>
@@ -897,6 +888,15 @@
   </si>
   <si>
     <t>Batt_SOC_init</t>
+  </si>
+  <si>
+    <t>logout.hvs_zfCetrax_gbx_gearAct</t>
+  </si>
+  <si>
+    <t>logout.mec_veh_FWheelTraction_info</t>
+  </si>
+  <si>
+    <t>logout.HVB_MaxDischrgPwr</t>
   </si>
 </sst>
 </file>
@@ -1146,7 +1146,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1209,7 +1209,11 @@
     <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1222,16 +1226,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1628,7 +1622,7 @@
         <v>8</v>
       </c>
       <c r="H28" s="15" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="I28" s="16" t="s">
         <v>10</v>
@@ -1636,7 +1630,7 @@
     </row>
     <row r="29" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G29" s="6"/>
-      <c r="H29" s="34" t="s">
+      <c r="H29" s="36" t="s">
         <v>6</v>
       </c>
       <c r="I29" s="7" t="s">
@@ -1645,14 +1639,14 @@
     </row>
     <row r="30" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G30" s="8"/>
-      <c r="H30" s="30"/>
+      <c r="H30" s="31"/>
       <c r="I30" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="31" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G31" s="9"/>
-      <c r="H31" s="35"/>
+      <c r="H31" s="32"/>
       <c r="I31" s="2" t="s">
         <v>32</v>
       </c>
@@ -1661,7 +1655,7 @@
       <c r="G32" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="H32" s="31" t="s">
+      <c r="H32" s="33" t="s">
         <v>0</v>
       </c>
       <c r="I32" s="7" t="s">
@@ -1672,7 +1666,7 @@
       <c r="G33" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="H33" s="32"/>
+      <c r="H33" s="34"/>
       <c r="I33" s="1" t="s">
         <v>12</v>
       </c>
@@ -1681,56 +1675,56 @@
       <c r="G34" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="H34" s="32"/>
+      <c r="H34" s="34"/>
       <c r="I34" s="1"/>
     </row>
     <row r="35" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G35" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="H35" s="32"/>
+      <c r="H35" s="34"/>
       <c r="I35" s="1"/>
     </row>
     <row r="36" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G36" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="H36" s="32"/>
+        <v>184</v>
+      </c>
+      <c r="H36" s="34"/>
       <c r="I36" s="1"/>
     </row>
     <row r="37" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G37" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="H37" s="33"/>
+      <c r="H37" s="35"/>
       <c r="I37" s="2"/>
     </row>
     <row r="38" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G38" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H38" s="34" t="s">
+      <c r="H38" s="36" t="s">
         <v>2</v>
       </c>
       <c r="I38" s="7" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="39" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G39" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="H39" s="35"/>
+      <c r="H39" s="32"/>
       <c r="I39" s="2" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
     </row>
     <row r="40" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G40" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="H40" s="31" t="s">
-        <v>111</v>
+        <v>176</v>
+      </c>
+      <c r="H40" s="33" t="s">
+        <v>108</v>
       </c>
       <c r="I40" s="7" t="s">
         <v>36</v>
@@ -1738,127 +1732,127 @@
     </row>
     <row r="41" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G41" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="H41" s="32"/>
+        <v>177</v>
+      </c>
+      <c r="H41" s="34"/>
       <c r="I41" s="1" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="42" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G42" s="8"/>
-      <c r="H42" s="32"/>
+      <c r="H42" s="34"/>
       <c r="I42" s="1" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="43" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G43" s="8"/>
-      <c r="H43" s="32"/>
+      <c r="H43" s="34"/>
       <c r="I43" s="1" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="44" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G44" s="8"/>
-      <c r="H44" s="32"/>
+      <c r="H44" s="34"/>
       <c r="I44" s="1" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="45" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G45" s="8"/>
-      <c r="H45" s="32"/>
+      <c r="H45" s="34"/>
       <c r="I45" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="46" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G46" s="8"/>
-      <c r="H46" s="32"/>
+      <c r="H46" s="34"/>
       <c r="I46" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="47" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G47" s="8"/>
-      <c r="H47" s="32"/>
+      <c r="H47" s="34"/>
       <c r="I47" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="48" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G48" s="8"/>
-      <c r="H48" s="32"/>
+      <c r="H48" s="34"/>
       <c r="I48" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="49" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G49" s="8"/>
-      <c r="H49" s="32"/>
+      <c r="H49" s="34"/>
       <c r="I49" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
     </row>
     <row r="50" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G50" s="8"/>
-      <c r="H50" s="32"/>
+      <c r="H50" s="34"/>
       <c r="I50" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="51" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G51" s="9"/>
-      <c r="H51" s="33"/>
+      <c r="H51" s="35"/>
       <c r="I51" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
     </row>
     <row r="52" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G52" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="H52" s="34" t="s">
-        <v>112</v>
+      <c r="H52" s="36" t="s">
+        <v>109</v>
       </c>
       <c r="I52" s="7" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
     </row>
     <row r="53" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G53" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="H53" s="30"/>
+      <c r="H53" s="31"/>
       <c r="I53" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
     </row>
     <row r="54" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G54" s="8"/>
-      <c r="H54" s="30"/>
+      <c r="H54" s="31"/>
       <c r="I54" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="55" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G55" s="8"/>
-      <c r="H55" s="30"/>
+      <c r="H55" s="31"/>
       <c r="I55" s="1" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="56" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G56" s="8"/>
-      <c r="H56" s="30"/>
+      <c r="H56" s="31"/>
       <c r="I56" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="57" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G57" s="17" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="H57" s="18" t="s">
         <v>17</v>
@@ -1871,25 +1865,25 @@
       <c r="G58" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="H58" s="31" t="s">
-        <v>113</v>
+      <c r="H58" s="33" t="s">
+        <v>110</v>
       </c>
       <c r="I58" s="7" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="59" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G59" s="8"/>
-      <c r="H59" s="38"/>
+      <c r="H59" s="34"/>
       <c r="I59" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="60" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G60" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H60" s="34" t="s">
+      <c r="H60" s="36" t="s">
         <v>19</v>
       </c>
       <c r="I60" s="7" t="s">
@@ -1898,149 +1892,149 @@
     </row>
     <row r="61" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G61" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="H61" s="37"/>
+        <v>185</v>
+      </c>
+      <c r="H61" s="31"/>
       <c r="I61" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="62" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G62" s="8"/>
-      <c r="H62" s="37"/>
+      <c r="H62" s="31"/>
       <c r="I62" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="63" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G63" s="8"/>
-      <c r="H63" s="37"/>
+      <c r="H63" s="31"/>
       <c r="I63" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="64" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G64" s="8"/>
-      <c r="H64" s="37"/>
+      <c r="H64" s="31"/>
       <c r="I64" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="65" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G65" s="8"/>
-      <c r="H65" s="37"/>
+      <c r="H65" s="31"/>
       <c r="I65" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="66" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G66" s="9"/>
-      <c r="H66" s="35"/>
+      <c r="H66" s="32"/>
       <c r="I66" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="67" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G67" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="H67" s="37" t="s">
-        <v>114</v>
+      <c r="H67" s="31" t="s">
+        <v>111</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="68" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G68" s="8"/>
-      <c r="H68" s="37"/>
+      <c r="H68" s="31"/>
       <c r="I68" s="1" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="69" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G69" s="8"/>
-      <c r="H69" s="37"/>
+      <c r="H69" s="31"/>
       <c r="I69" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="70" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G70" s="8"/>
-      <c r="H70" s="37"/>
+      <c r="H70" s="31"/>
       <c r="I70" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="71" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G71" s="8"/>
-      <c r="H71" s="37"/>
+      <c r="H71" s="31"/>
       <c r="I71" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="72" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G72" s="9"/>
-      <c r="H72" s="35"/>
+      <c r="H72" s="32"/>
       <c r="I72" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="73" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G73" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="H73" s="31" t="s">
-        <v>115</v>
+      <c r="H73" s="33" t="s">
+        <v>112</v>
       </c>
       <c r="I73" s="7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="74" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G74" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="H74" s="32"/>
+        <v>77</v>
+      </c>
+      <c r="H74" s="34"/>
       <c r="I74" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="75" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G75" s="8"/>
-      <c r="H75" s="32"/>
+      <c r="H75" s="34"/>
       <c r="I75" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="76" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G76" s="9"/>
-      <c r="H76" s="33"/>
+      <c r="H76" s="35"/>
       <c r="I76" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="77" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G77" s="8"/>
-      <c r="H77" s="30" t="s">
-        <v>116</v>
+      <c r="H77" s="31" t="s">
+        <v>113</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="78" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G78" s="8"/>
-      <c r="H78" s="30"/>
+      <c r="H78" s="31"/>
       <c r="I78" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="79" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G79" s="9"/>
-      <c r="H79" s="35"/>
+      <c r="H79" s="32"/>
       <c r="I79" s="2" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -2076,12 +2070,14 @@
     <col min="4" max="4" width="24.6640625" style="21" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="46.44140625" style="20" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="39.5546875" customWidth="1"/>
-    <col min="7" max="9" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28" customWidth="1"/>
+    <col min="8" max="8" width="31.88671875" customWidth="1"/>
+    <col min="9" max="9" width="17.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="22" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B1" s="22" t="s">
         <v>28</v>
@@ -2090,7 +2086,7 @@
         <v>9</v>
       </c>
       <c r="D1" s="23" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E1" s="22" t="s">
         <v>23</v>
@@ -2110,16 +2106,16 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="24" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B2" s="11" t="s">
         <v>29</v>
       </c>
       <c r="C2" s="25" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D2" s="29" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E2" s="26" t="s">
         <v>30</v>
@@ -2138,7 +2134,7 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B3" s="11" t="s">
         <v>7</v>
@@ -2147,7 +2143,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="29" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E3" s="26" t="s">
         <v>31</v>
@@ -2166,7 +2162,7 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="24" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B4" s="11" t="s">
         <v>32</v>
@@ -2175,7 +2171,7 @@
         <v>33</v>
       </c>
       <c r="D4" s="29" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="E4" s="26" t="s">
         <v>34</v>
@@ -2194,7 +2190,7 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="27" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>11</v>
@@ -2203,16 +2199,16 @@
         <v>1</v>
       </c>
       <c r="D5" s="29" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="E5" s="26" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="F5" s="26" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="G5" s="26" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="H5" s="11"/>
       <c r="I5" s="11"/>
@@ -2222,7 +2218,7 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="27" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>12</v>
@@ -2231,16 +2227,16 @@
         <v>1</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="E6" s="26" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="F6" s="26" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="G6" s="26" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="H6" s="11"/>
       <c r="I6" s="11"/>
@@ -2250,25 +2246,25 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="24" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C7" s="25" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="29" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="E7" s="26" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="F7" s="26" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="G7" s="26" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="H7" s="11"/>
       <c r="I7" s="11"/>
@@ -2278,25 +2274,25 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="24" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C8" s="25" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="29" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="E8" s="26" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="F8" s="26" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="G8" s="26" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="H8" s="11"/>
       <c r="I8" s="11"/>
@@ -2306,7 +2302,7 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="27" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>36</v>
@@ -2315,7 +2311,7 @@
         <v>3</v>
       </c>
       <c r="D9" s="29" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="E9" s="26" t="s">
         <v>37</v>
@@ -2334,7 +2330,7 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="27" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>38</v>
@@ -2343,7 +2339,7 @@
         <v>3</v>
       </c>
       <c r="D10" s="29" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E10" s="26" t="s">
         <v>39</v>
@@ -2362,7 +2358,7 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="27" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>40</v>
@@ -2371,7 +2367,7 @@
         <v>5</v>
       </c>
       <c r="D11" s="29" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E11" s="26" t="s">
         <v>41</v>
@@ -2390,7 +2386,7 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="27" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B12" s="11" t="s">
         <v>42</v>
@@ -2399,7 +2395,7 @@
         <v>5</v>
       </c>
       <c r="D12" s="29" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E12" s="26" t="s">
         <v>43</v>
@@ -2418,7 +2414,7 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="27" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B13" s="11" t="s">
         <v>44</v>
@@ -2427,7 +2423,7 @@
         <v>4</v>
       </c>
       <c r="D13" s="29" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E13" s="26" t="s">
         <v>45</v>
@@ -2446,7 +2442,7 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="27" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B14" s="11" t="s">
         <v>46</v>
@@ -2455,7 +2451,7 @@
         <v>4</v>
       </c>
       <c r="D14" s="29" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="E14" s="26" t="s">
         <v>47</v>
@@ -2474,16 +2470,16 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="27" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C15" s="25" t="s">
         <v>4</v>
       </c>
       <c r="D15" s="29" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="E15" s="26" t="s">
         <v>48</v>
@@ -2502,16 +2498,16 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="27" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C16" s="25" t="s">
         <v>4</v>
       </c>
       <c r="D16" s="29" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="E16" s="26" t="s">
         <v>49</v>
@@ -2530,7 +2526,7 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="27" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B17" s="11" t="s">
         <v>50</v>
@@ -2539,7 +2535,7 @@
         <v>3</v>
       </c>
       <c r="D17" s="29" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E17" s="26" t="s">
         <v>51</v>
@@ -2558,16 +2554,16 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="27" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C18" s="25" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="29" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E18" s="26" t="s">
         <v>52</v>
@@ -2586,7 +2582,7 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="27" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B19" s="11" t="s">
         <v>53</v>
@@ -2595,7 +2591,7 @@
         <v>3</v>
       </c>
       <c r="D19" s="29" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E19" s="26" t="s">
         <v>54</v>
@@ -2614,16 +2610,16 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="27" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C20" s="25" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="29" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="E20" s="26" t="s">
         <v>55</v>
@@ -2642,16 +2638,16 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="24" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C21" s="25" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="29" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="E21" s="26" t="s">
         <v>56</v>
@@ -2670,16 +2666,16 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="24" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C22" s="25" t="s">
         <v>5</v>
       </c>
       <c r="D22" s="29" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E22" s="26" t="s">
         <v>57</v>
@@ -2698,25 +2694,25 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="24" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B23" s="11" t="s">
         <v>15</v>
       </c>
       <c r="C23" s="25"/>
       <c r="D23" s="29" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E23" s="26" t="s">
-        <v>58</v>
+        <v>287</v>
       </c>
       <c r="F23" s="26" t="s">
-        <v>58</v>
+        <v>287</v>
       </c>
       <c r="G23" s="26" t="s">
-        <v>58</v>
-      </c>
-      <c r="H23" s="11"/>
+        <v>287</v>
+      </c>
+      <c r="H23" s="26"/>
       <c r="I23" s="11"/>
       <c r="J23" s="11"/>
       <c r="K23" s="11"/>
@@ -2724,14 +2720,14 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="24" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C24" s="25"/>
       <c r="D24" s="29" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="E24" s="26" t="s">
         <v>35</v>
@@ -2750,7 +2746,7 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="24" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B25" s="11" t="s">
         <v>16</v>
@@ -2759,16 +2755,16 @@
         <v>4</v>
       </c>
       <c r="D25" s="29" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="E25" s="26" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F25" s="26" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G25" s="26" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H25" s="11"/>
       <c r="I25" s="11"/>
@@ -2787,16 +2783,16 @@
         <v>3</v>
       </c>
       <c r="D26" s="29" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E26" s="28" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="F26" s="28" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="G26" s="28" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="H26" s="11"/>
       <c r="I26" s="11"/>
@@ -2806,25 +2802,25 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="24" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C27" s="25" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D27" s="29" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E27" s="28" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="F27" s="28" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="G27" s="28" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="H27" s="11"/>
       <c r="I27" s="11"/>
@@ -2834,25 +2830,25 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="24" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C28" s="25" t="s">
         <v>4</v>
       </c>
       <c r="D28" s="29" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="E28" s="26" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="F28" s="26" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="G28" s="26" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="H28" s="11"/>
       <c r="I28" s="11"/>
@@ -2862,25 +2858,25 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="27" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B29" s="11" t="s">
         <v>20</v>
       </c>
       <c r="C29" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="D29" s="29" t="s">
+        <v>217</v>
+      </c>
+      <c r="E29" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="D29" s="29" t="s">
-        <v>220</v>
-      </c>
-      <c r="E29" s="26" t="s">
-        <v>61</v>
-      </c>
       <c r="F29" s="26" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G29" s="26" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H29" s="11"/>
       <c r="I29" s="11"/>
@@ -2890,25 +2886,25 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="27" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B30" s="11" t="s">
         <v>21</v>
       </c>
       <c r="C30" s="25" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D30" s="29" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E30" s="26" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F30" s="26" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G30" s="26" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H30" s="11"/>
       <c r="I30" s="11"/>
@@ -2918,25 +2914,25 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="27" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B31" s="11" t="s">
         <v>22</v>
       </c>
       <c r="C31" s="25" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="D31" s="29" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E31" s="26" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F31" s="26" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G31" s="26" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H31" s="11"/>
       <c r="I31" s="11"/>
@@ -2946,25 +2942,25 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="27" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C32" s="25" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D32" s="29" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E32" s="26" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="F32" s="26" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="G32" s="26" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="H32" s="11"/>
       <c r="I32" s="11"/>
@@ -2974,25 +2970,25 @@
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="27" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B33" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="C33" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="C33" s="25" t="s">
+      <c r="D33" s="29" t="s">
+        <v>221</v>
+      </c>
+      <c r="E33" s="26" t="s">
         <v>66</v>
       </c>
-      <c r="D33" s="29" t="s">
-        <v>224</v>
-      </c>
-      <c r="E33" s="26" t="s">
-        <v>67</v>
-      </c>
       <c r="F33" s="26" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G33" s="26" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H33" s="11"/>
       <c r="I33" s="11"/>
@@ -3002,25 +2998,25 @@
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="27" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B34" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C34" s="25" t="s">
+        <v>65</v>
+      </c>
+      <c r="D34" s="29" t="s">
+        <v>222</v>
+      </c>
+      <c r="E34" s="26" t="s">
         <v>68</v>
       </c>
-      <c r="C34" s="25" t="s">
-        <v>66</v>
-      </c>
-      <c r="D34" s="29" t="s">
-        <v>225</v>
-      </c>
-      <c r="E34" s="26" t="s">
-        <v>69</v>
-      </c>
       <c r="F34" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G34" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H34" s="11"/>
       <c r="I34" s="11"/>
@@ -3030,27 +3026,27 @@
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="27" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C35" s="25" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D35" s="29" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E35" s="26" t="s">
-        <v>71</v>
+        <v>288</v>
       </c>
       <c r="F35" s="26" t="s">
-        <v>71</v>
+        <v>288</v>
       </c>
       <c r="G35" s="26" t="s">
-        <v>71</v>
-      </c>
-      <c r="H35" s="11"/>
+        <v>288</v>
+      </c>
+      <c r="H35" s="26"/>
       <c r="I35" s="11"/>
       <c r="J35" s="11"/>
       <c r="K35" s="11"/>
@@ -3058,25 +3054,25 @@
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="24" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B36" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="C36" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="D36" s="29" t="s">
+        <v>226</v>
+      </c>
+      <c r="E36" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="C36" s="25" t="s">
-        <v>73</v>
-      </c>
-      <c r="D36" s="29" t="s">
-        <v>229</v>
-      </c>
-      <c r="E36" s="26" t="s">
-        <v>74</v>
-      </c>
       <c r="F36" s="26" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G36" s="26" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H36" s="11"/>
       <c r="I36" s="11"/>
@@ -3086,25 +3082,25 @@
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="24" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C37" s="25" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D37" s="29" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E37" s="26" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F37" s="26" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G37" s="26" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H37" s="11"/>
       <c r="I37" s="11"/>
@@ -3114,25 +3110,25 @@
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="24" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C38" s="25" t="s">
         <v>4</v>
       </c>
       <c r="D38" s="29" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E38" s="26" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="G38" s="11" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="H38" s="11"/>
       <c r="I38" s="11"/>
@@ -3142,25 +3138,25 @@
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="24" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C39" s="25" t="s">
         <v>4</v>
       </c>
       <c r="D39" s="29" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E39" s="26" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="G39" s="11" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H39" s="11"/>
       <c r="I39" s="11"/>
@@ -3170,25 +3166,25 @@
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="24" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C40" s="25" t="s">
         <v>1</v>
       </c>
       <c r="D40" s="29" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="E40" s="26" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F40" s="26" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G40" s="26" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H40" s="11"/>
       <c r="I40" s="11"/>
@@ -3198,25 +3194,25 @@
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="24" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C41" s="25" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="29" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="E41" s="26" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="G41" s="11" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="H41" s="11"/>
       <c r="I41" s="11"/>
@@ -3226,25 +3222,25 @@
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="27" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C42" s="25" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D42" s="29" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="E42" s="26" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F42" s="26" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G42" s="26" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H42" s="11"/>
       <c r="I42" s="11"/>
@@ -3254,25 +3250,25 @@
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="27" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C43" s="25" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D43" s="29" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="E43" s="26" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F43" s="26" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G43" s="26" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H43" s="11"/>
       <c r="I43" s="11"/>
@@ -3282,25 +3278,25 @@
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="27" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C44" s="25" t="s">
         <v>4</v>
       </c>
       <c r="D44" s="29" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="E44" s="26" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F44" s="26" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G44" s="26" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H44" s="11"/>
       <c r="I44" s="11"/>
@@ -3310,25 +3306,25 @@
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="27" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C45" s="25" t="s">
         <v>4</v>
       </c>
       <c r="D45" s="29" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="E45" s="26" t="s">
-        <v>90</v>
+        <v>289</v>
       </c>
       <c r="F45" s="26" t="s">
-        <v>90</v>
+        <v>289</v>
       </c>
       <c r="G45" s="26" t="s">
-        <v>90</v>
+        <v>289</v>
       </c>
       <c r="H45" s="11"/>
       <c r="I45" s="11"/>
@@ -3338,25 +3334,25 @@
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="24" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C46" s="25" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D46" s="29" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="E46" s="28" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="F46" s="28" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="G46" s="28" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="H46" s="11"/>
       <c r="I46" s="11"/>
@@ -3366,25 +3362,25 @@
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="24" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C47" s="25" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D47" s="29" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="E47" s="28" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="F47" s="28" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G47" s="28" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="H47" s="11"/>
       <c r="I47" s="11"/>
@@ -4170,40 +4166,40 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E1" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="H1" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>107</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="24" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B2" s="10"/>
       <c r="C2" s="12"/>
-      <c r="D2" s="36"/>
+      <c r="D2" s="30"/>
       <c r="E2" s="11"/>
       <c r="F2" s="11"/>
       <c r="G2" s="11"/>
@@ -4212,11 +4208,11 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="27" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B3" s="10"/>
       <c r="C3" s="12"/>
-      <c r="D3" s="36"/>
+      <c r="D3" s="30"/>
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
       <c r="G3" s="11"/>
@@ -4225,11 +4221,11 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="24" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B4" s="10"/>
       <c r="C4" s="12"/>
-      <c r="D4" s="36"/>
+      <c r="D4" s="30"/>
       <c r="E4" s="11"/>
       <c r="F4" s="11"/>
       <c r="G4" s="11"/>
@@ -4238,311 +4234,311 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="27" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="36" t="s">
-        <v>259</v>
+      <c r="D5" s="30" t="s">
+        <v>256</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="H5" s="11"/>
       <c r="I5" s="11"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="27" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="36" t="s">
-        <v>260</v>
+      <c r="D6" s="30" t="s">
+        <v>257</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="H6" s="11"/>
       <c r="I6" s="11"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="27" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="36" t="s">
-        <v>261</v>
+      <c r="D7" s="30" t="s">
+        <v>258</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="H7" s="11"/>
       <c r="I7" s="11"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="27" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="36" t="s">
-        <v>262</v>
+      <c r="D8" s="30" t="s">
+        <v>259</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="H8" s="11"/>
       <c r="I8" s="11"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="27" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="D9" s="36" t="s">
-        <v>263</v>
+        <v>117</v>
+      </c>
+      <c r="D9" s="30" t="s">
+        <v>260</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="H9" s="11"/>
       <c r="I9" s="11"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="27" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C10" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="D10" s="36" t="s">
-        <v>264</v>
+      <c r="D10" s="30" t="s">
+        <v>261</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="27" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="D11" s="36" t="s">
-        <v>265</v>
+        <v>73</v>
+      </c>
+      <c r="D11" s="30" t="s">
+        <v>262</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="H11" s="11"/>
       <c r="I11" s="11"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="27" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="D12" s="36" t="s">
-        <v>266</v>
+        <v>117</v>
+      </c>
+      <c r="D12" s="30" t="s">
+        <v>263</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="H12" s="11"/>
       <c r="I12" s="11"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="27" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C13" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="D13" s="36" t="s">
-        <v>267</v>
+      <c r="D13" s="30" t="s">
+        <v>264</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="H13" s="11"/>
       <c r="I13" s="11"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="27" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="D14" s="36" t="s">
-        <v>268</v>
+        <v>73</v>
+      </c>
+      <c r="D14" s="30" t="s">
+        <v>265</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="H14" s="11"/>
       <c r="I14" s="11"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="27" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="D15" s="36" t="s">
-        <v>266</v>
+        <v>117</v>
+      </c>
+      <c r="D15" s="30" t="s">
+        <v>263</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="H15" s="11"/>
       <c r="I15" s="11"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="27" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C16" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="D16" s="36" t="s">
-        <v>269</v>
+      <c r="D16" s="30" t="s">
+        <v>266</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H16" s="11"/>
       <c r="I16" s="11"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="24" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B17" s="10"/>
       <c r="C17" s="12"/>
-      <c r="D17" s="36"/>
+      <c r="D17" s="30"/>
       <c r="E17" s="11"/>
       <c r="F17" s="11"/>
       <c r="G17" s="11"/>
@@ -4551,34 +4547,34 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="27" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C18" s="12"/>
-      <c r="D18" s="36" t="s">
-        <v>270</v>
+      <c r="D18" s="30" t="s">
+        <v>267</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="H18" s="11"/>
       <c r="I18" s="11"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="24" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B19" s="10"/>
       <c r="C19" s="12"/>
-      <c r="D19" s="36"/>
+      <c r="D19" s="30"/>
       <c r="E19" s="11"/>
       <c r="F19" s="11"/>
       <c r="G19" s="11"/>
@@ -4587,465 +4583,465 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="27" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C20" s="12"/>
-      <c r="D20" s="36" t="s">
-        <v>271</v>
+      <c r="D20" s="30" t="s">
+        <v>268</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="H20" s="11"/>
       <c r="I20" s="11"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="27" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C21" s="12"/>
-      <c r="D21" s="36" t="s">
-        <v>274</v>
+      <c r="D21" s="30" t="s">
+        <v>271</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="H21" s="11"/>
       <c r="I21" s="11"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="27" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C22" s="12"/>
-      <c r="D22" s="36" t="s">
-        <v>272</v>
+      <c r="D22" s="30" t="s">
+        <v>269</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="H22" s="11"/>
       <c r="I22" s="11"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="27" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B23" s="10" t="s">
         <v>13</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="D23" s="36" t="s">
-        <v>273</v>
+        <v>148</v>
+      </c>
+      <c r="D23" s="30" t="s">
+        <v>270</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="H23" s="11"/>
       <c r="I23" s="11"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="27" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C24" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="D24" s="36" t="s">
-        <v>275</v>
+      <c r="D24" s="30" t="s">
+        <v>272</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G24" s="11" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="H24" s="11"/>
       <c r="I24" s="11"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="27" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C25" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="D25" s="36" t="s">
-        <v>276</v>
+      <c r="D25" s="30" t="s">
+        <v>273</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="G25" s="11" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="H25" s="11"/>
       <c r="I25" s="11"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="27" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="D26" s="36" t="s">
-        <v>277</v>
+        <v>117</v>
+      </c>
+      <c r="D26" s="30" t="s">
+        <v>274</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="G26" s="11" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H26" s="11"/>
       <c r="I26" s="11"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="24" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C27" s="12"/>
-      <c r="D27" s="36" t="s">
-        <v>286</v>
+      <c r="D27" s="30" t="s">
+        <v>283</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="G27" s="11" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="H27" s="11"/>
       <c r="I27" s="11"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="24" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C28" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="D28" s="36" t="s">
-        <v>287</v>
+      <c r="D28" s="30" t="s">
+        <v>284</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="G28" s="11" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="H28" s="11"/>
       <c r="I28" s="11"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="24" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="D29" s="36" t="s">
-        <v>288</v>
+        <v>128</v>
+      </c>
+      <c r="D29" s="30" t="s">
+        <v>285</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="G29" s="11" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="H29" s="11"/>
       <c r="I29" s="11"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="24" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C30" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="D30" s="36" t="s">
-        <v>289</v>
+      <c r="D30" s="30" t="s">
+        <v>286</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="G30" s="11" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H30" s="11"/>
       <c r="I30" s="11"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="27" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="D31" s="36" t="s">
-        <v>278</v>
+        <v>71</v>
+      </c>
+      <c r="D31" s="30" t="s">
+        <v>275</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="H31" s="11"/>
       <c r="I31" s="11"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="27" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="D32" s="36" t="s">
-        <v>279</v>
+        <v>71</v>
+      </c>
+      <c r="D32" s="30" t="s">
+        <v>276</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="G32" s="11" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="H32" s="11"/>
       <c r="I32" s="11"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="27" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C33" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="D33" s="36" t="s">
-        <v>280</v>
+      <c r="D33" s="30" t="s">
+        <v>277</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="G33" s="11" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="H33" s="11"/>
       <c r="I33" s="11"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="27" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C34" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="D34" s="36" t="s">
-        <v>281</v>
+      <c r="D34" s="30" t="s">
+        <v>278</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="G34" s="11" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="H34" s="11"/>
       <c r="I34" s="11"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="27" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="D35" s="36" t="s">
-        <v>282</v>
+        <v>71</v>
+      </c>
+      <c r="D35" s="30" t="s">
+        <v>279</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="G35" s="11" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="H35" s="11"/>
       <c r="I35" s="11"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="27" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="D36" s="36" t="s">
-        <v>283</v>
+        <v>71</v>
+      </c>
+      <c r="D36" s="30" t="s">
+        <v>280</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="G36" s="11" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H36" s="11"/>
       <c r="I36" s="11"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="27" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C37" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="D37" s="36" t="s">
-        <v>284</v>
+      <c r="D37" s="30" t="s">
+        <v>281</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="G37" s="11" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="27" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C38" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="D38" s="36" t="s">
-        <v>285</v>
+      <c r="D38" s="30" t="s">
+        <v>282</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G38" s="11" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">

--- a/eBus_Functions/Post_Processing/Root_Cause_Analysis_Work/info/eBus_Model_Info.xlsx
+++ b/eBus_Functions/Post_Processing/Root_Cause_Analysis_Work/info/eBus_Model_Info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\TempData\Github\eBus_Tool\eBus_Functions\Post_Processing\Root_Cause_Analysis_Work\info\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D52C8A04-4B3B-4C6D-880C-5E9AB026301A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B4530FF-D445-45FB-B943-B2E10A2A4F91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Block Diagram" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="292">
   <si>
     <t>Driver</t>
   </si>
@@ -212,12 +212,6 @@
     <t>logout.mec_veh_transAcc</t>
   </si>
   <si>
-    <t>logout.mec_veh_transVel</t>
-  </si>
-  <si>
-    <t>logout.mec_veh_transPos</t>
-  </si>
-  <si>
     <t>Rolling Resistance Force</t>
   </si>
   <si>
@@ -897,6 +891,18 @@
   </si>
   <si>
     <t>logout.HVB_MaxDischrgPwr</t>
+  </si>
+  <si>
+    <t>logout.mec_veh_transPos*1000</t>
+  </si>
+  <si>
+    <t>logout.mec_veh_transVel*3.6</t>
+  </si>
+  <si>
+    <t>logout.drv_AccPdl_pos*100</t>
+  </si>
+  <si>
+    <t>logout.drv_BrkPdl_pos*100</t>
   </si>
 </sst>
 </file>
@@ -1210,6 +1216,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1223,9 +1232,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1622,7 +1628,7 @@
         <v>8</v>
       </c>
       <c r="H28" s="15" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I28" s="16" t="s">
         <v>10</v>
@@ -1630,7 +1636,7 @@
     </row>
     <row r="29" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G29" s="6"/>
-      <c r="H29" s="36" t="s">
+      <c r="H29" s="31" t="s">
         <v>6</v>
       </c>
       <c r="I29" s="7" t="s">
@@ -1639,14 +1645,14 @@
     </row>
     <row r="30" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G30" s="8"/>
-      <c r="H30" s="31"/>
+      <c r="H30" s="32"/>
       <c r="I30" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="31" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G31" s="9"/>
-      <c r="H31" s="32"/>
+      <c r="H31" s="33"/>
       <c r="I31" s="2" t="s">
         <v>32</v>
       </c>
@@ -1655,7 +1661,7 @@
       <c r="G32" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="H32" s="33" t="s">
+      <c r="H32" s="34" t="s">
         <v>0</v>
       </c>
       <c r="I32" s="7" t="s">
@@ -1666,7 +1672,7 @@
       <c r="G33" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="H33" s="34"/>
+      <c r="H33" s="35"/>
       <c r="I33" s="1" t="s">
         <v>12</v>
       </c>
@@ -1675,56 +1681,56 @@
       <c r="G34" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="H34" s="34"/>
+      <c r="H34" s="35"/>
       <c r="I34" s="1"/>
     </row>
     <row r="35" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G35" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="H35" s="34"/>
+      <c r="H35" s="35"/>
       <c r="I35" s="1"/>
     </row>
     <row r="36" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G36" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="H36" s="34"/>
+        <v>182</v>
+      </c>
+      <c r="H36" s="35"/>
       <c r="I36" s="1"/>
     </row>
     <row r="37" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G37" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="H37" s="35"/>
+      <c r="H37" s="36"/>
       <c r="I37" s="2"/>
     </row>
     <row r="38" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G38" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H38" s="36" t="s">
+      <c r="H38" s="31" t="s">
         <v>2</v>
       </c>
       <c r="I38" s="7" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="39" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G39" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="H39" s="32"/>
+      <c r="H39" s="33"/>
       <c r="I39" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="40" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G40" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="H40" s="33" t="s">
-        <v>108</v>
+        <v>174</v>
+      </c>
+      <c r="H40" s="34" t="s">
+        <v>106</v>
       </c>
       <c r="I40" s="7" t="s">
         <v>36</v>
@@ -1732,127 +1738,127 @@
     </row>
     <row r="41" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G41" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="H41" s="34"/>
+        <v>175</v>
+      </c>
+      <c r="H41" s="35"/>
       <c r="I41" s="1" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="42" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G42" s="8"/>
-      <c r="H42" s="34"/>
+      <c r="H42" s="35"/>
       <c r="I42" s="1" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="43" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G43" s="8"/>
-      <c r="H43" s="34"/>
+      <c r="H43" s="35"/>
       <c r="I43" s="1" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="44" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G44" s="8"/>
-      <c r="H44" s="34"/>
+      <c r="H44" s="35"/>
       <c r="I44" s="1" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="45" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G45" s="8"/>
-      <c r="H45" s="34"/>
+      <c r="H45" s="35"/>
       <c r="I45" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="46" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G46" s="8"/>
-      <c r="H46" s="34"/>
+      <c r="H46" s="35"/>
       <c r="I46" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="47" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G47" s="8"/>
-      <c r="H47" s="34"/>
+      <c r="H47" s="35"/>
       <c r="I47" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="48" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G48" s="8"/>
-      <c r="H48" s="34"/>
+      <c r="H48" s="35"/>
       <c r="I48" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="49" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G49" s="8"/>
-      <c r="H49" s="34"/>
+      <c r="H49" s="35"/>
       <c r="I49" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="50" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G50" s="8"/>
-      <c r="H50" s="34"/>
+      <c r="H50" s="35"/>
       <c r="I50" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="51" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G51" s="9"/>
-      <c r="H51" s="35"/>
+      <c r="H51" s="36"/>
       <c r="I51" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="52" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G52" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="H52" s="36" t="s">
-        <v>109</v>
+      <c r="H52" s="31" t="s">
+        <v>107</v>
       </c>
       <c r="I52" s="7" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="53" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G53" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="H53" s="31"/>
+      <c r="H53" s="32"/>
       <c r="I53" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="54" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G54" s="8"/>
-      <c r="H54" s="31"/>
+      <c r="H54" s="32"/>
       <c r="I54" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="55" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G55" s="8"/>
-      <c r="H55" s="31"/>
+      <c r="H55" s="32"/>
       <c r="I55" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="56" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G56" s="8"/>
-      <c r="H56" s="31"/>
+      <c r="H56" s="32"/>
       <c r="I56" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="57" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G57" s="17" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H57" s="18" t="s">
         <v>17</v>
@@ -1865,25 +1871,25 @@
       <c r="G58" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="H58" s="33" t="s">
-        <v>110</v>
+      <c r="H58" s="34" t="s">
+        <v>108</v>
       </c>
       <c r="I58" s="7" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="59" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G59" s="8"/>
-      <c r="H59" s="34"/>
+      <c r="H59" s="35"/>
       <c r="I59" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="60" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G60" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H60" s="36" t="s">
+      <c r="H60" s="31" t="s">
         <v>19</v>
       </c>
       <c r="I60" s="7" t="s">
@@ -1892,163 +1898,163 @@
     </row>
     <row r="61" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G61" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="H61" s="31"/>
+        <v>183</v>
+      </c>
+      <c r="H61" s="32"/>
       <c r="I61" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="62" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G62" s="8"/>
-      <c r="H62" s="31"/>
+      <c r="H62" s="32"/>
       <c r="I62" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="63" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G63" s="8"/>
-      <c r="H63" s="31"/>
+      <c r="H63" s="32"/>
       <c r="I63" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="64" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G64" s="8"/>
-      <c r="H64" s="31"/>
+      <c r="H64" s="32"/>
       <c r="I64" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="65" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G65" s="8"/>
-      <c r="H65" s="31"/>
+      <c r="H65" s="32"/>
       <c r="I65" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="66" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G66" s="9"/>
-      <c r="H66" s="32"/>
+      <c r="H66" s="33"/>
       <c r="I66" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="67" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G67" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="H67" s="31" t="s">
-        <v>111</v>
+      <c r="H67" s="32" t="s">
+        <v>109</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="68" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G68" s="8"/>
-      <c r="H68" s="31"/>
+      <c r="H68" s="32"/>
       <c r="I68" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="69" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G69" s="8"/>
-      <c r="H69" s="31"/>
+      <c r="H69" s="32"/>
       <c r="I69" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="70" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G70" s="8"/>
-      <c r="H70" s="31"/>
+      <c r="H70" s="32"/>
       <c r="I70" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="71" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G71" s="8"/>
-      <c r="H71" s="31"/>
+      <c r="H71" s="32"/>
       <c r="I71" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="72" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G72" s="9"/>
-      <c r="H72" s="32"/>
+      <c r="H72" s="33"/>
       <c r="I72" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="73" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G73" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="H73" s="33" t="s">
-        <v>112</v>
+      <c r="H73" s="34" t="s">
+        <v>110</v>
       </c>
       <c r="I73" s="7" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="74" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G74" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="H74" s="34"/>
+        <v>75</v>
+      </c>
+      <c r="H74" s="35"/>
       <c r="I74" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="75" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G75" s="8"/>
-      <c r="H75" s="34"/>
+      <c r="H75" s="35"/>
       <c r="I75" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="76" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G76" s="9"/>
-      <c r="H76" s="35"/>
+      <c r="H76" s="36"/>
       <c r="I76" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="77" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G77" s="8"/>
-      <c r="H77" s="31" t="s">
-        <v>113</v>
+      <c r="H77" s="32" t="s">
+        <v>111</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="78" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G78" s="8"/>
-      <c r="H78" s="31"/>
+      <c r="H78" s="32"/>
       <c r="I78" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="79" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G79" s="9"/>
-      <c r="H79" s="32"/>
+      <c r="H79" s="33"/>
       <c r="I79" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="H67:H72"/>
+    <mergeCell ref="H73:H76"/>
+    <mergeCell ref="H52:H56"/>
+    <mergeCell ref="H60:H66"/>
+    <mergeCell ref="H77:H79"/>
     <mergeCell ref="H29:H31"/>
     <mergeCell ref="H32:H37"/>
     <mergeCell ref="H38:H39"/>
     <mergeCell ref="H40:H51"/>
     <mergeCell ref="H58:H59"/>
-    <mergeCell ref="H67:H72"/>
-    <mergeCell ref="H73:H76"/>
-    <mergeCell ref="H52:H56"/>
-    <mergeCell ref="H60:H66"/>
-    <mergeCell ref="H77:H79"/>
   </mergeCells>
   <conditionalFormatting sqref="I29:I79 G29:G79">
     <cfRule type="duplicateValues" dxfId="4" priority="1"/>
@@ -2077,7 +2083,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="22" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B1" s="22" t="s">
         <v>28</v>
@@ -2086,7 +2092,7 @@
         <v>9</v>
       </c>
       <c r="D1" s="23" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E1" s="22" t="s">
         <v>23</v>
@@ -2106,16 +2112,16 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="24" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B2" s="11" t="s">
         <v>29</v>
       </c>
       <c r="C2" s="25" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D2" s="29" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E2" s="26" t="s">
         <v>30</v>
@@ -2134,7 +2140,7 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B3" s="11" t="s">
         <v>7</v>
@@ -2143,7 +2149,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="29" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E3" s="26" t="s">
         <v>31</v>
@@ -2162,7 +2168,7 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="24" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B4" s="11" t="s">
         <v>32</v>
@@ -2171,7 +2177,7 @@
         <v>33</v>
       </c>
       <c r="D4" s="29" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E4" s="26" t="s">
         <v>34</v>
@@ -2190,7 +2196,7 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="27" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>11</v>
@@ -2199,16 +2205,16 @@
         <v>1</v>
       </c>
       <c r="D5" s="29" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E5" s="26" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F5" s="26" t="s">
-        <v>239</v>
+        <v>290</v>
       </c>
       <c r="G5" s="26" t="s">
-        <v>239</v>
+        <v>290</v>
       </c>
       <c r="H5" s="11"/>
       <c r="I5" s="11"/>
@@ -2218,7 +2224,7 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="27" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>12</v>
@@ -2227,16 +2233,16 @@
         <v>1</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E6" s="26" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F6" s="26" t="s">
-        <v>240</v>
+        <v>291</v>
       </c>
       <c r="G6" s="26" t="s">
-        <v>240</v>
+        <v>291</v>
       </c>
       <c r="H6" s="11"/>
       <c r="I6" s="11"/>
@@ -2246,25 +2252,25 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="24" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C7" s="25" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="29" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E7" s="26" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F7" s="26" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G7" s="26" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="H7" s="11"/>
       <c r="I7" s="11"/>
@@ -2274,25 +2280,25 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="24" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C8" s="25" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="29" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E8" s="26" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F8" s="26" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G8" s="26" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="H8" s="11"/>
       <c r="I8" s="11"/>
@@ -2302,7 +2308,7 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="27" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>36</v>
@@ -2311,7 +2317,7 @@
         <v>3</v>
       </c>
       <c r="D9" s="29" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E9" s="26" t="s">
         <v>37</v>
@@ -2330,7 +2336,7 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="27" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>38</v>
@@ -2339,7 +2345,7 @@
         <v>3</v>
       </c>
       <c r="D10" s="29" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E10" s="26" t="s">
         <v>39</v>
@@ -2358,7 +2364,7 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="27" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>40</v>
@@ -2367,7 +2373,7 @@
         <v>5</v>
       </c>
       <c r="D11" s="29" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E11" s="26" t="s">
         <v>41</v>
@@ -2386,7 +2392,7 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="27" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B12" s="11" t="s">
         <v>42</v>
@@ -2395,7 +2401,7 @@
         <v>5</v>
       </c>
       <c r="D12" s="29" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E12" s="26" t="s">
         <v>43</v>
@@ -2414,7 +2420,7 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="27" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B13" s="11" t="s">
         <v>44</v>
@@ -2423,7 +2429,7 @@
         <v>4</v>
       </c>
       <c r="D13" s="29" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E13" s="26" t="s">
         <v>45</v>
@@ -2442,7 +2448,7 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="27" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B14" s="11" t="s">
         <v>46</v>
@@ -2451,7 +2457,7 @@
         <v>4</v>
       </c>
       <c r="D14" s="29" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E14" s="26" t="s">
         <v>47</v>
@@ -2470,16 +2476,16 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="27" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C15" s="25" t="s">
         <v>4</v>
       </c>
       <c r="D15" s="29" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E15" s="26" t="s">
         <v>48</v>
@@ -2498,16 +2504,16 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="27" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C16" s="25" t="s">
         <v>4</v>
       </c>
       <c r="D16" s="29" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E16" s="26" t="s">
         <v>49</v>
@@ -2526,7 +2532,7 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="27" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B17" s="11" t="s">
         <v>50</v>
@@ -2535,7 +2541,7 @@
         <v>3</v>
       </c>
       <c r="D17" s="29" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E17" s="26" t="s">
         <v>51</v>
@@ -2554,16 +2560,16 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="27" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C18" s="25" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="29" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E18" s="26" t="s">
         <v>52</v>
@@ -2582,7 +2588,7 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="27" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B19" s="11" t="s">
         <v>53</v>
@@ -2591,7 +2597,7 @@
         <v>3</v>
       </c>
       <c r="D19" s="29" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E19" s="26" t="s">
         <v>54</v>
@@ -2610,16 +2616,16 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="27" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C20" s="25" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="29" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E20" s="26" t="s">
         <v>55</v>
@@ -2638,16 +2644,16 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="24" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C21" s="25" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="29" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E21" s="26" t="s">
         <v>56</v>
@@ -2666,16 +2672,16 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="24" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C22" s="25" t="s">
         <v>5</v>
       </c>
       <c r="D22" s="29" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E22" s="26" t="s">
         <v>57</v>
@@ -2694,23 +2700,23 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="24" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B23" s="11" t="s">
         <v>15</v>
       </c>
       <c r="C23" s="25"/>
       <c r="D23" s="29" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E23" s="26" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F23" s="26" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G23" s="26" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="H23" s="26"/>
       <c r="I23" s="11"/>
@@ -2720,14 +2726,14 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="24" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C24" s="25"/>
       <c r="D24" s="29" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E24" s="26" t="s">
         <v>35</v>
@@ -2746,7 +2752,7 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="24" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B25" s="11" t="s">
         <v>16</v>
@@ -2755,7 +2761,7 @@
         <v>4</v>
       </c>
       <c r="D25" s="29" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E25" s="26" t="s">
         <v>58</v>
@@ -2783,16 +2789,16 @@
         <v>3</v>
       </c>
       <c r="D26" s="29" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E26" s="28" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F26" s="28" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="G26" s="28" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="H26" s="11"/>
       <c r="I26" s="11"/>
@@ -2802,25 +2808,25 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="24" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C27" s="25" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D27" s="29" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E27" s="28" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F27" s="28" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="G27" s="28" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="H27" s="11"/>
       <c r="I27" s="11"/>
@@ -2830,25 +2836,25 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="24" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C28" s="25" t="s">
         <v>4</v>
       </c>
       <c r="D28" s="29" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E28" s="26" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F28" s="26" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="G28" s="26" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="H28" s="11"/>
       <c r="I28" s="11"/>
@@ -2858,7 +2864,7 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="27" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B29" s="11" t="s">
         <v>20</v>
@@ -2867,7 +2873,7 @@
         <v>59</v>
       </c>
       <c r="D29" s="29" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E29" s="26" t="s">
         <v>60</v>
@@ -2886,25 +2892,25 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="27" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B30" s="11" t="s">
         <v>21</v>
       </c>
       <c r="C30" s="25" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D30" s="29" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E30" s="26" t="s">
-        <v>61</v>
+        <v>289</v>
       </c>
       <c r="F30" s="26" t="s">
-        <v>61</v>
+        <v>289</v>
       </c>
       <c r="G30" s="26" t="s">
-        <v>61</v>
+        <v>289</v>
       </c>
       <c r="H30" s="11"/>
       <c r="I30" s="11"/>
@@ -2914,25 +2920,25 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="27" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B31" s="11" t="s">
         <v>22</v>
       </c>
       <c r="C31" s="25" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D31" s="29" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E31" s="26" t="s">
-        <v>62</v>
+        <v>288</v>
       </c>
       <c r="F31" s="26" t="s">
-        <v>62</v>
+        <v>288</v>
       </c>
       <c r="G31" s="26" t="s">
-        <v>62</v>
+        <v>288</v>
       </c>
       <c r="H31" s="11"/>
       <c r="I31" s="11"/>
@@ -2942,25 +2948,25 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="27" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B32" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="C32" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="C32" s="25" t="s">
-        <v>65</v>
-      </c>
       <c r="D32" s="29" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E32" s="26" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F32" s="26" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="G32" s="26" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="H32" s="11"/>
       <c r="I32" s="11"/>
@@ -2970,25 +2976,25 @@
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="27" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B33" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="C33" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="D33" s="29" t="s">
+        <v>219</v>
+      </c>
+      <c r="E33" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="C33" s="25" t="s">
-        <v>65</v>
-      </c>
-      <c r="D33" s="29" t="s">
-        <v>221</v>
-      </c>
-      <c r="E33" s="26" t="s">
-        <v>66</v>
-      </c>
       <c r="F33" s="26" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G33" s="26" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H33" s="11"/>
       <c r="I33" s="11"/>
@@ -2998,25 +3004,25 @@
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="27" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C34" s="25" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D34" s="29" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E34" s="26" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F34" s="26" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G34" s="26" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H34" s="11"/>
       <c r="I34" s="11"/>
@@ -3026,25 +3032,25 @@
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="27" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C35" s="25" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D35" s="29" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E35" s="26" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F35" s="26" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="G35" s="26" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="H35" s="26"/>
       <c r="I35" s="11"/>
@@ -3054,25 +3060,25 @@
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="24" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B36" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="C36" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="D36" s="29" t="s">
+        <v>224</v>
+      </c>
+      <c r="E36" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="C36" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="D36" s="29" t="s">
-        <v>226</v>
-      </c>
-      <c r="E36" s="26" t="s">
-        <v>72</v>
-      </c>
       <c r="F36" s="26" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G36" s="26" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H36" s="11"/>
       <c r="I36" s="11"/>
@@ -3082,25 +3088,25 @@
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="24" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C37" s="25" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D37" s="29" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E37" s="26" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F37" s="26" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G37" s="26" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H37" s="11"/>
       <c r="I37" s="11"/>
@@ -3110,25 +3116,25 @@
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="24" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C38" s="25" t="s">
         <v>4</v>
       </c>
       <c r="D38" s="29" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E38" s="26" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="G38" s="11" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="H38" s="11"/>
       <c r="I38" s="11"/>
@@ -3138,25 +3144,25 @@
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="24" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C39" s="25" t="s">
         <v>4</v>
       </c>
       <c r="D39" s="29" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E39" s="26" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="G39" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="H39" s="11"/>
       <c r="I39" s="11"/>
@@ -3166,25 +3172,25 @@
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="24" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C40" s="25" t="s">
         <v>1</v>
       </c>
       <c r="D40" s="29" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E40" s="26" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F40" s="26" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G40" s="26" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="H40" s="11"/>
       <c r="I40" s="11"/>
@@ -3194,25 +3200,25 @@
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="24" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C41" s="25" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="29" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E41" s="26" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="G41" s="11" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="H41" s="11"/>
       <c r="I41" s="11"/>
@@ -3222,25 +3228,25 @@
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="27" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C42" s="25" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D42" s="29" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E42" s="26" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F42" s="26" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G42" s="26" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H42" s="11"/>
       <c r="I42" s="11"/>
@@ -3250,25 +3256,25 @@
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="27" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C43" s="25" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D43" s="29" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E43" s="26" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F43" s="26" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G43" s="26" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H43" s="11"/>
       <c r="I43" s="11"/>
@@ -3278,25 +3284,25 @@
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="27" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C44" s="25" t="s">
         <v>4</v>
       </c>
       <c r="D44" s="29" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E44" s="26" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F44" s="26" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G44" s="26" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H44" s="11"/>
       <c r="I44" s="11"/>
@@ -3306,25 +3312,25 @@
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="27" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C45" s="25" t="s">
         <v>4</v>
       </c>
       <c r="D45" s="29" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E45" s="26" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="F45" s="26" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="G45" s="26" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="H45" s="11"/>
       <c r="I45" s="11"/>
@@ -3334,25 +3340,25 @@
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="24" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C46" s="25" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D46" s="29" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E46" s="28" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F46" s="28" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="G46" s="28" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="H46" s="11"/>
       <c r="I46" s="11"/>
@@ -3362,25 +3368,25 @@
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="24" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C47" s="25" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D47" s="29" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E47" s="28" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F47" s="28" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="G47" s="28" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="H47" s="11"/>
       <c r="I47" s="11"/>
@@ -4166,36 +4172,36 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E1" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="G1" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>105</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="24" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B2" s="10"/>
       <c r="C2" s="12"/>
@@ -4208,7 +4214,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="27" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B3" s="10"/>
       <c r="C3" s="12"/>
@@ -4221,7 +4227,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="24" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B4" s="10"/>
       <c r="C4" s="12"/>
@@ -4234,307 +4240,307 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="27" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H5" s="11"/>
       <c r="I5" s="11"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="27" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H6" s="11"/>
       <c r="I6" s="11"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="27" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>4</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="H7" s="11"/>
       <c r="I7" s="11"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="27" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="30" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H8" s="11"/>
       <c r="I8" s="11"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="27" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D9" s="30" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H9" s="11"/>
       <c r="I9" s="11"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="27" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C10" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="30" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="27" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D11" s="30" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H11" s="11"/>
       <c r="I11" s="11"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="27" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D12" s="30" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="H12" s="11"/>
       <c r="I12" s="11"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="27" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C13" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="30" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H13" s="11"/>
       <c r="I13" s="11"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="27" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D14" s="30" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H14" s="11"/>
       <c r="I14" s="11"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="27" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D15" s="30" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="H15" s="11"/>
       <c r="I15" s="11"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="27" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C16" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="30" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H16" s="11"/>
       <c r="I16" s="11"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="24" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B17" s="10"/>
       <c r="C17" s="12"/>
@@ -4547,30 +4553,30 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="27" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="30" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H18" s="11"/>
       <c r="I18" s="11"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="24" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B19" s="10"/>
       <c r="C19" s="12"/>
@@ -4583,465 +4589,465 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="27" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="30" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="H20" s="11"/>
       <c r="I20" s="11"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="27" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="30" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="H21" s="11"/>
       <c r="I21" s="11"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="27" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="30" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H22" s="11"/>
       <c r="I22" s="11"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="27" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B23" s="10" t="s">
         <v>13</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D23" s="30" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="H23" s="11"/>
       <c r="I23" s="11"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="27" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C24" s="12" t="s">
         <v>4</v>
       </c>
       <c r="D24" s="30" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G24" s="11" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="H24" s="11"/>
       <c r="I24" s="11"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="27" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C25" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="30" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G25" s="11" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="H25" s="11"/>
       <c r="I25" s="11"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="27" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D26" s="30" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G26" s="11" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H26" s="11"/>
       <c r="I26" s="11"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="24" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="30" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G27" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H27" s="11"/>
       <c r="I27" s="11"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="24" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C28" s="12" t="s">
         <v>1</v>
       </c>
       <c r="D28" s="30" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G28" s="11" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="H28" s="11"/>
       <c r="I28" s="11"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="24" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D29" s="30" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="G29" s="11" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="H29" s="11"/>
       <c r="I29" s="11"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="24" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C30" s="12" t="s">
         <v>1</v>
       </c>
       <c r="D30" s="30" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G30" s="11" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="H30" s="11"/>
       <c r="I30" s="11"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="27" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D31" s="30" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H31" s="11"/>
       <c r="I31" s="11"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="27" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D32" s="30" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G32" s="11" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H32" s="11"/>
       <c r="I32" s="11"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="27" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C33" s="12" t="s">
         <v>1</v>
       </c>
       <c r="D33" s="30" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G33" s="11" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="H33" s="11"/>
       <c r="I33" s="11"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="27" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C34" s="12" t="s">
         <v>33</v>
       </c>
       <c r="D34" s="30" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G34" s="11" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H34" s="11"/>
       <c r="I34" s="11"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="27" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D35" s="30" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G35" s="11" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="H35" s="11"/>
       <c r="I35" s="11"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="27" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D36" s="30" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G36" s="11" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="H36" s="11"/>
       <c r="I36" s="11"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="27" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C37" s="12" t="s">
         <v>1</v>
       </c>
       <c r="D37" s="30" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G37" s="11" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="27" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C38" s="12" t="s">
         <v>33</v>
       </c>
       <c r="D38" s="30" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G38" s="11" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">

--- a/eBus_Functions/Post_Processing/Root_Cause_Analysis_Work/info/eBus_Model_Info.xlsx
+++ b/eBus_Functions/Post_Processing/Root_Cause_Analysis_Work/info/eBus_Model_Info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\TempData\Github\eBus_Tool\eBus_Functions\Post_Processing\Root_Cause_Analysis_Work\info\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B4530FF-D445-45FB-B943-B2E10A2A4F91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF1D4BBC-584A-40CA-865B-5B6F818D26AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Block Diagram" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="290">
   <si>
     <t>Driver</t>
   </si>
@@ -365,9 +365,6 @@
     <t>Auxiliary Load</t>
   </si>
   <si>
-    <t>sMP.phys.hvs.drvEmot.RefTqED</t>
-  </si>
-  <si>
     <t>sMP.phys.hvs.drvEmot.RefTqeMOT</t>
   </si>
   <si>
@@ -473,15 +470,9 @@
     <t>sMP.phys.mec.mec_iDiffAxle</t>
   </si>
   <si>
-    <t>sMP.phys.mec.aero</t>
-  </si>
-  <si>
     <t>sMP.phys.mec.wheel1.fRollCoeff</t>
   </si>
   <si>
-    <t>sMP.phys.mec.mec_rWheelDriven</t>
-  </si>
-  <si>
     <t>sMP.phys.mec.mec_massVehicle_kg</t>
   </si>
   <si>
@@ -740,12 +731,6 @@
     <t>logout.pne_brk_Axle1_BrakingPower+logout.pne_brk_Axle2_BrakingPower+logout.pne_brk_Axle3_BrakingPower+logout.pne_brk_Axle4_BrakingPower</t>
   </si>
   <si>
-    <t>logout.drv_AccPdl_pos</t>
-  </si>
-  <si>
-    <t>logout.drv_BrkPdl_pos</t>
-  </si>
-  <si>
     <t>logout.hvs_zfCetrax_gbxOut_torque*sMP.global.mec_iDiffAxle/(sMP.global.mec_rWheelDriven*0.001)-(logout.mec_brk_Axle1_TiBrk_info+logout.mec_brk_Axle2_TiBrk_info+logout.mec_brk_Axle3_TiBrk_info+logout.mec_brk_Axle4_TiBrk_info)</t>
   </si>
   <si>
@@ -827,27 +812,6 @@
     <t>FD_mec_iDiffAxle</t>
   </si>
   <si>
-    <t>VD_aero</t>
-  </si>
-  <si>
-    <t>VD_mec_rWheelDriven</t>
-  </si>
-  <si>
-    <t>VD_mec_massVehicle_kg</t>
-  </si>
-  <si>
-    <t>VD_wheel.fRollCoeff</t>
-  </si>
-  <si>
-    <t>VD_axleLoss_map_torqueAxleIn_Nm</t>
-  </si>
-  <si>
-    <t>VD_axleLoss_y_torqueAxleIn_Nm</t>
-  </si>
-  <si>
-    <t>VD_axleLoss_x_speedAxleOut_rpm</t>
-  </si>
-  <si>
     <t>BMS_ChargeLimit_Current_cont</t>
   </si>
   <si>
@@ -878,9 +842,6 @@
     <t>Batt_bat_soh</t>
   </si>
   <si>
-    <t>Batt_cell_Capacity</t>
-  </si>
-  <si>
     <t>Batt_SOC_init</t>
   </si>
   <si>
@@ -893,9 +854,6 @@
     <t>logout.HVB_MaxDischrgPwr</t>
   </si>
   <si>
-    <t>logout.mec_veh_transPos*1000</t>
-  </si>
-  <si>
     <t>logout.mec_veh_transVel*3.6</t>
   </si>
   <si>
@@ -903,6 +861,42 @@
   </si>
   <si>
     <t>logout.drv_BrkPdl_pos*100</t>
+  </si>
+  <si>
+    <t>logout.mec_veh_transPos/1000</t>
+  </si>
+  <si>
+    <t>Batt_cell_capacity</t>
+  </si>
+  <si>
+    <t>sMP.phys.mec.aero.aeroCdA_m2</t>
+  </si>
+  <si>
+    <t>sMP.phys.mec.mec_rWheelDriven/1000</t>
+  </si>
+  <si>
+    <t>sMP.phys.hvs.drvEmot.RefTqED*2</t>
+  </si>
+  <si>
+    <t>VDy_aero</t>
+  </si>
+  <si>
+    <t>VDy_wheel.fRollCoeff</t>
+  </si>
+  <si>
+    <t>VDy_mec_rWheelDriven</t>
+  </si>
+  <si>
+    <t>VDy_mec_massVehicle_kg</t>
+  </si>
+  <si>
+    <t>VDy_axleLoss_map_torqueAxleIn_Nm</t>
+  </si>
+  <si>
+    <t>VDy_axleLoss_y_torqueAxleIn_Nm</t>
+  </si>
+  <si>
+    <t>VDy_axleLoss_x_speedAxleOut_rpm</t>
   </si>
 </sst>
 </file>
@@ -1216,9 +1210,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1232,6 +1223,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1636,7 +1630,7 @@
     </row>
     <row r="29" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G29" s="6"/>
-      <c r="H29" s="31" t="s">
+      <c r="H29" s="36" t="s">
         <v>6</v>
       </c>
       <c r="I29" s="7" t="s">
@@ -1645,14 +1639,14 @@
     </row>
     <row r="30" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G30" s="8"/>
-      <c r="H30" s="32"/>
+      <c r="H30" s="31"/>
       <c r="I30" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="31" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G31" s="9"/>
-      <c r="H31" s="33"/>
+      <c r="H31" s="32"/>
       <c r="I31" s="2" t="s">
         <v>32</v>
       </c>
@@ -1661,7 +1655,7 @@
       <c r="G32" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="H32" s="34" t="s">
+      <c r="H32" s="33" t="s">
         <v>0</v>
       </c>
       <c r="I32" s="7" t="s">
@@ -1672,7 +1666,7 @@
       <c r="G33" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="H33" s="35"/>
+      <c r="H33" s="34"/>
       <c r="I33" s="1" t="s">
         <v>12</v>
       </c>
@@ -1681,55 +1675,55 @@
       <c r="G34" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="H34" s="35"/>
+      <c r="H34" s="34"/>
       <c r="I34" s="1"/>
     </row>
     <row r="35" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G35" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="H35" s="35"/>
+      <c r="H35" s="34"/>
       <c r="I35" s="1"/>
     </row>
     <row r="36" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G36" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="H36" s="35"/>
+        <v>179</v>
+      </c>
+      <c r="H36" s="34"/>
       <c r="I36" s="1"/>
     </row>
     <row r="37" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G37" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="H37" s="36"/>
+      <c r="H37" s="35"/>
       <c r="I37" s="2"/>
     </row>
     <row r="38" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G38" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H38" s="31" t="s">
+      <c r="H38" s="36" t="s">
         <v>2</v>
       </c>
       <c r="I38" s="7" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="39" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G39" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="H39" s="33"/>
+      <c r="H39" s="32"/>
       <c r="I39" s="2" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="40" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G40" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="H40" s="34" t="s">
+        <v>171</v>
+      </c>
+      <c r="H40" s="33" t="s">
         <v>106</v>
       </c>
       <c r="I40" s="7" t="s">
@@ -1738,127 +1732,127 @@
     </row>
     <row r="41" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G41" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="H41" s="35"/>
+        <v>172</v>
+      </c>
+      <c r="H41" s="34"/>
       <c r="I41" s="1" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="42" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G42" s="8"/>
-      <c r="H42" s="35"/>
+      <c r="H42" s="34"/>
       <c r="I42" s="1" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="43" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G43" s="8"/>
-      <c r="H43" s="35"/>
+      <c r="H43" s="34"/>
       <c r="I43" s="1" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="44" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G44" s="8"/>
-      <c r="H44" s="35"/>
+      <c r="H44" s="34"/>
       <c r="I44" s="1" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="45" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G45" s="8"/>
-      <c r="H45" s="35"/>
+      <c r="H45" s="34"/>
       <c r="I45" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="46" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G46" s="8"/>
-      <c r="H46" s="35"/>
+      <c r="H46" s="34"/>
       <c r="I46" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="47" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G47" s="8"/>
-      <c r="H47" s="35"/>
+      <c r="H47" s="34"/>
       <c r="I47" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="48" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G48" s="8"/>
-      <c r="H48" s="35"/>
+      <c r="H48" s="34"/>
       <c r="I48" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="49" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G49" s="8"/>
-      <c r="H49" s="35"/>
+      <c r="H49" s="34"/>
       <c r="I49" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="50" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G50" s="8"/>
-      <c r="H50" s="35"/>
+      <c r="H50" s="34"/>
       <c r="I50" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="51" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G51" s="9"/>
-      <c r="H51" s="36"/>
+      <c r="H51" s="35"/>
       <c r="I51" s="2" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="52" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G52" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="H52" s="31" t="s">
+      <c r="H52" s="36" t="s">
         <v>107</v>
       </c>
       <c r="I52" s="7" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
     </row>
     <row r="53" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G53" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="H53" s="32"/>
+      <c r="H53" s="31"/>
       <c r="I53" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="54" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G54" s="8"/>
-      <c r="H54" s="32"/>
+      <c r="H54" s="31"/>
       <c r="I54" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="55" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G55" s="8"/>
-      <c r="H55" s="32"/>
+      <c r="H55" s="31"/>
       <c r="I55" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="56" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G56" s="8"/>
-      <c r="H56" s="32"/>
+      <c r="H56" s="31"/>
       <c r="I56" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="57" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G57" s="17" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H57" s="18" t="s">
         <v>17</v>
@@ -1871,25 +1865,25 @@
       <c r="G58" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="H58" s="34" t="s">
+      <c r="H58" s="33" t="s">
         <v>108</v>
       </c>
       <c r="I58" s="7" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
     </row>
     <row r="59" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G59" s="8"/>
-      <c r="H59" s="35"/>
+      <c r="H59" s="34"/>
       <c r="I59" s="1" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
     </row>
     <row r="60" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G60" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H60" s="31" t="s">
+      <c r="H60" s="36" t="s">
         <v>19</v>
       </c>
       <c r="I60" s="7" t="s">
@@ -1898,44 +1892,44 @@
     </row>
     <row r="61" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G61" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="H61" s="32"/>
+        <v>180</v>
+      </c>
+      <c r="H61" s="31"/>
       <c r="I61" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="62" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G62" s="8"/>
-      <c r="H62" s="32"/>
+      <c r="H62" s="31"/>
       <c r="I62" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="63" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G63" s="8"/>
-      <c r="H63" s="32"/>
+      <c r="H63" s="31"/>
       <c r="I63" s="1" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="64" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G64" s="8"/>
-      <c r="H64" s="32"/>
+      <c r="H64" s="31"/>
       <c r="I64" s="1" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="65" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G65" s="8"/>
-      <c r="H65" s="32"/>
+      <c r="H65" s="31"/>
       <c r="I65" s="1" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="66" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G66" s="9"/>
-      <c r="H66" s="33"/>
+      <c r="H66" s="32"/>
       <c r="I66" s="2" t="s">
         <v>67</v>
       </c>
@@ -1944,7 +1938,7 @@
       <c r="G67" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="H67" s="32" t="s">
+      <c r="H67" s="31" t="s">
         <v>109</v>
       </c>
       <c r="I67" s="1" t="s">
@@ -1953,35 +1947,35 @@
     </row>
     <row r="68" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G68" s="8"/>
-      <c r="H68" s="32"/>
+      <c r="H68" s="31"/>
       <c r="I68" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
     </row>
     <row r="69" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G69" s="8"/>
-      <c r="H69" s="32"/>
+      <c r="H69" s="31"/>
       <c r="I69" s="1" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="70" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G70" s="8"/>
-      <c r="H70" s="32"/>
+      <c r="H70" s="31"/>
       <c r="I70" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="71" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G71" s="8"/>
-      <c r="H71" s="32"/>
+      <c r="H71" s="31"/>
       <c r="I71" s="1" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="72" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G72" s="9"/>
-      <c r="H72" s="33"/>
+      <c r="H72" s="32"/>
       <c r="I72" s="2" t="s">
         <v>77</v>
       </c>
@@ -1990,7 +1984,7 @@
       <c r="G73" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="H73" s="34" t="s">
+      <c r="H73" s="33" t="s">
         <v>110</v>
       </c>
       <c r="I73" s="7" t="s">
@@ -2001,60 +1995,60 @@
       <c r="G74" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="H74" s="35"/>
+      <c r="H74" s="34"/>
       <c r="I74" s="1" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="75" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G75" s="8"/>
-      <c r="H75" s="35"/>
+      <c r="H75" s="34"/>
       <c r="I75" s="1" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="76" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G76" s="9"/>
-      <c r="H76" s="36"/>
+      <c r="H76" s="35"/>
       <c r="I76" s="2" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="77" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G77" s="8"/>
-      <c r="H77" s="32" t="s">
+      <c r="H77" s="31" t="s">
         <v>111</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
     </row>
     <row r="78" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G78" s="8"/>
-      <c r="H78" s="32"/>
+      <c r="H78" s="31"/>
       <c r="I78" s="1" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="79" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G79" s="9"/>
-      <c r="H79" s="33"/>
+      <c r="H79" s="32"/>
       <c r="I79" s="2" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="H29:H31"/>
+    <mergeCell ref="H32:H37"/>
+    <mergeCell ref="H38:H39"/>
+    <mergeCell ref="H40:H51"/>
+    <mergeCell ref="H58:H59"/>
     <mergeCell ref="H67:H72"/>
     <mergeCell ref="H73:H76"/>
     <mergeCell ref="H52:H56"/>
     <mergeCell ref="H60:H66"/>
     <mergeCell ref="H77:H79"/>
-    <mergeCell ref="H29:H31"/>
-    <mergeCell ref="H32:H37"/>
-    <mergeCell ref="H38:H39"/>
-    <mergeCell ref="H40:H51"/>
-    <mergeCell ref="H58:H59"/>
   </mergeCells>
   <conditionalFormatting sqref="I29:I79 G29:G79">
     <cfRule type="duplicateValues" dxfId="4" priority="1"/>
@@ -2149,7 +2143,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="29" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E3" s="26" t="s">
         <v>31</v>
@@ -2177,7 +2171,7 @@
         <v>33</v>
       </c>
       <c r="D4" s="29" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="E4" s="26" t="s">
         <v>34</v>
@@ -2205,16 +2199,16 @@
         <v>1</v>
       </c>
       <c r="D5" s="29" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="E5" s="26" t="s">
-        <v>237</v>
+        <v>276</v>
       </c>
       <c r="F5" s="26" t="s">
-        <v>290</v>
+        <v>276</v>
       </c>
       <c r="G5" s="26" t="s">
-        <v>290</v>
+        <v>276</v>
       </c>
       <c r="H5" s="11"/>
       <c r="I5" s="11"/>
@@ -2233,16 +2227,16 @@
         <v>1</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E6" s="26" t="s">
-        <v>238</v>
+        <v>277</v>
       </c>
       <c r="F6" s="26" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="G6" s="26" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="H6" s="11"/>
       <c r="I6" s="11"/>
@@ -2255,22 +2249,22 @@
         <v>97</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C7" s="25" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="29" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E7" s="26" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F7" s="26" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="G7" s="26" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="H7" s="11"/>
       <c r="I7" s="11"/>
@@ -2283,22 +2277,22 @@
         <v>97</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C8" s="25" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="29" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E8" s="26" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F8" s="26" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="G8" s="26" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="H8" s="11"/>
       <c r="I8" s="11"/>
@@ -2317,7 +2311,7 @@
         <v>3</v>
       </c>
       <c r="D9" s="29" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="E9" s="26" t="s">
         <v>37</v>
@@ -2345,7 +2339,7 @@
         <v>3</v>
       </c>
       <c r="D10" s="29" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="E10" s="26" t="s">
         <v>39</v>
@@ -2373,7 +2367,7 @@
         <v>5</v>
       </c>
       <c r="D11" s="29" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="E11" s="26" t="s">
         <v>41</v>
@@ -2401,7 +2395,7 @@
         <v>5</v>
       </c>
       <c r="D12" s="29" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="E12" s="26" t="s">
         <v>43</v>
@@ -2429,7 +2423,7 @@
         <v>4</v>
       </c>
       <c r="D13" s="29" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="E13" s="26" t="s">
         <v>45</v>
@@ -2457,7 +2451,7 @@
         <v>4</v>
       </c>
       <c r="D14" s="29" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="E14" s="26" t="s">
         <v>47</v>
@@ -2479,13 +2473,13 @@
         <v>95</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C15" s="25" t="s">
         <v>4</v>
       </c>
       <c r="D15" s="29" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E15" s="26" t="s">
         <v>48</v>
@@ -2507,13 +2501,13 @@
         <v>95</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C16" s="25" t="s">
         <v>4</v>
       </c>
       <c r="D16" s="29" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E16" s="26" t="s">
         <v>49</v>
@@ -2541,7 +2535,7 @@
         <v>3</v>
       </c>
       <c r="D17" s="29" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E17" s="26" t="s">
         <v>51</v>
@@ -2563,13 +2557,13 @@
         <v>95</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C18" s="25" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="29" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E18" s="26" t="s">
         <v>52</v>
@@ -2597,7 +2591,7 @@
         <v>3</v>
       </c>
       <c r="D19" s="29" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="E19" s="26" t="s">
         <v>54</v>
@@ -2619,13 +2613,13 @@
         <v>95</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C20" s="25" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="29" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="E20" s="26" t="s">
         <v>55</v>
@@ -2647,13 +2641,13 @@
         <v>94</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C21" s="25" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="29" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="E21" s="26" t="s">
         <v>56</v>
@@ -2675,13 +2669,13 @@
         <v>94</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C22" s="25" t="s">
         <v>5</v>
       </c>
       <c r="D22" s="29" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E22" s="26" t="s">
         <v>57</v>
@@ -2707,16 +2701,16 @@
       </c>
       <c r="C23" s="25"/>
       <c r="D23" s="29" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E23" s="26" t="s">
-        <v>285</v>
+        <v>272</v>
       </c>
       <c r="F23" s="26" t="s">
-        <v>285</v>
+        <v>272</v>
       </c>
       <c r="G23" s="26" t="s">
-        <v>285</v>
+        <v>272</v>
       </c>
       <c r="H23" s="26"/>
       <c r="I23" s="11"/>
@@ -2729,11 +2723,11 @@
         <v>94</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C24" s="25"/>
       <c r="D24" s="29" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E24" s="26" t="s">
         <v>35</v>
@@ -2761,7 +2755,7 @@
         <v>4</v>
       </c>
       <c r="D25" s="29" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="E25" s="26" t="s">
         <v>58</v>
@@ -2786,19 +2780,19 @@
         <v>18</v>
       </c>
       <c r="C26" s="25" t="s">
-        <v>3</v>
+        <v>63</v>
       </c>
       <c r="D26" s="29" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="E26" s="28" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="F26" s="28" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="G26" s="28" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="H26" s="11"/>
       <c r="I26" s="11"/>
@@ -2811,22 +2805,22 @@
         <v>93</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C27" s="25" t="s">
         <v>63</v>
       </c>
       <c r="D27" s="29" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E27" s="28" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="F27" s="28" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="G27" s="28" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="H27" s="11"/>
       <c r="I27" s="11"/>
@@ -2839,22 +2833,22 @@
         <v>93</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C28" s="25" t="s">
         <v>4</v>
       </c>
       <c r="D28" s="29" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E28" s="26" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F28" s="26" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="G28" s="26" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="H28" s="11"/>
       <c r="I28" s="11"/>
@@ -2873,7 +2867,7 @@
         <v>59</v>
       </c>
       <c r="D29" s="29" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E29" s="26" t="s">
         <v>60</v>
@@ -2901,16 +2895,16 @@
         <v>98</v>
       </c>
       <c r="D30" s="29" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E30" s="26" t="s">
-        <v>289</v>
+        <v>275</v>
       </c>
       <c r="F30" s="26" t="s">
-        <v>289</v>
+        <v>275</v>
       </c>
       <c r="G30" s="26" t="s">
-        <v>289</v>
+        <v>275</v>
       </c>
       <c r="H30" s="11"/>
       <c r="I30" s="11"/>
@@ -2926,19 +2920,19 @@
         <v>22</v>
       </c>
       <c r="C31" s="25" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="D31" s="29" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="E31" s="26" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="F31" s="26" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="G31" s="26" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="H31" s="11"/>
       <c r="I31" s="11"/>
@@ -2957,16 +2951,16 @@
         <v>63</v>
       </c>
       <c r="D32" s="29" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="E32" s="26" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="F32" s="26" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="G32" s="26" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="H32" s="11"/>
       <c r="I32" s="11"/>
@@ -2985,7 +2979,7 @@
         <v>63</v>
       </c>
       <c r="D33" s="29" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E33" s="26" t="s">
         <v>64</v>
@@ -3013,7 +3007,7 @@
         <v>63</v>
       </c>
       <c r="D34" s="29" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E34" s="26" t="s">
         <v>66</v>
@@ -3041,16 +3035,16 @@
         <v>63</v>
       </c>
       <c r="D35" s="29" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E35" s="26" t="s">
-        <v>286</v>
+        <v>273</v>
       </c>
       <c r="F35" s="26" t="s">
-        <v>286</v>
+        <v>273</v>
       </c>
       <c r="G35" s="26" t="s">
-        <v>286</v>
+        <v>273</v>
       </c>
       <c r="H35" s="26"/>
       <c r="I35" s="11"/>
@@ -3069,7 +3063,7 @@
         <v>69</v>
       </c>
       <c r="D36" s="29" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="E36" s="26" t="s">
         <v>70</v>
@@ -3091,13 +3085,13 @@
         <v>90</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C37" s="25" t="s">
         <v>71</v>
       </c>
       <c r="D37" s="29" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E37" s="26" t="s">
         <v>72</v>
@@ -3125,16 +3119,16 @@
         <v>4</v>
       </c>
       <c r="D38" s="29" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E38" s="26" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G38" s="11" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="H38" s="11"/>
       <c r="I38" s="11"/>
@@ -3153,16 +3147,16 @@
         <v>4</v>
       </c>
       <c r="D39" s="29" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E39" s="26" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="G39" s="11" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="H39" s="11"/>
       <c r="I39" s="11"/>
@@ -3181,7 +3175,7 @@
         <v>1</v>
       </c>
       <c r="D40" s="29" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="E40" s="26" t="s">
         <v>76</v>
@@ -3209,16 +3203,16 @@
         <v>33</v>
       </c>
       <c r="D41" s="29" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E41" s="26" t="s">
         <v>78</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="G41" s="11" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H41" s="11"/>
       <c r="I41" s="11"/>
@@ -3237,7 +3231,7 @@
         <v>69</v>
       </c>
       <c r="D42" s="29" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E42" s="26" t="s">
         <v>80</v>
@@ -3265,7 +3259,7 @@
         <v>69</v>
       </c>
       <c r="D43" s="29" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E43" s="26" t="s">
         <v>82</v>
@@ -3293,7 +3287,7 @@
         <v>4</v>
       </c>
       <c r="D44" s="29" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E44" s="26" t="s">
         <v>84</v>
@@ -3321,16 +3315,16 @@
         <v>4</v>
       </c>
       <c r="D45" s="29" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="E45" s="26" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="F45" s="26" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="G45" s="26" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="H45" s="11"/>
       <c r="I45" s="11"/>
@@ -3343,22 +3337,22 @@
         <v>111</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C46" s="25" t="s">
         <v>69</v>
       </c>
       <c r="D46" s="29" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="E46" s="28" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="F46" s="28" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="G46" s="28" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="H46" s="11"/>
       <c r="I46" s="11"/>
@@ -3371,22 +3365,22 @@
         <v>111</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C47" s="25" t="s">
         <v>71</v>
       </c>
       <c r="D47" s="29" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="E47" s="28" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="F47" s="28" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="G47" s="28" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="H47" s="11"/>
       <c r="I47" s="11"/>
@@ -4243,22 +4237,22 @@
         <v>95</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>112</v>
+        <v>282</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>112</v>
+        <v>282</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>112</v>
+        <v>282</v>
       </c>
       <c r="H5" s="11"/>
       <c r="I5" s="11"/>
@@ -4268,22 +4262,22 @@
         <v>95</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H6" s="11"/>
       <c r="I6" s="11"/>
@@ -4293,22 +4287,22 @@
         <v>95</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>4</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="H7" s="11"/>
       <c r="I7" s="11"/>
@@ -4318,22 +4312,22 @@
         <v>95</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="30" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="H8" s="11"/>
       <c r="I8" s="11"/>
@@ -4343,22 +4337,22 @@
         <v>95</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D9" s="30" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="H9" s="11"/>
       <c r="I9" s="11"/>
@@ -4368,22 +4362,22 @@
         <v>95</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C10" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="30" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -4393,22 +4387,22 @@
         <v>95</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C11" s="12" t="s">
         <v>71</v>
       </c>
       <c r="D11" s="30" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="H11" s="11"/>
       <c r="I11" s="11"/>
@@ -4418,22 +4412,22 @@
         <v>95</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D12" s="30" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="H12" s="11"/>
       <c r="I12" s="11"/>
@@ -4443,22 +4437,22 @@
         <v>95</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C13" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="30" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="H13" s="11"/>
       <c r="I13" s="11"/>
@@ -4468,22 +4462,22 @@
         <v>95</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C14" s="12" t="s">
         <v>71</v>
       </c>
       <c r="D14" s="30" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="H14" s="11"/>
       <c r="I14" s="11"/>
@@ -4493,22 +4487,22 @@
         <v>95</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D15" s="30" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="H15" s="11"/>
       <c r="I15" s="11"/>
@@ -4518,22 +4512,22 @@
         <v>95</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C16" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="30" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="H16" s="11"/>
       <c r="I16" s="11"/>
@@ -4556,20 +4550,20 @@
         <v>99</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="30" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H18" s="11"/>
       <c r="I18" s="11"/>
@@ -4592,20 +4586,20 @@
         <v>92</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="30" t="s">
-        <v>266</v>
+        <v>283</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>148</v>
+        <v>280</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>148</v>
+        <v>280</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>148</v>
+        <v>280</v>
       </c>
       <c r="H20" s="11"/>
       <c r="I20" s="11"/>
@@ -4615,20 +4609,20 @@
         <v>92</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="30" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H21" s="11"/>
       <c r="I21" s="11"/>
@@ -4638,20 +4632,20 @@
         <v>92</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="30" t="s">
-        <v>267</v>
+        <v>285</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>150</v>
+        <v>281</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>150</v>
+        <v>281</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>150</v>
+        <v>281</v>
       </c>
       <c r="H22" s="11"/>
       <c r="I22" s="11"/>
@@ -4664,19 +4658,19 @@
         <v>13</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D23" s="30" t="s">
-        <v>268</v>
+        <v>286</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="H23" s="11"/>
       <c r="I23" s="11"/>
@@ -4686,22 +4680,22 @@
         <v>92</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C24" s="12" t="s">
         <v>4</v>
       </c>
       <c r="D24" s="30" t="s">
-        <v>270</v>
+        <v>287</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="G24" s="11" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="H24" s="11"/>
       <c r="I24" s="11"/>
@@ -4711,22 +4705,22 @@
         <v>92</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C25" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="30" t="s">
-        <v>271</v>
+        <v>288</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G25" s="11" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="H25" s="11"/>
       <c r="I25" s="11"/>
@@ -4736,22 +4730,22 @@
         <v>92</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D26" s="30" t="s">
-        <v>272</v>
+        <v>289</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G26" s="11" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="H26" s="11"/>
       <c r="I26" s="11"/>
@@ -4761,20 +4755,20 @@
         <v>90</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="30" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G27" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H27" s="11"/>
       <c r="I27" s="11"/>
@@ -4784,22 +4778,22 @@
         <v>90</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C28" s="12" t="s">
         <v>1</v>
       </c>
       <c r="D28" s="30" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G28" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H28" s="11"/>
       <c r="I28" s="11"/>
@@ -4809,22 +4803,22 @@
         <v>90</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D29" s="30" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="G29" s="11" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="H29" s="11"/>
       <c r="I29" s="11"/>
@@ -4834,22 +4828,22 @@
         <v>90</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C30" s="12" t="s">
         <v>1</v>
       </c>
       <c r="D30" s="30" t="s">
-        <v>284</v>
+        <v>271</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G30" s="11" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H30" s="11"/>
       <c r="I30" s="11"/>
@@ -4859,22 +4853,22 @@
         <v>91</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C31" s="12" t="s">
         <v>69</v>
       </c>
       <c r="D31" s="30" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H31" s="11"/>
       <c r="I31" s="11"/>
@@ -4884,22 +4878,22 @@
         <v>91</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C32" s="12" t="s">
         <v>69</v>
       </c>
       <c r="D32" s="30" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G32" s="11" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H32" s="11"/>
       <c r="I32" s="11"/>
@@ -4909,22 +4903,22 @@
         <v>91</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C33" s="12" t="s">
         <v>1</v>
       </c>
       <c r="D33" s="30" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G33" s="11" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H33" s="11"/>
       <c r="I33" s="11"/>
@@ -4934,22 +4928,22 @@
         <v>91</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C34" s="12" t="s">
         <v>33</v>
       </c>
       <c r="D34" s="30" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G34" s="11" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H34" s="11"/>
       <c r="I34" s="11"/>
@@ -4959,22 +4953,22 @@
         <v>91</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C35" s="12" t="s">
         <v>69</v>
       </c>
       <c r="D35" s="30" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G35" s="11" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H35" s="11"/>
       <c r="I35" s="11"/>
@@ -4984,22 +4978,22 @@
         <v>91</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C36" s="12" t="s">
         <v>69</v>
       </c>
       <c r="D36" s="30" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G36" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H36" s="11"/>
       <c r="I36" s="11"/>
@@ -5009,22 +5003,22 @@
         <v>91</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C37" s="12" t="s">
         <v>1</v>
       </c>
       <c r="D37" s="30" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G37" s="11" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
@@ -5032,22 +5026,22 @@
         <v>91</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C38" s="12" t="s">
         <v>33</v>
       </c>
       <c r="D38" s="30" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G38" s="11" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">

--- a/eBus_Functions/Post_Processing/Root_Cause_Analysis_Work/info/eBus_Model_Info.xlsx
+++ b/eBus_Functions/Post_Processing/Root_Cause_Analysis_Work/info/eBus_Model_Info.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\TempData\Github\eBus_Tool\eBus_Functions\Post_Processing\Root_Cause_Analysis_Work\info\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF1D4BBC-584A-40CA-865B-5B6F818D26AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28078C16-08E2-4DCC-BFC2-A6EFE62C8FD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Block Diagram" sheetId="1" r:id="rId1"/>
+    <sheet name="Block_Diagram" sheetId="1" r:id="rId1"/>
     <sheet name="Signal_Evaluation" sheetId="2" r:id="rId2"/>
     <sheet name="Specifications" sheetId="3" r:id="rId3"/>
   </sheets>
@@ -1210,6 +1210,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1223,9 +1226,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1630,7 +1630,7 @@
     </row>
     <row r="29" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G29" s="6"/>
-      <c r="H29" s="36" t="s">
+      <c r="H29" s="31" t="s">
         <v>6</v>
       </c>
       <c r="I29" s="7" t="s">
@@ -1639,14 +1639,14 @@
     </row>
     <row r="30" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G30" s="8"/>
-      <c r="H30" s="31"/>
+      <c r="H30" s="32"/>
       <c r="I30" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="31" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G31" s="9"/>
-      <c r="H31" s="32"/>
+      <c r="H31" s="33"/>
       <c r="I31" s="2" t="s">
         <v>32</v>
       </c>
@@ -1655,7 +1655,7 @@
       <c r="G32" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="H32" s="33" t="s">
+      <c r="H32" s="34" t="s">
         <v>0</v>
       </c>
       <c r="I32" s="7" t="s">
@@ -1666,7 +1666,7 @@
       <c r="G33" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="H33" s="34"/>
+      <c r="H33" s="35"/>
       <c r="I33" s="1" t="s">
         <v>12</v>
       </c>
@@ -1675,35 +1675,35 @@
       <c r="G34" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="H34" s="34"/>
+      <c r="H34" s="35"/>
       <c r="I34" s="1"/>
     </row>
     <row r="35" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G35" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="H35" s="34"/>
+      <c r="H35" s="35"/>
       <c r="I35" s="1"/>
     </row>
     <row r="36" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G36" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="H36" s="34"/>
+      <c r="H36" s="35"/>
       <c r="I36" s="1"/>
     </row>
     <row r="37" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G37" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="H37" s="35"/>
+      <c r="H37" s="36"/>
       <c r="I37" s="2"/>
     </row>
     <row r="38" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G38" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H38" s="36" t="s">
+      <c r="H38" s="31" t="s">
         <v>2</v>
       </c>
       <c r="I38" s="7" t="s">
@@ -1714,7 +1714,7 @@
       <c r="G39" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="H39" s="32"/>
+      <c r="H39" s="33"/>
       <c r="I39" s="2" t="s">
         <v>172</v>
       </c>
@@ -1723,7 +1723,7 @@
       <c r="G40" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="H40" s="33" t="s">
+      <c r="H40" s="34" t="s">
         <v>106</v>
       </c>
       <c r="I40" s="7" t="s">
@@ -1734,77 +1734,77 @@
       <c r="G41" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="H41" s="34"/>
+      <c r="H41" s="35"/>
       <c r="I41" s="1" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="42" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G42" s="8"/>
-      <c r="H42" s="34"/>
+      <c r="H42" s="35"/>
       <c r="I42" s="1" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="43" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G43" s="8"/>
-      <c r="H43" s="34"/>
+      <c r="H43" s="35"/>
       <c r="I43" s="1" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="44" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G44" s="8"/>
-      <c r="H44" s="34"/>
+      <c r="H44" s="35"/>
       <c r="I44" s="1" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="45" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G45" s="8"/>
-      <c r="H45" s="34"/>
+      <c r="H45" s="35"/>
       <c r="I45" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="46" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G46" s="8"/>
-      <c r="H46" s="34"/>
+      <c r="H46" s="35"/>
       <c r="I46" s="1" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="47" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G47" s="8"/>
-      <c r="H47" s="34"/>
+      <c r="H47" s="35"/>
       <c r="I47" s="1" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="48" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G48" s="8"/>
-      <c r="H48" s="34"/>
+      <c r="H48" s="35"/>
       <c r="I48" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="49" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G49" s="8"/>
-      <c r="H49" s="34"/>
+      <c r="H49" s="35"/>
       <c r="I49" s="1" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="50" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G50" s="8"/>
-      <c r="H50" s="34"/>
+      <c r="H50" s="35"/>
       <c r="I50" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="51" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G51" s="9"/>
-      <c r="H51" s="35"/>
+      <c r="H51" s="36"/>
       <c r="I51" s="2" t="s">
         <v>176</v>
       </c>
@@ -1813,7 +1813,7 @@
       <c r="G52" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="H52" s="36" t="s">
+      <c r="H52" s="31" t="s">
         <v>107</v>
       </c>
       <c r="I52" s="7" t="s">
@@ -1824,28 +1824,28 @@
       <c r="G53" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="H53" s="31"/>
+      <c r="H53" s="32"/>
       <c r="I53" s="1" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="54" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G54" s="8"/>
-      <c r="H54" s="31"/>
+      <c r="H54" s="32"/>
       <c r="I54" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="55" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G55" s="8"/>
-      <c r="H55" s="31"/>
+      <c r="H55" s="32"/>
       <c r="I55" s="1" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="56" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G56" s="8"/>
-      <c r="H56" s="31"/>
+      <c r="H56" s="32"/>
       <c r="I56" s="1" t="s">
         <v>16</v>
       </c>
@@ -1865,7 +1865,7 @@
       <c r="G58" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="H58" s="33" t="s">
+      <c r="H58" s="34" t="s">
         <v>108</v>
       </c>
       <c r="I58" s="7" t="s">
@@ -1874,7 +1874,7 @@
     </row>
     <row r="59" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G59" s="8"/>
-      <c r="H59" s="34"/>
+      <c r="H59" s="35"/>
       <c r="I59" s="1" t="s">
         <v>181</v>
       </c>
@@ -1883,7 +1883,7 @@
       <c r="G60" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H60" s="36" t="s">
+      <c r="H60" s="31" t="s">
         <v>19</v>
       </c>
       <c r="I60" s="7" t="s">
@@ -1894,42 +1894,42 @@
       <c r="G61" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="H61" s="31"/>
+      <c r="H61" s="32"/>
       <c r="I61" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="62" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G62" s="8"/>
-      <c r="H62" s="31"/>
+      <c r="H62" s="32"/>
       <c r="I62" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="63" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G63" s="8"/>
-      <c r="H63" s="31"/>
+      <c r="H63" s="32"/>
       <c r="I63" s="1" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="64" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G64" s="8"/>
-      <c r="H64" s="31"/>
+      <c r="H64" s="32"/>
       <c r="I64" s="1" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="65" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G65" s="8"/>
-      <c r="H65" s="31"/>
+      <c r="H65" s="32"/>
       <c r="I65" s="1" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="66" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G66" s="9"/>
-      <c r="H66" s="32"/>
+      <c r="H66" s="33"/>
       <c r="I66" s="2" t="s">
         <v>67</v>
       </c>
@@ -1938,7 +1938,7 @@
       <c r="G67" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="H67" s="31" t="s">
+      <c r="H67" s="32" t="s">
         <v>109</v>
       </c>
       <c r="I67" s="1" t="s">
@@ -1947,35 +1947,35 @@
     </row>
     <row r="68" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G68" s="8"/>
-      <c r="H68" s="31"/>
+      <c r="H68" s="32"/>
       <c r="I68" s="1" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="69" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G69" s="8"/>
-      <c r="H69" s="31"/>
+      <c r="H69" s="32"/>
       <c r="I69" s="1" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="70" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G70" s="8"/>
-      <c r="H70" s="31"/>
+      <c r="H70" s="32"/>
       <c r="I70" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="71" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G71" s="8"/>
-      <c r="H71" s="31"/>
+      <c r="H71" s="32"/>
       <c r="I71" s="1" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="72" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G72" s="9"/>
-      <c r="H72" s="32"/>
+      <c r="H72" s="33"/>
       <c r="I72" s="2" t="s">
         <v>77</v>
       </c>
@@ -1984,7 +1984,7 @@
       <c r="G73" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="H73" s="33" t="s">
+      <c r="H73" s="34" t="s">
         <v>110</v>
       </c>
       <c r="I73" s="7" t="s">
@@ -1995,28 +1995,28 @@
       <c r="G74" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="H74" s="34"/>
+      <c r="H74" s="35"/>
       <c r="I74" s="1" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="75" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G75" s="8"/>
-      <c r="H75" s="34"/>
+      <c r="H75" s="35"/>
       <c r="I75" s="1" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="76" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G76" s="9"/>
-      <c r="H76" s="35"/>
+      <c r="H76" s="36"/>
       <c r="I76" s="2" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="77" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G77" s="8"/>
-      <c r="H77" s="31" t="s">
+      <c r="H77" s="32" t="s">
         <v>111</v>
       </c>
       <c r="I77" s="1" t="s">
@@ -2025,30 +2025,30 @@
     </row>
     <row r="78" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G78" s="8"/>
-      <c r="H78" s="31"/>
+      <c r="H78" s="32"/>
       <c r="I78" s="1" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="79" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G79" s="9"/>
-      <c r="H79" s="32"/>
+      <c r="H79" s="33"/>
       <c r="I79" s="2" t="s">
         <v>185</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="H67:H72"/>
+    <mergeCell ref="H73:H76"/>
+    <mergeCell ref="H52:H56"/>
+    <mergeCell ref="H60:H66"/>
+    <mergeCell ref="H77:H79"/>
     <mergeCell ref="H29:H31"/>
     <mergeCell ref="H32:H37"/>
     <mergeCell ref="H38:H39"/>
     <mergeCell ref="H40:H51"/>
     <mergeCell ref="H58:H59"/>
-    <mergeCell ref="H67:H72"/>
-    <mergeCell ref="H73:H76"/>
-    <mergeCell ref="H52:H56"/>
-    <mergeCell ref="H60:H66"/>
-    <mergeCell ref="H77:H79"/>
   </mergeCells>
   <conditionalFormatting sqref="I29:I79 G29:G79">
     <cfRule type="duplicateValues" dxfId="4" priority="1"/>

--- a/eBus_Functions/Post_Processing/Root_Cause_Analysis_Work/info/eBus_Model_Info.xlsx
+++ b/eBus_Functions/Post_Processing/Root_Cause_Analysis_Work/info/eBus_Model_Info.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\TempData\Github\eBus_Tool\eBus_Functions\Post_Processing\Root_Cause_Analysis_Work\info\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28078C16-08E2-4DCC-BFC2-A6EFE62C8FD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDB3083A-0D9A-4053-A0E4-13B87157D318}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Block_Diagram" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="294">
   <si>
     <t>Driver</t>
   </si>
@@ -897,6 +897,18 @@
   </si>
   <si>
     <t>VDy_axleLoss_x_speedAxleOut_rpm</t>
+  </si>
+  <si>
+    <t>Time</t>
+  </si>
+  <si>
+    <t>sec</t>
+  </si>
+  <si>
+    <t>time_sim</t>
+  </si>
+  <si>
+    <t>logout.sec</t>
   </si>
 </sst>
 </file>
@@ -2061,7 +2073,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFA16316-83DB-41C7-8B25-B191695DD108}">
-  <dimension ref="A1:L100"/>
+  <dimension ref="A1:L101"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.109375" bestFit="1" customWidth="1"/>
@@ -2105,54 +2117,51 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="24" t="s">
-        <v>89</v>
+      <c r="A2" s="27" t="s">
+        <v>96</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>29</v>
+        <v>290</v>
       </c>
       <c r="C2" s="25" t="s">
-        <v>98</v>
+        <v>291</v>
       </c>
       <c r="D2" s="29" t="s">
-        <v>88</v>
+        <v>292</v>
       </c>
       <c r="E2" s="26" t="s">
-        <v>30</v>
+        <v>293</v>
       </c>
       <c r="F2" s="26" t="s">
-        <v>30</v>
+        <v>293</v>
       </c>
       <c r="G2" s="26" t="s">
-        <v>30</v>
+        <v>293</v>
       </c>
       <c r="H2" s="11"/>
       <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="11"/>
-      <c r="L2" s="11"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
         <v>89</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="C3" s="25" t="s">
-        <v>1</v>
+        <v>98</v>
       </c>
       <c r="D3" s="29" t="s">
-        <v>188</v>
+        <v>88</v>
       </c>
       <c r="E3" s="26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F3" s="26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G3" s="26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H3" s="11"/>
       <c r="I3" s="11"/>
@@ -2165,22 +2174,22 @@
         <v>89</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="C4" s="25" t="s">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="D4" s="29" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E4" s="26" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F4" s="26" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G4" s="26" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H4" s="11"/>
       <c r="I4" s="11"/>
@@ -2189,26 +2198,26 @@
       <c r="L4" s="11"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="27" t="s">
-        <v>96</v>
+      <c r="A5" s="24" t="s">
+        <v>89</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="D5" s="29" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E5" s="26" t="s">
-        <v>276</v>
+        <v>34</v>
       </c>
       <c r="F5" s="26" t="s">
-        <v>276</v>
+        <v>34</v>
       </c>
       <c r="G5" s="26" t="s">
-        <v>276</v>
+        <v>34</v>
       </c>
       <c r="H5" s="11"/>
       <c r="I5" s="11"/>
@@ -2221,22 +2230,22 @@
         <v>96</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C6" s="25" t="s">
         <v>1</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E6" s="26" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F6" s="26" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="G6" s="26" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H6" s="11"/>
       <c r="I6" s="11"/>
@@ -2245,26 +2254,26 @@
       <c r="L6" s="11"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="24" t="s">
-        <v>97</v>
+      <c r="A7" s="27" t="s">
+        <v>96</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>171</v>
+        <v>12</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D7" s="29" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E7" s="26" t="s">
-        <v>186</v>
+        <v>277</v>
       </c>
       <c r="F7" s="26" t="s">
-        <v>186</v>
+        <v>277</v>
       </c>
       <c r="G7" s="26" t="s">
-        <v>186</v>
+        <v>277</v>
       </c>
       <c r="H7" s="11"/>
       <c r="I7" s="11"/>
@@ -2277,13 +2286,13 @@
         <v>97</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C8" s="25" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="29" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E8" s="26" t="s">
         <v>186</v>
@@ -2301,26 +2310,26 @@
       <c r="L8" s="11"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="27" t="s">
-        <v>95</v>
+      <c r="A9" s="24" t="s">
+        <v>97</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>36</v>
+        <v>172</v>
       </c>
       <c r="C9" s="25" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="29" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E9" s="26" t="s">
-        <v>37</v>
+        <v>186</v>
       </c>
       <c r="F9" s="26" t="s">
-        <v>37</v>
+        <v>186</v>
       </c>
       <c r="G9" s="26" t="s">
-        <v>37</v>
+        <v>186</v>
       </c>
       <c r="H9" s="11"/>
       <c r="I9" s="11"/>
@@ -2333,22 +2342,22 @@
         <v>95</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C10" s="25" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="29" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E10" s="26" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F10" s="26" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G10" s="26" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -2361,22 +2370,22 @@
         <v>95</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D11" s="29" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E11" s="26" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F11" s="26" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G11" s="26" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H11" s="11"/>
       <c r="I11" s="11"/>
@@ -2389,22 +2398,22 @@
         <v>95</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C12" s="25" t="s">
         <v>5</v>
       </c>
       <c r="D12" s="29" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E12" s="26" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F12" s="26" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G12" s="26" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H12" s="11"/>
       <c r="I12" s="11"/>
@@ -2417,22 +2426,22 @@
         <v>95</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D13" s="29" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E13" s="26" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F13" s="26" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G13" s="26" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H13" s="11"/>
       <c r="I13" s="11"/>
@@ -2445,22 +2454,22 @@
         <v>95</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C14" s="25" t="s">
         <v>4</v>
       </c>
       <c r="D14" s="29" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E14" s="26" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F14" s="26" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G14" s="26" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H14" s="11"/>
       <c r="I14" s="11"/>
@@ -2473,22 +2482,22 @@
         <v>95</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>173</v>
+        <v>46</v>
       </c>
       <c r="C15" s="25" t="s">
         <v>4</v>
       </c>
       <c r="D15" s="29" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E15" s="26" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F15" s="26" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G15" s="26" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H15" s="11"/>
       <c r="I15" s="11"/>
@@ -2501,22 +2510,22 @@
         <v>95</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C16" s="25" t="s">
         <v>4</v>
       </c>
       <c r="D16" s="29" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E16" s="26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F16" s="26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G16" s="26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H16" s="11"/>
       <c r="I16" s="11"/>
@@ -2529,22 +2538,22 @@
         <v>95</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>50</v>
+        <v>174</v>
       </c>
       <c r="C17" s="25" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D17" s="29" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E17" s="26" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F17" s="26" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G17" s="26" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
@@ -2557,22 +2566,22 @@
         <v>95</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>175</v>
+        <v>50</v>
       </c>
       <c r="C18" s="25" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="29" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E18" s="26" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F18" s="26" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G18" s="26" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H18" s="11"/>
       <c r="I18" s="11"/>
@@ -2585,22 +2594,22 @@
         <v>95</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>53</v>
+        <v>175</v>
       </c>
       <c r="C19" s="25" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="29" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E19" s="26" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F19" s="26" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G19" s="26" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H19" s="11"/>
       <c r="I19" s="11"/>
@@ -2613,22 +2622,22 @@
         <v>95</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>176</v>
+        <v>53</v>
       </c>
       <c r="C20" s="25" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="29" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E20" s="26" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F20" s="26" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G20" s="26" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H20" s="11"/>
       <c r="I20" s="11"/>
@@ -2637,26 +2646,26 @@
       <c r="L20" s="11"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A21" s="24" t="s">
-        <v>94</v>
+      <c r="A21" s="27" t="s">
+        <v>95</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C21" s="25" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="29" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E21" s="26" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F21" s="26" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G21" s="26" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H21" s="11"/>
       <c r="I21" s="11"/>
@@ -2669,22 +2678,22 @@
         <v>94</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C22" s="25" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D22" s="29" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E22" s="26" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F22" s="26" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G22" s="26" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H22" s="11"/>
       <c r="I22" s="11"/>
@@ -2697,22 +2706,24 @@
         <v>94</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C23" s="25"/>
+        <v>178</v>
+      </c>
+      <c r="C23" s="25" t="s">
+        <v>5</v>
+      </c>
       <c r="D23" s="29" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E23" s="26" t="s">
-        <v>272</v>
+        <v>57</v>
       </c>
       <c r="F23" s="26" t="s">
-        <v>272</v>
+        <v>57</v>
       </c>
       <c r="G23" s="26" t="s">
-        <v>272</v>
-      </c>
-      <c r="H23" s="26"/>
+        <v>57</v>
+      </c>
+      <c r="H23" s="11"/>
       <c r="I23" s="11"/>
       <c r="J23" s="11"/>
       <c r="K23" s="11"/>
@@ -2723,22 +2734,22 @@
         <v>94</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>179</v>
+        <v>15</v>
       </c>
       <c r="C24" s="25"/>
       <c r="D24" s="29" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E24" s="26" t="s">
-        <v>35</v>
+        <v>272</v>
       </c>
       <c r="F24" s="26" t="s">
-        <v>35</v>
+        <v>272</v>
       </c>
       <c r="G24" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="H24" s="11"/>
+        <v>272</v>
+      </c>
+      <c r="H24" s="26"/>
       <c r="I24" s="11"/>
       <c r="J24" s="11"/>
       <c r="K24" s="11"/>
@@ -2749,22 +2760,20 @@
         <v>94</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C25" s="25" t="s">
-        <v>4</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="C25" s="25"/>
       <c r="D25" s="29" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E25" s="26" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="F25" s="26" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="G25" s="26" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="H25" s="11"/>
       <c r="I25" s="11"/>
@@ -2773,26 +2782,26 @@
       <c r="L25" s="11"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A26" s="27" t="s">
-        <v>17</v>
+      <c r="A26" s="24" t="s">
+        <v>94</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C26" s="25" t="s">
-        <v>63</v>
+        <v>4</v>
       </c>
       <c r="D26" s="29" t="s">
-        <v>211</v>
-      </c>
-      <c r="E26" s="28" t="s">
-        <v>234</v>
-      </c>
-      <c r="F26" s="28" t="s">
-        <v>234</v>
-      </c>
-      <c r="G26" s="28" t="s">
-        <v>234</v>
+        <v>210</v>
+      </c>
+      <c r="E26" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="F26" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="G26" s="26" t="s">
+        <v>58</v>
       </c>
       <c r="H26" s="11"/>
       <c r="I26" s="11"/>
@@ -2801,26 +2810,26 @@
       <c r="L26" s="11"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A27" s="24" t="s">
-        <v>93</v>
+      <c r="A27" s="27" t="s">
+        <v>17</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>180</v>
+        <v>18</v>
       </c>
       <c r="C27" s="25" t="s">
         <v>63</v>
       </c>
       <c r="D27" s="29" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="E27" s="28" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F27" s="28" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G27" s="28" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H27" s="11"/>
       <c r="I27" s="11"/>
@@ -2833,22 +2842,22 @@
         <v>93</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C28" s="25" t="s">
-        <v>4</v>
+        <v>63</v>
       </c>
       <c r="D28" s="29" t="s">
-        <v>220</v>
-      </c>
-      <c r="E28" s="26" t="s">
-        <v>233</v>
-      </c>
-      <c r="F28" s="26" t="s">
-        <v>233</v>
-      </c>
-      <c r="G28" s="26" t="s">
-        <v>233</v>
+        <v>219</v>
+      </c>
+      <c r="E28" s="28" t="s">
+        <v>235</v>
+      </c>
+      <c r="F28" s="28" t="s">
+        <v>235</v>
+      </c>
+      <c r="G28" s="28" t="s">
+        <v>235</v>
       </c>
       <c r="H28" s="11"/>
       <c r="I28" s="11"/>
@@ -2857,26 +2866,26 @@
       <c r="L28" s="11"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A29" s="27" t="s">
-        <v>92</v>
+      <c r="A29" s="24" t="s">
+        <v>93</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>20</v>
+        <v>181</v>
       </c>
       <c r="C29" s="25" t="s">
-        <v>59</v>
+        <v>4</v>
       </c>
       <c r="D29" s="29" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="E29" s="26" t="s">
-        <v>60</v>
+        <v>233</v>
       </c>
       <c r="F29" s="26" t="s">
-        <v>60</v>
+        <v>233</v>
       </c>
       <c r="G29" s="26" t="s">
-        <v>60</v>
+        <v>233</v>
       </c>
       <c r="H29" s="11"/>
       <c r="I29" s="11"/>
@@ -2889,22 +2898,22 @@
         <v>92</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C30" s="25" t="s">
-        <v>98</v>
+        <v>59</v>
       </c>
       <c r="D30" s="29" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E30" s="26" t="s">
-        <v>275</v>
+        <v>60</v>
       </c>
       <c r="F30" s="26" t="s">
-        <v>275</v>
+        <v>60</v>
       </c>
       <c r="G30" s="26" t="s">
-        <v>275</v>
+        <v>60</v>
       </c>
       <c r="H30" s="11"/>
       <c r="I30" s="11"/>
@@ -2917,22 +2926,22 @@
         <v>92</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C31" s="25" t="s">
-        <v>187</v>
+        <v>98</v>
       </c>
       <c r="D31" s="29" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E31" s="26" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="F31" s="26" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="G31" s="26" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="H31" s="11"/>
       <c r="I31" s="11"/>
@@ -2945,22 +2954,22 @@
         <v>92</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="C32" s="25" t="s">
-        <v>63</v>
+        <v>187</v>
       </c>
       <c r="D32" s="29" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E32" s="26" t="s">
-        <v>236</v>
+        <v>278</v>
       </c>
       <c r="F32" s="26" t="s">
-        <v>236</v>
+        <v>278</v>
       </c>
       <c r="G32" s="26" t="s">
-        <v>236</v>
+        <v>278</v>
       </c>
       <c r="H32" s="11"/>
       <c r="I32" s="11"/>
@@ -2973,22 +2982,22 @@
         <v>92</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C33" s="25" t="s">
         <v>63</v>
       </c>
       <c r="D33" s="29" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E33" s="26" t="s">
-        <v>64</v>
+        <v>236</v>
       </c>
       <c r="F33" s="26" t="s">
-        <v>64</v>
+        <v>236</v>
       </c>
       <c r="G33" s="26" t="s">
-        <v>64</v>
+        <v>236</v>
       </c>
       <c r="H33" s="11"/>
       <c r="I33" s="11"/>
@@ -3001,22 +3010,22 @@
         <v>92</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C34" s="25" t="s">
         <v>63</v>
       </c>
       <c r="D34" s="29" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E34" s="26" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F34" s="26" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G34" s="26" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H34" s="11"/>
       <c r="I34" s="11"/>
@@ -3029,52 +3038,52 @@
         <v>92</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C35" s="25" t="s">
         <v>63</v>
       </c>
       <c r="D35" s="29" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E35" s="26" t="s">
-        <v>273</v>
+        <v>66</v>
       </c>
       <c r="F35" s="26" t="s">
-        <v>273</v>
+        <v>66</v>
       </c>
       <c r="G35" s="26" t="s">
-        <v>273</v>
-      </c>
-      <c r="H35" s="26"/>
+        <v>66</v>
+      </c>
+      <c r="H35" s="11"/>
       <c r="I35" s="11"/>
       <c r="J35" s="11"/>
       <c r="K35" s="11"/>
       <c r="L35" s="11"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A36" s="24" t="s">
-        <v>90</v>
+      <c r="A36" s="27" t="s">
+        <v>92</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C36" s="25" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="D36" s="29" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E36" s="26" t="s">
-        <v>70</v>
+        <v>273</v>
       </c>
       <c r="F36" s="26" t="s">
-        <v>70</v>
+        <v>273</v>
       </c>
       <c r="G36" s="26" t="s">
-        <v>70</v>
-      </c>
-      <c r="H36" s="11"/>
+        <v>273</v>
+      </c>
+      <c r="H36" s="26"/>
       <c r="I36" s="11"/>
       <c r="J36" s="11"/>
       <c r="K36" s="11"/>
@@ -3085,22 +3094,22 @@
         <v>90</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>182</v>
+        <v>68</v>
       </c>
       <c r="C37" s="25" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D37" s="29" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E37" s="26" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F37" s="26" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G37" s="26" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H37" s="11"/>
       <c r="I37" s="11"/>
@@ -3113,22 +3122,22 @@
         <v>90</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>73</v>
+        <v>182</v>
       </c>
       <c r="C38" s="25" t="s">
-        <v>4</v>
+        <v>71</v>
       </c>
       <c r="D38" s="29" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E38" s="26" t="s">
-        <v>237</v>
-      </c>
-      <c r="F38" s="11" t="s">
-        <v>241</v>
-      </c>
-      <c r="G38" s="11" t="s">
-        <v>241</v>
+        <v>72</v>
+      </c>
+      <c r="F38" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="G38" s="26" t="s">
+        <v>72</v>
       </c>
       <c r="H38" s="11"/>
       <c r="I38" s="11"/>
@@ -3141,22 +3150,22 @@
         <v>90</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C39" s="25" t="s">
         <v>4</v>
       </c>
       <c r="D39" s="29" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E39" s="26" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G39" s="11" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H39" s="11"/>
       <c r="I39" s="11"/>
@@ -3169,22 +3178,22 @@
         <v>90</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C40" s="25" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D40" s="29" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E40" s="26" t="s">
-        <v>76</v>
-      </c>
-      <c r="F40" s="26" t="s">
-        <v>76</v>
-      </c>
-      <c r="G40" s="26" t="s">
-        <v>76</v>
+        <v>238</v>
+      </c>
+      <c r="F40" s="11" t="s">
+        <v>242</v>
+      </c>
+      <c r="G40" s="11" t="s">
+        <v>242</v>
       </c>
       <c r="H40" s="11"/>
       <c r="I40" s="11"/>
@@ -3197,22 +3206,22 @@
         <v>90</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C41" s="25" t="s">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="D41" s="29" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E41" s="26" t="s">
-        <v>78</v>
-      </c>
-      <c r="F41" s="11" t="s">
-        <v>243</v>
-      </c>
-      <c r="G41" s="11" t="s">
-        <v>243</v>
+        <v>76</v>
+      </c>
+      <c r="F41" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="G41" s="26" t="s">
+        <v>76</v>
       </c>
       <c r="H41" s="11"/>
       <c r="I41" s="11"/>
@@ -3221,26 +3230,26 @@
       <c r="L41" s="11"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A42" s="27" t="s">
-        <v>91</v>
+      <c r="A42" s="24" t="s">
+        <v>90</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C42" s="25" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="D42" s="29" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E42" s="26" t="s">
-        <v>80</v>
-      </c>
-      <c r="F42" s="26" t="s">
-        <v>80</v>
-      </c>
-      <c r="G42" s="26" t="s">
-        <v>80</v>
+        <v>78</v>
+      </c>
+      <c r="F42" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="G42" s="11" t="s">
+        <v>243</v>
       </c>
       <c r="H42" s="11"/>
       <c r="I42" s="11"/>
@@ -3253,22 +3262,22 @@
         <v>91</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C43" s="25" t="s">
         <v>69</v>
       </c>
       <c r="D43" s="29" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E43" s="26" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F43" s="26" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G43" s="26" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H43" s="11"/>
       <c r="I43" s="11"/>
@@ -3281,22 +3290,22 @@
         <v>91</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C44" s="25" t="s">
-        <v>4</v>
+        <v>69</v>
       </c>
       <c r="D44" s="29" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E44" s="26" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F44" s="26" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G44" s="26" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H44" s="11"/>
       <c r="I44" s="11"/>
@@ -3309,22 +3318,22 @@
         <v>91</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C45" s="25" t="s">
         <v>4</v>
       </c>
       <c r="D45" s="29" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E45" s="26" t="s">
-        <v>274</v>
+        <v>84</v>
       </c>
       <c r="F45" s="26" t="s">
-        <v>274</v>
+        <v>84</v>
       </c>
       <c r="G45" s="26" t="s">
-        <v>274</v>
+        <v>84</v>
       </c>
       <c r="H45" s="11"/>
       <c r="I45" s="11"/>
@@ -3333,26 +3342,26 @@
       <c r="L45" s="11"/>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A46" s="24" t="s">
-        <v>111</v>
+      <c r="A46" s="27" t="s">
+        <v>91</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>183</v>
+        <v>85</v>
       </c>
       <c r="C46" s="25" t="s">
-        <v>69</v>
+        <v>4</v>
       </c>
       <c r="D46" s="29" t="s">
-        <v>231</v>
-      </c>
-      <c r="E46" s="28" t="s">
-        <v>239</v>
-      </c>
-      <c r="F46" s="28" t="s">
-        <v>239</v>
-      </c>
-      <c r="G46" s="28" t="s">
-        <v>239</v>
+        <v>230</v>
+      </c>
+      <c r="E46" s="26" t="s">
+        <v>274</v>
+      </c>
+      <c r="F46" s="26" t="s">
+        <v>274</v>
+      </c>
+      <c r="G46" s="26" t="s">
+        <v>274</v>
       </c>
       <c r="H46" s="11"/>
       <c r="I46" s="11"/>
@@ -3365,22 +3374,22 @@
         <v>111</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C47" s="25" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D47" s="29" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E47" s="28" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F47" s="28" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G47" s="28" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H47" s="11"/>
       <c r="I47" s="11"/>
@@ -3389,13 +3398,27 @@
       <c r="L47" s="11"/>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A48" s="11"/>
-      <c r="B48" s="28"/>
-      <c r="C48" s="25"/>
-      <c r="D48" s="26"/>
-      <c r="E48" s="28"/>
-      <c r="F48" s="11"/>
-      <c r="G48" s="11"/>
+      <c r="A48" s="24" t="s">
+        <v>111</v>
+      </c>
+      <c r="B48" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="C48" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="D48" s="29" t="s">
+        <v>232</v>
+      </c>
+      <c r="E48" s="28" t="s">
+        <v>240</v>
+      </c>
+      <c r="F48" s="28" t="s">
+        <v>240</v>
+      </c>
+      <c r="G48" s="28" t="s">
+        <v>240</v>
+      </c>
       <c r="H48" s="11"/>
       <c r="I48" s="11"/>
       <c r="J48" s="11"/>
@@ -4130,18 +4153,32 @@
       <c r="K100" s="11"/>
       <c r="L100" s="11"/>
     </row>
+    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A101" s="11"/>
+      <c r="B101" s="28"/>
+      <c r="C101" s="25"/>
+      <c r="D101" s="26"/>
+      <c r="E101" s="28"/>
+      <c r="F101" s="11"/>
+      <c r="G101" s="11"/>
+      <c r="H101" s="11"/>
+      <c r="I101" s="11"/>
+      <c r="J101" s="11"/>
+      <c r="K101" s="11"/>
+      <c r="L101" s="11"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="B2:B6">
+  <conditionalFormatting sqref="B2:B7">
     <cfRule type="duplicateValues" dxfId="3" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B47">
+  <conditionalFormatting sqref="B2:B48">
     <cfRule type="duplicateValues" dxfId="2" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B7:B47">
+  <conditionalFormatting sqref="B8:B48">
     <cfRule type="duplicateValues" dxfId="1" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D47">
+  <conditionalFormatting sqref="D2:D48">
     <cfRule type="duplicateValues" dxfId="0" priority="7"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/eBus_Functions/Post_Processing/Root_Cause_Analysis_Work/info/eBus_Model_Info.xlsx
+++ b/eBus_Functions/Post_Processing/Root_Cause_Analysis_Work/info/eBus_Model_Info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\TempData\Github\eBus_Tool\eBus_Functions\Post_Processing\Root_Cause_Analysis_Work\info\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDB3083A-0D9A-4053-A0E4-13B87157D318}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7272B2ED-3F53-48A5-9A27-83D7642A9B46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Block_Diagram" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="307">
   <si>
     <t>Driver</t>
   </si>
@@ -909,6 +909,45 @@
   </si>
   <si>
     <t>logout.sec</t>
+  </si>
+  <si>
+    <t>Battery Current (Positive for Charge and Negative for Discharge)</t>
+  </si>
+  <si>
+    <t>Battery Power (Positive for Charge and Negative for Discharge)</t>
+  </si>
+  <si>
+    <t>Electric Motor 1 Demand Torque (Positive for Driving Torque and Negative for Recuperation Torque)</t>
+  </si>
+  <si>
+    <t>Electric Motor 2 Demand Torque (Positive for Driving Torque and Negative for Recuperation Torque)</t>
+  </si>
+  <si>
+    <t>Motor 1 Actual Torque (Positive for Driving Torque and Negative for Recuperation Torque)</t>
+  </si>
+  <si>
+    <t>Motor 2 Actual Torque (Positive for Driving Torque and Negative for Recuperation Torque)</t>
+  </si>
+  <si>
+    <t>Motor 1 Electrical Power (Positive for Driving Power and Negative for Recuperation Power)</t>
+  </si>
+  <si>
+    <t>Motor 2 Electrical Power (Positive for Driving Power and Negative for Recuperation Power)</t>
+  </si>
+  <si>
+    <t>Motor 1 Max Available Torque (Positive for Driving Torque and Negative for Recuperation Torque)</t>
+  </si>
+  <si>
+    <t>Motor 1 Min Available Torque (Positive for Driving Torque and Negative for Recuperation Torque)</t>
+  </si>
+  <si>
+    <t>Motor 2 Max Available Torque (Positive for Driving Torque and Negative for Recuperation Torque)</t>
+  </si>
+  <si>
+    <t>Motor 2 Min Available Torque (Positive for Driving Torque and Negative for Recuperation Torque)</t>
+  </si>
+  <si>
+    <t>Gear Box Output Torque (Positive for Driving Torque and Negative for Recuperation Torque)</t>
   </si>
 </sst>
 </file>
@@ -1222,9 +1261,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1238,6 +1274,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1642,7 +1681,7 @@
     </row>
     <row r="29" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G29" s="6"/>
-      <c r="H29" s="31" t="s">
+      <c r="H29" s="36" t="s">
         <v>6</v>
       </c>
       <c r="I29" s="7" t="s">
@@ -1651,14 +1690,14 @@
     </row>
     <row r="30" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G30" s="8"/>
-      <c r="H30" s="32"/>
+      <c r="H30" s="31"/>
       <c r="I30" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="31" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G31" s="9"/>
-      <c r="H31" s="33"/>
+      <c r="H31" s="32"/>
       <c r="I31" s="2" t="s">
         <v>32</v>
       </c>
@@ -1667,7 +1706,7 @@
       <c r="G32" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="H32" s="34" t="s">
+      <c r="H32" s="33" t="s">
         <v>0</v>
       </c>
       <c r="I32" s="7" t="s">
@@ -1678,7 +1717,7 @@
       <c r="G33" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="H33" s="35"/>
+      <c r="H33" s="34"/>
       <c r="I33" s="1" t="s">
         <v>12</v>
       </c>
@@ -1687,35 +1726,35 @@
       <c r="G34" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="H34" s="35"/>
+      <c r="H34" s="34"/>
       <c r="I34" s="1"/>
     </row>
     <row r="35" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G35" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="H35" s="35"/>
+      <c r="H35" s="34"/>
       <c r="I35" s="1"/>
     </row>
     <row r="36" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G36" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="H36" s="35"/>
+      <c r="H36" s="34"/>
       <c r="I36" s="1"/>
     </row>
     <row r="37" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G37" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="H37" s="36"/>
+      <c r="H37" s="35"/>
       <c r="I37" s="2"/>
     </row>
     <row r="38" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G38" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H38" s="31" t="s">
+      <c r="H38" s="36" t="s">
         <v>2</v>
       </c>
       <c r="I38" s="7" t="s">
@@ -1726,7 +1765,7 @@
       <c r="G39" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="H39" s="33"/>
+      <c r="H39" s="32"/>
       <c r="I39" s="2" t="s">
         <v>172</v>
       </c>
@@ -1735,7 +1774,7 @@
       <c r="G40" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="H40" s="34" t="s">
+      <c r="H40" s="33" t="s">
         <v>106</v>
       </c>
       <c r="I40" s="7" t="s">
@@ -1746,77 +1785,77 @@
       <c r="G41" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="H41" s="35"/>
+      <c r="H41" s="34"/>
       <c r="I41" s="1" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="42" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G42" s="8"/>
-      <c r="H42" s="35"/>
+      <c r="H42" s="34"/>
       <c r="I42" s="1" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="43" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G43" s="8"/>
-      <c r="H43" s="35"/>
+      <c r="H43" s="34"/>
       <c r="I43" s="1" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="44" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G44" s="8"/>
-      <c r="H44" s="35"/>
+      <c r="H44" s="34"/>
       <c r="I44" s="1" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="45" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G45" s="8"/>
-      <c r="H45" s="35"/>
+      <c r="H45" s="34"/>
       <c r="I45" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="46" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G46" s="8"/>
-      <c r="H46" s="35"/>
+      <c r="H46" s="34"/>
       <c r="I46" s="1" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="47" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G47" s="8"/>
-      <c r="H47" s="35"/>
+      <c r="H47" s="34"/>
       <c r="I47" s="1" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="48" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G48" s="8"/>
-      <c r="H48" s="35"/>
+      <c r="H48" s="34"/>
       <c r="I48" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="49" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G49" s="8"/>
-      <c r="H49" s="35"/>
+      <c r="H49" s="34"/>
       <c r="I49" s="1" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="50" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G50" s="8"/>
-      <c r="H50" s="35"/>
+      <c r="H50" s="34"/>
       <c r="I50" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="51" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G51" s="9"/>
-      <c r="H51" s="36"/>
+      <c r="H51" s="35"/>
       <c r="I51" s="2" t="s">
         <v>176</v>
       </c>
@@ -1825,7 +1864,7 @@
       <c r="G52" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="H52" s="31" t="s">
+      <c r="H52" s="36" t="s">
         <v>107</v>
       </c>
       <c r="I52" s="7" t="s">
@@ -1836,28 +1875,28 @@
       <c r="G53" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="H53" s="32"/>
+      <c r="H53" s="31"/>
       <c r="I53" s="1" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="54" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G54" s="8"/>
-      <c r="H54" s="32"/>
+      <c r="H54" s="31"/>
       <c r="I54" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="55" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G55" s="8"/>
-      <c r="H55" s="32"/>
+      <c r="H55" s="31"/>
       <c r="I55" s="1" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="56" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G56" s="8"/>
-      <c r="H56" s="32"/>
+      <c r="H56" s="31"/>
       <c r="I56" s="1" t="s">
         <v>16</v>
       </c>
@@ -1877,7 +1916,7 @@
       <c r="G58" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="H58" s="34" t="s">
+      <c r="H58" s="33" t="s">
         <v>108</v>
       </c>
       <c r="I58" s="7" t="s">
@@ -1886,7 +1925,7 @@
     </row>
     <row r="59" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G59" s="8"/>
-      <c r="H59" s="35"/>
+      <c r="H59" s="34"/>
       <c r="I59" s="1" t="s">
         <v>181</v>
       </c>
@@ -1895,7 +1934,7 @@
       <c r="G60" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H60" s="31" t="s">
+      <c r="H60" s="36" t="s">
         <v>19</v>
       </c>
       <c r="I60" s="7" t="s">
@@ -1906,42 +1945,42 @@
       <c r="G61" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="H61" s="32"/>
+      <c r="H61" s="31"/>
       <c r="I61" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="62" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G62" s="8"/>
-      <c r="H62" s="32"/>
+      <c r="H62" s="31"/>
       <c r="I62" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="63" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G63" s="8"/>
-      <c r="H63" s="32"/>
+      <c r="H63" s="31"/>
       <c r="I63" s="1" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="64" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G64" s="8"/>
-      <c r="H64" s="32"/>
+      <c r="H64" s="31"/>
       <c r="I64" s="1" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="65" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G65" s="8"/>
-      <c r="H65" s="32"/>
+      <c r="H65" s="31"/>
       <c r="I65" s="1" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="66" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G66" s="9"/>
-      <c r="H66" s="33"/>
+      <c r="H66" s="32"/>
       <c r="I66" s="2" t="s">
         <v>67</v>
       </c>
@@ -1950,7 +1989,7 @@
       <c r="G67" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="H67" s="32" t="s">
+      <c r="H67" s="31" t="s">
         <v>109</v>
       </c>
       <c r="I67" s="1" t="s">
@@ -1959,35 +1998,35 @@
     </row>
     <row r="68" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G68" s="8"/>
-      <c r="H68" s="32"/>
+      <c r="H68" s="31"/>
       <c r="I68" s="1" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="69" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G69" s="8"/>
-      <c r="H69" s="32"/>
+      <c r="H69" s="31"/>
       <c r="I69" s="1" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="70" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G70" s="8"/>
-      <c r="H70" s="32"/>
+      <c r="H70" s="31"/>
       <c r="I70" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="71" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G71" s="8"/>
-      <c r="H71" s="32"/>
+      <c r="H71" s="31"/>
       <c r="I71" s="1" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="72" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G72" s="9"/>
-      <c r="H72" s="33"/>
+      <c r="H72" s="32"/>
       <c r="I72" s="2" t="s">
         <v>77</v>
       </c>
@@ -1996,7 +2035,7 @@
       <c r="G73" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="H73" s="34" t="s">
+      <c r="H73" s="33" t="s">
         <v>110</v>
       </c>
       <c r="I73" s="7" t="s">
@@ -2007,28 +2046,28 @@
       <c r="G74" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="H74" s="35"/>
+      <c r="H74" s="34"/>
       <c r="I74" s="1" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="75" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G75" s="8"/>
-      <c r="H75" s="35"/>
+      <c r="H75" s="34"/>
       <c r="I75" s="1" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="76" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G76" s="9"/>
-      <c r="H76" s="36"/>
+      <c r="H76" s="35"/>
       <c r="I76" s="2" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="77" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G77" s="8"/>
-      <c r="H77" s="32" t="s">
+      <c r="H77" s="31" t="s">
         <v>111</v>
       </c>
       <c r="I77" s="1" t="s">
@@ -2037,30 +2076,30 @@
     </row>
     <row r="78" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G78" s="8"/>
-      <c r="H78" s="32"/>
+      <c r="H78" s="31"/>
       <c r="I78" s="1" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="79" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G79" s="9"/>
-      <c r="H79" s="33"/>
+      <c r="H79" s="32"/>
       <c r="I79" s="2" t="s">
         <v>185</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="H29:H31"/>
+    <mergeCell ref="H32:H37"/>
+    <mergeCell ref="H38:H39"/>
+    <mergeCell ref="H40:H51"/>
+    <mergeCell ref="H58:H59"/>
     <mergeCell ref="H67:H72"/>
     <mergeCell ref="H73:H76"/>
     <mergeCell ref="H52:H56"/>
     <mergeCell ref="H60:H66"/>
     <mergeCell ref="H77:H79"/>
-    <mergeCell ref="H29:H31"/>
-    <mergeCell ref="H32:H37"/>
-    <mergeCell ref="H38:H39"/>
-    <mergeCell ref="H40:H51"/>
-    <mergeCell ref="H58:H59"/>
   </mergeCells>
   <conditionalFormatting sqref="I29:I79 G29:G79">
     <cfRule type="duplicateValues" dxfId="4" priority="1"/>
@@ -2077,7 +2116,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28" style="20" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.88671875" style="20" customWidth="1"/>
     <col min="3" max="3" width="19" style="4" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24.6640625" style="21" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="46.44140625" style="20" bestFit="1" customWidth="1"/>
@@ -2286,7 +2325,7 @@
         <v>97</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>171</v>
+        <v>296</v>
       </c>
       <c r="C8" s="25" t="s">
         <v>3</v>
@@ -2314,7 +2353,7 @@
         <v>97</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>172</v>
+        <v>297</v>
       </c>
       <c r="C9" s="25" t="s">
         <v>3</v>
@@ -2342,7 +2381,7 @@
         <v>95</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>36</v>
+        <v>298</v>
       </c>
       <c r="C10" s="25" t="s">
         <v>3</v>
@@ -2370,7 +2409,7 @@
         <v>95</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>38</v>
+        <v>299</v>
       </c>
       <c r="C11" s="25" t="s">
         <v>3</v>
@@ -2454,7 +2493,7 @@
         <v>95</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>44</v>
+        <v>300</v>
       </c>
       <c r="C14" s="25" t="s">
         <v>4</v>
@@ -2482,7 +2521,7 @@
         <v>95</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>46</v>
+        <v>301</v>
       </c>
       <c r="C15" s="25" t="s">
         <v>4</v>
@@ -2566,7 +2605,7 @@
         <v>95</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>50</v>
+        <v>302</v>
       </c>
       <c r="C18" s="25" t="s">
         <v>3</v>
@@ -2594,7 +2633,7 @@
         <v>95</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>175</v>
+        <v>303</v>
       </c>
       <c r="C19" s="25" t="s">
         <v>3</v>
@@ -2622,7 +2661,7 @@
         <v>95</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>53</v>
+        <v>304</v>
       </c>
       <c r="C20" s="25" t="s">
         <v>3</v>
@@ -2650,7 +2689,7 @@
         <v>95</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>176</v>
+        <v>305</v>
       </c>
       <c r="C21" s="25" t="s">
         <v>3</v>
@@ -2678,7 +2717,7 @@
         <v>94</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>177</v>
+        <v>306</v>
       </c>
       <c r="C22" s="25" t="s">
         <v>3</v>
@@ -3094,7 +3133,7 @@
         <v>90</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>68</v>
+        <v>294</v>
       </c>
       <c r="C37" s="25" t="s">
         <v>69</v>
@@ -3150,7 +3189,7 @@
         <v>90</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>73</v>
+        <v>295</v>
       </c>
       <c r="C39" s="25" t="s">
         <v>4</v>

--- a/eBus_Functions/Post_Processing/Root_Cause_Analysis_Work/info/eBus_Model_Info.xlsx
+++ b/eBus_Functions/Post_Processing/Root_Cause_Analysis_Work/info/eBus_Model_Info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\TempData\Github\eBus_Tool\eBus_Functions\Post_Processing\Root_Cause_Analysis_Work\info\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7272B2ED-3F53-48A5-9A27-83D7642A9B46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30AB63F5-F1F8-493A-A929-D72CCA2CA18E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Block_Diagram" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="323">
   <si>
     <t>Driver</t>
   </si>
@@ -948,6 +948,54 @@
   </si>
   <si>
     <t>Gear Box Output Torque (Positive for Driving Torque and Negative for Recuperation Torque)</t>
+  </si>
+  <si>
+    <t>Max Available Electric Motor 1 Demand Torque</t>
+  </si>
+  <si>
+    <t>Max Available Electric Motor 2 Demand Torque</t>
+  </si>
+  <si>
+    <t>Max Available Electric Driving Power</t>
+  </si>
+  <si>
+    <t>Max Available Electric Regeneration Power</t>
+  </si>
+  <si>
+    <t>Min Available Electric Motor 1 Demand Torque</t>
+  </si>
+  <si>
+    <t>Min Available Electric Motor 2 Demand Torque</t>
+  </si>
+  <si>
+    <t>Max Available Motor 2 Demand Torque (Positive for Driving Torque and Negative for Recuperation Torque)</t>
+  </si>
+  <si>
+    <t>Max Available Motor 1 Demand Torque (Positive for Driving Torque and Negative for Recuperation Torque)</t>
+  </si>
+  <si>
+    <t>Min Available Motor 1 Demand Torque (Positive for Driving Torque and Negative for Recuperation Torque)</t>
+  </si>
+  <si>
+    <t>Min Available Motor 2 Demand Torque (Positive for Driving Torque and Negative for Recuperation Torque)</t>
+  </si>
+  <si>
+    <t>max_emot1_dem_trq</t>
+  </si>
+  <si>
+    <t>max_emot2_dem_trq</t>
+  </si>
+  <si>
+    <t>min_emot1_dem_trq</t>
+  </si>
+  <si>
+    <t>min_emot2_dem_trq</t>
+  </si>
+  <si>
+    <t>logout.MaxAvlEmotTrq_Cval_CPC/2</t>
+  </si>
+  <si>
+    <t>logout.MinAvlEmotTrq_Cval_CPC/2</t>
   </si>
 </sst>
 </file>
@@ -1068,7 +1116,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1084,39 +1132,6 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -1132,50 +1147,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="medium">
@@ -1184,23 +1155,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1210,30 +1170,21 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1261,22 +1212,17 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1357,10 +1303,10 @@
       <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>379373</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>2972078</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>53340</xdr:rowOff>
+      <xdr:rowOff>57150</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1659,432 +1605,489 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="G27:I79"/>
+  <dimension ref="G27:I88"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="7" max="7" width="27.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="26.33203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="31.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="26.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="54" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="27" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="28" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G28" s="14" t="s">
+    <row r="28" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G28" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="H28" s="15" t="s">
+      <c r="H28" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="I28" s="16" t="s">
+      <c r="I28" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="29" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G29" s="6"/>
-      <c r="H29" s="36" t="s">
+      <c r="G29" s="23"/>
+      <c r="H29" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="I29" s="7" t="s">
+      <c r="I29" s="23" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="30" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G30" s="8"/>
-      <c r="H30" s="31"/>
-      <c r="I30" s="1" t="s">
+      <c r="G30" s="23"/>
+      <c r="H30" s="24"/>
+      <c r="I30" s="23" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="31" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G31" s="9"/>
-      <c r="H31" s="32"/>
-      <c r="I31" s="2" t="s">
+    <row r="31" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G31" s="23"/>
+      <c r="H31" s="24"/>
+      <c r="I31" s="23" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="32" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G32" s="6" t="s">
+      <c r="G32" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="H32" s="33" t="s">
+      <c r="H32" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="I32" s="7" t="s">
+      <c r="I32" s="23" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="33" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G33" s="8" t="s">
+      <c r="G33" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="H33" s="34"/>
-      <c r="I33" s="1" t="s">
+      <c r="H33" s="25"/>
+      <c r="I33" s="23" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="34" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G34" s="8" t="s">
+      <c r="G34" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="H34" s="34"/>
-      <c r="I34" s="1"/>
+      <c r="H34" s="25"/>
+      <c r="I34" s="23"/>
     </row>
     <row r="35" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G35" s="8" t="s">
+      <c r="G35" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="H35" s="34"/>
-      <c r="I35" s="1"/>
+      <c r="H35" s="25"/>
+      <c r="I35" s="23"/>
     </row>
     <row r="36" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G36" s="8" t="s">
+      <c r="G36" s="23" t="s">
         <v>179</v>
       </c>
-      <c r="H36" s="34"/>
-      <c r="I36" s="1"/>
-    </row>
-    <row r="37" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G37" s="9" t="s">
+      <c r="H36" s="25"/>
+      <c r="I36" s="23"/>
+    </row>
+    <row r="37" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G37" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H37" s="35"/>
-      <c r="I37" s="2"/>
+      <c r="H37" s="25"/>
+      <c r="I37" s="23"/>
     </row>
     <row r="38" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G38" s="6" t="s">
+      <c r="G38" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="H38" s="36" t="s">
+      <c r="H38" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="I38" s="7" t="s">
+      <c r="I38" s="23" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="39" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G39" s="9" t="s">
+    <row r="39" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G39" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="H39" s="32"/>
-      <c r="I39" s="2" t="s">
+      <c r="H39" s="24"/>
+      <c r="I39" s="23" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="40" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G40" s="6" t="s">
+      <c r="G40" s="23"/>
+      <c r="H40" s="24"/>
+      <c r="I40" s="23" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="41" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G41" s="23"/>
+      <c r="H41" s="24"/>
+      <c r="I41" s="23" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="42" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G42" s="23"/>
+      <c r="H42" s="24"/>
+      <c r="I42" s="23" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="43" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G43" s="23"/>
+      <c r="H43" s="24"/>
+      <c r="I43" s="23" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="44" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G44" s="23"/>
+      <c r="H44" s="24"/>
+      <c r="I44" s="23"/>
+    </row>
+    <row r="45" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G45" s="23"/>
+      <c r="H45" s="24"/>
+      <c r="I45" s="23"/>
+    </row>
+    <row r="46" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G46" s="23"/>
+      <c r="H46" s="24"/>
+      <c r="I46" s="23"/>
+    </row>
+    <row r="47" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G47" s="23"/>
+      <c r="H47" s="24"/>
+      <c r="I47" s="23"/>
+    </row>
+    <row r="48" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G48" s="23"/>
+      <c r="H48" s="22"/>
+      <c r="I48" s="23"/>
+    </row>
+    <row r="49" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G49" s="23" t="s">
         <v>171</v>
       </c>
-      <c r="H40" s="33" t="s">
+      <c r="H49" s="25" t="s">
         <v>106</v>
       </c>
-      <c r="I40" s="7" t="s">
+      <c r="I49" s="23" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="41" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G41" s="8" t="s">
+    <row r="50" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G50" s="23" t="s">
         <v>172</v>
       </c>
-      <c r="H41" s="34"/>
-      <c r="I41" s="1" t="s">
+      <c r="H50" s="25"/>
+      <c r="I50" s="23" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="42" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G42" s="8"/>
-      <c r="H42" s="34"/>
-      <c r="I42" s="1" t="s">
+    <row r="51" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G51" s="23" t="s">
+        <v>309</v>
+      </c>
+      <c r="H51" s="25"/>
+      <c r="I51" s="23" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="43" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G43" s="8"/>
-      <c r="H43" s="34"/>
-      <c r="I43" s="1" t="s">
+    <row r="52" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G52" s="23" t="s">
+        <v>310</v>
+      </c>
+      <c r="H52" s="25"/>
+      <c r="I52" s="23" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G44" s="8"/>
-      <c r="H44" s="34"/>
-      <c r="I44" s="1" t="s">
+    <row r="53" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G53" s="23"/>
+      <c r="H53" s="25"/>
+      <c r="I53" s="23" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="45" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G45" s="8"/>
-      <c r="H45" s="34"/>
-      <c r="I45" s="1" t="s">
+    <row r="54" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G54" s="23"/>
+      <c r="H54" s="25"/>
+      <c r="I54" s="23" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="46" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G46" s="8"/>
-      <c r="H46" s="34"/>
-      <c r="I46" s="1" t="s">
+    <row r="55" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G55" s="23"/>
+      <c r="H55" s="25"/>
+      <c r="I55" s="23" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="47" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G47" s="8"/>
-      <c r="H47" s="34"/>
-      <c r="I47" s="1" t="s">
+    <row r="56" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G56" s="23"/>
+      <c r="H56" s="25"/>
+      <c r="I56" s="23" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="48" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G48" s="8"/>
-      <c r="H48" s="34"/>
-      <c r="I48" s="1" t="s">
+    <row r="57" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G57" s="23"/>
+      <c r="H57" s="25"/>
+      <c r="I57" s="23" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="49" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G49" s="8"/>
-      <c r="H49" s="34"/>
-      <c r="I49" s="1" t="s">
+    <row r="58" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G58" s="23"/>
+      <c r="H58" s="25"/>
+      <c r="I58" s="23" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="50" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G50" s="8"/>
-      <c r="H50" s="34"/>
-      <c r="I50" s="1" t="s">
+    <row r="59" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G59" s="23"/>
+      <c r="H59" s="25"/>
+      <c r="I59" s="23" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="51" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G51" s="9"/>
-      <c r="H51" s="35"/>
-      <c r="I51" s="2" t="s">
+    <row r="60" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G60" s="23"/>
+      <c r="H60" s="25"/>
+      <c r="I60" s="23" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="52" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G52" s="6" t="s">
+    <row r="61" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G61" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="H52" s="36" t="s">
+      <c r="H61" s="24" t="s">
         <v>107</v>
       </c>
-      <c r="I52" s="7" t="s">
+      <c r="I61" s="23" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="53" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G53" s="8" t="s">
+    <row r="62" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G62" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="H53" s="31"/>
-      <c r="I53" s="1" t="s">
+      <c r="H62" s="24"/>
+      <c r="I62" s="23" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="54" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G54" s="8"/>
-      <c r="H54" s="31"/>
-      <c r="I54" s="1" t="s">
+    <row r="63" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G63" s="23"/>
+      <c r="H63" s="24"/>
+      <c r="I63" s="23" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="55" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G55" s="8"/>
-      <c r="H55" s="31"/>
-      <c r="I55" s="1" t="s">
+    <row r="64" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G64" s="23"/>
+      <c r="H64" s="24"/>
+      <c r="I64" s="23" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="56" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G56" s="8"/>
-      <c r="H56" s="31"/>
-      <c r="I56" s="1" t="s">
+    <row r="65" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G65" s="23"/>
+      <c r="H65" s="24"/>
+      <c r="I65" s="23" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G57" s="17" t="s">
+    <row r="66" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G66" s="23" t="s">
         <v>177</v>
       </c>
-      <c r="H57" s="18" t="s">
+      <c r="H66" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="I57" s="19" t="s">
+      <c r="I66" s="23" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="58" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G58" s="6" t="s">
+    <row r="67" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G67" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="H58" s="33" t="s">
+      <c r="H67" s="25" t="s">
         <v>108</v>
       </c>
-      <c r="I58" s="7" t="s">
+      <c r="I67" s="23" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="59" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G59" s="8"/>
-      <c r="H59" s="34"/>
-      <c r="I59" s="1" t="s">
+    <row r="68" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G68" s="23"/>
+      <c r="H68" s="25"/>
+      <c r="I68" s="23" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="60" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G60" s="6" t="s">
+    <row r="69" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G69" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="H60" s="36" t="s">
+      <c r="H69" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="I60" s="7" t="s">
+      <c r="I69" s="23" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="61" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G61" s="8" t="s">
+    <row r="70" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G70" s="23" t="s">
         <v>180</v>
       </c>
-      <c r="H61" s="31"/>
-      <c r="I61" s="1" t="s">
+      <c r="H70" s="24"/>
+      <c r="I70" s="23" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="62" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G62" s="8"/>
-      <c r="H62" s="31"/>
-      <c r="I62" s="1" t="s">
+    <row r="71" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G71" s="23"/>
+      <c r="H71" s="24"/>
+      <c r="I71" s="23" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="63" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G63" s="8"/>
-      <c r="H63" s="31"/>
-      <c r="I63" s="1" t="s">
+    <row r="72" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G72" s="23"/>
+      <c r="H72" s="24"/>
+      <c r="I72" s="23" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="64" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G64" s="8"/>
-      <c r="H64" s="31"/>
-      <c r="I64" s="1" t="s">
+    <row r="73" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G73" s="23"/>
+      <c r="H73" s="24"/>
+      <c r="I73" s="23" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="65" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G65" s="8"/>
-      <c r="H65" s="31"/>
-      <c r="I65" s="1" t="s">
+    <row r="74" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G74" s="23"/>
+      <c r="H74" s="24"/>
+      <c r="I74" s="23" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="66" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G66" s="9"/>
-      <c r="H66" s="32"/>
-      <c r="I66" s="2" t="s">
+    <row r="75" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G75" s="23"/>
+      <c r="H75" s="24"/>
+      <c r="I75" s="23" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="67" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G67" s="8" t="s">
+    <row r="76" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G76" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="H67" s="31" t="s">
+      <c r="H76" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="I67" s="1" t="s">
+      <c r="I76" s="23" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="68" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G68" s="8"/>
-      <c r="H68" s="31"/>
-      <c r="I68" s="1" t="s">
+    <row r="77" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G77" s="23"/>
+      <c r="H77" s="24"/>
+      <c r="I77" s="23" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="69" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G69" s="8"/>
-      <c r="H69" s="31"/>
-      <c r="I69" s="1" t="s">
+    <row r="78" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G78" s="23"/>
+      <c r="H78" s="24"/>
+      <c r="I78" s="23" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="70" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G70" s="8"/>
-      <c r="H70" s="31"/>
-      <c r="I70" s="1" t="s">
+    <row r="79" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G79" s="23"/>
+      <c r="H79" s="24"/>
+      <c r="I79" s="23" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="71" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G71" s="8"/>
-      <c r="H71" s="31"/>
-      <c r="I71" s="1" t="s">
+    <row r="80" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G80" s="23"/>
+      <c r="H80" s="24"/>
+      <c r="I80" s="23" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="72" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G72" s="9"/>
-      <c r="H72" s="32"/>
-      <c r="I72" s="2" t="s">
+    <row r="81" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G81" s="23"/>
+      <c r="H81" s="24"/>
+      <c r="I81" s="23" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="73" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G73" s="6" t="s">
+    <row r="82" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G82" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="H73" s="33" t="s">
+      <c r="H82" s="25" t="s">
         <v>110</v>
       </c>
-      <c r="I73" s="7" t="s">
+      <c r="I82" s="23" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="74" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G74" s="8" t="s">
+    <row r="83" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G83" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="H74" s="34"/>
-      <c r="I74" s="1" t="s">
+      <c r="H83" s="25"/>
+      <c r="I83" s="23" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="75" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G75" s="8"/>
-      <c r="H75" s="34"/>
-      <c r="I75" s="1" t="s">
+    <row r="84" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G84" s="23"/>
+      <c r="H84" s="25"/>
+      <c r="I84" s="23" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="76" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G76" s="9"/>
-      <c r="H76" s="35"/>
-      <c r="I76" s="2" t="s">
+    <row r="85" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G85" s="23"/>
+      <c r="H85" s="25"/>
+      <c r="I85" s="23" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="77" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G77" s="8"/>
-      <c r="H77" s="31" t="s">
+    <row r="86" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G86" s="23"/>
+      <c r="H86" s="24" t="s">
         <v>111</v>
       </c>
-      <c r="I77" s="1" t="s">
+      <c r="I86" s="23" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="78" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G78" s="8"/>
-      <c r="H78" s="31"/>
-      <c r="I78" s="1" t="s">
+    <row r="87" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G87" s="23"/>
+      <c r="H87" s="24"/>
+      <c r="I87" s="23" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="79" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G79" s="9"/>
-      <c r="H79" s="32"/>
-      <c r="I79" s="2" t="s">
+    <row r="88" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G88" s="23"/>
+      <c r="H88" s="24"/>
+      <c r="I88" s="23" t="s">
         <v>185</v>
       </c>
     </row>
@@ -2092,16 +2095,16 @@
   <mergeCells count="10">
     <mergeCell ref="H29:H31"/>
     <mergeCell ref="H32:H37"/>
-    <mergeCell ref="H38:H39"/>
-    <mergeCell ref="H40:H51"/>
-    <mergeCell ref="H58:H59"/>
-    <mergeCell ref="H67:H72"/>
-    <mergeCell ref="H73:H76"/>
-    <mergeCell ref="H52:H56"/>
-    <mergeCell ref="H60:H66"/>
-    <mergeCell ref="H77:H79"/>
+    <mergeCell ref="H38:H47"/>
+    <mergeCell ref="H49:H60"/>
+    <mergeCell ref="H67:H68"/>
+    <mergeCell ref="H76:H81"/>
+    <mergeCell ref="H82:H85"/>
+    <mergeCell ref="H61:H65"/>
+    <mergeCell ref="H69:H75"/>
+    <mergeCell ref="H86:H88"/>
   </mergeCells>
-  <conditionalFormatting sqref="I29:I79 G29:G79">
+  <conditionalFormatting sqref="I29:I88 G29:G88">
     <cfRule type="duplicateValues" dxfId="4" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2112,14 +2115,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFA16316-83DB-41C7-8B25-B191695DD108}">
-  <dimension ref="A1:L101"/>
+  <dimension ref="A1:L105"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35.88671875" style="20" customWidth="1"/>
-    <col min="3" max="3" width="19" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.6640625" style="21" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="46.44140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="58.5546875" style="11" customWidth="1"/>
+    <col min="3" max="3" width="19" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.6640625" style="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="46.44140625" style="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="39.5546875" customWidth="1"/>
     <col min="7" max="7" width="28" customWidth="1"/>
     <col min="8" max="8" width="31.88671875" customWidth="1"/>
@@ -2127,2097 +2130,2209 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="B1" s="22" t="s">
+      <c r="B1" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="C1" s="22" t="s">
+      <c r="C1" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="23" t="s">
+      <c r="D1" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="E1" s="22" t="s">
+      <c r="E1" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="F1" s="22" t="s">
+      <c r="F1" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="G1" s="22" t="s">
+      <c r="G1" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="H1" s="22" t="s">
+      <c r="H1" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="I1" s="22" t="s">
+      <c r="I1" s="13" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="5" t="s">
         <v>290</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="C2" s="16" t="s">
         <v>291</v>
       </c>
-      <c r="D2" s="29" t="s">
+      <c r="D2" s="20" t="s">
         <v>292</v>
       </c>
-      <c r="E2" s="26" t="s">
+      <c r="E2" s="17" t="s">
         <v>293</v>
       </c>
-      <c r="F2" s="26" t="s">
+      <c r="F2" s="17" t="s">
         <v>293</v>
       </c>
-      <c r="G2" s="26" t="s">
+      <c r="G2" s="17" t="s">
         <v>293</v>
       </c>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="25" t="s">
+      <c r="C3" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="D3" s="29" t="s">
+      <c r="D3" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="E3" s="26" t="s">
+      <c r="E3" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="F3" s="26" t="s">
+      <c r="F3" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="G3" s="26" t="s">
+      <c r="G3" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11"/>
-      <c r="J3" s="11"/>
-      <c r="K3" s="11"/>
-      <c r="L3" s="11"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="25" t="s">
+      <c r="C4" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="29" t="s">
+      <c r="D4" s="20" t="s">
         <v>188</v>
       </c>
-      <c r="E4" s="26" t="s">
+      <c r="E4" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="F4" s="26" t="s">
+      <c r="F4" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="G4" s="26" t="s">
+      <c r="G4" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="H4" s="11"/>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="25" t="s">
+      <c r="C5" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="29" t="s">
+      <c r="D5" s="20" t="s">
         <v>189</v>
       </c>
-      <c r="E5" s="26" t="s">
+      <c r="E5" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="F5" s="26" t="s">
+      <c r="F5" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="G5" s="26" t="s">
+      <c r="G5" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="11"/>
-      <c r="L5" s="11"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="27" t="s">
+      <c r="A6" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="25" t="s">
+      <c r="C6" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="29" t="s">
+      <c r="D6" s="20" t="s">
         <v>190</v>
       </c>
-      <c r="E6" s="26" t="s">
+      <c r="E6" s="17" t="s">
         <v>276</v>
       </c>
-      <c r="F6" s="26" t="s">
+      <c r="F6" s="17" t="s">
         <v>276</v>
       </c>
-      <c r="G6" s="26" t="s">
+      <c r="G6" s="17" t="s">
         <v>276</v>
       </c>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="11"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="27" t="s">
+      <c r="A7" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="25" t="s">
+      <c r="C7" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="29" t="s">
+      <c r="D7" s="20" t="s">
         <v>191</v>
       </c>
-      <c r="E7" s="26" t="s">
+      <c r="E7" s="17" t="s">
         <v>277</v>
       </c>
-      <c r="F7" s="26" t="s">
+      <c r="F7" s="17" t="s">
         <v>277</v>
       </c>
-      <c r="G7" s="26" t="s">
+      <c r="G7" s="17" t="s">
         <v>277</v>
       </c>
-      <c r="H7" s="11"/>
-      <c r="I7" s="11"/>
-      <c r="J7" s="11"/>
-      <c r="K7" s="11"/>
-      <c r="L7" s="11"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
+      <c r="L7" s="5"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="24" t="s">
+      <c r="A8" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="C8" s="25" t="s">
+      <c r="C8" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="29" t="s">
+      <c r="D8" s="20" t="s">
         <v>192</v>
       </c>
-      <c r="E8" s="26" t="s">
+      <c r="E8" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="F8" s="26" t="s">
+      <c r="F8" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="G8" s="26" t="s">
+      <c r="G8" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
-      <c r="J8" s="11"/>
-      <c r="K8" s="11"/>
-      <c r="L8" s="11"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="24" t="s">
+      <c r="A9" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="5" t="s">
         <v>297</v>
       </c>
-      <c r="C9" s="25" t="s">
+      <c r="C9" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="D9" s="29" t="s">
+      <c r="D9" s="20" t="s">
         <v>193</v>
       </c>
-      <c r="E9" s="26" t="s">
+      <c r="E9" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="F9" s="26" t="s">
+      <c r="F9" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="G9" s="26" t="s">
+      <c r="G9" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
-      <c r="J9" s="11"/>
-      <c r="K9" s="11"/>
-      <c r="L9" s="11"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="27" t="s">
+      <c r="A10" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>317</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>321</v>
+      </c>
+      <c r="F10" s="17" t="s">
+        <v>321</v>
+      </c>
+      <c r="G10" s="17" t="s">
+        <v>321</v>
+      </c>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="5"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>318</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>321</v>
+      </c>
+      <c r="F11" s="17" t="s">
+        <v>321</v>
+      </c>
+      <c r="G11" s="17" t="s">
+        <v>321</v>
+      </c>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="5"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>319</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>322</v>
+      </c>
+      <c r="F12" s="17" t="s">
+        <v>322</v>
+      </c>
+      <c r="G12" s="17" t="s">
+        <v>322</v>
+      </c>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5"/>
+      <c r="L12" s="5"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>320</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>322</v>
+      </c>
+      <c r="F13" s="17" t="s">
+        <v>322</v>
+      </c>
+      <c r="G13" s="17" t="s">
+        <v>322</v>
+      </c>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="5"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B14" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="C10" s="25" t="s">
+      <c r="C14" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="D10" s="29" t="s">
+      <c r="D14" s="20" t="s">
         <v>194</v>
       </c>
-      <c r="E10" s="26" t="s">
+      <c r="E14" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="F10" s="26" t="s">
+      <c r="F14" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="G10" s="26" t="s">
+      <c r="G14" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
-      <c r="J10" s="11"/>
-      <c r="K10" s="11"/>
-      <c r="L10" s="11"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="27" t="s">
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A15" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B15" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="C11" s="25" t="s">
+      <c r="C15" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="D11" s="29" t="s">
+      <c r="D15" s="20" t="s">
         <v>195</v>
       </c>
-      <c r="E11" s="26" t="s">
+      <c r="E15" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="F11" s="26" t="s">
+      <c r="F15" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="G11" s="26" t="s">
+      <c r="G15" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
-      <c r="J11" s="11"/>
-      <c r="K11" s="11"/>
-      <c r="L11" s="11"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="27" t="s">
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="5"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A16" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B16" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C12" s="25" t="s">
+      <c r="C16" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="D12" s="29" t="s">
+      <c r="D16" s="20" t="s">
         <v>196</v>
       </c>
-      <c r="E12" s="26" t="s">
+      <c r="E16" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="F12" s="26" t="s">
+      <c r="F16" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="G12" s="26" t="s">
+      <c r="G16" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
-      <c r="J12" s="11"/>
-      <c r="K12" s="11"/>
-      <c r="L12" s="11"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="27" t="s">
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="5"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A17" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B17" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="25" t="s">
+      <c r="C17" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="D13" s="29" t="s">
+      <c r="D17" s="20" t="s">
         <v>197</v>
       </c>
-      <c r="E13" s="26" t="s">
+      <c r="E17" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="F13" s="26" t="s">
+      <c r="F17" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="G13" s="26" t="s">
+      <c r="G17" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
-      <c r="J13" s="11"/>
-      <c r="K13" s="11"/>
-      <c r="L13" s="11"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="27" t="s">
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+      <c r="K17" s="5"/>
+      <c r="L17" s="5"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A18" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B18" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="C14" s="25" t="s">
+      <c r="C18" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D14" s="29" t="s">
+      <c r="D18" s="20" t="s">
         <v>198</v>
       </c>
-      <c r="E14" s="26" t="s">
+      <c r="E18" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="F14" s="26" t="s">
+      <c r="F18" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="G14" s="26" t="s">
+      <c r="G18" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
-      <c r="J14" s="11"/>
-      <c r="K14" s="11"/>
-      <c r="L14" s="11"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="27" t="s">
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="5"/>
+      <c r="L18" s="5"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A19" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B19" s="5" t="s">
         <v>301</v>
       </c>
-      <c r="C15" s="25" t="s">
+      <c r="C19" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D15" s="29" t="s">
+      <c r="D19" s="20" t="s">
         <v>199</v>
       </c>
-      <c r="E15" s="26" t="s">
+      <c r="E19" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="F15" s="26" t="s">
+      <c r="F19" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="G15" s="26" t="s">
+      <c r="G19" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
-      <c r="J15" s="11"/>
-      <c r="K15" s="11"/>
-      <c r="L15" s="11"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="27" t="s">
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="5"/>
+      <c r="L19" s="5"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A20" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B20" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="C16" s="25" t="s">
+      <c r="C20" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D16" s="29" t="s">
+      <c r="D20" s="20" t="s">
         <v>200</v>
       </c>
-      <c r="E16" s="26" t="s">
+      <c r="E20" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="F16" s="26" t="s">
+      <c r="F20" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="26" t="s">
+      <c r="G20" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
-      <c r="J16" s="11"/>
-      <c r="K16" s="11"/>
-      <c r="L16" s="11"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" s="27" t="s">
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="5"/>
+      <c r="L20" s="5"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A21" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="B21" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="C17" s="25" t="s">
+      <c r="C21" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D17" s="29" t="s">
+      <c r="D21" s="20" t="s">
         <v>201</v>
       </c>
-      <c r="E17" s="26" t="s">
+      <c r="E21" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="F17" s="26" t="s">
+      <c r="F21" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="G17" s="26" t="s">
+      <c r="G21" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11"/>
-      <c r="J17" s="11"/>
-      <c r="K17" s="11"/>
-      <c r="L17" s="11"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18" s="27" t="s">
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="5"/>
+      <c r="L21" s="5"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A22" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="B22" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="C18" s="25" t="s">
+      <c r="C22" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="D18" s="29" t="s">
+      <c r="D22" s="20" t="s">
         <v>202</v>
       </c>
-      <c r="E18" s="26" t="s">
+      <c r="E22" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="F18" s="26" t="s">
+      <c r="F22" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="G18" s="26" t="s">
+      <c r="G22" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="H18" s="11"/>
-      <c r="I18" s="11"/>
-      <c r="J18" s="11"/>
-      <c r="K18" s="11"/>
-      <c r="L18" s="11"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A19" s="27" t="s">
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+      <c r="K22" s="5"/>
+      <c r="L22" s="5"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A23" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="B19" s="11" t="s">
+      <c r="B23" s="5" t="s">
         <v>303</v>
       </c>
-      <c r="C19" s="25" t="s">
+      <c r="C23" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="D19" s="29" t="s">
+      <c r="D23" s="20" t="s">
         <v>203</v>
       </c>
-      <c r="E19" s="26" t="s">
+      <c r="E23" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="F19" s="26" t="s">
+      <c r="F23" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="G19" s="26" t="s">
+      <c r="G23" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="H19" s="11"/>
-      <c r="I19" s="11"/>
-      <c r="J19" s="11"/>
-      <c r="K19" s="11"/>
-      <c r="L19" s="11"/>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" s="27" t="s">
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
+      <c r="K23" s="5"/>
+      <c r="L23" s="5"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A24" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="B24" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="C20" s="25" t="s">
+      <c r="C24" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="D20" s="29" t="s">
+      <c r="D24" s="20" t="s">
         <v>204</v>
       </c>
-      <c r="E20" s="26" t="s">
+      <c r="E24" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="F20" s="26" t="s">
+      <c r="F24" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="G20" s="26" t="s">
+      <c r="G24" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="H20" s="11"/>
-      <c r="I20" s="11"/>
-      <c r="J20" s="11"/>
-      <c r="K20" s="11"/>
-      <c r="L20" s="11"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A21" s="27" t="s">
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="5"/>
+      <c r="L24" s="5"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A25" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="B21" s="11" t="s">
+      <c r="B25" s="5" t="s">
         <v>305</v>
       </c>
-      <c r="C21" s="25" t="s">
+      <c r="C25" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="D21" s="29" t="s">
+      <c r="D25" s="20" t="s">
         <v>205</v>
       </c>
-      <c r="E21" s="26" t="s">
+      <c r="E25" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="F21" s="26" t="s">
+      <c r="F25" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="G21" s="26" t="s">
+      <c r="G25" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="H21" s="11"/>
-      <c r="I21" s="11"/>
-      <c r="J21" s="11"/>
-      <c r="K21" s="11"/>
-      <c r="L21" s="11"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22" s="24" t="s">
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="5"/>
+      <c r="K25" s="5"/>
+      <c r="L25" s="5"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A26" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="B22" s="11" t="s">
+      <c r="B26" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="C22" s="25" t="s">
+      <c r="C26" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="D22" s="29" t="s">
+      <c r="D26" s="20" t="s">
         <v>206</v>
       </c>
-      <c r="E22" s="26" t="s">
+      <c r="E26" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="F22" s="26" t="s">
+      <c r="F26" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="G22" s="26" t="s">
+      <c r="G26" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="H22" s="11"/>
-      <c r="I22" s="11"/>
-      <c r="J22" s="11"/>
-      <c r="K22" s="11"/>
-      <c r="L22" s="11"/>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A23" s="24" t="s">
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="5"/>
+      <c r="K26" s="5"/>
+      <c r="L26" s="5"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A27" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="B23" s="11" t="s">
+      <c r="B27" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="C23" s="25" t="s">
+      <c r="C27" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="D23" s="29" t="s">
+      <c r="D27" s="20" t="s">
         <v>207</v>
       </c>
-      <c r="E23" s="26" t="s">
+      <c r="E27" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="F23" s="26" t="s">
+      <c r="F27" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="G23" s="26" t="s">
+      <c r="G27" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="H23" s="11"/>
-      <c r="I23" s="11"/>
-      <c r="J23" s="11"/>
-      <c r="K23" s="11"/>
-      <c r="L23" s="11"/>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A24" s="24" t="s">
+      <c r="H27" s="5"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="5"/>
+      <c r="K27" s="5"/>
+      <c r="L27" s="5"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A28" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="B24" s="11" t="s">
+      <c r="B28" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C24" s="25"/>
-      <c r="D24" s="29" t="s">
+      <c r="C28" s="16"/>
+      <c r="D28" s="20" t="s">
         <v>208</v>
       </c>
-      <c r="E24" s="26" t="s">
+      <c r="E28" s="17" t="s">
         <v>272</v>
       </c>
-      <c r="F24" s="26" t="s">
+      <c r="F28" s="17" t="s">
         <v>272</v>
       </c>
-      <c r="G24" s="26" t="s">
+      <c r="G28" s="17" t="s">
         <v>272</v>
       </c>
-      <c r="H24" s="26"/>
-      <c r="I24" s="11"/>
-      <c r="J24" s="11"/>
-      <c r="K24" s="11"/>
-      <c r="L24" s="11"/>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A25" s="24" t="s">
+      <c r="H28" s="17"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="5"/>
+      <c r="K28" s="5"/>
+      <c r="L28" s="5"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A29" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="B25" s="11" t="s">
+      <c r="B29" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="C25" s="25"/>
-      <c r="D25" s="29" t="s">
+      <c r="C29" s="16"/>
+      <c r="D29" s="20" t="s">
         <v>209</v>
       </c>
-      <c r="E25" s="26" t="s">
+      <c r="E29" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="F25" s="26" t="s">
+      <c r="F29" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="G25" s="26" t="s">
+      <c r="G29" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="H25" s="11"/>
-      <c r="I25" s="11"/>
-      <c r="J25" s="11"/>
-      <c r="K25" s="11"/>
-      <c r="L25" s="11"/>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A26" s="24" t="s">
+      <c r="H29" s="5"/>
+      <c r="I29" s="5"/>
+      <c r="J29" s="5"/>
+      <c r="K29" s="5"/>
+      <c r="L29" s="5"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A30" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="B26" s="11" t="s">
+      <c r="B30" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C26" s="25" t="s">
+      <c r="C30" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D26" s="29" t="s">
+      <c r="D30" s="20" t="s">
         <v>210</v>
       </c>
-      <c r="E26" s="26" t="s">
+      <c r="E30" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="F26" s="26" t="s">
+      <c r="F30" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="G26" s="26" t="s">
+      <c r="G30" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="H26" s="11"/>
-      <c r="I26" s="11"/>
-      <c r="J26" s="11"/>
-      <c r="K26" s="11"/>
-      <c r="L26" s="11"/>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A27" s="27" t="s">
+      <c r="H30" s="5"/>
+      <c r="I30" s="5"/>
+      <c r="J30" s="5"/>
+      <c r="K30" s="5"/>
+      <c r="L30" s="5"/>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A31" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="B27" s="11" t="s">
+      <c r="B31" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="25" t="s">
+      <c r="C31" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="D27" s="29" t="s">
+      <c r="D31" s="20" t="s">
         <v>211</v>
       </c>
-      <c r="E27" s="28" t="s">
+      <c r="E31" s="19" t="s">
         <v>234</v>
       </c>
-      <c r="F27" s="28" t="s">
+      <c r="F31" s="19" t="s">
         <v>234</v>
       </c>
-      <c r="G27" s="28" t="s">
+      <c r="G31" s="19" t="s">
         <v>234</v>
       </c>
-      <c r="H27" s="11"/>
-      <c r="I27" s="11"/>
-      <c r="J27" s="11"/>
-      <c r="K27" s="11"/>
-      <c r="L27" s="11"/>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A28" s="24" t="s">
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
+      <c r="J31" s="5"/>
+      <c r="K31" s="5"/>
+      <c r="L31" s="5"/>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A32" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="B28" s="11" t="s">
+      <c r="B32" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="C28" s="25" t="s">
+      <c r="C32" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="D28" s="29" t="s">
+      <c r="D32" s="20" t="s">
         <v>219</v>
       </c>
-      <c r="E28" s="28" t="s">
+      <c r="E32" s="19" t="s">
         <v>235</v>
       </c>
-      <c r="F28" s="28" t="s">
+      <c r="F32" s="19" t="s">
         <v>235</v>
       </c>
-      <c r="G28" s="28" t="s">
+      <c r="G32" s="19" t="s">
         <v>235</v>
       </c>
-      <c r="H28" s="11"/>
-      <c r="I28" s="11"/>
-      <c r="J28" s="11"/>
-      <c r="K28" s="11"/>
-      <c r="L28" s="11"/>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A29" s="24" t="s">
+      <c r="H32" s="5"/>
+      <c r="I32" s="5"/>
+      <c r="J32" s="5"/>
+      <c r="K32" s="5"/>
+      <c r="L32" s="5"/>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A33" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="B29" s="11" t="s">
+      <c r="B33" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="C29" s="25" t="s">
+      <c r="C33" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D29" s="29" t="s">
+      <c r="D33" s="20" t="s">
         <v>220</v>
       </c>
-      <c r="E29" s="26" t="s">
+      <c r="E33" s="17" t="s">
         <v>233</v>
       </c>
-      <c r="F29" s="26" t="s">
+      <c r="F33" s="17" t="s">
         <v>233</v>
       </c>
-      <c r="G29" s="26" t="s">
+      <c r="G33" s="17" t="s">
         <v>233</v>
       </c>
-      <c r="H29" s="11"/>
-      <c r="I29" s="11"/>
-      <c r="J29" s="11"/>
-      <c r="K29" s="11"/>
-      <c r="L29" s="11"/>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A30" s="27" t="s">
+      <c r="H33" s="5"/>
+      <c r="I33" s="5"/>
+      <c r="J33" s="5"/>
+      <c r="K33" s="5"/>
+      <c r="L33" s="5"/>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A34" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="B30" s="11" t="s">
+      <c r="B34" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C30" s="25" t="s">
+      <c r="C34" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="D30" s="29" t="s">
+      <c r="D34" s="20" t="s">
         <v>212</v>
       </c>
-      <c r="E30" s="26" t="s">
+      <c r="E34" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="F30" s="26" t="s">
+      <c r="F34" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="G30" s="26" t="s">
+      <c r="G34" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="H30" s="11"/>
-      <c r="I30" s="11"/>
-      <c r="J30" s="11"/>
-      <c r="K30" s="11"/>
-      <c r="L30" s="11"/>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A31" s="27" t="s">
+      <c r="H34" s="5"/>
+      <c r="I34" s="5"/>
+      <c r="J34" s="5"/>
+      <c r="K34" s="5"/>
+      <c r="L34" s="5"/>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A35" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="B31" s="11" t="s">
+      <c r="B35" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C31" s="25" t="s">
+      <c r="C35" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="D31" s="29" t="s">
+      <c r="D35" s="20" t="s">
         <v>213</v>
       </c>
-      <c r="E31" s="26" t="s">
+      <c r="E35" s="17" t="s">
         <v>275</v>
       </c>
-      <c r="F31" s="26" t="s">
+      <c r="F35" s="17" t="s">
         <v>275</v>
       </c>
-      <c r="G31" s="26" t="s">
+      <c r="G35" s="17" t="s">
         <v>275</v>
       </c>
-      <c r="H31" s="11"/>
-      <c r="I31" s="11"/>
-      <c r="J31" s="11"/>
-      <c r="K31" s="11"/>
-      <c r="L31" s="11"/>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A32" s="27" t="s">
+      <c r="H35" s="5"/>
+      <c r="I35" s="5"/>
+      <c r="J35" s="5"/>
+      <c r="K35" s="5"/>
+      <c r="L35" s="5"/>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A36" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="B32" s="11" t="s">
+      <c r="B36" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C32" s="25" t="s">
+      <c r="C36" s="16" t="s">
         <v>187</v>
       </c>
-      <c r="D32" s="29" t="s">
+      <c r="D36" s="20" t="s">
         <v>214</v>
       </c>
-      <c r="E32" s="26" t="s">
+      <c r="E36" s="17" t="s">
         <v>278</v>
       </c>
-      <c r="F32" s="26" t="s">
+      <c r="F36" s="17" t="s">
         <v>278</v>
       </c>
-      <c r="G32" s="26" t="s">
+      <c r="G36" s="17" t="s">
         <v>278</v>
       </c>
-      <c r="H32" s="11"/>
-      <c r="I32" s="11"/>
-      <c r="J32" s="11"/>
-      <c r="K32" s="11"/>
-      <c r="L32" s="11"/>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A33" s="27" t="s">
+      <c r="H36" s="5"/>
+      <c r="I36" s="5"/>
+      <c r="J36" s="5"/>
+      <c r="K36" s="5"/>
+      <c r="L36" s="5"/>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A37" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="B33" s="11" t="s">
+      <c r="B37" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C33" s="25" t="s">
+      <c r="C37" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="D33" s="29" t="s">
+      <c r="D37" s="20" t="s">
         <v>215</v>
       </c>
-      <c r="E33" s="26" t="s">
+      <c r="E37" s="17" t="s">
         <v>236</v>
       </c>
-      <c r="F33" s="26" t="s">
+      <c r="F37" s="17" t="s">
         <v>236</v>
       </c>
-      <c r="G33" s="26" t="s">
+      <c r="G37" s="17" t="s">
         <v>236</v>
       </c>
-      <c r="H33" s="11"/>
-      <c r="I33" s="11"/>
-      <c r="J33" s="11"/>
-      <c r="K33" s="11"/>
-      <c r="L33" s="11"/>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A34" s="27" t="s">
+      <c r="H37" s="5"/>
+      <c r="I37" s="5"/>
+      <c r="J37" s="5"/>
+      <c r="K37" s="5"/>
+      <c r="L37" s="5"/>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A38" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="B34" s="11" t="s">
+      <c r="B38" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="C34" s="25" t="s">
+      <c r="C38" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="D34" s="29" t="s">
+      <c r="D38" s="20" t="s">
         <v>216</v>
       </c>
-      <c r="E34" s="26" t="s">
+      <c r="E38" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="F34" s="26" t="s">
+      <c r="F38" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="G34" s="26" t="s">
+      <c r="G38" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="H34" s="11"/>
-      <c r="I34" s="11"/>
-      <c r="J34" s="11"/>
-      <c r="K34" s="11"/>
-      <c r="L34" s="11"/>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A35" s="27" t="s">
+      <c r="H38" s="5"/>
+      <c r="I38" s="5"/>
+      <c r="J38" s="5"/>
+      <c r="K38" s="5"/>
+      <c r="L38" s="5"/>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A39" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="B35" s="11" t="s">
+      <c r="B39" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="C35" s="25" t="s">
+      <c r="C39" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="D35" s="29" t="s">
+      <c r="D39" s="20" t="s">
         <v>217</v>
       </c>
-      <c r="E35" s="26" t="s">
+      <c r="E39" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="F35" s="26" t="s">
+      <c r="F39" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="G35" s="26" t="s">
+      <c r="G39" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="H35" s="11"/>
-      <c r="I35" s="11"/>
-      <c r="J35" s="11"/>
-      <c r="K35" s="11"/>
-      <c r="L35" s="11"/>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A36" s="27" t="s">
+      <c r="H39" s="5"/>
+      <c r="I39" s="5"/>
+      <c r="J39" s="5"/>
+      <c r="K39" s="5"/>
+      <c r="L39" s="5"/>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A40" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="B36" s="11" t="s">
+      <c r="B40" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="C36" s="25" t="s">
+      <c r="C40" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="D36" s="29" t="s">
+      <c r="D40" s="20" t="s">
         <v>218</v>
       </c>
-      <c r="E36" s="26" t="s">
+      <c r="E40" s="17" t="s">
         <v>273</v>
       </c>
-      <c r="F36" s="26" t="s">
+      <c r="F40" s="17" t="s">
         <v>273</v>
       </c>
-      <c r="G36" s="26" t="s">
+      <c r="G40" s="17" t="s">
         <v>273</v>
       </c>
-      <c r="H36" s="26"/>
-      <c r="I36" s="11"/>
-      <c r="J36" s="11"/>
-      <c r="K36" s="11"/>
-      <c r="L36" s="11"/>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A37" s="24" t="s">
+      <c r="H40" s="17"/>
+      <c r="I40" s="5"/>
+      <c r="J40" s="5"/>
+      <c r="K40" s="5"/>
+      <c r="L40" s="5"/>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A41" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="B37" s="11" t="s">
+      <c r="B41" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="C37" s="25" t="s">
+      <c r="C41" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="D37" s="29" t="s">
+      <c r="D41" s="20" t="s">
         <v>221</v>
       </c>
-      <c r="E37" s="26" t="s">
+      <c r="E41" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="F37" s="26" t="s">
+      <c r="F41" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="G37" s="26" t="s">
+      <c r="G41" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="H37" s="11"/>
-      <c r="I37" s="11"/>
-      <c r="J37" s="11"/>
-      <c r="K37" s="11"/>
-      <c r="L37" s="11"/>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A38" s="24" t="s">
+      <c r="H41" s="5"/>
+      <c r="I41" s="5"/>
+      <c r="J41" s="5"/>
+      <c r="K41" s="5"/>
+      <c r="L41" s="5"/>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A42" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="B38" s="11" t="s">
+      <c r="B42" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="C38" s="25" t="s">
+      <c r="C42" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="D38" s="29" t="s">
+      <c r="D42" s="20" t="s">
         <v>222</v>
       </c>
-      <c r="E38" s="26" t="s">
+      <c r="E42" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="F38" s="26" t="s">
+      <c r="F42" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="G38" s="26" t="s">
+      <c r="G42" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="H38" s="11"/>
-      <c r="I38" s="11"/>
-      <c r="J38" s="11"/>
-      <c r="K38" s="11"/>
-      <c r="L38" s="11"/>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A39" s="24" t="s">
+      <c r="H42" s="5"/>
+      <c r="I42" s="5"/>
+      <c r="J42" s="5"/>
+      <c r="K42" s="5"/>
+      <c r="L42" s="5"/>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A43" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="B39" s="11" t="s">
+      <c r="B43" s="5" t="s">
         <v>295</v>
       </c>
-      <c r="C39" s="25" t="s">
+      <c r="C43" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D39" s="29" t="s">
+      <c r="D43" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="E39" s="26" t="s">
+      <c r="E43" s="17" t="s">
         <v>237</v>
       </c>
-      <c r="F39" s="11" t="s">
+      <c r="F43" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="G39" s="11" t="s">
+      <c r="G43" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="H39" s="11"/>
-      <c r="I39" s="11"/>
-      <c r="J39" s="11"/>
-      <c r="K39" s="11"/>
-      <c r="L39" s="11"/>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A40" s="24" t="s">
+      <c r="H43" s="5"/>
+      <c r="I43" s="5"/>
+      <c r="J43" s="5"/>
+      <c r="K43" s="5"/>
+      <c r="L43" s="5"/>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A44" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="B40" s="11" t="s">
+      <c r="B44" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="C40" s="25" t="s">
+      <c r="C44" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D40" s="29" t="s">
+      <c r="D44" s="20" t="s">
         <v>224</v>
       </c>
-      <c r="E40" s="26" t="s">
+      <c r="E44" s="17" t="s">
         <v>238</v>
       </c>
-      <c r="F40" s="11" t="s">
+      <c r="F44" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="G40" s="11" t="s">
+      <c r="G44" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="H40" s="11"/>
-      <c r="I40" s="11"/>
-      <c r="J40" s="11"/>
-      <c r="K40" s="11"/>
-      <c r="L40" s="11"/>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A41" s="24" t="s">
+      <c r="H44" s="5"/>
+      <c r="I44" s="5"/>
+      <c r="J44" s="5"/>
+      <c r="K44" s="5"/>
+      <c r="L44" s="5"/>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A45" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="B41" s="11" t="s">
+      <c r="B45" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="C41" s="25" t="s">
+      <c r="C45" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="D41" s="29" t="s">
+      <c r="D45" s="20" t="s">
         <v>225</v>
       </c>
-      <c r="E41" s="26" t="s">
+      <c r="E45" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="F41" s="26" t="s">
+      <c r="F45" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="G41" s="26" t="s">
+      <c r="G45" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="H41" s="11"/>
-      <c r="I41" s="11"/>
-      <c r="J41" s="11"/>
-      <c r="K41" s="11"/>
-      <c r="L41" s="11"/>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A42" s="24" t="s">
+      <c r="H45" s="5"/>
+      <c r="I45" s="5"/>
+      <c r="J45" s="5"/>
+      <c r="K45" s="5"/>
+      <c r="L45" s="5"/>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A46" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="B42" s="11" t="s">
+      <c r="B46" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="C42" s="25" t="s">
+      <c r="C46" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="D42" s="29" t="s">
+      <c r="D46" s="20" t="s">
         <v>226</v>
       </c>
-      <c r="E42" s="26" t="s">
+      <c r="E46" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="F42" s="11" t="s">
+      <c r="F46" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="G42" s="11" t="s">
+      <c r="G46" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="H42" s="11"/>
-      <c r="I42" s="11"/>
-      <c r="J42" s="11"/>
-      <c r="K42" s="11"/>
-      <c r="L42" s="11"/>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A43" s="27" t="s">
+      <c r="H46" s="5"/>
+      <c r="I46" s="5"/>
+      <c r="J46" s="5"/>
+      <c r="K46" s="5"/>
+      <c r="L46" s="5"/>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A47" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="B43" s="11" t="s">
+      <c r="B47" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C43" s="25" t="s">
+      <c r="C47" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="D43" s="29" t="s">
+      <c r="D47" s="20" t="s">
         <v>227</v>
       </c>
-      <c r="E43" s="26" t="s">
+      <c r="E47" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="F43" s="26" t="s">
+      <c r="F47" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="G43" s="26" t="s">
+      <c r="G47" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="H43" s="11"/>
-      <c r="I43" s="11"/>
-      <c r="J43" s="11"/>
-      <c r="K43" s="11"/>
-      <c r="L43" s="11"/>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A44" s="27" t="s">
+      <c r="H47" s="5"/>
+      <c r="I47" s="5"/>
+      <c r="J47" s="5"/>
+      <c r="K47" s="5"/>
+      <c r="L47" s="5"/>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A48" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="B44" s="11" t="s">
+      <c r="B48" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="C44" s="25" t="s">
+      <c r="C48" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="D44" s="29" t="s">
+      <c r="D48" s="20" t="s">
         <v>228</v>
       </c>
-      <c r="E44" s="26" t="s">
+      <c r="E48" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="F44" s="26" t="s">
+      <c r="F48" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="G44" s="26" t="s">
+      <c r="G48" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="H44" s="11"/>
-      <c r="I44" s="11"/>
-      <c r="J44" s="11"/>
-      <c r="K44" s="11"/>
-      <c r="L44" s="11"/>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A45" s="27" t="s">
+      <c r="H48" s="5"/>
+      <c r="I48" s="5"/>
+      <c r="J48" s="5"/>
+      <c r="K48" s="5"/>
+      <c r="L48" s="5"/>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A49" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="B45" s="11" t="s">
+      <c r="B49" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="C45" s="25" t="s">
+      <c r="C49" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D45" s="29" t="s">
+      <c r="D49" s="20" t="s">
         <v>229</v>
       </c>
-      <c r="E45" s="26" t="s">
+      <c r="E49" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="F45" s="26" t="s">
+      <c r="F49" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="G45" s="26" t="s">
+      <c r="G49" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="H45" s="11"/>
-      <c r="I45" s="11"/>
-      <c r="J45" s="11"/>
-      <c r="K45" s="11"/>
-      <c r="L45" s="11"/>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A46" s="27" t="s">
+      <c r="H49" s="5"/>
+      <c r="I49" s="5"/>
+      <c r="J49" s="5"/>
+      <c r="K49" s="5"/>
+      <c r="L49" s="5"/>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A50" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="B46" s="11" t="s">
+      <c r="B50" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="C46" s="25" t="s">
+      <c r="C50" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D46" s="29" t="s">
+      <c r="D50" s="20" t="s">
         <v>230</v>
       </c>
-      <c r="E46" s="26" t="s">
+      <c r="E50" s="17" t="s">
         <v>274</v>
       </c>
-      <c r="F46" s="26" t="s">
+      <c r="F50" s="17" t="s">
         <v>274</v>
       </c>
-      <c r="G46" s="26" t="s">
+      <c r="G50" s="17" t="s">
         <v>274</v>
       </c>
-      <c r="H46" s="11"/>
-      <c r="I46" s="11"/>
-      <c r="J46" s="11"/>
-      <c r="K46" s="11"/>
-      <c r="L46" s="11"/>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A47" s="24" t="s">
+      <c r="H50" s="5"/>
+      <c r="I50" s="5"/>
+      <c r="J50" s="5"/>
+      <c r="K50" s="5"/>
+      <c r="L50" s="5"/>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A51" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="B47" s="11" t="s">
+      <c r="B51" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="C47" s="25" t="s">
+      <c r="C51" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="D47" s="29" t="s">
+      <c r="D51" s="20" t="s">
         <v>231</v>
       </c>
-      <c r="E47" s="28" t="s">
+      <c r="E51" s="19" t="s">
         <v>239</v>
       </c>
-      <c r="F47" s="28" t="s">
+      <c r="F51" s="19" t="s">
         <v>239</v>
       </c>
-      <c r="G47" s="28" t="s">
+      <c r="G51" s="19" t="s">
         <v>239</v>
       </c>
-      <c r="H47" s="11"/>
-      <c r="I47" s="11"/>
-      <c r="J47" s="11"/>
-      <c r="K47" s="11"/>
-      <c r="L47" s="11"/>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A48" s="24" t="s">
+      <c r="H51" s="5"/>
+      <c r="I51" s="5"/>
+      <c r="J51" s="5"/>
+      <c r="K51" s="5"/>
+      <c r="L51" s="5"/>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A52" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="B48" s="11" t="s">
+      <c r="B52" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="C48" s="25" t="s">
+      <c r="C52" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="D48" s="29" t="s">
+      <c r="D52" s="20" t="s">
         <v>232</v>
       </c>
-      <c r="E48" s="28" t="s">
+      <c r="E52" s="19" t="s">
         <v>240</v>
       </c>
-      <c r="F48" s="28" t="s">
+      <c r="F52" s="19" t="s">
         <v>240</v>
       </c>
-      <c r="G48" s="28" t="s">
+      <c r="G52" s="19" t="s">
         <v>240</v>
       </c>
-      <c r="H48" s="11"/>
-      <c r="I48" s="11"/>
-      <c r="J48" s="11"/>
-      <c r="K48" s="11"/>
-      <c r="L48" s="11"/>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A49" s="11"/>
-      <c r="B49" s="28"/>
-      <c r="C49" s="25"/>
-      <c r="D49" s="26"/>
-      <c r="E49" s="28"/>
-      <c r="F49" s="11"/>
-      <c r="G49" s="11"/>
-      <c r="H49" s="11"/>
-      <c r="I49" s="11"/>
-      <c r="J49" s="11"/>
-      <c r="K49" s="11"/>
-      <c r="L49" s="11"/>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A50" s="11"/>
-      <c r="B50" s="28"/>
-      <c r="C50" s="25"/>
-      <c r="D50" s="26"/>
-      <c r="E50" s="28"/>
-      <c r="F50" s="11"/>
-      <c r="G50" s="11"/>
-      <c r="H50" s="11"/>
-      <c r="I50" s="11"/>
-      <c r="J50" s="11"/>
-      <c r="K50" s="11"/>
-      <c r="L50" s="11"/>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A51" s="11"/>
-      <c r="B51" s="28"/>
-      <c r="C51" s="25"/>
-      <c r="D51" s="26"/>
-      <c r="E51" s="28"/>
-      <c r="F51" s="11"/>
-      <c r="G51" s="11"/>
-      <c r="H51" s="11"/>
-      <c r="I51" s="11"/>
-      <c r="J51" s="11"/>
-      <c r="K51" s="11"/>
-      <c r="L51" s="11"/>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A52" s="11"/>
-      <c r="B52" s="28"/>
-      <c r="C52" s="25"/>
-      <c r="D52" s="26"/>
-      <c r="E52" s="28"/>
-      <c r="F52" s="11"/>
-      <c r="G52" s="11"/>
-      <c r="H52" s="11"/>
-      <c r="I52" s="11"/>
-      <c r="J52" s="11"/>
-      <c r="K52" s="11"/>
-      <c r="L52" s="11"/>
+      <c r="H52" s="5"/>
+      <c r="I52" s="5"/>
+      <c r="J52" s="5"/>
+      <c r="K52" s="5"/>
+      <c r="L52" s="5"/>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A53" s="11"/>
-      <c r="B53" s="28"/>
-      <c r="C53" s="25"/>
-      <c r="D53" s="26"/>
-      <c r="E53" s="28"/>
-      <c r="F53" s="11"/>
-      <c r="G53" s="11"/>
-      <c r="H53" s="11"/>
-      <c r="I53" s="11"/>
-      <c r="J53" s="11"/>
-      <c r="K53" s="11"/>
-      <c r="L53" s="11"/>
+      <c r="A53" s="5"/>
+      <c r="B53" s="19"/>
+      <c r="C53" s="16"/>
+      <c r="D53" s="17"/>
+      <c r="E53" s="19"/>
+      <c r="F53" s="5"/>
+      <c r="G53" s="5"/>
+      <c r="H53" s="5"/>
+      <c r="I53" s="5"/>
+      <c r="J53" s="5"/>
+      <c r="K53" s="5"/>
+      <c r="L53" s="5"/>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A54" s="11"/>
-      <c r="B54" s="28"/>
-      <c r="C54" s="25"/>
-      <c r="D54" s="26"/>
-      <c r="E54" s="28"/>
-      <c r="F54" s="11"/>
-      <c r="G54" s="11"/>
-      <c r="H54" s="11"/>
-      <c r="I54" s="11"/>
-      <c r="J54" s="11"/>
-      <c r="K54" s="11"/>
-      <c r="L54" s="11"/>
+      <c r="A54" s="5"/>
+      <c r="B54" s="19"/>
+      <c r="C54" s="16"/>
+      <c r="D54" s="17"/>
+      <c r="E54" s="19"/>
+      <c r="F54" s="5"/>
+      <c r="G54" s="5"/>
+      <c r="H54" s="5"/>
+      <c r="I54" s="5"/>
+      <c r="J54" s="5"/>
+      <c r="K54" s="5"/>
+      <c r="L54" s="5"/>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A55" s="11"/>
-      <c r="B55" s="28"/>
-      <c r="C55" s="25"/>
-      <c r="D55" s="26"/>
-      <c r="E55" s="28"/>
-      <c r="F55" s="11"/>
-      <c r="G55" s="11"/>
-      <c r="H55" s="11"/>
-      <c r="I55" s="11"/>
-      <c r="J55" s="11"/>
-      <c r="K55" s="11"/>
-      <c r="L55" s="11"/>
+      <c r="A55" s="5"/>
+      <c r="B55" s="19"/>
+      <c r="C55" s="16"/>
+      <c r="D55" s="17"/>
+      <c r="E55" s="19"/>
+      <c r="F55" s="5"/>
+      <c r="G55" s="5"/>
+      <c r="H55" s="5"/>
+      <c r="I55" s="5"/>
+      <c r="J55" s="5"/>
+      <c r="K55" s="5"/>
+      <c r="L55" s="5"/>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A56" s="11"/>
-      <c r="B56" s="28"/>
-      <c r="C56" s="25"/>
-      <c r="D56" s="26"/>
-      <c r="E56" s="28"/>
-      <c r="F56" s="11"/>
-      <c r="G56" s="11"/>
-      <c r="H56" s="11"/>
-      <c r="I56" s="11"/>
-      <c r="J56" s="11"/>
-      <c r="K56" s="11"/>
-      <c r="L56" s="11"/>
+      <c r="A56" s="5"/>
+      <c r="B56" s="19"/>
+      <c r="C56" s="16"/>
+      <c r="D56" s="17"/>
+      <c r="E56" s="19"/>
+      <c r="F56" s="5"/>
+      <c r="G56" s="5"/>
+      <c r="H56" s="5"/>
+      <c r="I56" s="5"/>
+      <c r="J56" s="5"/>
+      <c r="K56" s="5"/>
+      <c r="L56" s="5"/>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A57" s="11"/>
-      <c r="B57" s="28"/>
-      <c r="C57" s="25"/>
-      <c r="D57" s="26"/>
-      <c r="E57" s="28"/>
-      <c r="F57" s="11"/>
-      <c r="G57" s="11"/>
-      <c r="H57" s="11"/>
-      <c r="I57" s="11"/>
-      <c r="J57" s="11"/>
-      <c r="K57" s="11"/>
-      <c r="L57" s="11"/>
+      <c r="A57" s="5"/>
+      <c r="B57" s="19"/>
+      <c r="C57" s="16"/>
+      <c r="D57" s="17"/>
+      <c r="E57" s="19"/>
+      <c r="F57" s="5"/>
+      <c r="G57" s="5"/>
+      <c r="H57" s="5"/>
+      <c r="I57" s="5"/>
+      <c r="J57" s="5"/>
+      <c r="K57" s="5"/>
+      <c r="L57" s="5"/>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A58" s="11"/>
-      <c r="B58" s="28"/>
-      <c r="C58" s="25"/>
-      <c r="D58" s="26"/>
-      <c r="E58" s="28"/>
-      <c r="F58" s="11"/>
-      <c r="G58" s="11"/>
-      <c r="H58" s="11"/>
-      <c r="I58" s="11"/>
-      <c r="J58" s="11"/>
-      <c r="K58" s="11"/>
-      <c r="L58" s="11"/>
+      <c r="A58" s="5"/>
+      <c r="B58" s="19"/>
+      <c r="C58" s="16"/>
+      <c r="D58" s="17"/>
+      <c r="E58" s="19"/>
+      <c r="F58" s="5"/>
+      <c r="G58" s="5"/>
+      <c r="H58" s="5"/>
+      <c r="I58" s="5"/>
+      <c r="J58" s="5"/>
+      <c r="K58" s="5"/>
+      <c r="L58" s="5"/>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A59" s="11"/>
-      <c r="B59" s="28"/>
-      <c r="C59" s="25"/>
-      <c r="D59" s="26"/>
-      <c r="E59" s="28"/>
-      <c r="F59" s="11"/>
-      <c r="G59" s="11"/>
-      <c r="H59" s="11"/>
-      <c r="I59" s="11"/>
-      <c r="J59" s="11"/>
-      <c r="K59" s="11"/>
-      <c r="L59" s="11"/>
+      <c r="A59" s="5"/>
+      <c r="B59" s="19"/>
+      <c r="C59" s="16"/>
+      <c r="D59" s="17"/>
+      <c r="E59" s="19"/>
+      <c r="F59" s="5"/>
+      <c r="G59" s="5"/>
+      <c r="H59" s="5"/>
+      <c r="I59" s="5"/>
+      <c r="J59" s="5"/>
+      <c r="K59" s="5"/>
+      <c r="L59" s="5"/>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A60" s="11"/>
-      <c r="B60" s="28"/>
-      <c r="C60" s="25"/>
-      <c r="D60" s="26"/>
-      <c r="E60" s="28"/>
-      <c r="F60" s="11"/>
-      <c r="G60" s="11"/>
-      <c r="H60" s="11"/>
-      <c r="I60" s="11"/>
-      <c r="J60" s="11"/>
-      <c r="K60" s="11"/>
-      <c r="L60" s="11"/>
+      <c r="A60" s="5"/>
+      <c r="B60" s="19"/>
+      <c r="C60" s="16"/>
+      <c r="D60" s="17"/>
+      <c r="E60" s="19"/>
+      <c r="F60" s="5"/>
+      <c r="G60" s="5"/>
+      <c r="H60" s="5"/>
+      <c r="I60" s="5"/>
+      <c r="J60" s="5"/>
+      <c r="K60" s="5"/>
+      <c r="L60" s="5"/>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A61" s="11"/>
-      <c r="B61" s="28"/>
-      <c r="C61" s="25"/>
-      <c r="D61" s="26"/>
-      <c r="E61" s="28"/>
-      <c r="F61" s="11"/>
-      <c r="G61" s="11"/>
-      <c r="H61" s="11"/>
-      <c r="I61" s="11"/>
-      <c r="J61" s="11"/>
-      <c r="K61" s="11"/>
-      <c r="L61" s="11"/>
+      <c r="A61" s="5"/>
+      <c r="B61" s="19"/>
+      <c r="C61" s="16"/>
+      <c r="D61" s="17"/>
+      <c r="E61" s="19"/>
+      <c r="F61" s="5"/>
+      <c r="G61" s="5"/>
+      <c r="H61" s="5"/>
+      <c r="I61" s="5"/>
+      <c r="J61" s="5"/>
+      <c r="K61" s="5"/>
+      <c r="L61" s="5"/>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A62" s="11"/>
-      <c r="B62" s="28"/>
-      <c r="C62" s="25"/>
-      <c r="D62" s="26"/>
-      <c r="E62" s="28"/>
-      <c r="F62" s="11"/>
-      <c r="G62" s="11"/>
-      <c r="H62" s="11"/>
-      <c r="I62" s="11"/>
-      <c r="J62" s="11"/>
-      <c r="K62" s="11"/>
-      <c r="L62" s="11"/>
+      <c r="A62" s="5"/>
+      <c r="B62" s="19"/>
+      <c r="C62" s="16"/>
+      <c r="D62" s="17"/>
+      <c r="E62" s="19"/>
+      <c r="F62" s="5"/>
+      <c r="G62" s="5"/>
+      <c r="H62" s="5"/>
+      <c r="I62" s="5"/>
+      <c r="J62" s="5"/>
+      <c r="K62" s="5"/>
+      <c r="L62" s="5"/>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A63" s="11"/>
-      <c r="B63" s="28"/>
-      <c r="C63" s="25"/>
-      <c r="D63" s="26"/>
-      <c r="E63" s="28"/>
-      <c r="F63" s="11"/>
-      <c r="G63" s="11"/>
-      <c r="H63" s="11"/>
-      <c r="I63" s="11"/>
-      <c r="J63" s="11"/>
-      <c r="K63" s="11"/>
-      <c r="L63" s="11"/>
+      <c r="A63" s="5"/>
+      <c r="B63" s="19"/>
+      <c r="C63" s="16"/>
+      <c r="D63" s="17"/>
+      <c r="E63" s="19"/>
+      <c r="F63" s="5"/>
+      <c r="G63" s="5"/>
+      <c r="H63" s="5"/>
+      <c r="I63" s="5"/>
+      <c r="J63" s="5"/>
+      <c r="K63" s="5"/>
+      <c r="L63" s="5"/>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A64" s="11"/>
-      <c r="B64" s="28"/>
-      <c r="C64" s="25"/>
-      <c r="D64" s="26"/>
-      <c r="E64" s="28"/>
-      <c r="F64" s="11"/>
-      <c r="G64" s="11"/>
-      <c r="H64" s="11"/>
-      <c r="I64" s="11"/>
-      <c r="J64" s="11"/>
-      <c r="K64" s="11"/>
-      <c r="L64" s="11"/>
+      <c r="A64" s="5"/>
+      <c r="B64" s="19"/>
+      <c r="C64" s="16"/>
+      <c r="D64" s="17"/>
+      <c r="E64" s="19"/>
+      <c r="F64" s="5"/>
+      <c r="G64" s="5"/>
+      <c r="H64" s="5"/>
+      <c r="I64" s="5"/>
+      <c r="J64" s="5"/>
+      <c r="K64" s="5"/>
+      <c r="L64" s="5"/>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A65" s="11"/>
-      <c r="B65" s="28"/>
-      <c r="C65" s="25"/>
-      <c r="D65" s="26"/>
-      <c r="E65" s="28"/>
-      <c r="F65" s="11"/>
-      <c r="G65" s="11"/>
-      <c r="H65" s="11"/>
-      <c r="I65" s="11"/>
-      <c r="J65" s="11"/>
-      <c r="K65" s="11"/>
-      <c r="L65" s="11"/>
+      <c r="A65" s="5"/>
+      <c r="B65" s="19"/>
+      <c r="C65" s="16"/>
+      <c r="D65" s="17"/>
+      <c r="E65" s="19"/>
+      <c r="F65" s="5"/>
+      <c r="G65" s="5"/>
+      <c r="H65" s="5"/>
+      <c r="I65" s="5"/>
+      <c r="J65" s="5"/>
+      <c r="K65" s="5"/>
+      <c r="L65" s="5"/>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A66" s="11"/>
-      <c r="B66" s="28"/>
-      <c r="C66" s="25"/>
-      <c r="D66" s="26"/>
-      <c r="E66" s="28"/>
-      <c r="F66" s="11"/>
-      <c r="G66" s="11"/>
-      <c r="H66" s="11"/>
-      <c r="I66" s="11"/>
-      <c r="J66" s="11"/>
-      <c r="K66" s="11"/>
-      <c r="L66" s="11"/>
+      <c r="A66" s="5"/>
+      <c r="B66" s="19"/>
+      <c r="C66" s="16"/>
+      <c r="D66" s="17"/>
+      <c r="E66" s="19"/>
+      <c r="F66" s="5"/>
+      <c r="G66" s="5"/>
+      <c r="H66" s="5"/>
+      <c r="I66" s="5"/>
+      <c r="J66" s="5"/>
+      <c r="K66" s="5"/>
+      <c r="L66" s="5"/>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A67" s="11"/>
-      <c r="B67" s="28"/>
-      <c r="C67" s="25"/>
-      <c r="D67" s="26"/>
-      <c r="E67" s="28"/>
-      <c r="F67" s="11"/>
-      <c r="G67" s="11"/>
-      <c r="H67" s="11"/>
-      <c r="I67" s="11"/>
-      <c r="J67" s="11"/>
-      <c r="K67" s="11"/>
-      <c r="L67" s="11"/>
+      <c r="A67" s="5"/>
+      <c r="B67" s="19"/>
+      <c r="C67" s="16"/>
+      <c r="D67" s="17"/>
+      <c r="E67" s="19"/>
+      <c r="F67" s="5"/>
+      <c r="G67" s="5"/>
+      <c r="H67" s="5"/>
+      <c r="I67" s="5"/>
+      <c r="J67" s="5"/>
+      <c r="K67" s="5"/>
+      <c r="L67" s="5"/>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A68" s="11"/>
-      <c r="B68" s="28"/>
-      <c r="C68" s="25"/>
-      <c r="D68" s="26"/>
-      <c r="E68" s="28"/>
-      <c r="F68" s="11"/>
-      <c r="G68" s="11"/>
-      <c r="H68" s="11"/>
-      <c r="I68" s="11"/>
-      <c r="J68" s="11"/>
-      <c r="K68" s="11"/>
-      <c r="L68" s="11"/>
+      <c r="A68" s="5"/>
+      <c r="B68" s="19"/>
+      <c r="C68" s="16"/>
+      <c r="D68" s="17"/>
+      <c r="E68" s="19"/>
+      <c r="F68" s="5"/>
+      <c r="G68" s="5"/>
+      <c r="H68" s="5"/>
+      <c r="I68" s="5"/>
+      <c r="J68" s="5"/>
+      <c r="K68" s="5"/>
+      <c r="L68" s="5"/>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A69" s="11"/>
-      <c r="B69" s="28"/>
-      <c r="C69" s="25"/>
-      <c r="D69" s="26"/>
-      <c r="E69" s="28"/>
-      <c r="F69" s="11"/>
-      <c r="G69" s="11"/>
-      <c r="H69" s="11"/>
-      <c r="I69" s="11"/>
-      <c r="J69" s="11"/>
-      <c r="K69" s="11"/>
-      <c r="L69" s="11"/>
+      <c r="A69" s="5"/>
+      <c r="B69" s="19"/>
+      <c r="C69" s="16"/>
+      <c r="D69" s="17"/>
+      <c r="E69" s="19"/>
+      <c r="F69" s="5"/>
+      <c r="G69" s="5"/>
+      <c r="H69" s="5"/>
+      <c r="I69" s="5"/>
+      <c r="J69" s="5"/>
+      <c r="K69" s="5"/>
+      <c r="L69" s="5"/>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A70" s="11"/>
-      <c r="B70" s="28"/>
-      <c r="C70" s="25"/>
-      <c r="D70" s="26"/>
-      <c r="E70" s="28"/>
-      <c r="F70" s="11"/>
-      <c r="G70" s="11"/>
-      <c r="H70" s="11"/>
-      <c r="I70" s="11"/>
-      <c r="J70" s="11"/>
-      <c r="K70" s="11"/>
-      <c r="L70" s="11"/>
+      <c r="A70" s="5"/>
+      <c r="B70" s="19"/>
+      <c r="C70" s="16"/>
+      <c r="D70" s="17"/>
+      <c r="E70" s="19"/>
+      <c r="F70" s="5"/>
+      <c r="G70" s="5"/>
+      <c r="H70" s="5"/>
+      <c r="I70" s="5"/>
+      <c r="J70" s="5"/>
+      <c r="K70" s="5"/>
+      <c r="L70" s="5"/>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A71" s="11"/>
-      <c r="B71" s="28"/>
-      <c r="C71" s="25"/>
-      <c r="D71" s="26"/>
-      <c r="E71" s="28"/>
-      <c r="F71" s="11"/>
-      <c r="G71" s="11"/>
-      <c r="H71" s="11"/>
-      <c r="I71" s="11"/>
-      <c r="J71" s="11"/>
-      <c r="K71" s="11"/>
-      <c r="L71" s="11"/>
+      <c r="A71" s="5"/>
+      <c r="B71" s="19"/>
+      <c r="C71" s="16"/>
+      <c r="D71" s="17"/>
+      <c r="E71" s="19"/>
+      <c r="F71" s="5"/>
+      <c r="G71" s="5"/>
+      <c r="H71" s="5"/>
+      <c r="I71" s="5"/>
+      <c r="J71" s="5"/>
+      <c r="K71" s="5"/>
+      <c r="L71" s="5"/>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A72" s="11"/>
-      <c r="B72" s="28"/>
-      <c r="C72" s="25"/>
-      <c r="D72" s="26"/>
-      <c r="E72" s="28"/>
-      <c r="F72" s="11"/>
-      <c r="G72" s="11"/>
-      <c r="H72" s="11"/>
-      <c r="I72" s="11"/>
-      <c r="J72" s="11"/>
-      <c r="K72" s="11"/>
-      <c r="L72" s="11"/>
+      <c r="A72" s="5"/>
+      <c r="B72" s="19"/>
+      <c r="C72" s="16"/>
+      <c r="D72" s="17"/>
+      <c r="E72" s="19"/>
+      <c r="F72" s="5"/>
+      <c r="G72" s="5"/>
+      <c r="H72" s="5"/>
+      <c r="I72" s="5"/>
+      <c r="J72" s="5"/>
+      <c r="K72" s="5"/>
+      <c r="L72" s="5"/>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A73" s="11"/>
-      <c r="B73" s="28"/>
-      <c r="C73" s="25"/>
-      <c r="D73" s="26"/>
-      <c r="E73" s="28"/>
-      <c r="F73" s="11"/>
-      <c r="G73" s="11"/>
-      <c r="H73" s="11"/>
-      <c r="I73" s="11"/>
-      <c r="J73" s="11"/>
-      <c r="K73" s="11"/>
-      <c r="L73" s="11"/>
+      <c r="A73" s="5"/>
+      <c r="B73" s="19"/>
+      <c r="C73" s="16"/>
+      <c r="D73" s="17"/>
+      <c r="E73" s="19"/>
+      <c r="F73" s="5"/>
+      <c r="G73" s="5"/>
+      <c r="H73" s="5"/>
+      <c r="I73" s="5"/>
+      <c r="J73" s="5"/>
+      <c r="K73" s="5"/>
+      <c r="L73" s="5"/>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A74" s="11"/>
-      <c r="B74" s="28"/>
-      <c r="C74" s="25"/>
-      <c r="D74" s="26"/>
-      <c r="E74" s="28"/>
-      <c r="F74" s="11"/>
-      <c r="G74" s="11"/>
-      <c r="H74" s="11"/>
-      <c r="I74" s="11"/>
-      <c r="J74" s="11"/>
-      <c r="K74" s="11"/>
-      <c r="L74" s="11"/>
+      <c r="A74" s="5"/>
+      <c r="B74" s="19"/>
+      <c r="C74" s="16"/>
+      <c r="D74" s="17"/>
+      <c r="E74" s="19"/>
+      <c r="F74" s="5"/>
+      <c r="G74" s="5"/>
+      <c r="H74" s="5"/>
+      <c r="I74" s="5"/>
+      <c r="J74" s="5"/>
+      <c r="K74" s="5"/>
+      <c r="L74" s="5"/>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A75" s="11"/>
-      <c r="B75" s="28"/>
-      <c r="C75" s="25"/>
-      <c r="D75" s="26"/>
-      <c r="E75" s="28"/>
-      <c r="F75" s="11"/>
-      <c r="G75" s="11"/>
-      <c r="H75" s="11"/>
-      <c r="I75" s="11"/>
-      <c r="J75" s="11"/>
-      <c r="K75" s="11"/>
-      <c r="L75" s="11"/>
+      <c r="A75" s="5"/>
+      <c r="B75" s="19"/>
+      <c r="C75" s="16"/>
+      <c r="D75" s="17"/>
+      <c r="E75" s="19"/>
+      <c r="F75" s="5"/>
+      <c r="G75" s="5"/>
+      <c r="H75" s="5"/>
+      <c r="I75" s="5"/>
+      <c r="J75" s="5"/>
+      <c r="K75" s="5"/>
+      <c r="L75" s="5"/>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A76" s="11"/>
-      <c r="B76" s="28"/>
-      <c r="C76" s="25"/>
-      <c r="D76" s="26"/>
-      <c r="E76" s="28"/>
-      <c r="F76" s="11"/>
-      <c r="G76" s="11"/>
-      <c r="H76" s="11"/>
-      <c r="I76" s="11"/>
-      <c r="J76" s="11"/>
-      <c r="K76" s="11"/>
-      <c r="L76" s="11"/>
+      <c r="A76" s="5"/>
+      <c r="B76" s="19"/>
+      <c r="C76" s="16"/>
+      <c r="D76" s="17"/>
+      <c r="E76" s="19"/>
+      <c r="F76" s="5"/>
+      <c r="G76" s="5"/>
+      <c r="H76" s="5"/>
+      <c r="I76" s="5"/>
+      <c r="J76" s="5"/>
+      <c r="K76" s="5"/>
+      <c r="L76" s="5"/>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A77" s="11"/>
-      <c r="B77" s="28"/>
-      <c r="C77" s="25"/>
-      <c r="D77" s="26"/>
-      <c r="E77" s="28"/>
-      <c r="F77" s="11"/>
-      <c r="G77" s="11"/>
-      <c r="H77" s="11"/>
-      <c r="I77" s="11"/>
-      <c r="J77" s="11"/>
-      <c r="K77" s="11"/>
-      <c r="L77" s="11"/>
+      <c r="A77" s="5"/>
+      <c r="B77" s="19"/>
+      <c r="C77" s="16"/>
+      <c r="D77" s="17"/>
+      <c r="E77" s="19"/>
+      <c r="F77" s="5"/>
+      <c r="G77" s="5"/>
+      <c r="H77" s="5"/>
+      <c r="I77" s="5"/>
+      <c r="J77" s="5"/>
+      <c r="K77" s="5"/>
+      <c r="L77" s="5"/>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A78" s="11"/>
-      <c r="B78" s="28"/>
-      <c r="C78" s="25"/>
-      <c r="D78" s="26"/>
-      <c r="E78" s="28"/>
-      <c r="F78" s="11"/>
-      <c r="G78" s="11"/>
-      <c r="H78" s="11"/>
-      <c r="I78" s="11"/>
-      <c r="J78" s="11"/>
-      <c r="K78" s="11"/>
-      <c r="L78" s="11"/>
+      <c r="A78" s="5"/>
+      <c r="B78" s="19"/>
+      <c r="C78" s="16"/>
+      <c r="D78" s="17"/>
+      <c r="E78" s="19"/>
+      <c r="F78" s="5"/>
+      <c r="G78" s="5"/>
+      <c r="H78" s="5"/>
+      <c r="I78" s="5"/>
+      <c r="J78" s="5"/>
+      <c r="K78" s="5"/>
+      <c r="L78" s="5"/>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A79" s="11"/>
-      <c r="B79" s="28"/>
-      <c r="C79" s="25"/>
-      <c r="D79" s="26"/>
-      <c r="E79" s="28"/>
-      <c r="F79" s="11"/>
-      <c r="G79" s="11"/>
-      <c r="H79" s="11"/>
-      <c r="I79" s="11"/>
-      <c r="J79" s="11"/>
-      <c r="K79" s="11"/>
-      <c r="L79" s="11"/>
+      <c r="A79" s="5"/>
+      <c r="B79" s="19"/>
+      <c r="C79" s="16"/>
+      <c r="D79" s="17"/>
+      <c r="E79" s="19"/>
+      <c r="F79" s="5"/>
+      <c r="G79" s="5"/>
+      <c r="H79" s="5"/>
+      <c r="I79" s="5"/>
+      <c r="J79" s="5"/>
+      <c r="K79" s="5"/>
+      <c r="L79" s="5"/>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A80" s="11"/>
-      <c r="B80" s="28"/>
-      <c r="C80" s="25"/>
-      <c r="D80" s="26"/>
-      <c r="E80" s="28"/>
-      <c r="F80" s="11"/>
-      <c r="G80" s="11"/>
-      <c r="H80" s="11"/>
-      <c r="I80" s="11"/>
-      <c r="J80" s="11"/>
-      <c r="K80" s="11"/>
-      <c r="L80" s="11"/>
+      <c r="A80" s="5"/>
+      <c r="B80" s="19"/>
+      <c r="C80" s="16"/>
+      <c r="D80" s="17"/>
+      <c r="E80" s="19"/>
+      <c r="F80" s="5"/>
+      <c r="G80" s="5"/>
+      <c r="H80" s="5"/>
+      <c r="I80" s="5"/>
+      <c r="J80" s="5"/>
+      <c r="K80" s="5"/>
+      <c r="L80" s="5"/>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A81" s="11"/>
-      <c r="B81" s="28"/>
-      <c r="C81" s="25"/>
-      <c r="D81" s="26"/>
-      <c r="E81" s="28"/>
-      <c r="F81" s="11"/>
-      <c r="G81" s="11"/>
-      <c r="H81" s="11"/>
-      <c r="I81" s="11"/>
-      <c r="J81" s="11"/>
-      <c r="K81" s="11"/>
-      <c r="L81" s="11"/>
+      <c r="A81" s="5"/>
+      <c r="B81" s="19"/>
+      <c r="C81" s="16"/>
+      <c r="D81" s="17"/>
+      <c r="E81" s="19"/>
+      <c r="F81" s="5"/>
+      <c r="G81" s="5"/>
+      <c r="H81" s="5"/>
+      <c r="I81" s="5"/>
+      <c r="J81" s="5"/>
+      <c r="K81" s="5"/>
+      <c r="L81" s="5"/>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A82" s="11"/>
-      <c r="B82" s="28"/>
-      <c r="C82" s="25"/>
-      <c r="D82" s="26"/>
-      <c r="E82" s="28"/>
-      <c r="F82" s="11"/>
-      <c r="G82" s="11"/>
-      <c r="H82" s="11"/>
-      <c r="I82" s="11"/>
-      <c r="J82" s="11"/>
-      <c r="K82" s="11"/>
-      <c r="L82" s="11"/>
+      <c r="A82" s="5"/>
+      <c r="B82" s="19"/>
+      <c r="C82" s="16"/>
+      <c r="D82" s="17"/>
+      <c r="E82" s="19"/>
+      <c r="F82" s="5"/>
+      <c r="G82" s="5"/>
+      <c r="H82" s="5"/>
+      <c r="I82" s="5"/>
+      <c r="J82" s="5"/>
+      <c r="K82" s="5"/>
+      <c r="L82" s="5"/>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A83" s="11"/>
-      <c r="B83" s="28"/>
-      <c r="C83" s="25"/>
-      <c r="D83" s="26"/>
-      <c r="E83" s="28"/>
-      <c r="F83" s="11"/>
-      <c r="G83" s="11"/>
-      <c r="H83" s="11"/>
-      <c r="I83" s="11"/>
-      <c r="J83" s="11"/>
-      <c r="K83" s="11"/>
-      <c r="L83" s="11"/>
+      <c r="A83" s="5"/>
+      <c r="B83" s="19"/>
+      <c r="C83" s="16"/>
+      <c r="D83" s="17"/>
+      <c r="E83" s="19"/>
+      <c r="F83" s="5"/>
+      <c r="G83" s="5"/>
+      <c r="H83" s="5"/>
+      <c r="I83" s="5"/>
+      <c r="J83" s="5"/>
+      <c r="K83" s="5"/>
+      <c r="L83" s="5"/>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A84" s="11"/>
-      <c r="B84" s="28"/>
-      <c r="C84" s="25"/>
-      <c r="D84" s="26"/>
-      <c r="E84" s="28"/>
-      <c r="F84" s="11"/>
-      <c r="G84" s="11"/>
-      <c r="H84" s="11"/>
-      <c r="I84" s="11"/>
-      <c r="J84" s="11"/>
-      <c r="K84" s="11"/>
-      <c r="L84" s="11"/>
+      <c r="A84" s="5"/>
+      <c r="B84" s="19"/>
+      <c r="C84" s="16"/>
+      <c r="D84" s="17"/>
+      <c r="E84" s="19"/>
+      <c r="F84" s="5"/>
+      <c r="G84" s="5"/>
+      <c r="H84" s="5"/>
+      <c r="I84" s="5"/>
+      <c r="J84" s="5"/>
+      <c r="K84" s="5"/>
+      <c r="L84" s="5"/>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A85" s="11"/>
-      <c r="B85" s="28"/>
-      <c r="C85" s="25"/>
-      <c r="D85" s="26"/>
-      <c r="E85" s="28"/>
-      <c r="F85" s="11"/>
-      <c r="G85" s="11"/>
-      <c r="H85" s="11"/>
-      <c r="I85" s="11"/>
-      <c r="J85" s="11"/>
-      <c r="K85" s="11"/>
-      <c r="L85" s="11"/>
+      <c r="A85" s="5"/>
+      <c r="B85" s="19"/>
+      <c r="C85" s="16"/>
+      <c r="D85" s="17"/>
+      <c r="E85" s="19"/>
+      <c r="F85" s="5"/>
+      <c r="G85" s="5"/>
+      <c r="H85" s="5"/>
+      <c r="I85" s="5"/>
+      <c r="J85" s="5"/>
+      <c r="K85" s="5"/>
+      <c r="L85" s="5"/>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A86" s="11"/>
-      <c r="B86" s="28"/>
-      <c r="C86" s="25"/>
-      <c r="D86" s="26"/>
-      <c r="E86" s="28"/>
-      <c r="F86" s="11"/>
-      <c r="G86" s="11"/>
-      <c r="H86" s="11"/>
-      <c r="I86" s="11"/>
-      <c r="J86" s="11"/>
-      <c r="K86" s="11"/>
-      <c r="L86" s="11"/>
+      <c r="A86" s="5"/>
+      <c r="B86" s="19"/>
+      <c r="C86" s="16"/>
+      <c r="D86" s="17"/>
+      <c r="E86" s="19"/>
+      <c r="F86" s="5"/>
+      <c r="G86" s="5"/>
+      <c r="H86" s="5"/>
+      <c r="I86" s="5"/>
+      <c r="J86" s="5"/>
+      <c r="K86" s="5"/>
+      <c r="L86" s="5"/>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A87" s="11"/>
-      <c r="B87" s="28"/>
-      <c r="C87" s="25"/>
-      <c r="D87" s="26"/>
-      <c r="E87" s="28"/>
-      <c r="F87" s="11"/>
-      <c r="G87" s="11"/>
-      <c r="H87" s="11"/>
-      <c r="I87" s="11"/>
-      <c r="J87" s="11"/>
-      <c r="K87" s="11"/>
-      <c r="L87" s="11"/>
+      <c r="A87" s="5"/>
+      <c r="B87" s="19"/>
+      <c r="C87" s="16"/>
+      <c r="D87" s="17"/>
+      <c r="E87" s="19"/>
+      <c r="F87" s="5"/>
+      <c r="G87" s="5"/>
+      <c r="H87" s="5"/>
+      <c r="I87" s="5"/>
+      <c r="J87" s="5"/>
+      <c r="K87" s="5"/>
+      <c r="L87" s="5"/>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A88" s="11"/>
-      <c r="B88" s="28"/>
-      <c r="C88" s="25"/>
-      <c r="D88" s="26"/>
-      <c r="E88" s="28"/>
-      <c r="F88" s="11"/>
-      <c r="G88" s="11"/>
-      <c r="H88" s="11"/>
-      <c r="I88" s="11"/>
-      <c r="J88" s="11"/>
-      <c r="K88" s="11"/>
-      <c r="L88" s="11"/>
+      <c r="A88" s="5"/>
+      <c r="B88" s="19"/>
+      <c r="C88" s="16"/>
+      <c r="D88" s="17"/>
+      <c r="E88" s="19"/>
+      <c r="F88" s="5"/>
+      <c r="G88" s="5"/>
+      <c r="H88" s="5"/>
+      <c r="I88" s="5"/>
+      <c r="J88" s="5"/>
+      <c r="K88" s="5"/>
+      <c r="L88" s="5"/>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A89" s="11"/>
-      <c r="B89" s="28"/>
-      <c r="C89" s="25"/>
-      <c r="D89" s="26"/>
-      <c r="E89" s="28"/>
-      <c r="F89" s="11"/>
-      <c r="G89" s="11"/>
-      <c r="H89" s="11"/>
-      <c r="I89" s="11"/>
-      <c r="J89" s="11"/>
-      <c r="K89" s="11"/>
-      <c r="L89" s="11"/>
+      <c r="A89" s="5"/>
+      <c r="B89" s="19"/>
+      <c r="C89" s="16"/>
+      <c r="D89" s="17"/>
+      <c r="E89" s="19"/>
+      <c r="F89" s="5"/>
+      <c r="G89" s="5"/>
+      <c r="H89" s="5"/>
+      <c r="I89" s="5"/>
+      <c r="J89" s="5"/>
+      <c r="K89" s="5"/>
+      <c r="L89" s="5"/>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A90" s="11"/>
-      <c r="B90" s="28"/>
-      <c r="C90" s="25"/>
-      <c r="D90" s="26"/>
-      <c r="E90" s="28"/>
-      <c r="F90" s="11"/>
-      <c r="G90" s="11"/>
-      <c r="H90" s="11"/>
-      <c r="I90" s="11"/>
-      <c r="J90" s="11"/>
-      <c r="K90" s="11"/>
-      <c r="L90" s="11"/>
+      <c r="A90" s="5"/>
+      <c r="B90" s="19"/>
+      <c r="C90" s="16"/>
+      <c r="D90" s="17"/>
+      <c r="E90" s="19"/>
+      <c r="F90" s="5"/>
+      <c r="G90" s="5"/>
+      <c r="H90" s="5"/>
+      <c r="I90" s="5"/>
+      <c r="J90" s="5"/>
+      <c r="K90" s="5"/>
+      <c r="L90" s="5"/>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A91" s="11"/>
-      <c r="B91" s="28"/>
-      <c r="C91" s="25"/>
-      <c r="D91" s="26"/>
-      <c r="E91" s="28"/>
-      <c r="F91" s="11"/>
-      <c r="G91" s="11"/>
-      <c r="H91" s="11"/>
-      <c r="I91" s="11"/>
-      <c r="J91" s="11"/>
-      <c r="K91" s="11"/>
-      <c r="L91" s="11"/>
+      <c r="A91" s="5"/>
+      <c r="B91" s="19"/>
+      <c r="C91" s="16"/>
+      <c r="D91" s="17"/>
+      <c r="E91" s="19"/>
+      <c r="F91" s="5"/>
+      <c r="G91" s="5"/>
+      <c r="H91" s="5"/>
+      <c r="I91" s="5"/>
+      <c r="J91" s="5"/>
+      <c r="K91" s="5"/>
+      <c r="L91" s="5"/>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A92" s="11"/>
-      <c r="B92" s="28"/>
-      <c r="C92" s="25"/>
-      <c r="D92" s="26"/>
-      <c r="E92" s="28"/>
-      <c r="F92" s="11"/>
-      <c r="G92" s="11"/>
-      <c r="H92" s="11"/>
-      <c r="I92" s="11"/>
-      <c r="J92" s="11"/>
-      <c r="K92" s="11"/>
-      <c r="L92" s="11"/>
+      <c r="A92" s="5"/>
+      <c r="B92" s="19"/>
+      <c r="C92" s="16"/>
+      <c r="D92" s="17"/>
+      <c r="E92" s="19"/>
+      <c r="F92" s="5"/>
+      <c r="G92" s="5"/>
+      <c r="H92" s="5"/>
+      <c r="I92" s="5"/>
+      <c r="J92" s="5"/>
+      <c r="K92" s="5"/>
+      <c r="L92" s="5"/>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A93" s="11"/>
-      <c r="B93" s="28"/>
-      <c r="C93" s="25"/>
-      <c r="D93" s="26"/>
-      <c r="E93" s="28"/>
-      <c r="F93" s="11"/>
-      <c r="G93" s="11"/>
-      <c r="H93" s="11"/>
-      <c r="I93" s="11"/>
-      <c r="J93" s="11"/>
-      <c r="K93" s="11"/>
-      <c r="L93" s="11"/>
+      <c r="A93" s="5"/>
+      <c r="B93" s="19"/>
+      <c r="C93" s="16"/>
+      <c r="D93" s="17"/>
+      <c r="E93" s="19"/>
+      <c r="F93" s="5"/>
+      <c r="G93" s="5"/>
+      <c r="H93" s="5"/>
+      <c r="I93" s="5"/>
+      <c r="J93" s="5"/>
+      <c r="K93" s="5"/>
+      <c r="L93" s="5"/>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A94" s="11"/>
-      <c r="B94" s="28"/>
-      <c r="C94" s="25"/>
-      <c r="D94" s="26"/>
-      <c r="E94" s="28"/>
-      <c r="F94" s="11"/>
-      <c r="G94" s="11"/>
-      <c r="H94" s="11"/>
-      <c r="I94" s="11"/>
-      <c r="J94" s="11"/>
-      <c r="K94" s="11"/>
-      <c r="L94" s="11"/>
+      <c r="A94" s="5"/>
+      <c r="B94" s="19"/>
+      <c r="C94" s="16"/>
+      <c r="D94" s="17"/>
+      <c r="E94" s="19"/>
+      <c r="F94" s="5"/>
+      <c r="G94" s="5"/>
+      <c r="H94" s="5"/>
+      <c r="I94" s="5"/>
+      <c r="J94" s="5"/>
+      <c r="K94" s="5"/>
+      <c r="L94" s="5"/>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A95" s="11"/>
-      <c r="B95" s="28"/>
-      <c r="C95" s="25"/>
-      <c r="D95" s="26"/>
-      <c r="E95" s="28"/>
-      <c r="F95" s="11"/>
-      <c r="G95" s="11"/>
-      <c r="H95" s="11"/>
-      <c r="I95" s="11"/>
-      <c r="J95" s="11"/>
-      <c r="K95" s="11"/>
-      <c r="L95" s="11"/>
+      <c r="A95" s="5"/>
+      <c r="B95" s="19"/>
+      <c r="C95" s="16"/>
+      <c r="D95" s="17"/>
+      <c r="E95" s="19"/>
+      <c r="F95" s="5"/>
+      <c r="G95" s="5"/>
+      <c r="H95" s="5"/>
+      <c r="I95" s="5"/>
+      <c r="J95" s="5"/>
+      <c r="K95" s="5"/>
+      <c r="L95" s="5"/>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A96" s="11"/>
-      <c r="B96" s="28"/>
-      <c r="C96" s="25"/>
-      <c r="D96" s="26"/>
-      <c r="E96" s="28"/>
-      <c r="F96" s="11"/>
-      <c r="G96" s="11"/>
-      <c r="H96" s="11"/>
-      <c r="I96" s="11"/>
-      <c r="J96" s="11"/>
-      <c r="K96" s="11"/>
-      <c r="L96" s="11"/>
+      <c r="A96" s="5"/>
+      <c r="B96" s="19"/>
+      <c r="C96" s="16"/>
+      <c r="D96" s="17"/>
+      <c r="E96" s="19"/>
+      <c r="F96" s="5"/>
+      <c r="G96" s="5"/>
+      <c r="H96" s="5"/>
+      <c r="I96" s="5"/>
+      <c r="J96" s="5"/>
+      <c r="K96" s="5"/>
+      <c r="L96" s="5"/>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A97" s="11"/>
-      <c r="B97" s="28"/>
-      <c r="C97" s="25"/>
-      <c r="D97" s="26"/>
-      <c r="E97" s="28"/>
-      <c r="F97" s="11"/>
-      <c r="G97" s="11"/>
-      <c r="H97" s="11"/>
-      <c r="I97" s="11"/>
-      <c r="J97" s="11"/>
-      <c r="K97" s="11"/>
-      <c r="L97" s="11"/>
+      <c r="A97" s="5"/>
+      <c r="B97" s="19"/>
+      <c r="C97" s="16"/>
+      <c r="D97" s="17"/>
+      <c r="E97" s="19"/>
+      <c r="F97" s="5"/>
+      <c r="G97" s="5"/>
+      <c r="H97" s="5"/>
+      <c r="I97" s="5"/>
+      <c r="J97" s="5"/>
+      <c r="K97" s="5"/>
+      <c r="L97" s="5"/>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A98" s="11"/>
-      <c r="B98" s="28"/>
-      <c r="C98" s="25"/>
-      <c r="D98" s="26"/>
-      <c r="E98" s="28"/>
-      <c r="F98" s="11"/>
-      <c r="G98" s="11"/>
-      <c r="H98" s="11"/>
-      <c r="I98" s="11"/>
-      <c r="J98" s="11"/>
-      <c r="K98" s="11"/>
-      <c r="L98" s="11"/>
+      <c r="A98" s="5"/>
+      <c r="B98" s="19"/>
+      <c r="C98" s="16"/>
+      <c r="D98" s="17"/>
+      <c r="E98" s="19"/>
+      <c r="F98" s="5"/>
+      <c r="G98" s="5"/>
+      <c r="H98" s="5"/>
+      <c r="I98" s="5"/>
+      <c r="J98" s="5"/>
+      <c r="K98" s="5"/>
+      <c r="L98" s="5"/>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A99" s="11"/>
-      <c r="B99" s="28"/>
-      <c r="C99" s="25"/>
-      <c r="D99" s="26"/>
-      <c r="E99" s="28"/>
-      <c r="F99" s="11"/>
-      <c r="G99" s="11"/>
-      <c r="H99" s="11"/>
-      <c r="I99" s="11"/>
-      <c r="J99" s="11"/>
-      <c r="K99" s="11"/>
-      <c r="L99" s="11"/>
+      <c r="A99" s="5"/>
+      <c r="B99" s="19"/>
+      <c r="C99" s="16"/>
+      <c r="D99" s="17"/>
+      <c r="E99" s="19"/>
+      <c r="F99" s="5"/>
+      <c r="G99" s="5"/>
+      <c r="H99" s="5"/>
+      <c r="I99" s="5"/>
+      <c r="J99" s="5"/>
+      <c r="K99" s="5"/>
+      <c r="L99" s="5"/>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A100" s="11"/>
-      <c r="B100" s="28"/>
-      <c r="C100" s="25"/>
-      <c r="D100" s="26"/>
-      <c r="E100" s="28"/>
-      <c r="F100" s="11"/>
-      <c r="G100" s="11"/>
-      <c r="H100" s="11"/>
-      <c r="I100" s="11"/>
-      <c r="J100" s="11"/>
-      <c r="K100" s="11"/>
-      <c r="L100" s="11"/>
+      <c r="A100" s="5"/>
+      <c r="B100" s="19"/>
+      <c r="C100" s="16"/>
+      <c r="D100" s="17"/>
+      <c r="E100" s="19"/>
+      <c r="F100" s="5"/>
+      <c r="G100" s="5"/>
+      <c r="H100" s="5"/>
+      <c r="I100" s="5"/>
+      <c r="J100" s="5"/>
+      <c r="K100" s="5"/>
+      <c r="L100" s="5"/>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A101" s="11"/>
-      <c r="B101" s="28"/>
-      <c r="C101" s="25"/>
-      <c r="D101" s="26"/>
-      <c r="E101" s="28"/>
-      <c r="F101" s="11"/>
-      <c r="G101" s="11"/>
-      <c r="H101" s="11"/>
-      <c r="I101" s="11"/>
-      <c r="J101" s="11"/>
-      <c r="K101" s="11"/>
-      <c r="L101" s="11"/>
+      <c r="A101" s="5"/>
+      <c r="B101" s="19"/>
+      <c r="C101" s="16"/>
+      <c r="D101" s="17"/>
+      <c r="E101" s="19"/>
+      <c r="F101" s="5"/>
+      <c r="G101" s="5"/>
+      <c r="H101" s="5"/>
+      <c r="I101" s="5"/>
+      <c r="J101" s="5"/>
+      <c r="K101" s="5"/>
+      <c r="L101" s="5"/>
+    </row>
+    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A102" s="5"/>
+      <c r="B102" s="19"/>
+      <c r="C102" s="16"/>
+      <c r="D102" s="17"/>
+      <c r="E102" s="19"/>
+      <c r="F102" s="5"/>
+      <c r="G102" s="5"/>
+      <c r="H102" s="5"/>
+      <c r="I102" s="5"/>
+      <c r="J102" s="5"/>
+      <c r="K102" s="5"/>
+      <c r="L102" s="5"/>
+    </row>
+    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A103" s="5"/>
+      <c r="B103" s="19"/>
+      <c r="C103" s="16"/>
+      <c r="D103" s="17"/>
+      <c r="E103" s="19"/>
+      <c r="F103" s="5"/>
+      <c r="G103" s="5"/>
+      <c r="H103" s="5"/>
+      <c r="I103" s="5"/>
+      <c r="J103" s="5"/>
+      <c r="K103" s="5"/>
+      <c r="L103" s="5"/>
+    </row>
+    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A104" s="5"/>
+      <c r="B104" s="19"/>
+      <c r="C104" s="16"/>
+      <c r="D104" s="17"/>
+      <c r="E104" s="19"/>
+      <c r="F104" s="5"/>
+      <c r="G104" s="5"/>
+      <c r="H104" s="5"/>
+      <c r="I104" s="5"/>
+      <c r="J104" s="5"/>
+      <c r="K104" s="5"/>
+      <c r="L104" s="5"/>
+    </row>
+    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A105" s="5"/>
+      <c r="B105" s="19"/>
+      <c r="C105" s="16"/>
+      <c r="D105" s="17"/>
+      <c r="E105" s="19"/>
+      <c r="F105" s="5"/>
+      <c r="G105" s="5"/>
+      <c r="H105" s="5"/>
+      <c r="I105" s="5"/>
+      <c r="J105" s="5"/>
+      <c r="K105" s="5"/>
+      <c r="L105" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="B2:B7">
     <cfRule type="duplicateValues" dxfId="3" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B48">
+  <conditionalFormatting sqref="B2:B52">
     <cfRule type="duplicateValues" dxfId="2" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B8:B48">
+  <conditionalFormatting sqref="B8:B52">
     <cfRule type="duplicateValues" dxfId="1" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D48">
+  <conditionalFormatting sqref="D2:D52">
     <cfRule type="duplicateValues" dxfId="0" priority="7"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4232,7 +4347,7 @@
   <cols>
     <col min="1" max="1" width="29.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="48" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="34.109375" customWidth="1"/>
     <col min="5" max="5" width="43.109375" customWidth="1"/>
     <col min="6" max="6" width="39" customWidth="1"/>
@@ -4241,890 +4356,890 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="3" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="B3" s="10"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="11"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="30" t="s">
+      <c r="D5" s="21" t="s">
         <v>249</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="F5" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="G5" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="27" t="s">
+      <c r="A6" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="30" t="s">
+      <c r="D6" s="21" t="s">
         <v>250</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="G6" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="27" t="s">
+      <c r="A7" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="30" t="s">
+      <c r="D7" s="21" t="s">
         <v>251</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="F7" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="G7" s="11" t="s">
+      <c r="G7" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="H7" s="11"/>
-      <c r="I7" s="11"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="30" t="s">
+      <c r="D8" s="21" t="s">
         <v>252</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="G8" s="11" t="s">
+      <c r="G8" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="27" t="s">
+      <c r="A9" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="D9" s="30" t="s">
+      <c r="D9" s="21" t="s">
         <v>253</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="E9" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="F9" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="G9" s="11" t="s">
+      <c r="G9" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="27" t="s">
+      <c r="A10" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D10" s="30" t="s">
+      <c r="D10" s="21" t="s">
         <v>254</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="E10" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="F10" s="11" t="s">
+      <c r="F10" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="G10" s="11" t="s">
+      <c r="G10" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="27" t="s">
+      <c r="A11" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="D11" s="30" t="s">
+      <c r="D11" s="21" t="s">
         <v>255</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="E11" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="F11" s="11" t="s">
+      <c r="F11" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="G11" s="11" t="s">
+      <c r="G11" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="27" t="s">
+      <c r="A12" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="D12" s="30" t="s">
+      <c r="D12" s="21" t="s">
         <v>256</v>
       </c>
-      <c r="E12" s="11" t="s">
+      <c r="E12" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="F12" s="11" t="s">
+      <c r="F12" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="G12" s="11" t="s">
+      <c r="G12" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="27" t="s">
+      <c r="A13" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D13" s="30" t="s">
+      <c r="D13" s="21" t="s">
         <v>257</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="E13" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="F13" s="11" t="s">
+      <c r="F13" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="G13" s="11" t="s">
+      <c r="G13" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="27" t="s">
+      <c r="A14" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="D14" s="30" t="s">
+      <c r="D14" s="21" t="s">
         <v>258</v>
       </c>
-      <c r="E14" s="11" t="s">
+      <c r="E14" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="F14" s="11" t="s">
+      <c r="F14" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="G14" s="11" t="s">
+      <c r="G14" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="27" t="s">
+      <c r="A15" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B15" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="D15" s="30" t="s">
+      <c r="D15" s="21" t="s">
         <v>256</v>
       </c>
-      <c r="E15" s="11" t="s">
+      <c r="E15" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="F15" s="11" t="s">
+      <c r="F15" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="G15" s="11" t="s">
+      <c r="G15" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" s="27" t="s">
+      <c r="A16" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="B16" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D16" s="30" t="s">
+      <c r="D16" s="21" t="s">
         <v>259</v>
       </c>
-      <c r="E16" s="11" t="s">
+      <c r="E16" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="F16" s="11" t="s">
+      <c r="F16" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="G16" s="11" t="s">
+      <c r="G16" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" s="24" t="s">
+      <c r="A17" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="B17" s="10"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="27" t="s">
+      <c r="A18" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="C18" s="12"/>
-      <c r="D18" s="30" t="s">
+      <c r="C18" s="6"/>
+      <c r="D18" s="21" t="s">
         <v>260</v>
       </c>
-      <c r="E18" s="11" t="s">
+      <c r="E18" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="F18" s="11" t="s">
+      <c r="F18" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="G18" s="11" t="s">
+      <c r="G18" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="H18" s="11"/>
-      <c r="I18" s="11"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="24" t="s">
+      <c r="A19" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="B19" s="10"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="11"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="27" t="s">
+      <c r="A20" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="B20" s="10" t="s">
+      <c r="B20" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="C20" s="12"/>
-      <c r="D20" s="30" t="s">
+      <c r="C20" s="6"/>
+      <c r="D20" s="21" t="s">
         <v>283</v>
       </c>
-      <c r="E20" s="11" t="s">
+      <c r="E20" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="F20" s="11" t="s">
+      <c r="F20" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="G20" s="11" t="s">
+      <c r="G20" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="H20" s="11"/>
-      <c r="I20" s="11"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="27" t="s">
+      <c r="A21" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="B21" s="10" t="s">
+      <c r="B21" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="C21" s="12"/>
-      <c r="D21" s="30" t="s">
+      <c r="C21" s="6"/>
+      <c r="D21" s="21" t="s">
         <v>284</v>
       </c>
-      <c r="E21" s="11" t="s">
+      <c r="E21" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="F21" s="11" t="s">
+      <c r="F21" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="G21" s="11" t="s">
+      <c r="G21" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="H21" s="11"/>
-      <c r="I21" s="11"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="27" t="s">
+      <c r="A22" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="B22" s="10" t="s">
+      <c r="B22" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="C22" s="12"/>
-      <c r="D22" s="30" t="s">
+      <c r="C22" s="6"/>
+      <c r="D22" s="21" t="s">
         <v>285</v>
       </c>
-      <c r="E22" s="11" t="s">
+      <c r="E22" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="F22" s="11" t="s">
+      <c r="F22" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="G22" s="11" t="s">
+      <c r="G22" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="H22" s="11"/>
-      <c r="I22" s="11"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="27" t="s">
+      <c r="A23" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="B23" s="10" t="s">
+      <c r="B23" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="D23" s="30" t="s">
+      <c r="D23" s="21" t="s">
         <v>286</v>
       </c>
-      <c r="E23" s="11" t="s">
+      <c r="E23" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="F23" s="11" t="s">
+      <c r="F23" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="G23" s="11" t="s">
+      <c r="G23" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="H23" s="11"/>
-      <c r="I23" s="11"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="27" t="s">
+      <c r="A24" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="B24" s="10" t="s">
+      <c r="B24" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="C24" s="12" t="s">
+      <c r="C24" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D24" s="30" t="s">
+      <c r="D24" s="21" t="s">
         <v>287</v>
       </c>
-      <c r="E24" s="11" t="s">
+      <c r="E24" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="F24" s="11" t="s">
+      <c r="F24" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="G24" s="11" t="s">
+      <c r="G24" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="H24" s="11"/>
-      <c r="I24" s="11"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="27" t="s">
+      <c r="A25" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="B25" s="10" t="s">
+      <c r="B25" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="C25" s="12" t="s">
+      <c r="C25" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D25" s="30" t="s">
+      <c r="D25" s="21" t="s">
         <v>288</v>
       </c>
-      <c r="E25" s="11" t="s">
+      <c r="E25" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="F25" s="11" t="s">
+      <c r="F25" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="G25" s="11" t="s">
+      <c r="G25" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="H25" s="11"/>
-      <c r="I25" s="11"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A26" s="27" t="s">
+      <c r="A26" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="B26" s="10" t="s">
+      <c r="B26" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="C26" s="12" t="s">
+      <c r="C26" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="D26" s="30" t="s">
+      <c r="D26" s="21" t="s">
         <v>289</v>
       </c>
-      <c r="E26" s="11" t="s">
+      <c r="E26" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="F26" s="11" t="s">
+      <c r="F26" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="G26" s="11" t="s">
+      <c r="G26" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="H26" s="11"/>
-      <c r="I26" s="11"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A27" s="24" t="s">
+      <c r="A27" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="B27" s="10" t="s">
+      <c r="B27" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="C27" s="12"/>
-      <c r="D27" s="30" t="s">
+      <c r="C27" s="6"/>
+      <c r="D27" s="21" t="s">
         <v>269</v>
       </c>
-      <c r="E27" s="11" t="s">
+      <c r="E27" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="F27" s="11" t="s">
+      <c r="F27" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="G27" s="11" t="s">
+      <c r="G27" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="H27" s="11"/>
-      <c r="I27" s="11"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" s="24" t="s">
+      <c r="A28" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="B28" s="10" t="s">
+      <c r="B28" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="C28" s="12" t="s">
+      <c r="C28" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="D28" s="30" t="s">
+      <c r="D28" s="21" t="s">
         <v>270</v>
       </c>
-      <c r="E28" s="11" t="s">
+      <c r="E28" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="F28" s="11" t="s">
+      <c r="F28" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="G28" s="11" t="s">
+      <c r="G28" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="H28" s="11"/>
-      <c r="I28" s="11"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A29" s="24" t="s">
+      <c r="A29" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="B29" s="10" t="s">
+      <c r="B29" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="C29" s="12" t="s">
+      <c r="C29" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="D29" s="30" t="s">
+      <c r="D29" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="E29" s="11" t="s">
+      <c r="E29" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="F29" s="11" t="s">
+      <c r="F29" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="G29" s="11" t="s">
+      <c r="G29" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="H29" s="11"/>
-      <c r="I29" s="11"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="5"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A30" s="24" t="s">
+      <c r="A30" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="B30" s="10" t="s">
+      <c r="B30" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="C30" s="12" t="s">
+      <c r="C30" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="D30" s="30" t="s">
+      <c r="D30" s="21" t="s">
         <v>271</v>
       </c>
-      <c r="E30" s="11" t="s">
+      <c r="E30" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="F30" s="11" t="s">
+      <c r="F30" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="G30" s="11" t="s">
+      <c r="G30" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="H30" s="11"/>
-      <c r="I30" s="11"/>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A31" s="27" t="s">
+      <c r="A31" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="B31" s="10" t="s">
+      <c r="B31" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="C31" s="12" t="s">
+      <c r="C31" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="D31" s="30" t="s">
+      <c r="D31" s="21" t="s">
         <v>261</v>
       </c>
-      <c r="E31" s="11" t="s">
+      <c r="E31" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="F31" s="11" t="s">
+      <c r="F31" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="G31" s="11" t="s">
+      <c r="G31" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="H31" s="11"/>
-      <c r="I31" s="11"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A32" s="27" t="s">
+      <c r="A32" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="B32" s="10" t="s">
+      <c r="B32" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="C32" s="12" t="s">
+      <c r="C32" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="D32" s="30" t="s">
+      <c r="D32" s="21" t="s">
         <v>262</v>
       </c>
-      <c r="E32" s="11" t="s">
+      <c r="E32" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="F32" s="11" t="s">
+      <c r="F32" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="G32" s="11" t="s">
+      <c r="G32" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="H32" s="11"/>
-      <c r="I32" s="11"/>
+      <c r="H32" s="5"/>
+      <c r="I32" s="5"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A33" s="27" t="s">
+      <c r="A33" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="B33" s="10" t="s">
+      <c r="B33" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="C33" s="12" t="s">
+      <c r="C33" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="D33" s="30" t="s">
+      <c r="D33" s="21" t="s">
         <v>263</v>
       </c>
-      <c r="E33" s="11" t="s">
+      <c r="E33" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="F33" s="11" t="s">
+      <c r="F33" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="G33" s="11" t="s">
+      <c r="G33" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="H33" s="11"/>
-      <c r="I33" s="11"/>
+      <c r="H33" s="5"/>
+      <c r="I33" s="5"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A34" s="27" t="s">
+      <c r="A34" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="B34" s="10" t="s">
+      <c r="B34" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="C34" s="12" t="s">
+      <c r="C34" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D34" s="30" t="s">
+      <c r="D34" s="21" t="s">
         <v>264</v>
       </c>
-      <c r="E34" s="11" t="s">
+      <c r="E34" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="F34" s="11" t="s">
+      <c r="F34" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="G34" s="11" t="s">
+      <c r="G34" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="H34" s="11"/>
-      <c r="I34" s="11"/>
+      <c r="H34" s="5"/>
+      <c r="I34" s="5"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A35" s="27" t="s">
+      <c r="A35" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="B35" s="10" t="s">
+      <c r="B35" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="C35" s="12" t="s">
+      <c r="C35" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="D35" s="30" t="s">
+      <c r="D35" s="21" t="s">
         <v>265</v>
       </c>
-      <c r="E35" s="11" t="s">
+      <c r="E35" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="F35" s="11" t="s">
+      <c r="F35" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="G35" s="11" t="s">
+      <c r="G35" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="H35" s="11"/>
-      <c r="I35" s="11"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="5"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A36" s="27" t="s">
+      <c r="A36" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="B36" s="10" t="s">
+      <c r="B36" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="C36" s="12" t="s">
+      <c r="C36" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="D36" s="30" t="s">
+      <c r="D36" s="21" t="s">
         <v>266</v>
       </c>
-      <c r="E36" s="11" t="s">
+      <c r="E36" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="F36" s="11" t="s">
+      <c r="F36" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="G36" s="11" t="s">
+      <c r="G36" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="H36" s="11"/>
-      <c r="I36" s="11"/>
+      <c r="H36" s="5"/>
+      <c r="I36" s="5"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A37" s="27" t="s">
+      <c r="A37" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="B37" s="10" t="s">
+      <c r="B37" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="C37" s="12" t="s">
+      <c r="C37" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="D37" s="30" t="s">
+      <c r="D37" s="21" t="s">
         <v>267</v>
       </c>
-      <c r="E37" s="11" t="s">
+      <c r="E37" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="F37" s="11" t="s">
+      <c r="F37" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="G37" s="11" t="s">
+      <c r="G37" s="5" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A38" s="27" t="s">
+      <c r="A38" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="B38" s="10" t="s">
+      <c r="B38" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="C38" s="12" t="s">
+      <c r="C38" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D38" s="30" t="s">
+      <c r="D38" s="21" t="s">
         <v>268</v>
       </c>
-      <c r="E38" s="11" t="s">
+      <c r="E38" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="F38" s="11" t="s">
+      <c r="F38" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="G38" s="11" t="s">
+      <c r="G38" s="5" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B39" s="13"/>
+      <c r="B39" s="7"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B40" s="13"/>
+      <c r="B40" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/eBus_Functions/Post_Processing/Root_Cause_Analysis_Work/info/eBus_Model_Info.xlsx
+++ b/eBus_Functions/Post_Processing/Root_Cause_Analysis_Work/info/eBus_Model_Info.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\TempData\Github\eBus_Tool\eBus_Functions\Post_Processing\Root_Cause_Analysis_Work\info\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30AB63F5-F1F8-493A-A929-D72CCA2CA18E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8325D24C-37B5-484E-BEFB-0DD5230CE88D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Block_Diagram" sheetId="1" r:id="rId1"/>
     <sheet name="Signal_Evaluation" sheetId="2" r:id="rId2"/>
     <sheet name="Specifications" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="324">
   <si>
     <t>Driver</t>
   </si>
@@ -374,9 +375,6 @@
     <t>rpm</t>
   </si>
   <si>
-    <t>Wheel Rolling Resistance</t>
-  </si>
-  <si>
     <t>Wheel Radius</t>
   </si>
   <si>
@@ -996,6 +994,12 @@
   </si>
   <si>
     <t>logout.MinAvlEmotTrq_Cval_CPC/2</t>
+  </si>
+  <si>
+    <t>Wheel Rolling Resistance Coefficient</t>
+  </si>
+  <si>
+    <t>m</t>
   </si>
 </sst>
 </file>
@@ -1159,7 +1163,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1212,17 +1216,16 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1626,469 +1629,421 @@
       </c>
     </row>
     <row r="29" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G29" s="23"/>
       <c r="H29" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="I29" s="23" t="s">
+      <c r="I29" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="30" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G30" s="23"/>
       <c r="H30" s="24"/>
-      <c r="I30" s="23" t="s">
+      <c r="I30" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="31" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G31" s="23"/>
       <c r="H31" s="24"/>
-      <c r="I31" s="23" t="s">
+      <c r="I31" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="32" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G32" s="23" t="s">
+      <c r="G32" t="s">
         <v>21</v>
       </c>
       <c r="H32" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="I32" s="23" t="s">
+      <c r="I32" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="33" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G33" s="23" t="s">
+      <c r="G33" t="s">
         <v>29</v>
       </c>
       <c r="H33" s="25"/>
-      <c r="I33" s="23" t="s">
+      <c r="I33" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="34" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G34" s="23" t="s">
+      <c r="G34" t="s">
         <v>7</v>
       </c>
       <c r="H34" s="25"/>
-      <c r="I34" s="23"/>
     </row>
     <row r="35" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G35" s="23" t="s">
+      <c r="G35" t="s">
         <v>13</v>
       </c>
       <c r="H35" s="25"/>
-      <c r="I35" s="23"/>
     </row>
     <row r="36" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G36" s="23" t="s">
-        <v>179</v>
+      <c r="G36" t="s">
+        <v>178</v>
       </c>
       <c r="H36" s="25"/>
-      <c r="I36" s="23"/>
     </row>
     <row r="37" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G37" s="23" t="s">
+      <c r="G37" t="s">
         <v>14</v>
       </c>
       <c r="H37" s="25"/>
-      <c r="I37" s="23"/>
     </row>
     <row r="38" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G38" s="23" t="s">
+      <c r="G38" t="s">
         <v>11</v>
       </c>
       <c r="H38" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="I38" s="23" t="s">
+      <c r="I38" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="39" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G39" t="s">
+        <v>12</v>
+      </c>
+      <c r="H39" s="24"/>
+      <c r="I39" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="39" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G39" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="H39" s="24"/>
-      <c r="I39" s="23" t="s">
-        <v>172</v>
-      </c>
-    </row>
     <row r="40" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G40" s="23"/>
       <c r="H40" s="24"/>
-      <c r="I40" s="23" t="s">
+      <c r="I40" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="41" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="H41" s="24"/>
+      <c r="I41" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="41" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G41" s="23"/>
-      <c r="H41" s="24"/>
-      <c r="I41" s="23" t="s">
-        <v>308</v>
-      </c>
-    </row>
     <row r="42" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G42" s="23"/>
       <c r="H42" s="24"/>
-      <c r="I42" s="23" t="s">
+      <c r="I42" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="43" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="H43" s="24"/>
+      <c r="I43" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="43" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G43" s="23"/>
-      <c r="H43" s="24"/>
-      <c r="I43" s="23" t="s">
-        <v>312</v>
-      </c>
-    </row>
     <row r="44" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G44" s="23"/>
       <c r="H44" s="24"/>
-      <c r="I44" s="23"/>
     </row>
     <row r="45" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G45" s="23"/>
       <c r="H45" s="24"/>
-      <c r="I45" s="23"/>
     </row>
     <row r="46" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G46" s="23"/>
       <c r="H46" s="24"/>
-      <c r="I46" s="23"/>
     </row>
     <row r="47" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G47" s="23"/>
       <c r="H47" s="24"/>
-      <c r="I47" s="23"/>
     </row>
     <row r="48" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G48" s="23"/>
       <c r="H48" s="22"/>
-      <c r="I48" s="23"/>
     </row>
     <row r="49" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G49" s="23" t="s">
-        <v>171</v>
+      <c r="G49" t="s">
+        <v>170</v>
       </c>
       <c r="H49" s="25" t="s">
         <v>106</v>
       </c>
-      <c r="I49" s="23" t="s">
+      <c r="I49" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="50" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G50" s="23" t="s">
+      <c r="G50" t="s">
+        <v>171</v>
+      </c>
+      <c r="H50" s="25"/>
+      <c r="I50" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="51" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G51" t="s">
+        <v>308</v>
+      </c>
+      <c r="H51" s="25"/>
+      <c r="I51" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="52" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G52" t="s">
+        <v>309</v>
+      </c>
+      <c r="H52" s="25"/>
+      <c r="I52" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="53" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="H53" s="25"/>
+      <c r="I53" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="54" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="H54" s="25"/>
+      <c r="I54" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="55" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="H55" s="25"/>
+      <c r="I55" t="s">
         <v>172</v>
       </c>
-      <c r="H50" s="25"/>
-      <c r="I50" s="23" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="51" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G51" s="23" t="s">
-        <v>309</v>
-      </c>
-      <c r="H51" s="25"/>
-      <c r="I51" s="23" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="52" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G52" s="23" t="s">
-        <v>310</v>
-      </c>
-      <c r="H52" s="25"/>
-      <c r="I52" s="23" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="53" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G53" s="23"/>
-      <c r="H53" s="25"/>
-      <c r="I53" s="23" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="54" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G54" s="23"/>
-      <c r="H54" s="25"/>
-      <c r="I54" s="23" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="55" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G55" s="23"/>
-      <c r="H55" s="25"/>
-      <c r="I55" s="23" t="s">
+    </row>
+    <row r="56" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="H56" s="25"/>
+      <c r="I56" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="56" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G56" s="23"/>
-      <c r="H56" s="25"/>
-      <c r="I56" s="23" t="s">
+    <row r="57" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="H57" s="25"/>
+      <c r="I57" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="58" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="H58" s="25"/>
+      <c r="I58" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="57" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G57" s="23"/>
-      <c r="H57" s="25"/>
-      <c r="I57" s="23" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="58" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G58" s="23"/>
-      <c r="H58" s="25"/>
-      <c r="I58" s="23" t="s">
+    <row r="59" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="H59" s="25"/>
+      <c r="I59" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="60" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="H60" s="25"/>
+      <c r="I60" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="59" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G59" s="23"/>
-      <c r="H59" s="25"/>
-      <c r="I59" s="23" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="60" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G60" s="23"/>
-      <c r="H60" s="25"/>
-      <c r="I60" s="23" t="s">
-        <v>176</v>
-      </c>
-    </row>
     <row r="61" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G61" s="23" t="s">
+      <c r="G61" t="s">
         <v>36</v>
       </c>
       <c r="H61" s="24" t="s">
         <v>107</v>
       </c>
-      <c r="I61" s="23" t="s">
+      <c r="I61" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="62" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G62" t="s">
+        <v>38</v>
+      </c>
+      <c r="H62" s="24"/>
+      <c r="I62" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="62" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G62" s="23" t="s">
-        <v>38</v>
-      </c>
-      <c r="H62" s="24"/>
-      <c r="I62" s="23" t="s">
+    <row r="63" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="H63" s="24"/>
+      <c r="I63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="64" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="H64" s="24"/>
+      <c r="I64" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="63" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G63" s="23"/>
-      <c r="H63" s="24"/>
-      <c r="I63" s="23" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="64" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G64" s="23"/>
-      <c r="H64" s="24"/>
-      <c r="I64" s="23" t="s">
-        <v>179</v>
-      </c>
-    </row>
     <row r="65" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G65" s="23"/>
       <c r="H65" s="24"/>
-      <c r="I65" s="23" t="s">
+      <c r="I65" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="66" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G66" s="23" t="s">
-        <v>177</v>
-      </c>
-      <c r="H66" s="26" t="s">
+      <c r="G66" t="s">
+        <v>176</v>
+      </c>
+      <c r="H66" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="I66" s="23" t="s">
+      <c r="I66" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="67" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G67" s="23" t="s">
+      <c r="G67" t="s">
         <v>12</v>
       </c>
       <c r="H67" s="25" t="s">
         <v>108</v>
       </c>
-      <c r="I67" s="23" t="s">
+      <c r="I67" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="68" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="H68" s="25"/>
+      <c r="I68" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="68" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G68" s="23"/>
-      <c r="H68" s="25"/>
-      <c r="I68" s="23" t="s">
-        <v>181</v>
-      </c>
-    </row>
     <row r="69" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G69" s="23" t="s">
+      <c r="G69" t="s">
         <v>18</v>
       </c>
       <c r="H69" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="I69" s="23" t="s">
+      <c r="I69" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="70" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G70" s="23" t="s">
-        <v>180</v>
+      <c r="G70" t="s">
+        <v>179</v>
       </c>
       <c r="H70" s="24"/>
-      <c r="I70" s="23" t="s">
+      <c r="I70" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="71" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G71" s="23"/>
       <c r="H71" s="24"/>
-      <c r="I71" s="23" t="s">
+      <c r="I71" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="72" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G72" s="23"/>
       <c r="H72" s="24"/>
-      <c r="I72" s="23" t="s">
+      <c r="I72" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="73" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G73" s="23"/>
       <c r="H73" s="24"/>
-      <c r="I73" s="23" t="s">
+      <c r="I73" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="74" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G74" s="23"/>
       <c r="H74" s="24"/>
-      <c r="I74" s="23" t="s">
+      <c r="I74" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="75" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G75" s="23"/>
       <c r="H75" s="24"/>
-      <c r="I75" s="23" t="s">
+      <c r="I75" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="76" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G76" s="23" t="s">
+      <c r="G76" t="s">
         <v>32</v>
       </c>
       <c r="H76" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="I76" s="23" t="s">
+      <c r="I76" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="77" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G77" s="23"/>
       <c r="H77" s="24"/>
-      <c r="I77" s="23" t="s">
-        <v>182</v>
+      <c r="I77" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="78" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G78" s="23"/>
       <c r="H78" s="24"/>
-      <c r="I78" s="23" t="s">
+      <c r="I78" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="79" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G79" s="23"/>
       <c r="H79" s="24"/>
-      <c r="I79" s="23" t="s">
+      <c r="I79" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="80" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G80" s="23"/>
       <c r="H80" s="24"/>
-      <c r="I80" s="23" t="s">
+      <c r="I80" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="81" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G81" s="23"/>
       <c r="H81" s="24"/>
-      <c r="I81" s="23" t="s">
+      <c r="I81" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="82" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G82" s="23" t="s">
+      <c r="G82" t="s">
         <v>32</v>
       </c>
       <c r="H82" s="25" t="s">
         <v>110</v>
       </c>
-      <c r="I82" s="23" t="s">
+      <c r="I82" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="83" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G83" s="23" t="s">
+      <c r="G83" t="s">
         <v>75</v>
       </c>
       <c r="H83" s="25"/>
-      <c r="I83" s="23" t="s">
+      <c r="I83" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="84" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G84" s="23"/>
       <c r="H84" s="25"/>
-      <c r="I84" s="23" t="s">
+      <c r="I84" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="85" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G85" s="23"/>
       <c r="H85" s="25"/>
-      <c r="I85" s="23" t="s">
+      <c r="I85" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="86" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G86" s="23"/>
       <c r="H86" s="24" t="s">
         <v>111</v>
       </c>
-      <c r="I86" s="23" t="s">
+      <c r="I86" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="87" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="H87" s="24"/>
+      <c r="I87" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="87" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G87" s="23"/>
-      <c r="H87" s="24"/>
-      <c r="I87" s="23" t="s">
+    <row r="88" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="H88" s="24"/>
+      <c r="I88" t="s">
         <v>184</v>
-      </c>
-    </row>
-    <row r="88" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G88" s="23"/>
-      <c r="H88" s="24"/>
-      <c r="I88" s="23" t="s">
-        <v>185</v>
       </c>
     </row>
   </sheetData>
@@ -2163,22 +2118,22 @@
         <v>96</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="C2" s="16" t="s">
         <v>290</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="D2" s="20" t="s">
         <v>291</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="E2" s="17" t="s">
         <v>292</v>
       </c>
-      <c r="E2" s="17" t="s">
-        <v>293</v>
-      </c>
       <c r="F2" s="17" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="G2" s="17" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
@@ -2222,7 +2177,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E4" s="17" t="s">
         <v>31</v>
@@ -2250,7 +2205,7 @@
         <v>33</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E5" s="17" t="s">
         <v>34</v>
@@ -2278,16 +2233,16 @@
         <v>1</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
@@ -2306,16 +2261,16 @@
         <v>1</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="G7" s="17" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H7" s="5"/>
       <c r="I7" s="5"/>
@@ -2328,22 +2283,22 @@
         <v>97</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C8" s="16" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F8" s="17" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H8" s="5"/>
       <c r="I8" s="5"/>
@@ -2356,22 +2311,22 @@
         <v>97</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C9" s="16" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F9" s="17" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G9" s="17" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H9" s="5"/>
       <c r="I9" s="5"/>
@@ -2384,22 +2339,22 @@
         <v>97</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C10" s="16" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G10" s="17" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
@@ -2412,22 +2367,22 @@
         <v>97</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C11" s="16" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F11" s="17" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G11" s="17" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H11" s="5"/>
       <c r="I11" s="5"/>
@@ -2440,22 +2395,22 @@
         <v>97</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C12" s="16" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F12" s="17" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G12" s="17" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
@@ -2468,22 +2423,22 @@
         <v>97</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C13" s="16" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F13" s="17" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G13" s="17" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
@@ -2496,13 +2451,13 @@
         <v>95</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C14" s="16" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="20" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E14" s="17" t="s">
         <v>37</v>
@@ -2524,13 +2479,13 @@
         <v>95</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C15" s="16" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E15" s="17" t="s">
         <v>39</v>
@@ -2558,7 +2513,7 @@
         <v>5</v>
       </c>
       <c r="D16" s="20" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E16" s="17" t="s">
         <v>41</v>
@@ -2586,7 +2541,7 @@
         <v>5</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E17" s="17" t="s">
         <v>43</v>
@@ -2608,13 +2563,13 @@
         <v>95</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C18" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D18" s="20" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E18" s="17" t="s">
         <v>45</v>
@@ -2636,13 +2591,13 @@
         <v>95</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C19" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D19" s="20" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E19" s="17" t="s">
         <v>47</v>
@@ -2664,13 +2619,13 @@
         <v>95</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C20" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D20" s="20" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E20" s="17" t="s">
         <v>48</v>
@@ -2692,13 +2647,13 @@
         <v>95</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C21" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D21" s="20" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E21" s="17" t="s">
         <v>49</v>
@@ -2720,13 +2675,13 @@
         <v>95</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C22" s="16" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="20" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E22" s="17" t="s">
         <v>51</v>
@@ -2748,13 +2703,13 @@
         <v>95</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C23" s="16" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="20" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E23" s="17" t="s">
         <v>52</v>
@@ -2776,13 +2731,13 @@
         <v>95</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C24" s="16" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="20" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E24" s="17" t="s">
         <v>54</v>
@@ -2804,13 +2759,13 @@
         <v>95</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C25" s="16" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="20" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E25" s="17" t="s">
         <v>55</v>
@@ -2832,13 +2787,13 @@
         <v>94</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C26" s="16" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="20" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E26" s="17" t="s">
         <v>56</v>
@@ -2860,13 +2815,13 @@
         <v>94</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C27" s="16" t="s">
         <v>5</v>
       </c>
       <c r="D27" s="20" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E27" s="17" t="s">
         <v>57</v>
@@ -2892,16 +2847,16 @@
       </c>
       <c r="C28" s="16"/>
       <c r="D28" s="20" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E28" s="17" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F28" s="17" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G28" s="17" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H28" s="17"/>
       <c r="I28" s="5"/>
@@ -2914,11 +2869,11 @@
         <v>94</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C29" s="16"/>
       <c r="D29" s="20" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E29" s="17" t="s">
         <v>35</v>
@@ -2946,7 +2901,7 @@
         <v>4</v>
       </c>
       <c r="D30" s="20" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E30" s="17" t="s">
         <v>58</v>
@@ -2974,16 +2929,16 @@
         <v>63</v>
       </c>
       <c r="D31" s="20" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E31" s="19" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F31" s="19" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G31" s="19" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H31" s="5"/>
       <c r="I31" s="5"/>
@@ -2996,22 +2951,22 @@
         <v>93</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C32" s="16" t="s">
         <v>63</v>
       </c>
       <c r="D32" s="20" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E32" s="19" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F32" s="19" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G32" s="19" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H32" s="5"/>
       <c r="I32" s="5"/>
@@ -3024,22 +2979,22 @@
         <v>93</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C33" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D33" s="20" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E33" s="17" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F33" s="17" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G33" s="17" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H33" s="5"/>
       <c r="I33" s="5"/>
@@ -3058,7 +3013,7 @@
         <v>59</v>
       </c>
       <c r="D34" s="20" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E34" s="17" t="s">
         <v>60</v>
@@ -3086,16 +3041,16 @@
         <v>98</v>
       </c>
       <c r="D35" s="20" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E35" s="17" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F35" s="17" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G35" s="17" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H35" s="5"/>
       <c r="I35" s="5"/>
@@ -3111,19 +3066,19 @@
         <v>22</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D36" s="20" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E36" s="17" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F36" s="17" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G36" s="17" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H36" s="5"/>
       <c r="I36" s="5"/>
@@ -3142,16 +3097,16 @@
         <v>63</v>
       </c>
       <c r="D37" s="20" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E37" s="17" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F37" s="17" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G37" s="17" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H37" s="5"/>
       <c r="I37" s="5"/>
@@ -3170,7 +3125,7 @@
         <v>63</v>
       </c>
       <c r="D38" s="20" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E38" s="17" t="s">
         <v>64</v>
@@ -3198,7 +3153,7 @@
         <v>63</v>
       </c>
       <c r="D39" s="20" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E39" s="17" t="s">
         <v>66</v>
@@ -3226,16 +3181,16 @@
         <v>63</v>
       </c>
       <c r="D40" s="20" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E40" s="17" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F40" s="17" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G40" s="17" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H40" s="17"/>
       <c r="I40" s="5"/>
@@ -3248,13 +3203,13 @@
         <v>90</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C41" s="16" t="s">
         <v>69</v>
       </c>
       <c r="D41" s="20" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E41" s="17" t="s">
         <v>70</v>
@@ -3276,13 +3231,13 @@
         <v>90</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C42" s="16" t="s">
         <v>71</v>
       </c>
       <c r="D42" s="20" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E42" s="17" t="s">
         <v>72</v>
@@ -3304,22 +3259,22 @@
         <v>90</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C43" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D43" s="20" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E43" s="17" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H43" s="5"/>
       <c r="I43" s="5"/>
@@ -3338,16 +3293,16 @@
         <v>4</v>
       </c>
       <c r="D44" s="20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E44" s="17" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H44" s="5"/>
       <c r="I44" s="5"/>
@@ -3366,7 +3321,7 @@
         <v>1</v>
       </c>
       <c r="D45" s="20" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E45" s="17" t="s">
         <v>76</v>
@@ -3394,16 +3349,16 @@
         <v>33</v>
       </c>
       <c r="D46" s="20" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E46" s="17" t="s">
         <v>78</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H46" s="5"/>
       <c r="I46" s="5"/>
@@ -3422,7 +3377,7 @@
         <v>69</v>
       </c>
       <c r="D47" s="20" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E47" s="17" t="s">
         <v>80</v>
@@ -3450,7 +3405,7 @@
         <v>69</v>
       </c>
       <c r="D48" s="20" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E48" s="17" t="s">
         <v>82</v>
@@ -3478,7 +3433,7 @@
         <v>4</v>
       </c>
       <c r="D49" s="20" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E49" s="17" t="s">
         <v>84</v>
@@ -3506,16 +3461,16 @@
         <v>4</v>
       </c>
       <c r="D50" s="20" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E50" s="17" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F50" s="17" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G50" s="17" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H50" s="5"/>
       <c r="I50" s="5"/>
@@ -3528,22 +3483,22 @@
         <v>111</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C51" s="16" t="s">
         <v>69</v>
       </c>
       <c r="D51" s="20" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E51" s="19" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F51" s="19" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G51" s="19" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H51" s="5"/>
       <c r="I51" s="5"/>
@@ -3556,22 +3511,22 @@
         <v>111</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C52" s="16" t="s">
         <v>71</v>
       </c>
       <c r="D52" s="20" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E52" s="19" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F52" s="19" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G52" s="19" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H52" s="5"/>
       <c r="I52" s="5"/>
@@ -4342,7 +4297,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E71F352-39EA-49E2-AB89-A39562B80CB1}">
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.109375" bestFit="1" customWidth="1"/>
@@ -4428,22 +4383,22 @@
         <v>95</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
@@ -4453,13 +4408,13 @@
         <v>95</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>112</v>
@@ -4484,16 +4439,16 @@
         <v>4</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H7" s="5"/>
       <c r="I7" s="5"/>
@@ -4503,22 +4458,22 @@
         <v>95</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H8" s="5"/>
       <c r="I8" s="5"/>
@@ -4528,22 +4483,22 @@
         <v>95</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>114</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H9" s="5"/>
       <c r="I9" s="5"/>
@@ -4553,22 +4508,22 @@
         <v>95</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
@@ -4578,22 +4533,22 @@
         <v>95</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>71</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H11" s="5"/>
       <c r="I11" s="5"/>
@@ -4603,22 +4558,22 @@
         <v>95</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>114</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
@@ -4628,22 +4583,22 @@
         <v>95</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
@@ -4653,22 +4608,22 @@
         <v>95</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>71</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H14" s="5"/>
       <c r="I14" s="5"/>
@@ -4678,22 +4633,22 @@
         <v>95</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>114</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
@@ -4703,22 +4658,22 @@
         <v>95</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H16" s="5"/>
       <c r="I16" s="5"/>
@@ -4741,20 +4696,20 @@
         <v>99</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="21" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
@@ -4777,20 +4732,20 @@
         <v>92</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="21" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H20" s="5"/>
       <c r="I20" s="5"/>
@@ -4800,20 +4755,20 @@
         <v>92</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>115</v>
+        <v>322</v>
       </c>
       <c r="C21" s="6"/>
       <c r="D21" s="21" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H21" s="5"/>
       <c r="I21" s="5"/>
@@ -4823,20 +4778,22 @@
         <v>92</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="C22" s="6"/>
+        <v>115</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>323</v>
+      </c>
       <c r="D22" s="21" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
@@ -4849,94 +4806,92 @@
         <v>13</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D23" s="21" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H23" s="5"/>
       <c r="I23" s="5"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="18" t="s">
-        <v>92</v>
+      <c r="A24" s="15" t="s">
+        <v>90</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>4</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="C24" s="6"/>
       <c r="D24" s="21" t="s">
-        <v>287</v>
+        <v>268</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>149</v>
+        <v>245</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>149</v>
+        <v>125</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>149</v>
+        <v>125</v>
       </c>
       <c r="H24" s="5"/>
       <c r="I24" s="5"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="18" t="s">
-        <v>92</v>
+      <c r="A25" s="15" t="s">
+        <v>90</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>288</v>
+        <v>269</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>150</v>
+        <v>126</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>150</v>
+        <v>126</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>150</v>
+        <v>126</v>
       </c>
       <c r="H25" s="5"/>
       <c r="I25" s="5"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A26" s="18" t="s">
-        <v>92</v>
+      <c r="A26" s="15" t="s">
+        <v>90</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>120</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="D26" s="21" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>151</v>
+        <v>246</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="H26" s="5"/>
       <c r="I26" s="5"/>
@@ -4946,95 +4901,97 @@
         <v>90</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="C27" s="6"/>
+        <v>121</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>1</v>
+      </c>
       <c r="D27" s="21" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>246</v>
+        <v>127</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H27" s="5"/>
       <c r="I27" s="5"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" s="15" t="s">
-        <v>90</v>
+      <c r="A28" s="18" t="s">
+        <v>91</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>1</v>
+        <v>69</v>
       </c>
       <c r="D28" s="21" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="H28" s="5"/>
       <c r="I28" s="5"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A29" s="15" t="s">
-        <v>90</v>
+      <c r="A29" s="18" t="s">
+        <v>91</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>125</v>
+        <v>69</v>
       </c>
       <c r="D29" s="21" t="s">
-        <v>279</v>
+        <v>261</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>247</v>
+        <v>137</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>248</v>
+        <v>137</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>248</v>
+        <v>137</v>
       </c>
       <c r="H29" s="5"/>
       <c r="I29" s="5"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A30" s="15" t="s">
-        <v>90</v>
+      <c r="A30" s="18" t="s">
+        <v>91</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>1</v>
       </c>
       <c r="D30" s="21" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="H30" s="5"/>
       <c r="I30" s="5"/>
@@ -5047,19 +5004,19 @@
         <v>129</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="D31" s="21" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H31" s="5"/>
       <c r="I31" s="5"/>
@@ -5069,22 +5026,22 @@
         <v>91</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>69</v>
       </c>
       <c r="D32" s="21" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H32" s="5"/>
       <c r="I32" s="5"/>
@@ -5094,22 +5051,22 @@
         <v>91</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>1</v>
+        <v>69</v>
       </c>
       <c r="D33" s="21" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H33" s="5"/>
       <c r="I33" s="5"/>
@@ -5119,131 +5076,141 @@
         <v>91</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="D34" s="21" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="H34" s="5"/>
-      <c r="I34" s="5"/>
+        <v>142</v>
+      </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="18" t="s">
         <v>91</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="D35" s="21" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="H35" s="5"/>
-      <c r="I35" s="5"/>
+        <v>143</v>
+      </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A36" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="D36" s="21" t="s">
-        <v>266</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="F36" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="G36" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="H36" s="5"/>
-      <c r="I36" s="5"/>
+      <c r="B36" s="7"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A37" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D37" s="21" t="s">
-        <v>267</v>
-      </c>
-      <c r="E37" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="F37" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="G37" s="5" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A38" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="C38" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D38" s="21" t="s">
-        <v>268</v>
-      </c>
-      <c r="E38" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="F38" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="G38" s="5" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B39" s="7"/>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B40" s="7"/>
+      <c r="B37" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6C1B83A-C39F-40B8-8309-44C0020910F4}">
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="21" t="s">
+        <v>286</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="21" t="s">
+        <v>287</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>288</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/eBus_Functions/Post_Processing/Root_Cause_Analysis_Work/info/eBus_Model_Info.xlsx
+++ b/eBus_Functions/Post_Processing/Root_Cause_Analysis_Work/info/eBus_Model_Info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\TempData\Github\eBus_Tool\eBus_Functions\Post_Processing\Root_Cause_Analysis_Work\info\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8325D24C-37B5-484E-BEFB-0DD5230CE88D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6579860E-F8BB-4EE3-915C-DF903BFDBA69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Block_Diagram" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="701" uniqueCount="332">
   <si>
     <t>Driver</t>
   </si>
@@ -582,9 +582,6 @@
     <t>Auxiliary Load Voltage</t>
   </si>
   <si>
-    <t>Auxiliary Load Power</t>
-  </si>
-  <si>
     <t>logout.CmdTrq_Req_PTIce1/2</t>
   </si>
   <si>
@@ -729,15 +726,6 @@
     <t>logout.pne_brk_Axle1_BrakingPower+logout.pne_brk_Axle2_BrakingPower+logout.pne_brk_Axle3_BrakingPower+logout.pne_brk_Axle4_BrakingPower</t>
   </si>
   <si>
-    <t>logout.hvs_zfCetrax_gbxOut_torque*sMP.global.mec_iDiffAxle/(sMP.global.mec_rWheelDriven*0.001)-(logout.mec_brk_Axle1_TiBrk_info+logout.mec_brk_Axle2_TiBrk_info+logout.mec_brk_Axle3_TiBrk_info+logout.mec_brk_Axle4_TiBrk_info)</t>
-  </si>
-  <si>
-    <t>logout.mec_brk_Axle1_TiBrk_info+logout.mec_brk_Axle2_TiBrk_info+logout.mec_brk_Axle3_TiBrk_info+logout.mec_brk_Axle4_TiBrk_info</t>
-  </si>
-  <si>
-    <t>logout.mec_brk_Wheel1_TiLossRollRes_info+logout.mec_brk_Wheel2_TiLossRollRes_info+logout.mec_brk_Wheel3_TiLossRollRes_info+logout.mec_brk_Wheel4_TiLossRollRes_info</t>
-  </si>
-  <si>
     <t>logout.eess_BatHW_P_BatPwr/1000</t>
   </si>
   <si>
@@ -1000,6 +988,46 @@
   </si>
   <si>
     <t>m</t>
+  </si>
+  <si>
+    <t>Inertial Force</t>
+  </si>
+  <si>
+    <t>veh_ma</t>
+  </si>
+  <si>
+    <t>logout.mec_veh_transAcc*sMP.global.mec_massVehicle_kg</t>
+  </si>
+  <si>
+    <t>(logout.mec_brk_Wheel1_TiLossRollRes_info+logout.mec_brk_Wheel2_TiLossRollRes_info+logout.mec_brk_Wheel3_TiLossRollRes_info+logout.mec_brk_Wheel4_TiLossRollRes_info)/(sMP.global.mec_rWheelDriven*0.001)</t>
+  </si>
+  <si>
+    <t>veh_long_force</t>
+  </si>
+  <si>
+    <t>logout.hvs_zfCetrax_gbxOut_torque*sMP.global.mec_iDiffAxle/(sMP.global.mec_rWheelDriven*0.001)</t>
+  </si>
+  <si>
+    <t>logout.hvs_zfCetrax_gbxOut_torque*sMP.global.mec_iDiffAxle</t>
+  </si>
+  <si>
+    <t>Vehicle Propulsion Force</t>
+  </si>
+  <si>
+    <t>(logout.mec_brk_Axle1_TiBrk_info+logout.mec_brk_Axle2_TiBrk_info+logout.mec_brk_Axle3_TiBrk_info+logout.mec_brk_Axle4_TiBrk_info)//(sMP.global.mec_rWheelDriven*0.001)</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>These Battery Current and Power Limits are sent to Powertrain Controller, so that power train controller can demand the torque, that is adhered to these limits</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In Vehicle Dynamics, 
+Vehicle Propulsion Force = Net Traction Torque / Tire Radius;
+Vehicle Propulsion Force - Friction Brake Force = Wheel Force;
+Wheel Force = AeroDynamic Force + Gradient Force + Rolling Resistance Force + Inertial Force;
+</t>
   </si>
 </sst>
 </file>
@@ -1120,7 +1148,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -1159,11 +1187,136 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1216,17 +1369,66 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1309,7 +1511,7 @@
       <xdr:col>8</xdr:col>
       <xdr:colOff>2972078</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:rowOff>53340</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1608,16 +1810,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="G27:I88"/>
+  <dimension ref="G27:J88"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="7" max="7" width="30.109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="26.33203125" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="54" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="82.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="27" spans="7:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="28" spans="7:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="7:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="28" spans="7:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G28" s="8" t="s">
         <v>8</v>
       </c>
@@ -1627,440 +1830,565 @@
       <c r="I28" s="10" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="29" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="H29" s="24" t="s">
+      <c r="J28" s="9" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="29" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G29" s="22"/>
+      <c r="H29" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="I29" t="s">
+      <c r="I29" s="23" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="30" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="H30" s="24"/>
-      <c r="I30" t="s">
+      <c r="J29" s="28"/>
+    </row>
+    <row r="30" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G30" s="24"/>
+      <c r="H30" s="38"/>
+      <c r="I30" s="25" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="31" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="H31" s="24"/>
-      <c r="I31" t="s">
+      <c r="J30" s="29"/>
+    </row>
+    <row r="31" spans="7:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G31" s="26"/>
+      <c r="H31" s="39"/>
+      <c r="I31" s="27" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="32" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G32" t="s">
+      <c r="J31" s="30"/>
+    </row>
+    <row r="32" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G32" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="H32" s="25" t="s">
+      <c r="H32" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="I32" t="s">
+      <c r="I32" s="23" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="33" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G33" t="s">
+      <c r="J32" s="28"/>
+    </row>
+    <row r="33" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G33" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="H33" s="25"/>
-      <c r="I33" t="s">
+      <c r="H33" s="41"/>
+      <c r="I33" s="25" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="34" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G34" t="s">
+      <c r="J33" s="29"/>
+    </row>
+    <row r="34" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G34" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="H34" s="25"/>
-    </row>
-    <row r="35" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G35" t="s">
+      <c r="H34" s="41"/>
+      <c r="I34" s="25"/>
+      <c r="J34" s="29"/>
+    </row>
+    <row r="35" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G35" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="H35" s="25"/>
-    </row>
-    <row r="36" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G36" t="s">
+      <c r="H35" s="41"/>
+      <c r="I35" s="25"/>
+      <c r="J35" s="29"/>
+    </row>
+    <row r="36" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G36" s="24" t="s">
         <v>178</v>
       </c>
-      <c r="H36" s="25"/>
-    </row>
-    <row r="37" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G37" t="s">
+      <c r="H36" s="41"/>
+      <c r="I36" s="25"/>
+      <c r="J36" s="29"/>
+    </row>
+    <row r="37" spans="7:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G37" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="H37" s="25"/>
-    </row>
-    <row r="38" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G38" t="s">
+      <c r="H37" s="42"/>
+      <c r="I37" s="27"/>
+      <c r="J37" s="30"/>
+    </row>
+    <row r="38" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G38" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="H38" s="24" t="s">
+      <c r="H38" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="I38" t="s">
+      <c r="I38" s="23" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="39" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G39" t="s">
+      <c r="J38" s="28"/>
+    </row>
+    <row r="39" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G39" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="H39" s="24"/>
-      <c r="I39" t="s">
+      <c r="H39" s="38"/>
+      <c r="I39" s="25" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="40" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="H40" s="24"/>
-      <c r="I40" t="s">
+      <c r="J39" s="29"/>
+    </row>
+    <row r="40" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G40" s="24"/>
+      <c r="H40" s="38"/>
+      <c r="I40" s="25" t="s">
+        <v>302</v>
+      </c>
+      <c r="J40" s="29"/>
+    </row>
+    <row r="41" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G41" s="24"/>
+      <c r="H41" s="38"/>
+      <c r="I41" s="25" t="s">
+        <v>303</v>
+      </c>
+      <c r="J41" s="29"/>
+    </row>
+    <row r="42" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G42" s="24"/>
+      <c r="H42" s="38"/>
+      <c r="I42" s="25" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="41" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="H41" s="24"/>
-      <c r="I41" t="s">
+      <c r="J42" s="29"/>
+    </row>
+    <row r="43" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G43" s="24"/>
+      <c r="H43" s="38"/>
+      <c r="I43" s="25" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="42" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="H42" s="24"/>
-      <c r="I42" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="43" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="H43" s="24"/>
-      <c r="I43" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="44" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="H44" s="24"/>
-    </row>
-    <row r="45" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="H45" s="24"/>
-    </row>
-    <row r="46" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="H46" s="24"/>
-    </row>
-    <row r="47" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="H47" s="24"/>
-    </row>
-    <row r="48" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="H48" s="22"/>
-    </row>
-    <row r="49" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G49" t="s">
+      <c r="J43" s="29"/>
+    </row>
+    <row r="44" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G44" s="24"/>
+      <c r="H44" s="38"/>
+      <c r="I44" s="25"/>
+      <c r="J44" s="29"/>
+    </row>
+    <row r="45" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G45" s="24"/>
+      <c r="H45" s="38"/>
+      <c r="I45" s="25"/>
+      <c r="J45" s="29"/>
+    </row>
+    <row r="46" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G46" s="24"/>
+      <c r="H46" s="38"/>
+      <c r="I46" s="25"/>
+      <c r="J46" s="29"/>
+    </row>
+    <row r="47" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G47" s="24"/>
+      <c r="H47" s="38"/>
+      <c r="I47" s="25"/>
+      <c r="J47" s="29"/>
+    </row>
+    <row r="48" spans="7:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G48" s="26"/>
+      <c r="H48" s="39"/>
+      <c r="I48" s="27"/>
+      <c r="J48" s="30"/>
+    </row>
+    <row r="49" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G49" s="22" t="s">
         <v>170</v>
       </c>
-      <c r="H49" s="25" t="s">
+      <c r="H49" s="40" t="s">
         <v>106</v>
       </c>
-      <c r="I49" t="s">
+      <c r="I49" s="31" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="50" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G50" t="s">
+      <c r="J49" s="28"/>
+    </row>
+    <row r="50" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G50" s="24" t="s">
         <v>171</v>
       </c>
-      <c r="H50" s="25"/>
-      <c r="I50" t="s">
+      <c r="H50" s="41"/>
+      <c r="I50" s="32" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="51" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G51" t="s">
-        <v>308</v>
-      </c>
-      <c r="H51" s="25"/>
-      <c r="I51" t="s">
+      <c r="J50" s="29"/>
+    </row>
+    <row r="51" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G51" s="24" t="s">
+        <v>304</v>
+      </c>
+      <c r="H51" s="41"/>
+      <c r="I51" s="32" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="52" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G52" t="s">
-        <v>309</v>
-      </c>
-      <c r="H52" s="25"/>
-      <c r="I52" t="s">
+      <c r="J51" s="29"/>
+    </row>
+    <row r="52" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G52" s="24" t="s">
+        <v>305</v>
+      </c>
+      <c r="H52" s="41"/>
+      <c r="I52" s="32" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="53" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="H53" s="25"/>
-      <c r="I53" t="s">
+      <c r="J52" s="29"/>
+    </row>
+    <row r="53" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G53" s="24"/>
+      <c r="H53" s="41"/>
+      <c r="I53" s="32" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="54" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="H54" s="25"/>
-      <c r="I54" t="s">
+      <c r="J53" s="29"/>
+    </row>
+    <row r="54" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G54" s="24"/>
+      <c r="H54" s="41"/>
+      <c r="I54" s="32" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="55" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="H55" s="25"/>
-      <c r="I55" t="s">
+      <c r="J54" s="29"/>
+    </row>
+    <row r="55" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G55" s="24"/>
+      <c r="H55" s="41"/>
+      <c r="I55" s="32" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="56" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="H56" s="25"/>
-      <c r="I56" t="s">
+      <c r="J55" s="29"/>
+    </row>
+    <row r="56" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G56" s="24"/>
+      <c r="H56" s="41"/>
+      <c r="I56" s="32" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="57" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="H57" s="25"/>
-      <c r="I57" t="s">
+      <c r="J56" s="29"/>
+    </row>
+    <row r="57" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G57" s="24"/>
+      <c r="H57" s="41"/>
+      <c r="I57" s="32" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="58" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="H58" s="25"/>
-      <c r="I58" t="s">
+      <c r="J57" s="29"/>
+    </row>
+    <row r="58" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G58" s="24"/>
+      <c r="H58" s="41"/>
+      <c r="I58" s="32" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="59" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="H59" s="25"/>
-      <c r="I59" t="s">
+      <c r="J58" s="29"/>
+    </row>
+    <row r="59" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G59" s="24"/>
+      <c r="H59" s="41"/>
+      <c r="I59" s="32" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="60" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="H60" s="25"/>
-      <c r="I60" t="s">
+      <c r="J59" s="29"/>
+    </row>
+    <row r="60" spans="7:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G60" s="26"/>
+      <c r="H60" s="42"/>
+      <c r="I60" s="33" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="61" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G61" t="s">
+      <c r="J60" s="30"/>
+    </row>
+    <row r="61" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G61" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="H61" s="24" t="s">
+      <c r="H61" s="37" t="s">
         <v>107</v>
       </c>
-      <c r="I61" t="s">
+      <c r="I61" s="31" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="62" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G62" t="s">
+      <c r="J61" s="28"/>
+    </row>
+    <row r="62" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G62" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="H62" s="24"/>
-      <c r="I62" t="s">
+      <c r="H62" s="38"/>
+      <c r="I62" s="32" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="63" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="H63" s="24"/>
-      <c r="I63" t="s">
+      <c r="J62" s="29"/>
+    </row>
+    <row r="63" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G63" s="24"/>
+      <c r="H63" s="38"/>
+      <c r="I63" s="32" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="64" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="H64" s="24"/>
-      <c r="I64" t="s">
+      <c r="J63" s="29"/>
+    </row>
+    <row r="64" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G64" s="24"/>
+      <c r="H64" s="38"/>
+      <c r="I64" s="32" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="65" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="H65" s="24"/>
-      <c r="I65" t="s">
+      <c r="J64" s="29"/>
+    </row>
+    <row r="65" spans="7:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G65" s="26"/>
+      <c r="H65" s="39"/>
+      <c r="I65" s="33" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="66" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G66" t="s">
+      <c r="J65" s="30"/>
+    </row>
+    <row r="66" spans="7:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G66" s="34" t="s">
         <v>176</v>
       </c>
-      <c r="H66" s="23" t="s">
+      <c r="H66" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="I66" t="s">
+      <c r="I66" s="35" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="67" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G67" t="s">
+      <c r="J66" s="36"/>
+    </row>
+    <row r="67" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G67" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="H67" s="25" t="s">
+      <c r="H67" s="40" t="s">
         <v>108</v>
       </c>
-      <c r="I67" t="s">
+      <c r="I67" s="31" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="68" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="H68" s="25"/>
-      <c r="I68" t="s">
+      <c r="J67" s="28"/>
+    </row>
+    <row r="68" spans="7:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G68" s="26"/>
+      <c r="H68" s="42"/>
+      <c r="I68" s="33" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="69" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G69" t="s">
-        <v>18</v>
-      </c>
-      <c r="H69" s="24" t="s">
+      <c r="J68" s="30"/>
+    </row>
+    <row r="69" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G69" s="22" t="s">
+        <v>327</v>
+      </c>
+      <c r="H69" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="I69" t="s">
+      <c r="I69" s="31" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="70" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G70" t="s">
+      <c r="J69" s="48" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="70" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G70" s="24" t="s">
         <v>179</v>
       </c>
-      <c r="H70" s="24"/>
-      <c r="I70" t="s">
+      <c r="H70" s="38"/>
+      <c r="I70" s="32" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="71" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="H71" s="24"/>
-      <c r="I71" t="s">
+      <c r="J70" s="49"/>
+    </row>
+    <row r="71" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G71" s="24"/>
+      <c r="H71" s="38"/>
+      <c r="I71" s="32" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="72" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="H72" s="24"/>
-      <c r="I72" t="s">
+      <c r="J71" s="49"/>
+    </row>
+    <row r="72" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G72" s="24"/>
+      <c r="H72" s="38"/>
+      <c r="I72" s="32" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="73" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="H73" s="24"/>
-      <c r="I73" t="s">
+      <c r="J72" s="49"/>
+    </row>
+    <row r="73" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G73" s="24"/>
+      <c r="H73" s="38"/>
+      <c r="I73" s="32" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="74" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="H74" s="24"/>
-      <c r="I74" t="s">
+      <c r="J73" s="49"/>
+    </row>
+    <row r="74" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G74" s="24"/>
+      <c r="H74" s="38"/>
+      <c r="I74" s="32" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="75" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="H75" s="24"/>
-      <c r="I75" t="s">
+      <c r="J74" s="49"/>
+    </row>
+    <row r="75" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G75" s="24"/>
+      <c r="H75" s="38"/>
+      <c r="I75" s="44" t="s">
+        <v>320</v>
+      </c>
+      <c r="J75" s="49"/>
+    </row>
+    <row r="76" spans="7:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G76" s="26"/>
+      <c r="H76" s="39"/>
+      <c r="I76" s="33" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="76" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G76" t="s">
+      <c r="J76" s="50"/>
+    </row>
+    <row r="77" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G77" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="H76" s="24" t="s">
+      <c r="H77" s="37" t="s">
         <v>109</v>
       </c>
-      <c r="I76" t="s">
+      <c r="I77" s="31" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="77" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="H77" s="24"/>
-      <c r="I77" t="s">
+      <c r="J77" s="45"/>
+    </row>
+    <row r="78" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G78" s="24"/>
+      <c r="H78" s="38"/>
+      <c r="I78" s="32" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="78" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="H78" s="24"/>
-      <c r="I78" t="s">
+      <c r="J78" s="46"/>
+    </row>
+    <row r="79" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G79" s="24"/>
+      <c r="H79" s="38"/>
+      <c r="I79" s="32" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="79" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="H79" s="24"/>
-      <c r="I79" t="s">
+      <c r="J79" s="46"/>
+    </row>
+    <row r="80" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G80" s="24"/>
+      <c r="H80" s="38"/>
+      <c r="I80" s="32" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="80" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="H80" s="24"/>
-      <c r="I80" t="s">
+      <c r="J80" s="46"/>
+    </row>
+    <row r="81" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G81" s="24"/>
+      <c r="H81" s="38"/>
+      <c r="I81" s="32" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="81" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="H81" s="24"/>
-      <c r="I81" t="s">
+      <c r="J81" s="46"/>
+    </row>
+    <row r="82" spans="7:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G82" s="26"/>
+      <c r="H82" s="39"/>
+      <c r="I82" s="33" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="82" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G82" t="s">
+      <c r="J82" s="47"/>
+    </row>
+    <row r="83" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G83" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="H82" s="25" t="s">
+      <c r="H83" s="40" t="s">
         <v>110</v>
       </c>
-      <c r="I82" t="s">
+      <c r="I83" s="31" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="83" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="G83" t="s">
+      <c r="J83" s="48" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="84" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G84" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="H83" s="25"/>
-      <c r="I83" t="s">
+      <c r="H84" s="41"/>
+      <c r="I84" s="32" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="84" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="H84" s="25"/>
-      <c r="I84" t="s">
+      <c r="J84" s="49"/>
+    </row>
+    <row r="85" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G85" s="24"/>
+      <c r="H85" s="41"/>
+      <c r="I85" s="32" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="85" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="H85" s="25"/>
-      <c r="I85" t="s">
+      <c r="J85" s="49"/>
+    </row>
+    <row r="86" spans="7:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G86" s="26"/>
+      <c r="H86" s="42"/>
+      <c r="I86" s="33" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="86" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="H86" s="24" t="s">
+      <c r="J86" s="50"/>
+    </row>
+    <row r="87" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G87" s="22"/>
+      <c r="H87" s="37" t="s">
         <v>111</v>
       </c>
-      <c r="I86" t="s">
+      <c r="I87" s="31" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="87" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="H87" s="24"/>
-      <c r="I87" t="s">
+      <c r="J87" s="28"/>
+    </row>
+    <row r="88" spans="7:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G88" s="26"/>
+      <c r="H88" s="39"/>
+      <c r="I88" s="33" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="88" spans="7:9" x14ac:dyDescent="0.3">
-      <c r="H88" s="24"/>
-      <c r="I88" t="s">
-        <v>184</v>
-      </c>
+      <c r="J88" s="30"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="20">
+    <mergeCell ref="J87:J88"/>
+    <mergeCell ref="J77:J82"/>
+    <mergeCell ref="J69:J76"/>
+    <mergeCell ref="J67:J68"/>
+    <mergeCell ref="H38:H48"/>
+    <mergeCell ref="J83:J86"/>
+    <mergeCell ref="J29:J31"/>
+    <mergeCell ref="J32:J37"/>
+    <mergeCell ref="J38:J48"/>
+    <mergeCell ref="J49:J60"/>
+    <mergeCell ref="J61:J65"/>
+    <mergeCell ref="H77:H82"/>
+    <mergeCell ref="H83:H86"/>
+    <mergeCell ref="H61:H65"/>
+    <mergeCell ref="H69:H76"/>
+    <mergeCell ref="H87:H88"/>
     <mergeCell ref="H29:H31"/>
     <mergeCell ref="H32:H37"/>
-    <mergeCell ref="H38:H47"/>
     <mergeCell ref="H49:H60"/>
     <mergeCell ref="H67:H68"/>
-    <mergeCell ref="H76:H81"/>
-    <mergeCell ref="H82:H85"/>
-    <mergeCell ref="H61:H65"/>
-    <mergeCell ref="H69:H75"/>
-    <mergeCell ref="H86:H88"/>
   </mergeCells>
   <conditionalFormatting sqref="I29:I88 G29:G88">
-    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -2070,7 +2398,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFA16316-83DB-41C7-8B25-B191695DD108}">
-  <dimension ref="A1:L105"/>
+  <dimension ref="A1:L107"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.109375" bestFit="1" customWidth="1"/>
@@ -2118,22 +2446,22 @@
         <v>96</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="G2" s="17" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
@@ -2177,7 +2505,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E4" s="17" t="s">
         <v>31</v>
@@ -2205,7 +2533,7 @@
         <v>33</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E5" s="17" t="s">
         <v>34</v>
@@ -2233,16 +2561,16 @@
         <v>1</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
@@ -2261,16 +2589,16 @@
         <v>1</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="G7" s="17" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="H7" s="5"/>
       <c r="I7" s="5"/>
@@ -2283,22 +2611,22 @@
         <v>97</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="C8" s="16" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F8" s="17" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H8" s="5"/>
       <c r="I8" s="5"/>
@@ -2311,22 +2639,22 @@
         <v>97</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="C9" s="16" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F9" s="17" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G9" s="17" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H9" s="5"/>
       <c r="I9" s="5"/>
@@ -2339,22 +2667,22 @@
         <v>97</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C10" s="16" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="20" t="s">
+        <v>312</v>
+      </c>
+      <c r="E10" s="17" t="s">
         <v>316</v>
       </c>
-      <c r="E10" s="17" t="s">
-        <v>320</v>
-      </c>
       <c r="F10" s="17" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="G10" s="17" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
@@ -2367,22 +2695,22 @@
         <v>97</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="C11" s="16" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="F11" s="17" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="G11" s="17" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="H11" s="5"/>
       <c r="I11" s="5"/>
@@ -2395,22 +2723,22 @@
         <v>97</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="C12" s="16" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="F12" s="17" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="G12" s="17" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
@@ -2423,22 +2751,22 @@
         <v>97</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="C13" s="16" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="F13" s="17" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="G13" s="17" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
@@ -2451,13 +2779,13 @@
         <v>95</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="C14" s="16" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="20" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E14" s="17" t="s">
         <v>37</v>
@@ -2479,13 +2807,13 @@
         <v>95</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C15" s="16" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E15" s="17" t="s">
         <v>39</v>
@@ -2513,7 +2841,7 @@
         <v>5</v>
       </c>
       <c r="D16" s="20" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E16" s="17" t="s">
         <v>41</v>
@@ -2541,7 +2869,7 @@
         <v>5</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E17" s="17" t="s">
         <v>43</v>
@@ -2563,13 +2891,13 @@
         <v>95</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="C18" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D18" s="20" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E18" s="17" t="s">
         <v>45</v>
@@ -2591,13 +2919,13 @@
         <v>95</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="C19" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D19" s="20" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E19" s="17" t="s">
         <v>47</v>
@@ -2625,7 +2953,7 @@
         <v>4</v>
       </c>
       <c r="D20" s="20" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E20" s="17" t="s">
         <v>48</v>
@@ -2653,7 +2981,7 @@
         <v>4</v>
       </c>
       <c r="D21" s="20" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E21" s="17" t="s">
         <v>49</v>
@@ -2675,13 +3003,13 @@
         <v>95</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="C22" s="16" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="20" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E22" s="17" t="s">
         <v>51</v>
@@ -2703,13 +3031,13 @@
         <v>95</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="C23" s="16" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="20" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E23" s="17" t="s">
         <v>52</v>
@@ -2731,13 +3059,13 @@
         <v>95</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C24" s="16" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="20" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E24" s="17" t="s">
         <v>54</v>
@@ -2759,13 +3087,13 @@
         <v>95</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="C25" s="16" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="20" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E25" s="17" t="s">
         <v>55</v>
@@ -2787,13 +3115,13 @@
         <v>94</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="C26" s="16" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="20" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E26" s="17" t="s">
         <v>56</v>
@@ -2821,7 +3149,7 @@
         <v>5</v>
       </c>
       <c r="D27" s="20" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E27" s="17" t="s">
         <v>57</v>
@@ -2847,16 +3175,16 @@
       </c>
       <c r="C28" s="16"/>
       <c r="D28" s="20" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E28" s="17" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="F28" s="17" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="G28" s="17" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="H28" s="17"/>
       <c r="I28" s="5"/>
@@ -2873,7 +3201,7 @@
       </c>
       <c r="C29" s="16"/>
       <c r="D29" s="20" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E29" s="17" t="s">
         <v>35</v>
@@ -2901,7 +3229,7 @@
         <v>4</v>
       </c>
       <c r="D30" s="20" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E30" s="17" t="s">
         <v>58</v>
@@ -2926,19 +3254,19 @@
         <v>18</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>63</v>
+        <v>3</v>
       </c>
       <c r="D31" s="20" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E31" s="19" t="s">
-        <v>233</v>
+        <v>326</v>
       </c>
       <c r="F31" s="19" t="s">
-        <v>233</v>
+        <v>326</v>
       </c>
       <c r="G31" s="19" t="s">
-        <v>233</v>
+        <v>326</v>
       </c>
       <c r="H31" s="5"/>
       <c r="I31" s="5"/>
@@ -2957,16 +3285,16 @@
         <v>63</v>
       </c>
       <c r="D32" s="20" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E32" s="19" t="s">
-        <v>234</v>
+        <v>328</v>
       </c>
       <c r="F32" s="19" t="s">
-        <v>234</v>
+        <v>328</v>
       </c>
       <c r="G32" s="19" t="s">
-        <v>234</v>
+        <v>328</v>
       </c>
       <c r="H32" s="5"/>
       <c r="I32" s="5"/>
@@ -2985,16 +3313,16 @@
         <v>4</v>
       </c>
       <c r="D33" s="20" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E33" s="17" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F33" s="17" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G33" s="17" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H33" s="5"/>
       <c r="I33" s="5"/>
@@ -3007,22 +3335,22 @@
         <v>92</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>20</v>
+        <v>327</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D34" s="20" t="s">
-        <v>211</v>
-      </c>
-      <c r="E34" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="F34" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="G34" s="17" t="s">
-        <v>60</v>
+        <v>324</v>
+      </c>
+      <c r="E34" s="19" t="s">
+        <v>325</v>
+      </c>
+      <c r="F34" s="19" t="s">
+        <v>325</v>
+      </c>
+      <c r="G34" s="19" t="s">
+        <v>325</v>
       </c>
       <c r="H34" s="5"/>
       <c r="I34" s="5"/>
@@ -3035,22 +3363,22 @@
         <v>92</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="C35" s="16" t="s">
-        <v>98</v>
+        <v>63</v>
       </c>
       <c r="D35" s="20" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E35" s="17" t="s">
-        <v>274</v>
+        <v>323</v>
       </c>
       <c r="F35" s="17" t="s">
-        <v>274</v>
+        <v>323</v>
       </c>
       <c r="G35" s="17" t="s">
-        <v>274</v>
+        <v>323</v>
       </c>
       <c r="H35" s="5"/>
       <c r="I35" s="5"/>
@@ -3063,22 +3391,22 @@
         <v>92</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>186</v>
+        <v>63</v>
       </c>
       <c r="D36" s="20" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E36" s="17" t="s">
-        <v>277</v>
+        <v>64</v>
       </c>
       <c r="F36" s="17" t="s">
-        <v>277</v>
+        <v>64</v>
       </c>
       <c r="G36" s="17" t="s">
-        <v>277</v>
+        <v>64</v>
       </c>
       <c r="H36" s="5"/>
       <c r="I36" s="5"/>
@@ -3091,22 +3419,22 @@
         <v>92</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C37" s="16" t="s">
         <v>63</v>
       </c>
       <c r="D37" s="20" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E37" s="17" t="s">
-        <v>235</v>
+        <v>66</v>
       </c>
       <c r="F37" s="17" t="s">
-        <v>235</v>
+        <v>66</v>
       </c>
       <c r="G37" s="17" t="s">
-        <v>235</v>
+        <v>66</v>
       </c>
       <c r="H37" s="5"/>
       <c r="I37" s="5"/>
@@ -3119,22 +3447,22 @@
         <v>92</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>62</v>
+        <v>320</v>
       </c>
       <c r="C38" s="16" t="s">
         <v>63</v>
       </c>
       <c r="D38" s="20" t="s">
-        <v>215</v>
+        <v>321</v>
       </c>
       <c r="E38" s="17" t="s">
-        <v>64</v>
+        <v>322</v>
       </c>
       <c r="F38" s="17" t="s">
-        <v>64</v>
+        <v>322</v>
       </c>
       <c r="G38" s="17" t="s">
-        <v>64</v>
+        <v>322</v>
       </c>
       <c r="H38" s="5"/>
       <c r="I38" s="5"/>
@@ -3147,22 +3475,22 @@
         <v>92</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="C39" s="16" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D39" s="20" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="E39" s="17" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="F39" s="17" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="G39" s="17" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="H39" s="5"/>
       <c r="I39" s="5"/>
@@ -3175,50 +3503,50 @@
         <v>92</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="C40" s="16" t="s">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="D40" s="20" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="E40" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F40" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="G40" s="17" t="s">
-        <v>272</v>
-      </c>
-      <c r="H40" s="17"/>
+        <v>270</v>
+      </c>
+      <c r="H40" s="5"/>
       <c r="I40" s="5"/>
       <c r="J40" s="5"/>
       <c r="K40" s="5"/>
       <c r="L40" s="5"/>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A41" s="15" t="s">
-        <v>90</v>
+      <c r="A41" s="18" t="s">
+        <v>92</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>293</v>
+        <v>22</v>
       </c>
       <c r="C41" s="16" t="s">
-        <v>69</v>
+        <v>185</v>
       </c>
       <c r="D41" s="20" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="E41" s="17" t="s">
-        <v>70</v>
+        <v>273</v>
       </c>
       <c r="F41" s="17" t="s">
-        <v>70</v>
+        <v>273</v>
       </c>
       <c r="G41" s="17" t="s">
-        <v>70</v>
+        <v>273</v>
       </c>
       <c r="H41" s="5"/>
       <c r="I41" s="5"/>
@@ -3227,28 +3555,28 @@
       <c r="L41" s="5"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A42" s="15" t="s">
-        <v>90</v>
+      <c r="A42" s="18" t="s">
+        <v>92</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>181</v>
+        <v>67</v>
       </c>
       <c r="C42" s="16" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D42" s="20" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="E42" s="17" t="s">
-        <v>72</v>
+        <v>268</v>
       </c>
       <c r="F42" s="17" t="s">
-        <v>72</v>
+        <v>268</v>
       </c>
       <c r="G42" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="H42" s="5"/>
+        <v>268</v>
+      </c>
+      <c r="H42" s="17"/>
       <c r="I42" s="5"/>
       <c r="J42" s="5"/>
       <c r="K42" s="5"/>
@@ -3259,22 +3587,22 @@
         <v>90</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="C43" s="16" t="s">
-        <v>4</v>
+        <v>69</v>
       </c>
       <c r="D43" s="20" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E43" s="17" t="s">
-        <v>236</v>
-      </c>
-      <c r="F43" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="G43" s="5" t="s">
-        <v>240</v>
+        <v>70</v>
+      </c>
+      <c r="F43" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="G43" s="17" t="s">
+        <v>70</v>
       </c>
       <c r="H43" s="5"/>
       <c r="I43" s="5"/>
@@ -3287,22 +3615,22 @@
         <v>90</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>74</v>
+        <v>181</v>
       </c>
       <c r="C44" s="16" t="s">
-        <v>4</v>
+        <v>71</v>
       </c>
       <c r="D44" s="20" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E44" s="17" t="s">
-        <v>237</v>
-      </c>
-      <c r="F44" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="G44" s="5" t="s">
-        <v>241</v>
+        <v>72</v>
+      </c>
+      <c r="F44" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="G44" s="17" t="s">
+        <v>72</v>
       </c>
       <c r="H44" s="5"/>
       <c r="I44" s="5"/>
@@ -3315,22 +3643,22 @@
         <v>90</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>75</v>
+        <v>290</v>
       </c>
       <c r="C45" s="16" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D45" s="20" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="E45" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="F45" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="G45" s="17" t="s">
-        <v>76</v>
+        <v>232</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>236</v>
       </c>
       <c r="H45" s="5"/>
       <c r="I45" s="5"/>
@@ -3343,22 +3671,22 @@
         <v>90</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C46" s="16" t="s">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="D46" s="20" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E46" s="17" t="s">
-        <v>78</v>
+        <v>233</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="H46" s="5"/>
       <c r="I46" s="5"/>
@@ -3367,26 +3695,26 @@
       <c r="L46" s="5"/>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A47" s="18" t="s">
-        <v>91</v>
+      <c r="A47" s="15" t="s">
+        <v>90</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C47" s="16" t="s">
-        <v>69</v>
+        <v>1</v>
       </c>
       <c r="D47" s="20" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E47" s="17" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F47" s="17" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G47" s="17" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H47" s="5"/>
       <c r="I47" s="5"/>
@@ -3395,26 +3723,26 @@
       <c r="L47" s="5"/>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A48" s="18" t="s">
-        <v>91</v>
+      <c r="A48" s="15" t="s">
+        <v>90</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C48" s="16" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="D48" s="20" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E48" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="F48" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="G48" s="17" t="s">
-        <v>82</v>
+        <v>78</v>
+      </c>
+      <c r="F48" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="G48" s="5" t="s">
+        <v>238</v>
       </c>
       <c r="H48" s="5"/>
       <c r="I48" s="5"/>
@@ -3427,22 +3755,22 @@
         <v>91</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C49" s="16" t="s">
-        <v>4</v>
+        <v>69</v>
       </c>
       <c r="D49" s="20" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="E49" s="17" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F49" s="17" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="G49" s="17" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="H49" s="5"/>
       <c r="I49" s="5"/>
@@ -3455,22 +3783,22 @@
         <v>91</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C50" s="16" t="s">
-        <v>4</v>
+        <v>69</v>
       </c>
       <c r="D50" s="20" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E50" s="17" t="s">
-        <v>273</v>
+        <v>82</v>
       </c>
       <c r="F50" s="17" t="s">
-        <v>273</v>
+        <v>82</v>
       </c>
       <c r="G50" s="17" t="s">
-        <v>273</v>
+        <v>82</v>
       </c>
       <c r="H50" s="5"/>
       <c r="I50" s="5"/>
@@ -3479,26 +3807,26 @@
       <c r="L50" s="5"/>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A51" s="15" t="s">
-        <v>111</v>
+      <c r="A51" s="18" t="s">
+        <v>91</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>182</v>
+        <v>83</v>
       </c>
       <c r="C51" s="16" t="s">
-        <v>69</v>
+        <v>4</v>
       </c>
       <c r="D51" s="20" t="s">
-        <v>230</v>
-      </c>
-      <c r="E51" s="19" t="s">
-        <v>238</v>
-      </c>
-      <c r="F51" s="19" t="s">
-        <v>238</v>
-      </c>
-      <c r="G51" s="19" t="s">
-        <v>238</v>
+        <v>227</v>
+      </c>
+      <c r="E51" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="F51" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G51" s="17" t="s">
+        <v>84</v>
       </c>
       <c r="H51" s="5"/>
       <c r="I51" s="5"/>
@@ -3507,26 +3835,26 @@
       <c r="L51" s="5"/>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A52" s="15" t="s">
-        <v>111</v>
+      <c r="A52" s="18" t="s">
+        <v>91</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>183</v>
+        <v>85</v>
       </c>
       <c r="C52" s="16" t="s">
-        <v>71</v>
+        <v>4</v>
       </c>
       <c r="D52" s="20" t="s">
-        <v>231</v>
-      </c>
-      <c r="E52" s="19" t="s">
-        <v>239</v>
-      </c>
-      <c r="F52" s="19" t="s">
-        <v>239</v>
-      </c>
-      <c r="G52" s="19" t="s">
-        <v>239</v>
+        <v>228</v>
+      </c>
+      <c r="E52" s="17" t="s">
+        <v>269</v>
+      </c>
+      <c r="F52" s="17" t="s">
+        <v>269</v>
+      </c>
+      <c r="G52" s="17" t="s">
+        <v>269</v>
       </c>
       <c r="H52" s="5"/>
       <c r="I52" s="5"/>
@@ -3535,13 +3863,27 @@
       <c r="L52" s="5"/>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A53" s="5"/>
-      <c r="B53" s="19"/>
-      <c r="C53" s="16"/>
-      <c r="D53" s="17"/>
-      <c r="E53" s="19"/>
-      <c r="F53" s="5"/>
-      <c r="G53" s="5"/>
+      <c r="A53" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="C53" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="D53" s="20" t="s">
+        <v>229</v>
+      </c>
+      <c r="E53" s="19" t="s">
+        <v>234</v>
+      </c>
+      <c r="F53" s="19" t="s">
+        <v>234</v>
+      </c>
+      <c r="G53" s="19" t="s">
+        <v>234</v>
+      </c>
       <c r="H53" s="5"/>
       <c r="I53" s="5"/>
       <c r="J53" s="5"/>
@@ -3549,13 +3891,27 @@
       <c r="L53" s="5"/>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A54" s="5"/>
-      <c r="B54" s="19"/>
-      <c r="C54" s="16"/>
-      <c r="D54" s="17"/>
-      <c r="E54" s="19"/>
-      <c r="F54" s="5"/>
-      <c r="G54" s="5"/>
+      <c r="A54" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="C54" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="D54" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="E54" s="19" t="s">
+        <v>235</v>
+      </c>
+      <c r="F54" s="19" t="s">
+        <v>235</v>
+      </c>
+      <c r="G54" s="19" t="s">
+        <v>235</v>
+      </c>
       <c r="H54" s="5"/>
       <c r="I54" s="5"/>
       <c r="J54" s="5"/>
@@ -4276,19 +4632,47 @@
       <c r="K105" s="5"/>
       <c r="L105" s="5"/>
     </row>
+    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A106" s="5"/>
+      <c r="B106" s="19"/>
+      <c r="C106" s="16"/>
+      <c r="D106" s="17"/>
+      <c r="E106" s="19"/>
+      <c r="F106" s="5"/>
+      <c r="G106" s="5"/>
+      <c r="H106" s="5"/>
+      <c r="I106" s="5"/>
+      <c r="J106" s="5"/>
+      <c r="K106" s="5"/>
+      <c r="L106" s="5"/>
+    </row>
+    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A107" s="5"/>
+      <c r="B107" s="19"/>
+      <c r="C107" s="16"/>
+      <c r="D107" s="17"/>
+      <c r="E107" s="19"/>
+      <c r="F107" s="5"/>
+      <c r="G107" s="5"/>
+      <c r="H107" s="5"/>
+      <c r="I107" s="5"/>
+      <c r="J107" s="5"/>
+      <c r="K107" s="5"/>
+      <c r="L107" s="5"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="B2:B7">
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B52">
-    <cfRule type="duplicateValues" dxfId="2" priority="5"/>
+  <conditionalFormatting sqref="B2:B54">
+    <cfRule type="duplicateValues" dxfId="3" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B8:B52">
-    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
+  <conditionalFormatting sqref="B8:B54">
+    <cfRule type="duplicateValues" dxfId="2" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D52">
-    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+  <conditionalFormatting sqref="D2:D54">
+    <cfRule type="duplicateValues" dxfId="1" priority="12"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -4383,22 +4767,22 @@
         <v>95</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
@@ -4414,7 +4798,7 @@
         <v>3</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>112</v>
@@ -4439,7 +4823,7 @@
         <v>4</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>159</v>
@@ -4464,7 +4848,7 @@
         <v>4</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>160</v>
@@ -4489,7 +4873,7 @@
         <v>114</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>164</v>
@@ -4514,7 +4898,7 @@
         <v>3</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>165</v>
@@ -4539,7 +4923,7 @@
         <v>71</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>166</v>
@@ -4564,7 +4948,7 @@
         <v>114</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>161</v>
@@ -4589,7 +4973,7 @@
         <v>3</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>162</v>
@@ -4614,7 +4998,7 @@
         <v>71</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>163</v>
@@ -4639,7 +5023,7 @@
         <v>114</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>161</v>
@@ -4664,7 +5048,7 @@
         <v>3</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>169</v>
@@ -4700,7 +5084,7 @@
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="21" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>145</v>
@@ -4732,20 +5116,20 @@
         <v>92</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="21" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="H20" s="5"/>
       <c r="I20" s="5"/>
@@ -4755,11 +5139,11 @@
         <v>92</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="C21" s="6"/>
       <c r="D21" s="21" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="E21" s="5" t="s">
         <v>146</v>
@@ -4781,19 +5165,19 @@
         <v>115</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="D22" s="21" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
@@ -4809,7 +5193,7 @@
         <v>144</v>
       </c>
       <c r="D23" s="21" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>147</v>
@@ -4832,10 +5216,10 @@
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="21" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>125</v>
@@ -4857,7 +5241,7 @@
         <v>1</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>126</v>
@@ -4882,16 +5266,16 @@
         <v>124</v>
       </c>
       <c r="D26" s="21" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="H26" s="5"/>
       <c r="I26" s="5"/>
@@ -4907,7 +5291,7 @@
         <v>1</v>
       </c>
       <c r="D27" s="21" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="E27" s="5" t="s">
         <v>127</v>
@@ -4932,7 +5316,7 @@
         <v>69</v>
       </c>
       <c r="D28" s="21" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="E28" s="5" t="s">
         <v>136</v>
@@ -4957,7 +5341,7 @@
         <v>69</v>
       </c>
       <c r="D29" s="21" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="E29" s="5" t="s">
         <v>137</v>
@@ -4982,7 +5366,7 @@
         <v>1</v>
       </c>
       <c r="D30" s="21" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="E30" s="5" t="s">
         <v>138</v>
@@ -5007,7 +5391,7 @@
         <v>33</v>
       </c>
       <c r="D31" s="21" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="E31" s="5" t="s">
         <v>139</v>
@@ -5032,7 +5416,7 @@
         <v>69</v>
       </c>
       <c r="D32" s="21" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="E32" s="5" t="s">
         <v>140</v>
@@ -5057,7 +5441,7 @@
         <v>69</v>
       </c>
       <c r="D33" s="21" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="E33" s="5" t="s">
         <v>141</v>
@@ -5082,7 +5466,7 @@
         <v>1</v>
       </c>
       <c r="D34" s="21" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="E34" s="5" t="s">
         <v>142</v>
@@ -5105,7 +5489,7 @@
         <v>33</v>
       </c>
       <c r="D35" s="21" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E35" s="5" t="s">
         <v>143</v>
@@ -5146,7 +5530,7 @@
         <v>4</v>
       </c>
       <c r="D1" s="21" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>148</v>
@@ -5171,7 +5555,7 @@
         <v>3</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>149</v>
@@ -5196,7 +5580,7 @@
         <v>114</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>150</v>

--- a/eBus_Functions/Post_Processing/Root_Cause_Analysis_Work/info/eBus_Model_Info.xlsx
+++ b/eBus_Functions/Post_Processing/Root_Cause_Analysis_Work/info/eBus_Model_Info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\TempData\Github\eBus_Tool\eBus_Functions\Post_Processing\Root_Cause_Analysis_Work\info\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6579860E-F8BB-4EE3-915C-DF903BFDBA69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E79914EF-CCAB-49C9-9C0F-2D2CB603C8DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Block_Diagram" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="701" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="352">
   <si>
     <t>Driver</t>
   </si>
@@ -726,12 +726,6 @@
     <t>logout.pne_brk_Axle1_BrakingPower+logout.pne_brk_Axle2_BrakingPower+logout.pne_brk_Axle3_BrakingPower+logout.pne_brk_Axle4_BrakingPower</t>
   </si>
   <si>
-    <t>logout.eess_BatHW_P_BatPwr/1000</t>
-  </si>
-  <si>
-    <t>logout.eess_BatHW_P_BatLossPwr/1000</t>
-  </si>
-  <si>
     <t>logout.hvs_dcLink_aux_current</t>
   </si>
   <si>
@@ -1020,14 +1014,88 @@
     <t>Description</t>
   </si>
   <si>
-    <t>These Battery Current and Power Limits are sent to Powertrain Controller, so that power train controller can demand the torque, that is adhered to these limits</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In Vehicle Dynamics, 
+    <t>The Electric Drive System takes the Electric Motor Demand Torque from power train controller and gives out the actual electric motor torque, actual motor speed, actual motor electrical power, motor loss power. It also gives out the maximum and minimum  possible/available torque from electric drive system.</t>
+  </si>
+  <si>
+    <t>The sum of electric motor torques are input to Tranmission system. The transmission system can be of single speed or multi speed transmission. It gives out the Gear box torque, Gearbox speed, current Gear Number and Gear Ratio, Gearbox power loss</t>
+  </si>
+  <si>
+    <t>The gearbox output torque is fed to final drive. The output of final drive is the propulsion torque to wheel shaft.</t>
+  </si>
+  <si>
+    <t>The Pneumatic system, gives out the Friction Brake Force and Firction Brake Power</t>
+  </si>
+  <si>
+    <t>The Battery system caters the demand current. 
+The outputs from the Battery System are - Battery Current, Voltage, Power, Loss Power, State of Charge and Temperature</t>
+  </si>
+  <si>
+    <t>The Auxiliary Load System gives out the net auxiliary load current and voltage</t>
+  </si>
+  <si>
+    <t>Battery Charge Current Limit (Positive for Charge and Negative for Discharge)</t>
+  </si>
+  <si>
+    <t>Battery Discharge Current Limit (Positive for Charge and Negative for Discharge)</t>
+  </si>
+  <si>
+    <t>Battery Charge Power Limit (Positive for Charge and Negative for Discharge)</t>
+  </si>
+  <si>
+    <t>Battery Discharge Power Limit (Positive for Charge and Negative for Discharge)</t>
+  </si>
+  <si>
+    <t>The Driver model subsystem gets the Desired Velocity Input from Environmnet and Vehicle Velocity input from vehicle dynamics, the difference as an error is fed to PI (Proportional Integral) Controller. These driver model also has feedforward controller which makes use of the Vehicle Weight, Actual Gear Ration and Max Motor Torque information that assist in calculating the Acc Pedal and Brake Pedal along with PI controller. The accelerator and brake pedal are outcome of combination of PI and Feedforward controller.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Powertrain controller takes the Accelerator and Brake Pedal command from Driver model and demands the Electric Motor Torque from Electric drive system. 
+It gives out the Max and Min available electirc Motor demand torque.
+It also gives out the Max available Electric DrivingPower and Max available Electric Regeneration Power.
+The Powertrain controller also gets the information about Max Discharge Power and Max Charge Power from Battery Management System, State of Charge from Battery System. It also takes the feedback of Actual Motor Torque, Gear Ratio, Gear Number, Motor Torque-Speed profile data. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">In Vehicle Dynamics, the Force equations.
 Vehicle Propulsion Force = Net Traction Torque / Tire Radius;
-Vehicle Propulsion Force - Friction Brake Force = Wheel Force;
+Wheel Force = Vehicle Propulsion Force - Friction Brake Force;
 Wheel Force = AeroDynamic Force + Gradient Force + Rolling Resistance Force + Inertial Force;
+The inputs to the Vehicle Dynamics subsystems are the Vehicle Propulsion Force and Friction Brake Force.
+The outputs are Vehicle acceleration, velocity and distance. 
+It also gives out Aerodynamic Force, Gradient Force, Rolling Resistance Force and Intertial Force.
 </t>
+  </si>
+  <si>
+    <t>logout.eess_PresBatCur.*logout.eess_PresBatVolt/1000</t>
+  </si>
+  <si>
+    <t>logout.eess_BatHW_P_BatLossPwr.*sMP.phys.eess.BatHW_n_packs/1000</t>
+  </si>
+  <si>
+    <t>High Power Resistor</t>
+  </si>
+  <si>
+    <t>High Power Resistor Power</t>
+  </si>
+  <si>
+    <t>High Power Resistor Max allowed Power</t>
+  </si>
+  <si>
+    <t>hpr_pwr</t>
+  </si>
+  <si>
+    <t>hpr_max_pwr</t>
+  </si>
+  <si>
+    <t>logout.HPRS_Pwr_Cval</t>
+  </si>
+  <si>
+    <t>logout.HPRS_MaxPwr_Cval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Battery Management System calculates the Battery current limit and the power limit based on Ambient Temperature and State of Charge. These Battery Current and Power Limits are sent to Powertrain Controller, so that power train controller can demand the torque, that is adhered to these limits.
+Net Battery Power = Electric Motor 1 Power + Electric Motor 2 Power + Auxiliary Power + High Power Resistor Power </t>
+  </si>
+  <si>
+    <t>The High Power Resistor is activated during the regeneration braking on condition when power requirement for the auxiliary load and battery is fullfilled and left over power is dumped in HPR. The HPR is also activated, when there is heating requirment, which draws the power from battery.</t>
   </si>
 </sst>
 </file>
@@ -1370,26 +1438,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1408,27 +1462,59 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1503,22 +1589,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>485775</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:colOff>1524000</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>2972078</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>53340</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>4283317</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>17472</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
+        <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5FF86932-813C-2708-AD25-9E22B3903EE5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{83846FB4-A9EC-5919-9D3A-5E3ED017C0C2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1534,8 +1620,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1095375" y="771525"/>
-          <a:ext cx="9439553" cy="3444240"/>
+          <a:off x="2133600" y="238125"/>
+          <a:ext cx="10116427" cy="3774132"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1810,585 +1896,688 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="G27:J88"/>
+  <dimension ref="B27:H90"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="2" max="2" width="38.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="42.109375" style="41" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="121.44140625" style="12" customWidth="1"/>
     <col min="7" max="7" width="30.109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="26.33203125" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="54" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="82.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="27" spans="7:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="28" spans="7:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G28" s="8" t="s">
+    <row r="27" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="28" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B28" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="H28" s="9" t="s">
+      <c r="C28" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="I28" s="10" t="s">
+      <c r="D28" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="J28" s="9" t="s">
+      <c r="E28" s="33" t="s">
+        <v>327</v>
+      </c>
+      <c r="H28"/>
+    </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B29" s="22"/>
+      <c r="C29" s="27" t="s">
+        <v>6</v>
+      </c>
+      <c r="D29" s="42" t="s">
+        <v>29</v>
+      </c>
+      <c r="E29" s="34"/>
+      <c r="H29"/>
+    </row>
+    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B30" s="23"/>
+      <c r="C30" s="28"/>
+      <c r="D30" s="43" t="s">
+        <v>7</v>
+      </c>
+      <c r="E30" s="35"/>
+      <c r="H30"/>
+    </row>
+    <row r="31" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B31" s="24"/>
+      <c r="C31" s="29"/>
+      <c r="D31" s="44" t="s">
+        <v>32</v>
+      </c>
+      <c r="E31" s="36"/>
+      <c r="H31"/>
+    </row>
+    <row r="32" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B32" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="C32" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="D32" s="42" t="s">
+        <v>11</v>
+      </c>
+      <c r="E32" s="37" t="s">
+        <v>338</v>
+      </c>
+      <c r="H32"/>
+    </row>
+    <row r="33" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B33" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C33" s="31"/>
+      <c r="D33" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="E33" s="38"/>
+      <c r="H33"/>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B34" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="31"/>
+      <c r="D34" s="43"/>
+      <c r="E34" s="38"/>
+      <c r="H34"/>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B35" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C35" s="31"/>
+      <c r="D35" s="43"/>
+      <c r="E35" s="38"/>
+      <c r="H35"/>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B36" s="23" t="s">
+        <v>178</v>
+      </c>
+      <c r="C36" s="31"/>
+      <c r="D36" s="43"/>
+      <c r="E36" s="38"/>
+      <c r="H36"/>
+    </row>
+    <row r="37" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B37" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="C37" s="32"/>
+      <c r="D37" s="44"/>
+      <c r="E37" s="39"/>
+      <c r="H37"/>
+    </row>
+    <row r="38" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B38" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C38" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="D38" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="E38" s="37" t="s">
+        <v>339</v>
+      </c>
+      <c r="H38"/>
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B39" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="C39" s="28"/>
+      <c r="D39" s="43" t="s">
+        <v>171</v>
+      </c>
+      <c r="E39" s="38"/>
+      <c r="H39"/>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B40" s="23"/>
+      <c r="C40" s="28"/>
+      <c r="D40" s="43" t="s">
+        <v>300</v>
+      </c>
+      <c r="E40" s="38"/>
+      <c r="H40"/>
+    </row>
+    <row r="41" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B41" s="23"/>
+      <c r="C41" s="28"/>
+      <c r="D41" s="43" t="s">
+        <v>301</v>
+      </c>
+      <c r="E41" s="38"/>
+      <c r="H41"/>
+    </row>
+    <row r="42" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B42" s="23"/>
+      <c r="C42" s="28"/>
+      <c r="D42" s="43" t="s">
+        <v>304</v>
+      </c>
+      <c r="E42" s="38"/>
+      <c r="H42"/>
+    </row>
+    <row r="43" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B43" s="23"/>
+      <c r="C43" s="28"/>
+      <c r="D43" s="43" t="s">
+        <v>305</v>
+      </c>
+      <c r="E43" s="38"/>
+      <c r="H43"/>
+    </row>
+    <row r="44" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B44" s="23"/>
+      <c r="C44" s="28"/>
+      <c r="D44" s="43"/>
+      <c r="E44" s="38"/>
+      <c r="H44"/>
+    </row>
+    <row r="45" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B45" s="23"/>
+      <c r="C45" s="28"/>
+      <c r="D45" s="43"/>
+      <c r="E45" s="38"/>
+      <c r="H45"/>
+    </row>
+    <row r="46" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B46" s="23"/>
+      <c r="C46" s="28"/>
+      <c r="D46" s="43"/>
+      <c r="E46" s="38"/>
+      <c r="H46"/>
+    </row>
+    <row r="47" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B47" s="23"/>
+      <c r="C47" s="28"/>
+      <c r="D47" s="43"/>
+      <c r="E47" s="38"/>
+      <c r="H47"/>
+    </row>
+    <row r="48" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B48" s="24"/>
+      <c r="C48" s="29"/>
+      <c r="D48" s="44"/>
+      <c r="E48" s="39"/>
+      <c r="H48"/>
+    </row>
+    <row r="49" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B49" s="22" t="s">
+        <v>170</v>
+      </c>
+      <c r="C49" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="D49" s="45" t="s">
+        <v>36</v>
+      </c>
+      <c r="E49" s="37" t="s">
+        <v>328</v>
+      </c>
+      <c r="H49"/>
+    </row>
+    <row r="50" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B50" s="23" t="s">
+        <v>171</v>
+      </c>
+      <c r="C50" s="31"/>
+      <c r="D50" s="41" t="s">
+        <v>38</v>
+      </c>
+      <c r="E50" s="38"/>
+      <c r="H50"/>
+    </row>
+    <row r="51" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B51" s="23" t="s">
+        <v>302</v>
+      </c>
+      <c r="C51" s="31"/>
+      <c r="D51" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="E51" s="38"/>
+      <c r="H51"/>
+    </row>
+    <row r="52" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B52" s="23" t="s">
+        <v>303</v>
+      </c>
+      <c r="C52" s="31"/>
+      <c r="D52" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="E52" s="38"/>
+      <c r="H52"/>
+    </row>
+    <row r="53" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B53" s="23"/>
+      <c r="C53" s="31"/>
+      <c r="D53" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="E53" s="38"/>
+      <c r="H53"/>
+    </row>
+    <row r="54" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B54" s="23"/>
+      <c r="C54" s="31"/>
+      <c r="D54" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="E54" s="38"/>
+      <c r="H54"/>
+    </row>
+    <row r="55" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B55" s="23"/>
+      <c r="C55" s="31"/>
+      <c r="D55" s="41" t="s">
+        <v>172</v>
+      </c>
+      <c r="E55" s="38"/>
+      <c r="H55"/>
+    </row>
+    <row r="56" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B56" s="23"/>
+      <c r="C56" s="31"/>
+      <c r="D56" s="41" t="s">
+        <v>173</v>
+      </c>
+      <c r="E56" s="38"/>
+      <c r="H56"/>
+    </row>
+    <row r="57" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B57" s="23"/>
+      <c r="C57" s="31"/>
+      <c r="D57" s="41" t="s">
+        <v>50</v>
+      </c>
+      <c r="E57" s="38"/>
+      <c r="H57"/>
+    </row>
+    <row r="58" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B58" s="23"/>
+      <c r="C58" s="31"/>
+      <c r="D58" s="41" t="s">
+        <v>174</v>
+      </c>
+      <c r="E58" s="38"/>
+      <c r="H58"/>
+    </row>
+    <row r="59" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B59" s="23"/>
+      <c r="C59" s="31"/>
+      <c r="D59" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="E59" s="38"/>
+      <c r="H59"/>
+    </row>
+    <row r="60" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B60" s="24"/>
+      <c r="C60" s="32"/>
+      <c r="D60" s="46" t="s">
+        <v>175</v>
+      </c>
+      <c r="E60" s="39"/>
+      <c r="H60"/>
+    </row>
+    <row r="61" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B61" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="C61" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="D61" s="45" t="s">
+        <v>176</v>
+      </c>
+      <c r="E61" s="37" t="s">
         <v>329</v>
       </c>
-    </row>
-    <row r="29" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G29" s="22"/>
-      <c r="H29" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="I29" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="J29" s="28"/>
-    </row>
-    <row r="30" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G30" s="24"/>
-      <c r="H30" s="38"/>
-      <c r="I30" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="J30" s="29"/>
-    </row>
-    <row r="31" spans="7:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G31" s="26"/>
-      <c r="H31" s="39"/>
-      <c r="I31" s="27" t="s">
+      <c r="H61"/>
+    </row>
+    <row r="62" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B62" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="C62" s="28"/>
+      <c r="D62" s="41" t="s">
+        <v>177</v>
+      </c>
+      <c r="E62" s="38"/>
+      <c r="H62"/>
+    </row>
+    <row r="63" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B63" s="23"/>
+      <c r="C63" s="28"/>
+      <c r="D63" s="41" t="s">
+        <v>15</v>
+      </c>
+      <c r="E63" s="38"/>
+      <c r="H63"/>
+    </row>
+    <row r="64" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B64" s="23"/>
+      <c r="C64" s="28"/>
+      <c r="D64" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="E64" s="38"/>
+      <c r="H64"/>
+    </row>
+    <row r="65" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B65" s="24"/>
+      <c r="C65" s="29"/>
+      <c r="D65" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="E65" s="39"/>
+      <c r="H65"/>
+    </row>
+    <row r="66" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B66" s="25" t="s">
+        <v>176</v>
+      </c>
+      <c r="C66" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="D66" s="47" t="s">
+        <v>18</v>
+      </c>
+      <c r="E66" s="40" t="s">
+        <v>330</v>
+      </c>
+      <c r="H66"/>
+    </row>
+    <row r="67" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B67" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="C67" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="D67" s="45" t="s">
+        <v>179</v>
+      </c>
+      <c r="E67" s="34" t="s">
+        <v>331</v>
+      </c>
+      <c r="H67"/>
+    </row>
+    <row r="68" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B68" s="24"/>
+      <c r="C68" s="32"/>
+      <c r="D68" s="46" t="s">
+        <v>180</v>
+      </c>
+      <c r="E68" s="36"/>
+      <c r="H68"/>
+    </row>
+    <row r="69" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B69" s="22" t="s">
+        <v>325</v>
+      </c>
+      <c r="C69" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="D69" s="45" t="s">
+        <v>20</v>
+      </c>
+      <c r="E69" s="37" t="s">
+        <v>340</v>
+      </c>
+      <c r="H69"/>
+    </row>
+    <row r="70" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B70" s="23" t="s">
+        <v>179</v>
+      </c>
+      <c r="C70" s="28"/>
+      <c r="D70" s="41" t="s">
+        <v>21</v>
+      </c>
+      <c r="E70" s="38"/>
+      <c r="H70"/>
+    </row>
+    <row r="71" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B71" s="23"/>
+      <c r="C71" s="28"/>
+      <c r="D71" s="41" t="s">
+        <v>22</v>
+      </c>
+      <c r="E71" s="38"/>
+      <c r="H71"/>
+    </row>
+    <row r="72" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B72" s="23"/>
+      <c r="C72" s="28"/>
+      <c r="D72" s="41" t="s">
+        <v>61</v>
+      </c>
+      <c r="E72" s="38"/>
+      <c r="H72"/>
+    </row>
+    <row r="73" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B73" s="23"/>
+      <c r="C73" s="28"/>
+      <c r="D73" s="41" t="s">
+        <v>62</v>
+      </c>
+      <c r="E73" s="38"/>
+      <c r="H73"/>
+    </row>
+    <row r="74" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B74" s="23"/>
+      <c r="C74" s="28"/>
+      <c r="D74" s="41" t="s">
+        <v>65</v>
+      </c>
+      <c r="E74" s="38"/>
+      <c r="H74"/>
+    </row>
+    <row r="75" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B75" s="23"/>
+      <c r="C75" s="28"/>
+      <c r="D75" s="41" t="s">
+        <v>318</v>
+      </c>
+      <c r="E75" s="38"/>
+      <c r="H75"/>
+    </row>
+    <row r="76" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B76" s="24"/>
+      <c r="C76" s="29"/>
+      <c r="D76" s="46" t="s">
+        <v>67</v>
+      </c>
+      <c r="E76" s="39"/>
+      <c r="H76"/>
+    </row>
+    <row r="77" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B77" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="J31" s="30"/>
-    </row>
-    <row r="32" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G32" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="H32" s="40" t="s">
-        <v>0</v>
-      </c>
-      <c r="I32" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="J32" s="28"/>
-    </row>
-    <row r="33" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G33" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="H33" s="41"/>
-      <c r="I33" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="J33" s="29"/>
-    </row>
-    <row r="34" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G34" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="H34" s="41"/>
-      <c r="I34" s="25"/>
-      <c r="J34" s="29"/>
-    </row>
-    <row r="35" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G35" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="H35" s="41"/>
-      <c r="I35" s="25"/>
-      <c r="J35" s="29"/>
-    </row>
-    <row r="36" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G36" s="24" t="s">
-        <v>178</v>
-      </c>
-      <c r="H36" s="41"/>
-      <c r="I36" s="25"/>
-      <c r="J36" s="29"/>
-    </row>
-    <row r="37" spans="7:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G37" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="H37" s="42"/>
-      <c r="I37" s="27"/>
-      <c r="J37" s="30"/>
-    </row>
-    <row r="38" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G38" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="H38" s="37" t="s">
-        <v>2</v>
-      </c>
-      <c r="I38" s="23" t="s">
-        <v>170</v>
-      </c>
-      <c r="J38" s="28"/>
-    </row>
-    <row r="39" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G39" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="H39" s="38"/>
-      <c r="I39" s="25" t="s">
-        <v>171</v>
-      </c>
-      <c r="J39" s="29"/>
-    </row>
-    <row r="40" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G40" s="24"/>
-      <c r="H40" s="38"/>
-      <c r="I40" s="25" t="s">
-        <v>302</v>
-      </c>
-      <c r="J40" s="29"/>
-    </row>
-    <row r="41" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G41" s="24"/>
-      <c r="H41" s="38"/>
-      <c r="I41" s="25" t="s">
-        <v>303</v>
-      </c>
-      <c r="J41" s="29"/>
-    </row>
-    <row r="42" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G42" s="24"/>
-      <c r="H42" s="38"/>
-      <c r="I42" s="25" t="s">
-        <v>306</v>
-      </c>
-      <c r="J42" s="29"/>
-    </row>
-    <row r="43" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G43" s="24"/>
-      <c r="H43" s="38"/>
-      <c r="I43" s="25" t="s">
-        <v>307</v>
-      </c>
-      <c r="J43" s="29"/>
-    </row>
-    <row r="44" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G44" s="24"/>
-      <c r="H44" s="38"/>
-      <c r="I44" s="25"/>
-      <c r="J44" s="29"/>
-    </row>
-    <row r="45" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G45" s="24"/>
-      <c r="H45" s="38"/>
-      <c r="I45" s="25"/>
-      <c r="J45" s="29"/>
-    </row>
-    <row r="46" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G46" s="24"/>
-      <c r="H46" s="38"/>
-      <c r="I46" s="25"/>
-      <c r="J46" s="29"/>
-    </row>
-    <row r="47" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G47" s="24"/>
-      <c r="H47" s="38"/>
-      <c r="I47" s="25"/>
-      <c r="J47" s="29"/>
-    </row>
-    <row r="48" spans="7:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G48" s="26"/>
-      <c r="H48" s="39"/>
-      <c r="I48" s="27"/>
-      <c r="J48" s="30"/>
-    </row>
-    <row r="49" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G49" s="22" t="s">
-        <v>170</v>
-      </c>
-      <c r="H49" s="40" t="s">
-        <v>106</v>
-      </c>
-      <c r="I49" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="J49" s="28"/>
-    </row>
-    <row r="50" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G50" s="24" t="s">
-        <v>171</v>
-      </c>
-      <c r="H50" s="41"/>
-      <c r="I50" s="32" t="s">
-        <v>38</v>
-      </c>
-      <c r="J50" s="29"/>
-    </row>
-    <row r="51" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G51" s="24" t="s">
-        <v>304</v>
-      </c>
-      <c r="H51" s="41"/>
-      <c r="I51" s="32" t="s">
-        <v>40</v>
-      </c>
-      <c r="J51" s="29"/>
-    </row>
-    <row r="52" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G52" s="24" t="s">
-        <v>305</v>
-      </c>
-      <c r="H52" s="41"/>
-      <c r="I52" s="32" t="s">
-        <v>42</v>
-      </c>
-      <c r="J52" s="29"/>
-    </row>
-    <row r="53" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G53" s="24"/>
-      <c r="H53" s="41"/>
-      <c r="I53" s="32" t="s">
-        <v>44</v>
-      </c>
-      <c r="J53" s="29"/>
-    </row>
-    <row r="54" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G54" s="24"/>
-      <c r="H54" s="41"/>
-      <c r="I54" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="J54" s="29"/>
-    </row>
-    <row r="55" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G55" s="24"/>
-      <c r="H55" s="41"/>
-      <c r="I55" s="32" t="s">
-        <v>172</v>
-      </c>
-      <c r="J55" s="29"/>
-    </row>
-    <row r="56" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G56" s="24"/>
-      <c r="H56" s="41"/>
-      <c r="I56" s="32" t="s">
-        <v>173</v>
-      </c>
-      <c r="J56" s="29"/>
-    </row>
-    <row r="57" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G57" s="24"/>
-      <c r="H57" s="41"/>
-      <c r="I57" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="J57" s="29"/>
-    </row>
-    <row r="58" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G58" s="24"/>
-      <c r="H58" s="41"/>
-      <c r="I58" s="32" t="s">
-        <v>174</v>
-      </c>
-      <c r="J58" s="29"/>
-    </row>
-    <row r="59" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G59" s="24"/>
-      <c r="H59" s="41"/>
-      <c r="I59" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="J59" s="29"/>
-    </row>
-    <row r="60" spans="7:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G60" s="26"/>
-      <c r="H60" s="42"/>
-      <c r="I60" s="33" t="s">
-        <v>175</v>
-      </c>
-      <c r="J60" s="30"/>
-    </row>
-    <row r="61" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G61" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="H61" s="37" t="s">
-        <v>107</v>
-      </c>
-      <c r="I61" s="31" t="s">
-        <v>176</v>
-      </c>
-      <c r="J61" s="28"/>
-    </row>
-    <row r="62" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G62" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="H62" s="38"/>
-      <c r="I62" s="32" t="s">
-        <v>177</v>
-      </c>
-      <c r="J62" s="29"/>
-    </row>
-    <row r="63" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G63" s="24"/>
-      <c r="H63" s="38"/>
-      <c r="I63" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="J63" s="29"/>
-    </row>
-    <row r="64" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G64" s="24"/>
-      <c r="H64" s="38"/>
-      <c r="I64" s="32" t="s">
-        <v>178</v>
-      </c>
-      <c r="J64" s="29"/>
-    </row>
-    <row r="65" spans="7:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G65" s="26"/>
-      <c r="H65" s="39"/>
-      <c r="I65" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="J65" s="30"/>
-    </row>
-    <row r="66" spans="7:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G66" s="34" t="s">
-        <v>176</v>
-      </c>
-      <c r="H66" s="43" t="s">
-        <v>17</v>
-      </c>
-      <c r="I66" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J66" s="36"/>
-    </row>
-    <row r="67" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G67" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="H67" s="40" t="s">
-        <v>108</v>
-      </c>
-      <c r="I67" s="31" t="s">
-        <v>179</v>
-      </c>
-      <c r="J67" s="28"/>
-    </row>
-    <row r="68" spans="7:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G68" s="26"/>
-      <c r="H68" s="42"/>
-      <c r="I68" s="33" t="s">
-        <v>180</v>
-      </c>
-      <c r="J68" s="30"/>
-    </row>
-    <row r="69" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G69" s="22" t="s">
-        <v>327</v>
-      </c>
-      <c r="H69" s="37" t="s">
-        <v>19</v>
-      </c>
-      <c r="I69" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="J69" s="48" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="70" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G70" s="24" t="s">
-        <v>179</v>
-      </c>
-      <c r="H70" s="38"/>
-      <c r="I70" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="J70" s="49"/>
-    </row>
-    <row r="71" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G71" s="24"/>
-      <c r="H71" s="38"/>
-      <c r="I71" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J71" s="49"/>
-    </row>
-    <row r="72" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G72" s="24"/>
-      <c r="H72" s="38"/>
-      <c r="I72" s="32" t="s">
-        <v>61</v>
-      </c>
-      <c r="J72" s="49"/>
-    </row>
-    <row r="73" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G73" s="24"/>
-      <c r="H73" s="38"/>
-      <c r="I73" s="32" t="s">
-        <v>62</v>
-      </c>
-      <c r="J73" s="49"/>
-    </row>
-    <row r="74" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G74" s="24"/>
-      <c r="H74" s="38"/>
-      <c r="I74" s="32" t="s">
-        <v>65</v>
-      </c>
-      <c r="J74" s="49"/>
-    </row>
-    <row r="75" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G75" s="24"/>
-      <c r="H75" s="38"/>
-      <c r="I75" s="44" t="s">
-        <v>320</v>
-      </c>
-      <c r="J75" s="49"/>
-    </row>
-    <row r="76" spans="7:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G76" s="26"/>
-      <c r="H76" s="39"/>
-      <c r="I76" s="33" t="s">
-        <v>67</v>
-      </c>
-      <c r="J76" s="50"/>
-    </row>
-    <row r="77" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G77" s="22" t="s">
+      <c r="C77" s="27" t="s">
+        <v>109</v>
+      </c>
+      <c r="D77" s="45" t="s">
+        <v>68</v>
+      </c>
+      <c r="E77" s="37" t="s">
+        <v>332</v>
+      </c>
+      <c r="H77"/>
+    </row>
+    <row r="78" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B78" s="23"/>
+      <c r="C78" s="28"/>
+      <c r="D78" s="41" t="s">
+        <v>181</v>
+      </c>
+      <c r="E78" s="38"/>
+      <c r="H78"/>
+    </row>
+    <row r="79" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B79" s="23"/>
+      <c r="C79" s="28"/>
+      <c r="D79" s="41" t="s">
+        <v>73</v>
+      </c>
+      <c r="E79" s="38"/>
+      <c r="H79"/>
+    </row>
+    <row r="80" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B80" s="23"/>
+      <c r="C80" s="28"/>
+      <c r="D80" s="41" t="s">
+        <v>74</v>
+      </c>
+      <c r="E80" s="38"/>
+      <c r="H80"/>
+    </row>
+    <row r="81" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B81" s="23"/>
+      <c r="C81" s="28"/>
+      <c r="D81" s="41" t="s">
+        <v>75</v>
+      </c>
+      <c r="E81" s="38"/>
+      <c r="H81"/>
+    </row>
+    <row r="82" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B82" s="24"/>
+      <c r="C82" s="29"/>
+      <c r="D82" s="46" t="s">
+        <v>77</v>
+      </c>
+      <c r="E82" s="39"/>
+      <c r="H82"/>
+    </row>
+    <row r="83" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B83" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="H77" s="37" t="s">
-        <v>109</v>
-      </c>
-      <c r="I77" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="J77" s="45"/>
-    </row>
-    <row r="78" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G78" s="24"/>
-      <c r="H78" s="38"/>
-      <c r="I78" s="32" t="s">
-        <v>181</v>
-      </c>
-      <c r="J78" s="46"/>
-    </row>
-    <row r="79" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G79" s="24"/>
-      <c r="H79" s="38"/>
-      <c r="I79" s="32" t="s">
-        <v>73</v>
-      </c>
-      <c r="J79" s="46"/>
-    </row>
-    <row r="80" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G80" s="24"/>
-      <c r="H80" s="38"/>
-      <c r="I80" s="32" t="s">
-        <v>74</v>
-      </c>
-      <c r="J80" s="46"/>
-    </row>
-    <row r="81" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G81" s="24"/>
-      <c r="H81" s="38"/>
-      <c r="I81" s="32" t="s">
+      <c r="C83" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="D83" s="45" t="s">
+        <v>79</v>
+      </c>
+      <c r="E83" s="37" t="s">
+        <v>350</v>
+      </c>
+      <c r="H83"/>
+    </row>
+    <row r="84" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B84" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="J81" s="46"/>
-    </row>
-    <row r="82" spans="7:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G82" s="26"/>
-      <c r="H82" s="39"/>
-      <c r="I82" s="33" t="s">
-        <v>77</v>
-      </c>
-      <c r="J82" s="47"/>
-    </row>
-    <row r="83" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G83" s="22" t="s">
-        <v>32</v>
-      </c>
-      <c r="H83" s="40" t="s">
-        <v>110</v>
-      </c>
-      <c r="I83" s="31" t="s">
-        <v>79</v>
-      </c>
-      <c r="J83" s="48" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="84" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G84" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="H84" s="41"/>
-      <c r="I84" s="32" t="s">
+      <c r="C84" s="31"/>
+      <c r="D84" s="41" t="s">
         <v>81</v>
       </c>
-      <c r="J84" s="49"/>
-    </row>
-    <row r="85" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G85" s="24"/>
-      <c r="H85" s="41"/>
-      <c r="I85" s="32" t="s">
+      <c r="E84" s="38"/>
+      <c r="H84"/>
+    </row>
+    <row r="85" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B85" s="23"/>
+      <c r="C85" s="31"/>
+      <c r="D85" s="41" t="s">
         <v>83</v>
       </c>
-      <c r="J85" s="49"/>
-    </row>
-    <row r="86" spans="7:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G86" s="26"/>
-      <c r="H86" s="42"/>
-      <c r="I86" s="33" t="s">
+      <c r="E85" s="38"/>
+      <c r="H85"/>
+    </row>
+    <row r="86" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B86" s="24"/>
+      <c r="C86" s="32"/>
+      <c r="D86" s="46" t="s">
         <v>85</v>
       </c>
-      <c r="J86" s="50"/>
-    </row>
-    <row r="87" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G87" s="22"/>
-      <c r="H87" s="37" t="s">
+      <c r="E86" s="39"/>
+      <c r="H86"/>
+    </row>
+    <row r="87" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B87" s="22"/>
+      <c r="C87" s="27" t="s">
         <v>111</v>
       </c>
-      <c r="I87" s="31" t="s">
+      <c r="D87" s="45" t="s">
         <v>182</v>
       </c>
-      <c r="J87" s="28"/>
-    </row>
-    <row r="88" spans="7:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G88" s="26"/>
-      <c r="H88" s="39"/>
-      <c r="I88" s="33" t="s">
+      <c r="E87" s="34" t="s">
+        <v>333</v>
+      </c>
+      <c r="H87"/>
+    </row>
+    <row r="88" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B88" s="23"/>
+      <c r="C88" s="28"/>
+      <c r="D88" s="48" t="s">
         <v>183</v>
       </c>
-      <c r="J88" s="30"/>
+      <c r="E88" s="35"/>
+      <c r="H88"/>
+    </row>
+    <row r="89" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B89" s="22"/>
+      <c r="C89" s="30" t="s">
+        <v>343</v>
+      </c>
+      <c r="D89" s="49" t="s">
+        <v>344</v>
+      </c>
+      <c r="E89" s="37" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="90" spans="2:8" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B90" s="24"/>
+      <c r="C90" s="32"/>
+      <c r="D90" s="50" t="s">
+        <v>345</v>
+      </c>
+      <c r="E90" s="39"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
-    <mergeCell ref="J87:J88"/>
-    <mergeCell ref="J77:J82"/>
-    <mergeCell ref="J69:J76"/>
-    <mergeCell ref="J67:J68"/>
-    <mergeCell ref="H38:H48"/>
-    <mergeCell ref="J83:J86"/>
-    <mergeCell ref="J29:J31"/>
-    <mergeCell ref="J32:J37"/>
-    <mergeCell ref="J38:J48"/>
-    <mergeCell ref="J49:J60"/>
-    <mergeCell ref="J61:J65"/>
-    <mergeCell ref="H77:H82"/>
-    <mergeCell ref="H83:H86"/>
-    <mergeCell ref="H61:H65"/>
-    <mergeCell ref="H69:H76"/>
-    <mergeCell ref="H87:H88"/>
-    <mergeCell ref="H29:H31"/>
-    <mergeCell ref="H32:H37"/>
-    <mergeCell ref="H49:H60"/>
-    <mergeCell ref="H67:H68"/>
+  <mergeCells count="22">
+    <mergeCell ref="C89:C90"/>
+    <mergeCell ref="E89:E90"/>
+    <mergeCell ref="C29:C31"/>
+    <mergeCell ref="C32:C37"/>
+    <mergeCell ref="C49:C60"/>
+    <mergeCell ref="C67:C68"/>
+    <mergeCell ref="E29:E31"/>
+    <mergeCell ref="E32:E37"/>
+    <mergeCell ref="E38:E48"/>
+    <mergeCell ref="E49:E60"/>
+    <mergeCell ref="E61:E65"/>
+    <mergeCell ref="E87:E88"/>
+    <mergeCell ref="E77:E82"/>
+    <mergeCell ref="E69:E76"/>
+    <mergeCell ref="E67:E68"/>
+    <mergeCell ref="C38:C48"/>
+    <mergeCell ref="E83:E86"/>
+    <mergeCell ref="C77:C82"/>
+    <mergeCell ref="C83:C86"/>
+    <mergeCell ref="C61:C65"/>
+    <mergeCell ref="C69:C76"/>
+    <mergeCell ref="C87:C88"/>
   </mergeCells>
-  <conditionalFormatting sqref="I29:I88 G29:G88">
-    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
+  <conditionalFormatting sqref="B29:B88 D29:D90">
+    <cfRule type="duplicateValues" dxfId="4" priority="13"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -2402,7 +2591,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="58.5546875" style="11" customWidth="1"/>
+    <col min="2" max="2" width="57" style="11" customWidth="1"/>
     <col min="3" max="3" width="19" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24.6640625" style="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="46.44140625" style="11" bestFit="1" customWidth="1"/>
@@ -2446,22 +2635,22 @@
         <v>96</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>284</v>
+      </c>
+      <c r="D2" s="20" t="s">
         <v>285</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="E2" s="17" t="s">
         <v>286</v>
       </c>
-      <c r="D2" s="20" t="s">
-        <v>287</v>
-      </c>
-      <c r="E2" s="17" t="s">
-        <v>288</v>
-      </c>
       <c r="F2" s="17" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="G2" s="17" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
@@ -2564,13 +2753,13 @@
         <v>188</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
@@ -2592,13 +2781,13 @@
         <v>189</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="G7" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="H7" s="5"/>
       <c r="I7" s="5"/>
@@ -2611,7 +2800,7 @@
         <v>97</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C8" s="16" t="s">
         <v>3</v>
@@ -2639,7 +2828,7 @@
         <v>97</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C9" s="16" t="s">
         <v>3</v>
@@ -2667,22 +2856,22 @@
         <v>97</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C10" s="16" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="G10" s="17" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
@@ -2695,22 +2884,22 @@
         <v>97</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C11" s="16" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="F11" s="17" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="G11" s="17" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="H11" s="5"/>
       <c r="I11" s="5"/>
@@ -2723,22 +2912,22 @@
         <v>97</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C12" s="16" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="F12" s="17" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="G12" s="17" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
@@ -2751,22 +2940,22 @@
         <v>97</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C13" s="16" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="20" t="s">
+        <v>313</v>
+      </c>
+      <c r="E13" s="17" t="s">
         <v>315</v>
       </c>
-      <c r="E13" s="17" t="s">
-        <v>317</v>
-      </c>
       <c r="F13" s="17" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="G13" s="17" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
@@ -2779,7 +2968,7 @@
         <v>95</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C14" s="16" t="s">
         <v>3</v>
@@ -2807,7 +2996,7 @@
         <v>95</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C15" s="16" t="s">
         <v>3</v>
@@ -2891,7 +3080,7 @@
         <v>95</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C18" s="16" t="s">
         <v>4</v>
@@ -2919,7 +3108,7 @@
         <v>95</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C19" s="16" t="s">
         <v>4</v>
@@ -3003,7 +3192,7 @@
         <v>95</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C22" s="16" t="s">
         <v>3</v>
@@ -3031,7 +3220,7 @@
         <v>95</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C23" s="16" t="s">
         <v>3</v>
@@ -3059,7 +3248,7 @@
         <v>95</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C24" s="16" t="s">
         <v>3</v>
@@ -3087,7 +3276,7 @@
         <v>95</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C25" s="16" t="s">
         <v>3</v>
@@ -3115,7 +3304,7 @@
         <v>94</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C26" s="16" t="s">
         <v>3</v>
@@ -3178,13 +3367,13 @@
         <v>206</v>
       </c>
       <c r="E28" s="17" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F28" s="17" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="G28" s="17" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="H28" s="17"/>
       <c r="I28" s="5"/>
@@ -3260,13 +3449,13 @@
         <v>209</v>
       </c>
       <c r="E31" s="19" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="F31" s="19" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G31" s="19" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="H31" s="5"/>
       <c r="I31" s="5"/>
@@ -3288,13 +3477,13 @@
         <v>217</v>
       </c>
       <c r="E32" s="19" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="F32" s="19" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="G32" s="19" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="H32" s="5"/>
       <c r="I32" s="5"/>
@@ -3335,22 +3524,22 @@
         <v>92</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C34" s="16" t="s">
         <v>63</v>
       </c>
       <c r="D34" s="20" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E34" s="19" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="F34" s="19" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="G34" s="19" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="H34" s="5"/>
       <c r="I34" s="5"/>
@@ -3372,13 +3561,13 @@
         <v>213</v>
       </c>
       <c r="E35" s="17" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="F35" s="17" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="G35" s="17" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="H35" s="5"/>
       <c r="I35" s="5"/>
@@ -3447,22 +3636,22 @@
         <v>92</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C38" s="16" t="s">
         <v>63</v>
       </c>
       <c r="D38" s="20" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="E38" s="17" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="F38" s="17" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="G38" s="17" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="H38" s="5"/>
       <c r="I38" s="5"/>
@@ -3512,13 +3701,13 @@
         <v>211</v>
       </c>
       <c r="E40" s="17" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="F40" s="17" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="G40" s="17" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="H40" s="5"/>
       <c r="I40" s="5"/>
@@ -3540,13 +3729,13 @@
         <v>212</v>
       </c>
       <c r="E41" s="17" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="F41" s="17" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="G41" s="17" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H41" s="5"/>
       <c r="I41" s="5"/>
@@ -3568,13 +3757,13 @@
         <v>216</v>
       </c>
       <c r="E42" s="17" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="F42" s="17" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="G42" s="17" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="H42" s="17"/>
       <c r="I42" s="5"/>
@@ -3587,7 +3776,7 @@
         <v>90</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C43" s="16" t="s">
         <v>69</v>
@@ -3643,7 +3832,7 @@
         <v>90</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C45" s="16" t="s">
         <v>4</v>
@@ -3652,13 +3841,13 @@
         <v>221</v>
       </c>
       <c r="E45" s="17" t="s">
-        <v>232</v>
+        <v>341</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="H45" s="5"/>
       <c r="I45" s="5"/>
@@ -3680,13 +3869,13 @@
         <v>222</v>
       </c>
       <c r="E46" s="17" t="s">
-        <v>233</v>
+        <v>342</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="H46" s="5"/>
       <c r="I46" s="5"/>
@@ -3739,10 +3928,10 @@
         <v>78</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="H48" s="5"/>
       <c r="I48" s="5"/>
@@ -3755,7 +3944,7 @@
         <v>91</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>79</v>
+        <v>334</v>
       </c>
       <c r="C49" s="16" t="s">
         <v>69</v>
@@ -3783,7 +3972,7 @@
         <v>91</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>81</v>
+        <v>335</v>
       </c>
       <c r="C50" s="16" t="s">
         <v>69</v>
@@ -3811,7 +4000,7 @@
         <v>91</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>83</v>
+        <v>336</v>
       </c>
       <c r="C51" s="16" t="s">
         <v>4</v>
@@ -3839,7 +4028,7 @@
         <v>91</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>85</v>
+        <v>337</v>
       </c>
       <c r="C52" s="16" t="s">
         <v>4</v>
@@ -3848,13 +4037,13 @@
         <v>228</v>
       </c>
       <c r="E52" s="17" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="F52" s="17" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G52" s="17" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="H52" s="5"/>
       <c r="I52" s="5"/>
@@ -3876,13 +4065,13 @@
         <v>229</v>
       </c>
       <c r="E53" s="19" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F53" s="19" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="G53" s="19" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="H53" s="5"/>
       <c r="I53" s="5"/>
@@ -3904,13 +4093,13 @@
         <v>230</v>
       </c>
       <c r="E54" s="19" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F54" s="19" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="G54" s="19" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="H54" s="5"/>
       <c r="I54" s="5"/>
@@ -3919,13 +4108,27 @@
       <c r="L54" s="5"/>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A55" s="5"/>
-      <c r="B55" s="19"/>
-      <c r="C55" s="16"/>
-      <c r="D55" s="17"/>
-      <c r="E55" s="19"/>
-      <c r="F55" s="5"/>
-      <c r="G55" s="5"/>
+      <c r="A55" s="18" t="s">
+        <v>343</v>
+      </c>
+      <c r="B55" s="19" t="s">
+        <v>344</v>
+      </c>
+      <c r="C55" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D55" s="20" t="s">
+        <v>346</v>
+      </c>
+      <c r="E55" s="19" t="s">
+        <v>348</v>
+      </c>
+      <c r="F55" s="19" t="s">
+        <v>348</v>
+      </c>
+      <c r="G55" s="19" t="s">
+        <v>348</v>
+      </c>
       <c r="H55" s="5"/>
       <c r="I55" s="5"/>
       <c r="J55" s="5"/>
@@ -3933,13 +4136,27 @@
       <c r="L55" s="5"/>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A56" s="5"/>
-      <c r="B56" s="19"/>
-      <c r="C56" s="16"/>
-      <c r="D56" s="17"/>
-      <c r="E56" s="19"/>
-      <c r="F56" s="5"/>
-      <c r="G56" s="5"/>
+      <c r="A56" s="18" t="s">
+        <v>343</v>
+      </c>
+      <c r="B56" s="19" t="s">
+        <v>345</v>
+      </c>
+      <c r="C56" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D56" s="20" t="s">
+        <v>347</v>
+      </c>
+      <c r="E56" s="19" t="s">
+        <v>349</v>
+      </c>
+      <c r="F56" s="19" t="s">
+        <v>349</v>
+      </c>
+      <c r="G56" s="19" t="s">
+        <v>349</v>
+      </c>
       <c r="H56" s="5"/>
       <c r="I56" s="5"/>
       <c r="J56" s="5"/>
@@ -4663,16 +4880,16 @@
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="B2:B7">
-    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:B54">
-    <cfRule type="duplicateValues" dxfId="3" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8:B54">
-    <cfRule type="duplicateValues" dxfId="2" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D54">
-    <cfRule type="duplicateValues" dxfId="1" priority="12"/>
+  <conditionalFormatting sqref="D2:D56">
+    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -4686,7 +4903,7 @@
   <cols>
     <col min="1" max="1" width="29.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="48" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" style="1" customWidth="1"/>
     <col min="4" max="4" width="34.109375" customWidth="1"/>
     <col min="5" max="5" width="43.109375" customWidth="1"/>
     <col min="6" max="6" width="39" customWidth="1"/>
@@ -4767,22 +4984,22 @@
         <v>95</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
@@ -4798,7 +5015,7 @@
         <v>3</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>112</v>
@@ -4823,7 +5040,7 @@
         <v>4</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>159</v>
@@ -4848,7 +5065,7 @@
         <v>4</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>160</v>
@@ -4873,7 +5090,7 @@
         <v>114</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>164</v>
@@ -4898,7 +5115,7 @@
         <v>3</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>165</v>
@@ -4923,7 +5140,7 @@
         <v>71</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>166</v>
@@ -4948,7 +5165,7 @@
         <v>114</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>161</v>
@@ -4973,7 +5190,7 @@
         <v>3</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>162</v>
@@ -4998,7 +5215,7 @@
         <v>71</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>163</v>
@@ -5023,7 +5240,7 @@
         <v>114</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>161</v>
@@ -5048,7 +5265,7 @@
         <v>3</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>169</v>
@@ -5084,7 +5301,7 @@
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="21" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>145</v>
@@ -5116,20 +5333,20 @@
         <v>92</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="21" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="H20" s="5"/>
       <c r="I20" s="5"/>
@@ -5139,11 +5356,11 @@
         <v>92</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C21" s="6"/>
       <c r="D21" s="21" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E21" s="5" t="s">
         <v>146</v>
@@ -5165,19 +5382,19 @@
         <v>115</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D22" s="21" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
@@ -5193,7 +5410,7 @@
         <v>144</v>
       </c>
       <c r="D23" s="21" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>147</v>
@@ -5216,10 +5433,10 @@
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="21" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>125</v>
@@ -5241,7 +5458,7 @@
         <v>1</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>126</v>
@@ -5266,16 +5483,16 @@
         <v>124</v>
       </c>
       <c r="D26" s="21" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="H26" s="5"/>
       <c r="I26" s="5"/>
@@ -5291,7 +5508,7 @@
         <v>1</v>
       </c>
       <c r="D27" s="21" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E27" s="5" t="s">
         <v>127</v>
@@ -5316,7 +5533,7 @@
         <v>69</v>
       </c>
       <c r="D28" s="21" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E28" s="5" t="s">
         <v>136</v>
@@ -5341,7 +5558,7 @@
         <v>69</v>
       </c>
       <c r="D29" s="21" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E29" s="5" t="s">
         <v>137</v>
@@ -5366,7 +5583,7 @@
         <v>1</v>
       </c>
       <c r="D30" s="21" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E30" s="5" t="s">
         <v>138</v>
@@ -5391,7 +5608,7 @@
         <v>33</v>
       </c>
       <c r="D31" s="21" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E31" s="5" t="s">
         <v>139</v>
@@ -5416,7 +5633,7 @@
         <v>69</v>
       </c>
       <c r="D32" s="21" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E32" s="5" t="s">
         <v>140</v>
@@ -5441,7 +5658,7 @@
         <v>69</v>
       </c>
       <c r="D33" s="21" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E33" s="5" t="s">
         <v>141</v>
@@ -5466,7 +5683,7 @@
         <v>1</v>
       </c>
       <c r="D34" s="21" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E34" s="5" t="s">
         <v>142</v>
@@ -5489,7 +5706,7 @@
         <v>33</v>
       </c>
       <c r="D35" s="21" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E35" s="5" t="s">
         <v>143</v>
@@ -5530,7 +5747,7 @@
         <v>4</v>
       </c>
       <c r="D1" s="21" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>148</v>
@@ -5555,7 +5772,7 @@
         <v>3</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>149</v>
@@ -5580,7 +5797,7 @@
         <v>114</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>150</v>

--- a/eBus_Functions/Post_Processing/Root_Cause_Analysis_Work/info/eBus_Model_Info.xlsx
+++ b/eBus_Functions/Post_Processing/Root_Cause_Analysis_Work/info/eBus_Model_Info.xlsx
@@ -8,15 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\TempData\Github\eBus_Tool\eBus_Functions\Post_Processing\Root_Cause_Analysis_Work\info\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E79914EF-CCAB-49C9-9C0F-2D2CB603C8DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF227378-3B1D-4275-BAFD-D07C7631569C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Block_Diagram" sheetId="1" r:id="rId1"/>
     <sheet name="Signal_Evaluation" sheetId="2" r:id="rId2"/>
     <sheet name="Specifications" sheetId="3" r:id="rId3"/>
-    <sheet name="Sheet1" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="706" uniqueCount="344">
   <si>
     <t>Driver</t>
   </si>
@@ -381,15 +380,6 @@
     <t>Final Drive Ratio</t>
   </si>
   <si>
-    <t>Axle Torque Loss map [m x n]</t>
-  </si>
-  <si>
-    <t>Axle Torque In Breakpoint [m]</t>
-  </si>
-  <si>
-    <t>Axle Speed Out Breakpoint [n]</t>
-  </si>
-  <si>
     <t>Battery Capacity</t>
   </si>
   <si>
@@ -474,15 +464,6 @@
     <t>sMP.phys.mec.mec_massVehicle_kg</t>
   </si>
   <si>
-    <t>sMP.phys.mec.axle2.axleLoss_map_torqueAxleIn_Nm</t>
-  </si>
-  <si>
-    <t>sMP.phys.mec.axle2.axleLoss_y_torqueAxleIn_Nm</t>
-  </si>
-  <si>
-    <t>sMP.phys.mec.axle2.axleLoss_x_speedAxleOut_rpm</t>
-  </si>
-  <si>
     <t>Motor Power Loss map [m x n x v]</t>
   </si>
   <si>
@@ -868,15 +849,6 @@
   </si>
   <si>
     <t>VDy_mec_massVehicle_kg</t>
-  </si>
-  <si>
-    <t>VDy_axleLoss_map_torqueAxleIn_Nm</t>
-  </si>
-  <si>
-    <t>VDy_axleLoss_y_torqueAxleIn_Nm</t>
-  </si>
-  <si>
-    <t>VDy_axleLoss_x_speedAxleOut_rpm</t>
   </si>
   <si>
     <t>Time</t>
@@ -1097,12 +1069,15 @@
   <si>
     <t>The High Power Resistor is activated during the regeneration braking on condition when power requirement for the auxiliary load and battery is fullfilled and left over power is dumped in HPR. The HPR is also activated, when there is heating requirment, which draws the power from battery.</t>
   </si>
+  <si>
+    <t>(logout.mec_brk_Axle1_TiBrk_info+logout.mec_brk_Axle2_TiBrk_info+logout.mec_brk_Axle3_TiBrk_info+logout.mec_brk_Axle4_TiBrk_info)/(sMP.global.mec_rWheelDriven*0.001)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1154,6 +1129,14 @@
     <font>
       <b/>
       <sz val="12"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
       <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -1384,7 +1367,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1401,15 +1384,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1444,45 +1418,6 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1507,14 +1442,56 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1589,22 +1566,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1524000</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:colOff>2082165</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>17145</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>4283317</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>17472</xdr:rowOff>
+      <xdr:colOff>4803378</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>97492</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2">
+        <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{83846FB4-A9EC-5919-9D3A-5E3ED017C0C2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1CA4102B-FC93-C383-6B45-010F97127767}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1620,8 +1597,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2133600" y="238125"/>
-          <a:ext cx="10116427" cy="3774132"/>
+          <a:off x="2691765" y="379095"/>
+          <a:ext cx="10074513" cy="3888442"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1901,8 +1878,8 @@
   <cols>
     <col min="2" max="2" width="38.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="42.109375" style="41" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="121.44140625" style="12" customWidth="1"/>
+    <col min="4" max="4" width="42.109375" style="25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="121.44140625" style="9" customWidth="1"/>
     <col min="7" max="7" width="30.109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="26.33203125" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="54" bestFit="1" customWidth="1"/>
@@ -1910,646 +1887,646 @@
   </cols>
   <sheetData>
     <row r="27" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="28" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B28" s="8" t="s">
+    <row r="28" spans="2:8" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B28" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="C28" s="9" t="s">
+      <c r="C28" s="35" t="s">
         <v>86</v>
       </c>
-      <c r="D28" s="10" t="s">
+      <c r="D28" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="E28" s="33" t="s">
-        <v>327</v>
+      <c r="E28" s="35" t="s">
+        <v>318</v>
       </c>
       <c r="H28"/>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B29" s="22"/>
-      <c r="C29" s="27" t="s">
+      <c r="B29" s="19"/>
+      <c r="C29" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="D29" s="42" t="s">
+      <c r="D29" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="E29" s="34"/>
+      <c r="E29" s="46"/>
       <c r="H29"/>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B30" s="23"/>
-      <c r="C30" s="28"/>
-      <c r="D30" s="43" t="s">
+      <c r="B30" s="20"/>
+      <c r="C30" s="38"/>
+      <c r="D30" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="E30" s="35"/>
+      <c r="E30" s="47"/>
       <c r="H30"/>
     </row>
     <row r="31" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="24"/>
-      <c r="C31" s="29"/>
-      <c r="D31" s="44" t="s">
+      <c r="B31" s="21"/>
+      <c r="C31" s="42"/>
+      <c r="D31" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="E31" s="36"/>
+      <c r="E31" s="48"/>
       <c r="H31"/>
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B32" s="22" t="s">
+      <c r="B32" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="C32" s="30" t="s">
+      <c r="C32" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="D32" s="42" t="s">
+      <c r="D32" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="E32" s="37" t="s">
-        <v>338</v>
+      <c r="E32" s="39" t="s">
+        <v>329</v>
       </c>
       <c r="H32"/>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B33" s="23" t="s">
+      <c r="B33" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="C33" s="31"/>
-      <c r="D33" s="43" t="s">
+      <c r="C33" s="44"/>
+      <c r="D33" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="E33" s="38"/>
+      <c r="E33" s="40"/>
       <c r="H33"/>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B34" s="23" t="s">
+      <c r="B34" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C34" s="31"/>
-      <c r="D34" s="43"/>
-      <c r="E34" s="38"/>
+      <c r="C34" s="44"/>
+      <c r="D34" s="27"/>
+      <c r="E34" s="40"/>
       <c r="H34"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B35" s="23" t="s">
+      <c r="B35" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="C35" s="31"/>
-      <c r="D35" s="43"/>
-      <c r="E35" s="38"/>
+      <c r="C35" s="44"/>
+      <c r="D35" s="27"/>
+      <c r="E35" s="40"/>
       <c r="H35"/>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B36" s="23" t="s">
-        <v>178</v>
-      </c>
-      <c r="C36" s="31"/>
-      <c r="D36" s="43"/>
-      <c r="E36" s="38"/>
+      <c r="B36" s="20" t="s">
+        <v>172</v>
+      </c>
+      <c r="C36" s="44"/>
+      <c r="D36" s="27"/>
+      <c r="E36" s="40"/>
       <c r="H36"/>
     </row>
     <row r="37" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="24" t="s">
+      <c r="B37" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="C37" s="32"/>
-      <c r="D37" s="44"/>
-      <c r="E37" s="39"/>
+      <c r="C37" s="45"/>
+      <c r="D37" s="28"/>
+      <c r="E37" s="41"/>
       <c r="H37"/>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B38" s="22" t="s">
+      <c r="B38" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="C38" s="27" t="s">
+      <c r="C38" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="D38" s="42" t="s">
+      <c r="D38" s="26" t="s">
+        <v>164</v>
+      </c>
+      <c r="E38" s="39" t="s">
+        <v>330</v>
+      </c>
+      <c r="H38"/>
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B39" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="C39" s="38"/>
+      <c r="D39" s="27" t="s">
+        <v>165</v>
+      </c>
+      <c r="E39" s="40"/>
+      <c r="H39"/>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B40" s="20"/>
+      <c r="C40" s="38"/>
+      <c r="D40" s="27" t="s">
+        <v>291</v>
+      </c>
+      <c r="E40" s="40"/>
+      <c r="H40"/>
+    </row>
+    <row r="41" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B41" s="20"/>
+      <c r="C41" s="38"/>
+      <c r="D41" s="27" t="s">
+        <v>292</v>
+      </c>
+      <c r="E41" s="40"/>
+      <c r="H41"/>
+    </row>
+    <row r="42" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B42" s="20"/>
+      <c r="C42" s="38"/>
+      <c r="D42" s="27" t="s">
+        <v>295</v>
+      </c>
+      <c r="E42" s="40"/>
+      <c r="H42"/>
+    </row>
+    <row r="43" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B43" s="20"/>
+      <c r="C43" s="38"/>
+      <c r="D43" s="27" t="s">
+        <v>296</v>
+      </c>
+      <c r="E43" s="40"/>
+      <c r="H43"/>
+    </row>
+    <row r="44" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B44" s="20"/>
+      <c r="C44" s="38"/>
+      <c r="D44" s="27"/>
+      <c r="E44" s="40"/>
+      <c r="H44"/>
+    </row>
+    <row r="45" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B45" s="20"/>
+      <c r="C45" s="38"/>
+      <c r="D45" s="27"/>
+      <c r="E45" s="40"/>
+      <c r="H45"/>
+    </row>
+    <row r="46" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B46" s="20"/>
+      <c r="C46" s="38"/>
+      <c r="D46" s="27"/>
+      <c r="E46" s="40"/>
+      <c r="H46"/>
+    </row>
+    <row r="47" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B47" s="20"/>
+      <c r="C47" s="38"/>
+      <c r="D47" s="27"/>
+      <c r="E47" s="40"/>
+      <c r="H47"/>
+    </row>
+    <row r="48" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B48" s="21"/>
+      <c r="C48" s="42"/>
+      <c r="D48" s="28"/>
+      <c r="E48" s="41"/>
+      <c r="H48"/>
+    </row>
+    <row r="49" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B49" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="C49" s="43" t="s">
+        <v>106</v>
+      </c>
+      <c r="D49" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="E49" s="39" t="s">
+        <v>319</v>
+      </c>
+      <c r="H49"/>
+    </row>
+    <row r="50" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B50" s="20" t="s">
+        <v>165</v>
+      </c>
+      <c r="C50" s="44"/>
+      <c r="D50" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="E50" s="40"/>
+      <c r="H50"/>
+    </row>
+    <row r="51" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B51" s="20" t="s">
+        <v>293</v>
+      </c>
+      <c r="C51" s="44"/>
+      <c r="D51" s="25" t="s">
+        <v>40</v>
+      </c>
+      <c r="E51" s="40"/>
+      <c r="H51"/>
+    </row>
+    <row r="52" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B52" s="20" t="s">
+        <v>294</v>
+      </c>
+      <c r="C52" s="44"/>
+      <c r="D52" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="E52" s="40"/>
+      <c r="H52"/>
+    </row>
+    <row r="53" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B53" s="20"/>
+      <c r="C53" s="44"/>
+      <c r="D53" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="E53" s="40"/>
+      <c r="H53"/>
+    </row>
+    <row r="54" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B54" s="20"/>
+      <c r="C54" s="44"/>
+      <c r="D54" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="E54" s="40"/>
+      <c r="H54"/>
+    </row>
+    <row r="55" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B55" s="20"/>
+      <c r="C55" s="44"/>
+      <c r="D55" s="25" t="s">
+        <v>166</v>
+      </c>
+      <c r="E55" s="40"/>
+      <c r="H55"/>
+    </row>
+    <row r="56" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B56" s="20"/>
+      <c r="C56" s="44"/>
+      <c r="D56" s="25" t="s">
+        <v>167</v>
+      </c>
+      <c r="E56" s="40"/>
+      <c r="H56"/>
+    </row>
+    <row r="57" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B57" s="20"/>
+      <c r="C57" s="44"/>
+      <c r="D57" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="E57" s="40"/>
+      <c r="H57"/>
+    </row>
+    <row r="58" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B58" s="20"/>
+      <c r="C58" s="44"/>
+      <c r="D58" s="25" t="s">
+        <v>168</v>
+      </c>
+      <c r="E58" s="40"/>
+      <c r="H58"/>
+    </row>
+    <row r="59" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B59" s="20"/>
+      <c r="C59" s="44"/>
+      <c r="D59" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="E59" s="40"/>
+      <c r="H59"/>
+    </row>
+    <row r="60" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B60" s="21"/>
+      <c r="C60" s="45"/>
+      <c r="D60" s="30" t="s">
+        <v>169</v>
+      </c>
+      <c r="E60" s="41"/>
+      <c r="H60"/>
+    </row>
+    <row r="61" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B61" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="C61" s="37" t="s">
+        <v>107</v>
+      </c>
+      <c r="D61" s="29" t="s">
         <v>170</v>
       </c>
-      <c r="E38" s="37" t="s">
-        <v>339</v>
-      </c>
-      <c r="H38"/>
-    </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B39" s="23" t="s">
+      <c r="E61" s="39" t="s">
+        <v>320</v>
+      </c>
+      <c r="H61"/>
+    </row>
+    <row r="62" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B62" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="C62" s="38"/>
+      <c r="D62" s="25" t="s">
+        <v>171</v>
+      </c>
+      <c r="E62" s="40"/>
+      <c r="H62"/>
+    </row>
+    <row r="63" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B63" s="20"/>
+      <c r="C63" s="38"/>
+      <c r="D63" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="E63" s="40"/>
+      <c r="H63"/>
+    </row>
+    <row r="64" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B64" s="20"/>
+      <c r="C64" s="38"/>
+      <c r="D64" s="25" t="s">
+        <v>172</v>
+      </c>
+      <c r="E64" s="40"/>
+      <c r="H64"/>
+    </row>
+    <row r="65" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B65" s="21"/>
+      <c r="C65" s="42"/>
+      <c r="D65" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="E65" s="41"/>
+      <c r="H65"/>
+    </row>
+    <row r="66" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B66" s="22" t="s">
+        <v>170</v>
+      </c>
+      <c r="C66" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="D66" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="E66" s="24" t="s">
+        <v>321</v>
+      </c>
+      <c r="H66"/>
+    </row>
+    <row r="67" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B67" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="C39" s="28"/>
-      <c r="D39" s="43" t="s">
-        <v>171</v>
-      </c>
-      <c r="E39" s="38"/>
-      <c r="H39"/>
-    </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B40" s="23"/>
-      <c r="C40" s="28"/>
-      <c r="D40" s="43" t="s">
-        <v>300</v>
-      </c>
-      <c r="E40" s="38"/>
-      <c r="H40"/>
-    </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B41" s="23"/>
-      <c r="C41" s="28"/>
-      <c r="D41" s="43" t="s">
-        <v>301</v>
-      </c>
-      <c r="E41" s="38"/>
-      <c r="H41"/>
-    </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B42" s="23"/>
-      <c r="C42" s="28"/>
-      <c r="D42" s="43" t="s">
-        <v>304</v>
-      </c>
-      <c r="E42" s="38"/>
-      <c r="H42"/>
-    </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B43" s="23"/>
-      <c r="C43" s="28"/>
-      <c r="D43" s="43" t="s">
-        <v>305</v>
-      </c>
-      <c r="E43" s="38"/>
-      <c r="H43"/>
-    </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B44" s="23"/>
-      <c r="C44" s="28"/>
-      <c r="D44" s="43"/>
-      <c r="E44" s="38"/>
-      <c r="H44"/>
-    </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B45" s="23"/>
-      <c r="C45" s="28"/>
-      <c r="D45" s="43"/>
-      <c r="E45" s="38"/>
-      <c r="H45"/>
-    </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B46" s="23"/>
-      <c r="C46" s="28"/>
-      <c r="D46" s="43"/>
-      <c r="E46" s="38"/>
-      <c r="H46"/>
-    </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B47" s="23"/>
-      <c r="C47" s="28"/>
-      <c r="D47" s="43"/>
-      <c r="E47" s="38"/>
-      <c r="H47"/>
-    </row>
-    <row r="48" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B48" s="24"/>
-      <c r="C48" s="29"/>
-      <c r="D48" s="44"/>
-      <c r="E48" s="39"/>
-      <c r="H48"/>
-    </row>
-    <row r="49" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B49" s="22" t="s">
-        <v>170</v>
-      </c>
-      <c r="C49" s="30" t="s">
-        <v>106</v>
-      </c>
-      <c r="D49" s="45" t="s">
-        <v>36</v>
-      </c>
-      <c r="E49" s="37" t="s">
-        <v>328</v>
-      </c>
-      <c r="H49"/>
-    </row>
-    <row r="50" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B50" s="23" t="s">
-        <v>171</v>
-      </c>
-      <c r="C50" s="31"/>
-      <c r="D50" s="41" t="s">
-        <v>38</v>
-      </c>
-      <c r="E50" s="38"/>
-      <c r="H50"/>
-    </row>
-    <row r="51" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B51" s="23" t="s">
-        <v>302</v>
-      </c>
-      <c r="C51" s="31"/>
-      <c r="D51" s="41" t="s">
-        <v>40</v>
-      </c>
-      <c r="E51" s="38"/>
-      <c r="H51"/>
-    </row>
-    <row r="52" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B52" s="23" t="s">
-        <v>303</v>
-      </c>
-      <c r="C52" s="31"/>
-      <c r="D52" s="41" t="s">
-        <v>42</v>
-      </c>
-      <c r="E52" s="38"/>
-      <c r="H52"/>
-    </row>
-    <row r="53" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B53" s="23"/>
-      <c r="C53" s="31"/>
-      <c r="D53" s="41" t="s">
-        <v>44</v>
-      </c>
-      <c r="E53" s="38"/>
-      <c r="H53"/>
-    </row>
-    <row r="54" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B54" s="23"/>
-      <c r="C54" s="31"/>
-      <c r="D54" s="41" t="s">
-        <v>46</v>
-      </c>
-      <c r="E54" s="38"/>
-      <c r="H54"/>
-    </row>
-    <row r="55" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B55" s="23"/>
-      <c r="C55" s="31"/>
-      <c r="D55" s="41" t="s">
-        <v>172</v>
-      </c>
-      <c r="E55" s="38"/>
-      <c r="H55"/>
-    </row>
-    <row r="56" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B56" s="23"/>
-      <c r="C56" s="31"/>
-      <c r="D56" s="41" t="s">
+      <c r="C67" s="43" t="s">
+        <v>108</v>
+      </c>
+      <c r="D67" s="29" t="s">
         <v>173</v>
       </c>
-      <c r="E56" s="38"/>
-      <c r="H56"/>
-    </row>
-    <row r="57" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B57" s="23"/>
-      <c r="C57" s="31"/>
-      <c r="D57" s="41" t="s">
-        <v>50</v>
-      </c>
-      <c r="E57" s="38"/>
-      <c r="H57"/>
-    </row>
-    <row r="58" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B58" s="23"/>
-      <c r="C58" s="31"/>
-      <c r="D58" s="41" t="s">
+      <c r="E67" s="46" t="s">
+        <v>322</v>
+      </c>
+      <c r="H67"/>
+    </row>
+    <row r="68" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B68" s="21"/>
+      <c r="C68" s="45"/>
+      <c r="D68" s="30" t="s">
         <v>174</v>
       </c>
-      <c r="E58" s="38"/>
-      <c r="H58"/>
-    </row>
-    <row r="59" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B59" s="23"/>
-      <c r="C59" s="31"/>
-      <c r="D59" s="41" t="s">
-        <v>53</v>
-      </c>
-      <c r="E59" s="38"/>
-      <c r="H59"/>
-    </row>
-    <row r="60" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B60" s="24"/>
-      <c r="C60" s="32"/>
-      <c r="D60" s="46" t="s">
+      <c r="E68" s="48"/>
+      <c r="H68"/>
+    </row>
+    <row r="69" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B69" s="19" t="s">
+        <v>316</v>
+      </c>
+      <c r="C69" s="37" t="s">
+        <v>19</v>
+      </c>
+      <c r="D69" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="E69" s="39" t="s">
+        <v>331</v>
+      </c>
+      <c r="H69"/>
+    </row>
+    <row r="70" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B70" s="20" t="s">
+        <v>173</v>
+      </c>
+      <c r="C70" s="38"/>
+      <c r="D70" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="E70" s="40"/>
+      <c r="H70"/>
+    </row>
+    <row r="71" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B71" s="20"/>
+      <c r="C71" s="38"/>
+      <c r="D71" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="E71" s="40"/>
+      <c r="H71"/>
+    </row>
+    <row r="72" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B72" s="20"/>
+      <c r="C72" s="38"/>
+      <c r="D72" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="E72" s="40"/>
+      <c r="H72"/>
+    </row>
+    <row r="73" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B73" s="20"/>
+      <c r="C73" s="38"/>
+      <c r="D73" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="E73" s="40"/>
+      <c r="H73"/>
+    </row>
+    <row r="74" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B74" s="20"/>
+      <c r="C74" s="38"/>
+      <c r="D74" s="25" t="s">
+        <v>65</v>
+      </c>
+      <c r="E74" s="40"/>
+      <c r="H74"/>
+    </row>
+    <row r="75" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B75" s="20"/>
+      <c r="C75" s="38"/>
+      <c r="D75" s="25" t="s">
+        <v>309</v>
+      </c>
+      <c r="E75" s="40"/>
+      <c r="H75"/>
+    </row>
+    <row r="76" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B76" s="21"/>
+      <c r="C76" s="42"/>
+      <c r="D76" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="E76" s="41"/>
+      <c r="H76"/>
+    </row>
+    <row r="77" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B77" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C77" s="37" t="s">
+        <v>109</v>
+      </c>
+      <c r="D77" s="29" t="s">
+        <v>68</v>
+      </c>
+      <c r="E77" s="39" t="s">
+        <v>323</v>
+      </c>
+      <c r="H77"/>
+    </row>
+    <row r="78" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B78" s="20"/>
+      <c r="C78" s="38"/>
+      <c r="D78" s="25" t="s">
         <v>175</v>
       </c>
-      <c r="E60" s="39"/>
-      <c r="H60"/>
-    </row>
-    <row r="61" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B61" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="C61" s="27" t="s">
-        <v>107</v>
-      </c>
-      <c r="D61" s="45" t="s">
+      <c r="E78" s="40"/>
+      <c r="H78"/>
+    </row>
+    <row r="79" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B79" s="20"/>
+      <c r="C79" s="38"/>
+      <c r="D79" s="25" t="s">
+        <v>73</v>
+      </c>
+      <c r="E79" s="40"/>
+      <c r="H79"/>
+    </row>
+    <row r="80" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B80" s="20"/>
+      <c r="C80" s="38"/>
+      <c r="D80" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="E80" s="40"/>
+      <c r="H80"/>
+    </row>
+    <row r="81" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B81" s="20"/>
+      <c r="C81" s="38"/>
+      <c r="D81" s="25" t="s">
+        <v>75</v>
+      </c>
+      <c r="E81" s="40"/>
+      <c r="H81"/>
+    </row>
+    <row r="82" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B82" s="21"/>
+      <c r="C82" s="42"/>
+      <c r="D82" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="E82" s="41"/>
+      <c r="H82"/>
+    </row>
+    <row r="83" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B83" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C83" s="43" t="s">
+        <v>110</v>
+      </c>
+      <c r="D83" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="E83" s="39" t="s">
+        <v>341</v>
+      </c>
+      <c r="H83"/>
+    </row>
+    <row r="84" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B84" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="C84" s="44"/>
+      <c r="D84" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="E84" s="40"/>
+      <c r="H84"/>
+    </row>
+    <row r="85" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B85" s="20"/>
+      <c r="C85" s="44"/>
+      <c r="D85" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="E85" s="40"/>
+      <c r="H85"/>
+    </row>
+    <row r="86" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B86" s="21"/>
+      <c r="C86" s="45"/>
+      <c r="D86" s="30" t="s">
+        <v>85</v>
+      </c>
+      <c r="E86" s="41"/>
+      <c r="H86"/>
+    </row>
+    <row r="87" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B87" s="19"/>
+      <c r="C87" s="37" t="s">
+        <v>111</v>
+      </c>
+      <c r="D87" s="29" t="s">
         <v>176</v>
       </c>
-      <c r="E61" s="37" t="s">
-        <v>329</v>
-      </c>
-      <c r="H61"/>
-    </row>
-    <row r="62" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B62" s="23" t="s">
-        <v>38</v>
-      </c>
-      <c r="C62" s="28"/>
-      <c r="D62" s="41" t="s">
+      <c r="E87" s="46" t="s">
+        <v>324</v>
+      </c>
+      <c r="H87"/>
+    </row>
+    <row r="88" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B88" s="20"/>
+      <c r="C88" s="38"/>
+      <c r="D88" s="25" t="s">
         <v>177</v>
       </c>
-      <c r="E62" s="38"/>
-      <c r="H62"/>
-    </row>
-    <row r="63" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B63" s="23"/>
-      <c r="C63" s="28"/>
-      <c r="D63" s="41" t="s">
-        <v>15</v>
-      </c>
-      <c r="E63" s="38"/>
-      <c r="H63"/>
-    </row>
-    <row r="64" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B64" s="23"/>
-      <c r="C64" s="28"/>
-      <c r="D64" s="41" t="s">
-        <v>178</v>
-      </c>
-      <c r="E64" s="38"/>
-      <c r="H64"/>
-    </row>
-    <row r="65" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B65" s="24"/>
-      <c r="C65" s="29"/>
-      <c r="D65" s="46" t="s">
-        <v>16</v>
-      </c>
-      <c r="E65" s="39"/>
-      <c r="H65"/>
-    </row>
-    <row r="66" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B66" s="25" t="s">
-        <v>176</v>
-      </c>
-      <c r="C66" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="D66" s="47" t="s">
-        <v>18</v>
-      </c>
-      <c r="E66" s="40" t="s">
-        <v>330</v>
-      </c>
-      <c r="H66"/>
-    </row>
-    <row r="67" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B67" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="C67" s="30" t="s">
-        <v>108</v>
-      </c>
-      <c r="D67" s="45" t="s">
-        <v>179</v>
-      </c>
-      <c r="E67" s="34" t="s">
-        <v>331</v>
-      </c>
-      <c r="H67"/>
-    </row>
-    <row r="68" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B68" s="24"/>
-      <c r="C68" s="32"/>
-      <c r="D68" s="46" t="s">
-        <v>180</v>
-      </c>
-      <c r="E68" s="36"/>
-      <c r="H68"/>
-    </row>
-    <row r="69" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B69" s="22" t="s">
-        <v>325</v>
-      </c>
-      <c r="C69" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="D69" s="45" t="s">
-        <v>20</v>
-      </c>
-      <c r="E69" s="37" t="s">
-        <v>340</v>
-      </c>
-      <c r="H69"/>
-    </row>
-    <row r="70" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B70" s="23" t="s">
-        <v>179</v>
-      </c>
-      <c r="C70" s="28"/>
-      <c r="D70" s="41" t="s">
-        <v>21</v>
-      </c>
-      <c r="E70" s="38"/>
-      <c r="H70"/>
-    </row>
-    <row r="71" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B71" s="23"/>
-      <c r="C71" s="28"/>
-      <c r="D71" s="41" t="s">
-        <v>22</v>
-      </c>
-      <c r="E71" s="38"/>
-      <c r="H71"/>
-    </row>
-    <row r="72" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B72" s="23"/>
-      <c r="C72" s="28"/>
-      <c r="D72" s="41" t="s">
-        <v>61</v>
-      </c>
-      <c r="E72" s="38"/>
-      <c r="H72"/>
-    </row>
-    <row r="73" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B73" s="23"/>
-      <c r="C73" s="28"/>
-      <c r="D73" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="E73" s="38"/>
-      <c r="H73"/>
-    </row>
-    <row r="74" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B74" s="23"/>
-      <c r="C74" s="28"/>
-      <c r="D74" s="41" t="s">
-        <v>65</v>
-      </c>
-      <c r="E74" s="38"/>
-      <c r="H74"/>
-    </row>
-    <row r="75" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B75" s="23"/>
-      <c r="C75" s="28"/>
-      <c r="D75" s="41" t="s">
-        <v>318</v>
-      </c>
-      <c r="E75" s="38"/>
-      <c r="H75"/>
-    </row>
-    <row r="76" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B76" s="24"/>
-      <c r="C76" s="29"/>
-      <c r="D76" s="46" t="s">
-        <v>67</v>
-      </c>
-      <c r="E76" s="39"/>
-      <c r="H76"/>
-    </row>
-    <row r="77" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B77" s="22" t="s">
-        <v>32</v>
-      </c>
-      <c r="C77" s="27" t="s">
-        <v>109</v>
-      </c>
-      <c r="D77" s="45" t="s">
-        <v>68</v>
-      </c>
-      <c r="E77" s="37" t="s">
-        <v>332</v>
-      </c>
-      <c r="H77"/>
-    </row>
-    <row r="78" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B78" s="23"/>
-      <c r="C78" s="28"/>
-      <c r="D78" s="41" t="s">
-        <v>181</v>
-      </c>
-      <c r="E78" s="38"/>
-      <c r="H78"/>
-    </row>
-    <row r="79" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B79" s="23"/>
-      <c r="C79" s="28"/>
-      <c r="D79" s="41" t="s">
-        <v>73</v>
-      </c>
-      <c r="E79" s="38"/>
-      <c r="H79"/>
-    </row>
-    <row r="80" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B80" s="23"/>
-      <c r="C80" s="28"/>
-      <c r="D80" s="41" t="s">
-        <v>74</v>
-      </c>
-      <c r="E80" s="38"/>
-      <c r="H80"/>
-    </row>
-    <row r="81" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B81" s="23"/>
-      <c r="C81" s="28"/>
-      <c r="D81" s="41" t="s">
-        <v>75</v>
-      </c>
-      <c r="E81" s="38"/>
-      <c r="H81"/>
-    </row>
-    <row r="82" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B82" s="24"/>
-      <c r="C82" s="29"/>
-      <c r="D82" s="46" t="s">
-        <v>77</v>
-      </c>
-      <c r="E82" s="39"/>
-      <c r="H82"/>
-    </row>
-    <row r="83" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B83" s="22" t="s">
-        <v>32</v>
-      </c>
-      <c r="C83" s="30" t="s">
-        <v>110</v>
-      </c>
-      <c r="D83" s="45" t="s">
-        <v>79</v>
-      </c>
-      <c r="E83" s="37" t="s">
-        <v>350</v>
-      </c>
-      <c r="H83"/>
-    </row>
-    <row r="84" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B84" s="23" t="s">
-        <v>75</v>
-      </c>
-      <c r="C84" s="31"/>
-      <c r="D84" s="41" t="s">
-        <v>81</v>
-      </c>
-      <c r="E84" s="38"/>
-      <c r="H84"/>
-    </row>
-    <row r="85" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B85" s="23"/>
-      <c r="C85" s="31"/>
-      <c r="D85" s="41" t="s">
-        <v>83</v>
-      </c>
-      <c r="E85" s="38"/>
-      <c r="H85"/>
-    </row>
-    <row r="86" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B86" s="24"/>
-      <c r="C86" s="32"/>
-      <c r="D86" s="46" t="s">
-        <v>85</v>
-      </c>
-      <c r="E86" s="39"/>
-      <c r="H86"/>
-    </row>
-    <row r="87" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B87" s="22"/>
-      <c r="C87" s="27" t="s">
-        <v>111</v>
-      </c>
-      <c r="D87" s="45" t="s">
-        <v>182</v>
-      </c>
-      <c r="E87" s="34" t="s">
-        <v>333</v>
-      </c>
-      <c r="H87"/>
-    </row>
-    <row r="88" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B88" s="23"/>
-      <c r="C88" s="28"/>
-      <c r="D88" s="48" t="s">
-        <v>183</v>
-      </c>
-      <c r="E88" s="35"/>
+      <c r="E88" s="47"/>
       <c r="H88"/>
     </row>
     <row r="89" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B89" s="22"/>
-      <c r="C89" s="30" t="s">
-        <v>343</v>
-      </c>
-      <c r="D89" s="49" t="s">
-        <v>344</v>
-      </c>
-      <c r="E89" s="37" t="s">
-        <v>351</v>
+      <c r="B89" s="19"/>
+      <c r="C89" s="43" t="s">
+        <v>334</v>
+      </c>
+      <c r="D89" s="32" t="s">
+        <v>335</v>
+      </c>
+      <c r="E89" s="39" t="s">
+        <v>342</v>
       </c>
     </row>
     <row r="90" spans="2:8" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B90" s="24"/>
-      <c r="C90" s="32"/>
-      <c r="D90" s="50" t="s">
-        <v>345</v>
-      </c>
-      <c r="E90" s="39"/>
+      <c r="B90" s="21"/>
+      <c r="C90" s="45"/>
+      <c r="D90" s="33" t="s">
+        <v>336</v>
+      </c>
+      <c r="E90" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="22">
@@ -2569,12 +2546,12 @@
     <mergeCell ref="E69:E76"/>
     <mergeCell ref="E67:E68"/>
     <mergeCell ref="C38:C48"/>
+    <mergeCell ref="C87:C88"/>
     <mergeCell ref="E83:E86"/>
     <mergeCell ref="C77:C82"/>
     <mergeCell ref="C83:C86"/>
     <mergeCell ref="C61:C65"/>
     <mergeCell ref="C69:C76"/>
-    <mergeCell ref="C87:C88"/>
   </mergeCells>
   <conditionalFormatting sqref="B29:B88 D29:D90">
     <cfRule type="duplicateValues" dxfId="4" priority="13"/>
@@ -2591,10 +2568,10 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="57" style="11" customWidth="1"/>
+    <col min="2" max="2" width="57" style="8" customWidth="1"/>
     <col min="3" max="3" width="19" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.6640625" style="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="46.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.6640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="46.44140625" style="8" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="39.5546875" customWidth="1"/>
     <col min="7" max="7" width="28" customWidth="1"/>
     <col min="8" max="8" width="31.88671875" customWidth="1"/>
@@ -2602,79 +2579,79 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="10" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="18" t="s">
-        <v>96</v>
+      <c r="A2" s="12" t="s">
+        <v>89</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="C2" s="16" t="s">
-        <v>284</v>
-      </c>
-      <c r="D2" s="20" t="s">
-        <v>285</v>
-      </c>
-      <c r="E2" s="17" t="s">
-        <v>286</v>
-      </c>
-      <c r="F2" s="17" t="s">
-        <v>286</v>
-      </c>
-      <c r="G2" s="17" t="s">
-        <v>286</v>
+        <v>274</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>276</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>277</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>277</v>
+      </c>
+      <c r="G2" s="14" t="s">
+        <v>277</v>
       </c>
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="12" t="s">
         <v>89</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="D3" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="F3" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="G3" s="17" t="s">
+      <c r="G3" s="14" t="s">
         <v>30</v>
       </c>
       <c r="H3" s="5"/>
@@ -2684,25 +2661,25 @@
       <c r="L3" s="5"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="12" t="s">
         <v>89</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="20" t="s">
-        <v>186</v>
-      </c>
-      <c r="E4" s="17" t="s">
+      <c r="D4" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="E4" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="F4" s="17" t="s">
+      <c r="F4" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="G4" s="17" t="s">
+      <c r="G4" s="14" t="s">
         <v>31</v>
       </c>
       <c r="H4" s="5"/>
@@ -2712,25 +2689,25 @@
       <c r="L4" s="5"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="12" t="s">
         <v>89</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="E5" s="17" t="s">
+      <c r="D5" s="17" t="s">
+        <v>181</v>
+      </c>
+      <c r="E5" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="F5" s="17" t="s">
+      <c r="F5" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="G5" s="17" t="s">
+      <c r="G5" s="14" t="s">
         <v>34</v>
       </c>
       <c r="H5" s="5"/>
@@ -2740,26 +2717,26 @@
       <c r="L5" s="5"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="15" t="s">
         <v>96</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="20" t="s">
-        <v>188</v>
-      </c>
-      <c r="E6" s="17" t="s">
-        <v>269</v>
-      </c>
-      <c r="F6" s="17" t="s">
-        <v>269</v>
-      </c>
-      <c r="G6" s="17" t="s">
-        <v>269</v>
+      <c r="D6" s="17" t="s">
+        <v>182</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>263</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>263</v>
+      </c>
+      <c r="G6" s="14" t="s">
+        <v>263</v>
       </c>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
@@ -2768,26 +2745,26 @@
       <c r="L6" s="5"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="15" t="s">
         <v>96</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="20" t="s">
-        <v>189</v>
-      </c>
-      <c r="E7" s="17" t="s">
-        <v>270</v>
-      </c>
-      <c r="F7" s="17" t="s">
-        <v>270</v>
-      </c>
-      <c r="G7" s="17" t="s">
-        <v>270</v>
+      <c r="D7" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>264</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>264</v>
+      </c>
+      <c r="G7" s="14" t="s">
+        <v>264</v>
       </c>
       <c r="H7" s="5"/>
       <c r="I7" s="5"/>
@@ -2796,26 +2773,26 @@
       <c r="L7" s="5"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="12" t="s">
         <v>97</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="C8" s="16" t="s">
+        <v>280</v>
+      </c>
+      <c r="C8" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="E8" s="17" t="s">
+      <c r="D8" s="17" t="s">
         <v>184</v>
       </c>
-      <c r="F8" s="17" t="s">
-        <v>184</v>
-      </c>
-      <c r="G8" s="17" t="s">
-        <v>184</v>
+      <c r="E8" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="G8" s="14" t="s">
+        <v>178</v>
       </c>
       <c r="H8" s="5"/>
       <c r="I8" s="5"/>
@@ -2824,26 +2801,26 @@
       <c r="L8" s="5"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="15" t="s">
+      <c r="A9" s="12" t="s">
         <v>97</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="C9" s="16" t="s">
+        <v>281</v>
+      </c>
+      <c r="C9" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="D9" s="20" t="s">
-        <v>191</v>
-      </c>
-      <c r="E9" s="17" t="s">
-        <v>184</v>
-      </c>
-      <c r="F9" s="17" t="s">
-        <v>184</v>
-      </c>
-      <c r="G9" s="17" t="s">
-        <v>184</v>
+      <c r="D9" s="17" t="s">
+        <v>185</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>178</v>
       </c>
       <c r="H9" s="5"/>
       <c r="I9" s="5"/>
@@ -2852,26 +2829,26 @@
       <c r="L9" s="5"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="15" t="s">
+      <c r="A10" s="12" t="s">
         <v>97</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="C10" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="C10" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="D10" s="20" t="s">
-        <v>310</v>
-      </c>
-      <c r="E10" s="17" t="s">
-        <v>314</v>
-      </c>
-      <c r="F10" s="17" t="s">
-        <v>314</v>
-      </c>
-      <c r="G10" s="17" t="s">
-        <v>314</v>
+      <c r="D10" s="17" t="s">
+        <v>301</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>305</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>305</v>
+      </c>
+      <c r="G10" s="14" t="s">
+        <v>305</v>
       </c>
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
@@ -2880,26 +2857,26 @@
       <c r="L10" s="5"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="15" t="s">
+      <c r="A11" s="12" t="s">
         <v>97</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="C11" s="16" t="s">
+        <v>297</v>
+      </c>
+      <c r="C11" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="D11" s="20" t="s">
-        <v>311</v>
-      </c>
-      <c r="E11" s="17" t="s">
-        <v>314</v>
-      </c>
-      <c r="F11" s="17" t="s">
-        <v>314</v>
-      </c>
-      <c r="G11" s="17" t="s">
-        <v>314</v>
+      <c r="D11" s="17" t="s">
+        <v>302</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>305</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>305</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>305</v>
       </c>
       <c r="H11" s="5"/>
       <c r="I11" s="5"/>
@@ -2908,26 +2885,26 @@
       <c r="L11" s="5"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="15" t="s">
+      <c r="A12" s="12" t="s">
         <v>97</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="C12" s="16" t="s">
+        <v>299</v>
+      </c>
+      <c r="C12" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="D12" s="20" t="s">
-        <v>312</v>
-      </c>
-      <c r="E12" s="17" t="s">
-        <v>315</v>
-      </c>
-      <c r="F12" s="17" t="s">
-        <v>315</v>
-      </c>
-      <c r="G12" s="17" t="s">
-        <v>315</v>
+      <c r="D12" s="17" t="s">
+        <v>303</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>306</v>
+      </c>
+      <c r="F12" s="14" t="s">
+        <v>306</v>
+      </c>
+      <c r="G12" s="14" t="s">
+        <v>306</v>
       </c>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
@@ -2936,26 +2913,26 @@
       <c r="L12" s="5"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="12" t="s">
         <v>97</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="C13" s="16" t="s">
+        <v>300</v>
+      </c>
+      <c r="C13" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="D13" s="20" t="s">
-        <v>313</v>
-      </c>
-      <c r="E13" s="17" t="s">
-        <v>315</v>
-      </c>
-      <c r="F13" s="17" t="s">
-        <v>315</v>
-      </c>
-      <c r="G13" s="17" t="s">
-        <v>315</v>
+      <c r="D13" s="17" t="s">
+        <v>304</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>306</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>306</v>
+      </c>
+      <c r="G13" s="14" t="s">
+        <v>306</v>
       </c>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
@@ -2964,25 +2941,25 @@
       <c r="L13" s="5"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="18" t="s">
+      <c r="A14" s="15" t="s">
         <v>95</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="C14" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="C14" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="D14" s="20" t="s">
-        <v>192</v>
-      </c>
-      <c r="E14" s="17" t="s">
+      <c r="D14" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="E14" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="F14" s="17" t="s">
+      <c r="F14" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="G14" s="17" t="s">
+      <c r="G14" s="14" t="s">
         <v>37</v>
       </c>
       <c r="H14" s="5"/>
@@ -2992,25 +2969,25 @@
       <c r="L14" s="5"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="18" t="s">
+      <c r="A15" s="15" t="s">
         <v>95</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>292</v>
-      </c>
-      <c r="C15" s="16" t="s">
+        <v>283</v>
+      </c>
+      <c r="C15" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="D15" s="20" t="s">
-        <v>193</v>
-      </c>
-      <c r="E15" s="17" t="s">
+      <c r="D15" s="17" t="s">
+        <v>187</v>
+      </c>
+      <c r="E15" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="F15" s="17" t="s">
+      <c r="F15" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="G15" s="17" t="s">
+      <c r="G15" s="14" t="s">
         <v>39</v>
       </c>
       <c r="H15" s="5"/>
@@ -3020,25 +2997,25 @@
       <c r="L15" s="5"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="18" t="s">
+      <c r="A16" s="15" t="s">
         <v>95</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="C16" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="D16" s="20" t="s">
-        <v>194</v>
-      </c>
-      <c r="E16" s="17" t="s">
+      <c r="D16" s="17" t="s">
+        <v>188</v>
+      </c>
+      <c r="E16" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="F16" s="17" t="s">
+      <c r="F16" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="G16" s="17" t="s">
+      <c r="G16" s="14" t="s">
         <v>41</v>
       </c>
       <c r="H16" s="5"/>
@@ -3048,25 +3025,25 @@
       <c r="L16" s="5"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" s="18" t="s">
+      <c r="A17" s="15" t="s">
         <v>95</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C17" s="16" t="s">
+      <c r="C17" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="D17" s="20" t="s">
-        <v>195</v>
-      </c>
-      <c r="E17" s="17" t="s">
+      <c r="D17" s="17" t="s">
+        <v>189</v>
+      </c>
+      <c r="E17" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="F17" s="17" t="s">
+      <c r="F17" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="G17" s="17" t="s">
+      <c r="G17" s="14" t="s">
         <v>43</v>
       </c>
       <c r="H17" s="5"/>
@@ -3076,25 +3053,25 @@
       <c r="L17" s="5"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18" s="18" t="s">
+      <c r="A18" s="15" t="s">
         <v>95</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="C18" s="16" t="s">
+        <v>284</v>
+      </c>
+      <c r="C18" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="D18" s="20" t="s">
-        <v>196</v>
-      </c>
-      <c r="E18" s="17" t="s">
+      <c r="D18" s="17" t="s">
+        <v>190</v>
+      </c>
+      <c r="E18" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="F18" s="17" t="s">
+      <c r="F18" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="G18" s="17" t="s">
+      <c r="G18" s="14" t="s">
         <v>45</v>
       </c>
       <c r="H18" s="5"/>
@@ -3104,25 +3081,25 @@
       <c r="L18" s="5"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A19" s="18" t="s">
+      <c r="A19" s="15" t="s">
         <v>95</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>294</v>
-      </c>
-      <c r="C19" s="16" t="s">
+        <v>285</v>
+      </c>
+      <c r="C19" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="D19" s="20" t="s">
-        <v>197</v>
-      </c>
-      <c r="E19" s="17" t="s">
+      <c r="D19" s="17" t="s">
+        <v>191</v>
+      </c>
+      <c r="E19" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="F19" s="17" t="s">
+      <c r="F19" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="G19" s="17" t="s">
+      <c r="G19" s="14" t="s">
         <v>47</v>
       </c>
       <c r="H19" s="5"/>
@@ -3132,25 +3109,25 @@
       <c r="L19" s="5"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" s="18" t="s">
+      <c r="A20" s="15" t="s">
         <v>95</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="C20" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="C20" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="D20" s="20" t="s">
-        <v>198</v>
-      </c>
-      <c r="E20" s="17" t="s">
+      <c r="D20" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="E20" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="F20" s="17" t="s">
+      <c r="F20" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="G20" s="17" t="s">
+      <c r="G20" s="14" t="s">
         <v>48</v>
       </c>
       <c r="H20" s="5"/>
@@ -3160,25 +3137,25 @@
       <c r="L20" s="5"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A21" s="18" t="s">
+      <c r="A21" s="15" t="s">
         <v>95</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="C21" s="16" t="s">
+        <v>167</v>
+      </c>
+      <c r="C21" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="D21" s="20" t="s">
-        <v>199</v>
-      </c>
-      <c r="E21" s="17" t="s">
+      <c r="D21" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="E21" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="F21" s="17" t="s">
+      <c r="F21" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="G21" s="17" t="s">
+      <c r="G21" s="14" t="s">
         <v>49</v>
       </c>
       <c r="H21" s="5"/>
@@ -3188,25 +3165,25 @@
       <c r="L21" s="5"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22" s="18" t="s">
+      <c r="A22" s="15" t="s">
         <v>95</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>295</v>
-      </c>
-      <c r="C22" s="16" t="s">
+        <v>286</v>
+      </c>
+      <c r="C22" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="D22" s="20" t="s">
-        <v>200</v>
-      </c>
-      <c r="E22" s="17" t="s">
+      <c r="D22" s="17" t="s">
+        <v>194</v>
+      </c>
+      <c r="E22" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="F22" s="17" t="s">
+      <c r="F22" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="G22" s="17" t="s">
+      <c r="G22" s="14" t="s">
         <v>51</v>
       </c>
       <c r="H22" s="5"/>
@@ -3216,25 +3193,25 @@
       <c r="L22" s="5"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A23" s="18" t="s">
+      <c r="A23" s="15" t="s">
         <v>95</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="C23" s="16" t="s">
+        <v>287</v>
+      </c>
+      <c r="C23" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="D23" s="20" t="s">
-        <v>201</v>
-      </c>
-      <c r="E23" s="17" t="s">
+      <c r="D23" s="17" t="s">
+        <v>195</v>
+      </c>
+      <c r="E23" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="F23" s="17" t="s">
+      <c r="F23" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="G23" s="17" t="s">
+      <c r="G23" s="14" t="s">
         <v>52</v>
       </c>
       <c r="H23" s="5"/>
@@ -3244,25 +3221,25 @@
       <c r="L23" s="5"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A24" s="18" t="s">
+      <c r="A24" s="15" t="s">
         <v>95</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>297</v>
-      </c>
-      <c r="C24" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="C24" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="D24" s="20" t="s">
-        <v>202</v>
-      </c>
-      <c r="E24" s="17" t="s">
+      <c r="D24" s="17" t="s">
+        <v>196</v>
+      </c>
+      <c r="E24" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="F24" s="17" t="s">
+      <c r="F24" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="G24" s="17" t="s">
+      <c r="G24" s="14" t="s">
         <v>54</v>
       </c>
       <c r="H24" s="5"/>
@@ -3272,25 +3249,25 @@
       <c r="L24" s="5"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A25" s="18" t="s">
+      <c r="A25" s="15" t="s">
         <v>95</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="C25" s="16" t="s">
+        <v>289</v>
+      </c>
+      <c r="C25" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="D25" s="20" t="s">
-        <v>203</v>
-      </c>
-      <c r="E25" s="17" t="s">
+      <c r="D25" s="17" t="s">
+        <v>197</v>
+      </c>
+      <c r="E25" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="F25" s="17" t="s">
+      <c r="F25" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="G25" s="17" t="s">
+      <c r="G25" s="14" t="s">
         <v>55</v>
       </c>
       <c r="H25" s="5"/>
@@ -3300,25 +3277,25 @@
       <c r="L25" s="5"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A26" s="15" t="s">
+      <c r="A26" s="12" t="s">
         <v>94</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="C26" s="16" t="s">
+        <v>290</v>
+      </c>
+      <c r="C26" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="D26" s="20" t="s">
-        <v>204</v>
-      </c>
-      <c r="E26" s="17" t="s">
+      <c r="D26" s="17" t="s">
+        <v>198</v>
+      </c>
+      <c r="E26" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="F26" s="17" t="s">
+      <c r="F26" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="G26" s="17" t="s">
+      <c r="G26" s="14" t="s">
         <v>56</v>
       </c>
       <c r="H26" s="5"/>
@@ -3328,25 +3305,25 @@
       <c r="L26" s="5"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A27" s="15" t="s">
+      <c r="A27" s="12" t="s">
         <v>94</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="C27" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="C27" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="D27" s="20" t="s">
-        <v>205</v>
-      </c>
-      <c r="E27" s="17" t="s">
+      <c r="D27" s="17" t="s">
+        <v>199</v>
+      </c>
+      <c r="E27" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="F27" s="17" t="s">
+      <c r="F27" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="G27" s="17" t="s">
+      <c r="G27" s="14" t="s">
         <v>57</v>
       </c>
       <c r="H27" s="5"/>
@@ -3356,49 +3333,49 @@
       <c r="L27" s="5"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A28" s="15" t="s">
+      <c r="A28" s="12" t="s">
         <v>94</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C28" s="16"/>
-      <c r="D28" s="20" t="s">
-        <v>206</v>
-      </c>
-      <c r="E28" s="17" t="s">
-        <v>265</v>
-      </c>
-      <c r="F28" s="17" t="s">
-        <v>265</v>
-      </c>
-      <c r="G28" s="17" t="s">
-        <v>265</v>
-      </c>
-      <c r="H28" s="17"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="17" t="s">
+        <v>200</v>
+      </c>
+      <c r="E28" s="14" t="s">
+        <v>259</v>
+      </c>
+      <c r="F28" s="14" t="s">
+        <v>259</v>
+      </c>
+      <c r="G28" s="14" t="s">
+        <v>259</v>
+      </c>
+      <c r="H28" s="14"/>
       <c r="I28" s="5"/>
       <c r="J28" s="5"/>
       <c r="K28" s="5"/>
       <c r="L28" s="5"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A29" s="15" t="s">
+      <c r="A29" s="12" t="s">
         <v>94</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="C29" s="16"/>
-      <c r="D29" s="20" t="s">
-        <v>207</v>
-      </c>
-      <c r="E29" s="17" t="s">
+        <v>172</v>
+      </c>
+      <c r="C29" s="13"/>
+      <c r="D29" s="17" t="s">
+        <v>201</v>
+      </c>
+      <c r="E29" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="F29" s="17" t="s">
+      <c r="F29" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="G29" s="17" t="s">
+      <c r="G29" s="14" t="s">
         <v>35</v>
       </c>
       <c r="H29" s="5"/>
@@ -3408,25 +3385,25 @@
       <c r="L29" s="5"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A30" s="15" t="s">
+      <c r="A30" s="12" t="s">
         <v>94</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C30" s="16" t="s">
+      <c r="C30" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="D30" s="20" t="s">
-        <v>208</v>
-      </c>
-      <c r="E30" s="17" t="s">
+      <c r="D30" s="17" t="s">
+        <v>202</v>
+      </c>
+      <c r="E30" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="F30" s="17" t="s">
+      <c r="F30" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="G30" s="17" t="s">
+      <c r="G30" s="14" t="s">
         <v>58</v>
       </c>
       <c r="H30" s="5"/>
@@ -3436,26 +3413,26 @@
       <c r="L30" s="5"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A31" s="18" t="s">
+      <c r="A31" s="15" t="s">
         <v>17</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C31" s="16" t="s">
+      <c r="C31" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="D31" s="20" t="s">
-        <v>209</v>
-      </c>
-      <c r="E31" s="19" t="s">
-        <v>324</v>
-      </c>
-      <c r="F31" s="19" t="s">
-        <v>324</v>
-      </c>
-      <c r="G31" s="19" t="s">
-        <v>324</v>
+      <c r="D31" s="17" t="s">
+        <v>203</v>
+      </c>
+      <c r="E31" s="16" t="s">
+        <v>315</v>
+      </c>
+      <c r="F31" s="16" t="s">
+        <v>315</v>
+      </c>
+      <c r="G31" s="16" t="s">
+        <v>315</v>
       </c>
       <c r="H31" s="5"/>
       <c r="I31" s="5"/>
@@ -3464,26 +3441,26 @@
       <c r="L31" s="5"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A32" s="15" t="s">
+      <c r="A32" s="12" t="s">
         <v>93</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="C32" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="C32" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="D32" s="20" t="s">
-        <v>217</v>
-      </c>
-      <c r="E32" s="19" t="s">
-        <v>326</v>
-      </c>
-      <c r="F32" s="19" t="s">
-        <v>326</v>
-      </c>
-      <c r="G32" s="19" t="s">
-        <v>326</v>
+      <c r="D32" s="17" t="s">
+        <v>211</v>
+      </c>
+      <c r="E32" s="16" t="s">
+        <v>343</v>
+      </c>
+      <c r="F32" s="16" t="s">
+        <v>317</v>
+      </c>
+      <c r="G32" s="16" t="s">
+        <v>317</v>
       </c>
       <c r="H32" s="5"/>
       <c r="I32" s="5"/>
@@ -3492,26 +3469,26 @@
       <c r="L32" s="5"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A33" s="15" t="s">
+      <c r="A33" s="12" t="s">
         <v>93</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="C33" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="C33" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="D33" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="E33" s="17" t="s">
-        <v>231</v>
-      </c>
-      <c r="F33" s="17" t="s">
-        <v>231</v>
-      </c>
-      <c r="G33" s="17" t="s">
-        <v>231</v>
+      <c r="D33" s="17" t="s">
+        <v>212</v>
+      </c>
+      <c r="E33" s="14" t="s">
+        <v>225</v>
+      </c>
+      <c r="F33" s="14" t="s">
+        <v>225</v>
+      </c>
+      <c r="G33" s="14" t="s">
+        <v>225</v>
       </c>
       <c r="H33" s="5"/>
       <c r="I33" s="5"/>
@@ -3520,26 +3497,26 @@
       <c r="L33" s="5"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A34" s="18" t="s">
+      <c r="A34" s="15" t="s">
         <v>92</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>325</v>
-      </c>
-      <c r="C34" s="16" t="s">
+        <v>316</v>
+      </c>
+      <c r="C34" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="D34" s="20" t="s">
-        <v>322</v>
-      </c>
-      <c r="E34" s="19" t="s">
-        <v>323</v>
-      </c>
-      <c r="F34" s="19" t="s">
-        <v>323</v>
-      </c>
-      <c r="G34" s="19" t="s">
-        <v>323</v>
+      <c r="D34" s="17" t="s">
+        <v>313</v>
+      </c>
+      <c r="E34" s="16" t="s">
+        <v>314</v>
+      </c>
+      <c r="F34" s="16" t="s">
+        <v>314</v>
+      </c>
+      <c r="G34" s="16" t="s">
+        <v>314</v>
       </c>
       <c r="H34" s="5"/>
       <c r="I34" s="5"/>
@@ -3548,26 +3525,26 @@
       <c r="L34" s="5"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A35" s="18" t="s">
+      <c r="A35" s="15" t="s">
         <v>92</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C35" s="16" t="s">
+      <c r="C35" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="D35" s="20" t="s">
-        <v>213</v>
-      </c>
-      <c r="E35" s="17" t="s">
-        <v>321</v>
-      </c>
-      <c r="F35" s="17" t="s">
-        <v>321</v>
-      </c>
-      <c r="G35" s="17" t="s">
-        <v>321</v>
+      <c r="D35" s="17" t="s">
+        <v>207</v>
+      </c>
+      <c r="E35" s="14" t="s">
+        <v>312</v>
+      </c>
+      <c r="F35" s="14" t="s">
+        <v>312</v>
+      </c>
+      <c r="G35" s="14" t="s">
+        <v>312</v>
       </c>
       <c r="H35" s="5"/>
       <c r="I35" s="5"/>
@@ -3576,25 +3553,25 @@
       <c r="L35" s="5"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A36" s="18" t="s">
+      <c r="A36" s="15" t="s">
         <v>92</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="C36" s="16" t="s">
+      <c r="C36" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="D36" s="20" t="s">
-        <v>214</v>
-      </c>
-      <c r="E36" s="17" t="s">
+      <c r="D36" s="17" t="s">
+        <v>208</v>
+      </c>
+      <c r="E36" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="F36" s="17" t="s">
+      <c r="F36" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="G36" s="17" t="s">
+      <c r="G36" s="14" t="s">
         <v>64</v>
       </c>
       <c r="H36" s="5"/>
@@ -3604,25 +3581,25 @@
       <c r="L36" s="5"/>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A37" s="18" t="s">
+      <c r="A37" s="15" t="s">
         <v>92</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="C37" s="16" t="s">
+      <c r="C37" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="D37" s="20" t="s">
-        <v>215</v>
-      </c>
-      <c r="E37" s="17" t="s">
+      <c r="D37" s="17" t="s">
+        <v>209</v>
+      </c>
+      <c r="E37" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="F37" s="17" t="s">
+      <c r="F37" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="G37" s="17" t="s">
+      <c r="G37" s="14" t="s">
         <v>66</v>
       </c>
       <c r="H37" s="5"/>
@@ -3632,26 +3609,26 @@
       <c r="L37" s="5"/>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A38" s="18" t="s">
+      <c r="A38" s="15" t="s">
         <v>92</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="C38" s="16" t="s">
+        <v>309</v>
+      </c>
+      <c r="C38" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="D38" s="20" t="s">
-        <v>319</v>
-      </c>
-      <c r="E38" s="17" t="s">
-        <v>320</v>
-      </c>
-      <c r="F38" s="17" t="s">
-        <v>320</v>
-      </c>
-      <c r="G38" s="17" t="s">
-        <v>320</v>
+      <c r="D38" s="17" t="s">
+        <v>310</v>
+      </c>
+      <c r="E38" s="14" t="s">
+        <v>311</v>
+      </c>
+      <c r="F38" s="14" t="s">
+        <v>311</v>
+      </c>
+      <c r="G38" s="14" t="s">
+        <v>311</v>
       </c>
       <c r="H38" s="5"/>
       <c r="I38" s="5"/>
@@ -3660,25 +3637,25 @@
       <c r="L38" s="5"/>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A39" s="18" t="s">
+      <c r="A39" s="15" t="s">
         <v>92</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C39" s="16" t="s">
+      <c r="C39" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="D39" s="20" t="s">
-        <v>210</v>
-      </c>
-      <c r="E39" s="17" t="s">
+      <c r="D39" s="17" t="s">
+        <v>204</v>
+      </c>
+      <c r="E39" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="F39" s="17" t="s">
+      <c r="F39" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="G39" s="17" t="s">
+      <c r="G39" s="14" t="s">
         <v>60</v>
       </c>
       <c r="H39" s="5"/>
@@ -3688,26 +3665,26 @@
       <c r="L39" s="5"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A40" s="18" t="s">
+      <c r="A40" s="15" t="s">
         <v>92</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C40" s="16" t="s">
+      <c r="C40" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="D40" s="20" t="s">
-        <v>211</v>
-      </c>
-      <c r="E40" s="17" t="s">
-        <v>268</v>
-      </c>
-      <c r="F40" s="17" t="s">
-        <v>268</v>
-      </c>
-      <c r="G40" s="17" t="s">
-        <v>268</v>
+      <c r="D40" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="E40" s="14" t="s">
+        <v>262</v>
+      </c>
+      <c r="F40" s="14" t="s">
+        <v>262</v>
+      </c>
+      <c r="G40" s="14" t="s">
+        <v>262</v>
       </c>
       <c r="H40" s="5"/>
       <c r="I40" s="5"/>
@@ -3716,26 +3693,26 @@
       <c r="L40" s="5"/>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A41" s="18" t="s">
+      <c r="A41" s="15" t="s">
         <v>92</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C41" s="16" t="s">
-        <v>185</v>
-      </c>
-      <c r="D41" s="20" t="s">
-        <v>212</v>
-      </c>
-      <c r="E41" s="17" t="s">
-        <v>271</v>
-      </c>
-      <c r="F41" s="17" t="s">
-        <v>271</v>
-      </c>
-      <c r="G41" s="17" t="s">
-        <v>271</v>
+      <c r="C41" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="D41" s="17" t="s">
+        <v>206</v>
+      </c>
+      <c r="E41" s="14" t="s">
+        <v>265</v>
+      </c>
+      <c r="F41" s="14" t="s">
+        <v>265</v>
+      </c>
+      <c r="G41" s="14" t="s">
+        <v>265</v>
       </c>
       <c r="H41" s="5"/>
       <c r="I41" s="5"/>
@@ -3744,53 +3721,53 @@
       <c r="L41" s="5"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A42" s="18" t="s">
+      <c r="A42" s="15" t="s">
         <v>92</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="C42" s="16" t="s">
+      <c r="C42" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="D42" s="20" t="s">
-        <v>216</v>
-      </c>
-      <c r="E42" s="17" t="s">
-        <v>266</v>
-      </c>
-      <c r="F42" s="17" t="s">
-        <v>266</v>
-      </c>
-      <c r="G42" s="17" t="s">
-        <v>266</v>
-      </c>
-      <c r="H42" s="17"/>
+      <c r="D42" s="17" t="s">
+        <v>210</v>
+      </c>
+      <c r="E42" s="14" t="s">
+        <v>260</v>
+      </c>
+      <c r="F42" s="14" t="s">
+        <v>260</v>
+      </c>
+      <c r="G42" s="14" t="s">
+        <v>260</v>
+      </c>
+      <c r="H42" s="14"/>
       <c r="I42" s="5"/>
       <c r="J42" s="5"/>
       <c r="K42" s="5"/>
       <c r="L42" s="5"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A43" s="15" t="s">
+      <c r="A43" s="12" t="s">
         <v>90</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="C43" s="16" t="s">
+        <v>278</v>
+      </c>
+      <c r="C43" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="D43" s="20" t="s">
-        <v>219</v>
-      </c>
-      <c r="E43" s="17" t="s">
+      <c r="D43" s="17" t="s">
+        <v>213</v>
+      </c>
+      <c r="E43" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="F43" s="17" t="s">
+      <c r="F43" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="G43" s="17" t="s">
+      <c r="G43" s="14" t="s">
         <v>70</v>
       </c>
       <c r="H43" s="5"/>
@@ -3800,25 +3777,25 @@
       <c r="L43" s="5"/>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A44" s="15" t="s">
+      <c r="A44" s="12" t="s">
         <v>90</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="C44" s="16" t="s">
+        <v>175</v>
+      </c>
+      <c r="C44" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="D44" s="20" t="s">
-        <v>220</v>
-      </c>
-      <c r="E44" s="17" t="s">
+      <c r="D44" s="17" t="s">
+        <v>214</v>
+      </c>
+      <c r="E44" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="F44" s="17" t="s">
+      <c r="F44" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="G44" s="17" t="s">
+      <c r="G44" s="14" t="s">
         <v>72</v>
       </c>
       <c r="H44" s="5"/>
@@ -3828,26 +3805,26 @@
       <c r="L44" s="5"/>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A45" s="15" t="s">
+      <c r="A45" s="12" t="s">
         <v>90</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="C45" s="16" t="s">
+        <v>279</v>
+      </c>
+      <c r="C45" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="D45" s="20" t="s">
-        <v>221</v>
-      </c>
-      <c r="E45" s="17" t="s">
-        <v>341</v>
+      <c r="D45" s="17" t="s">
+        <v>215</v>
+      </c>
+      <c r="E45" s="14" t="s">
+        <v>332</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="H45" s="5"/>
       <c r="I45" s="5"/>
@@ -3856,26 +3833,26 @@
       <c r="L45" s="5"/>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A46" s="15" t="s">
+      <c r="A46" s="12" t="s">
         <v>90</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="C46" s="16" t="s">
+      <c r="C46" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="D46" s="20" t="s">
-        <v>222</v>
-      </c>
-      <c r="E46" s="17" t="s">
-        <v>342</v>
+      <c r="D46" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="E46" s="14" t="s">
+        <v>333</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="H46" s="5"/>
       <c r="I46" s="5"/>
@@ -3884,25 +3861,25 @@
       <c r="L46" s="5"/>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A47" s="15" t="s">
+      <c r="A47" s="12" t="s">
         <v>90</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="C47" s="16" t="s">
+      <c r="C47" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="D47" s="20" t="s">
-        <v>223</v>
-      </c>
-      <c r="E47" s="17" t="s">
+      <c r="D47" s="17" t="s">
+        <v>217</v>
+      </c>
+      <c r="E47" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="F47" s="17" t="s">
+      <c r="F47" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="G47" s="17" t="s">
+      <c r="G47" s="14" t="s">
         <v>76</v>
       </c>
       <c r="H47" s="5"/>
@@ -3912,26 +3889,26 @@
       <c r="L47" s="5"/>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A48" s="15" t="s">
+      <c r="A48" s="12" t="s">
         <v>90</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="C48" s="16" t="s">
+      <c r="C48" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="D48" s="20" t="s">
-        <v>224</v>
-      </c>
-      <c r="E48" s="17" t="s">
+      <c r="D48" s="17" t="s">
+        <v>218</v>
+      </c>
+      <c r="E48" s="14" t="s">
         <v>78</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="H48" s="5"/>
       <c r="I48" s="5"/>
@@ -3940,25 +3917,25 @@
       <c r="L48" s="5"/>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A49" s="18" t="s">
+      <c r="A49" s="15" t="s">
         <v>91</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>334</v>
-      </c>
-      <c r="C49" s="16" t="s">
+        <v>325</v>
+      </c>
+      <c r="C49" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="D49" s="20" t="s">
-        <v>225</v>
-      </c>
-      <c r="E49" s="17" t="s">
+      <c r="D49" s="17" t="s">
+        <v>219</v>
+      </c>
+      <c r="E49" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="F49" s="17" t="s">
+      <c r="F49" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="G49" s="17" t="s">
+      <c r="G49" s="14" t="s">
         <v>80</v>
       </c>
       <c r="H49" s="5"/>
@@ -3968,25 +3945,25 @@
       <c r="L49" s="5"/>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A50" s="18" t="s">
+      <c r="A50" s="15" t="s">
         <v>91</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>335</v>
-      </c>
-      <c r="C50" s="16" t="s">
+        <v>326</v>
+      </c>
+      <c r="C50" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="D50" s="20" t="s">
-        <v>226</v>
-      </c>
-      <c r="E50" s="17" t="s">
+      <c r="D50" s="17" t="s">
+        <v>220</v>
+      </c>
+      <c r="E50" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="F50" s="17" t="s">
+      <c r="F50" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="G50" s="17" t="s">
+      <c r="G50" s="14" t="s">
         <v>82</v>
       </c>
       <c r="H50" s="5"/>
@@ -3996,25 +3973,25 @@
       <c r="L50" s="5"/>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A51" s="18" t="s">
+      <c r="A51" s="15" t="s">
         <v>91</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>336</v>
-      </c>
-      <c r="C51" s="16" t="s">
+        <v>327</v>
+      </c>
+      <c r="C51" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="D51" s="20" t="s">
-        <v>227</v>
-      </c>
-      <c r="E51" s="17" t="s">
+      <c r="D51" s="17" t="s">
+        <v>221</v>
+      </c>
+      <c r="E51" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="F51" s="17" t="s">
+      <c r="F51" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="G51" s="17" t="s">
+      <c r="G51" s="14" t="s">
         <v>84</v>
       </c>
       <c r="H51" s="5"/>
@@ -4024,26 +4001,26 @@
       <c r="L51" s="5"/>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A52" s="18" t="s">
+      <c r="A52" s="15" t="s">
         <v>91</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>337</v>
-      </c>
-      <c r="C52" s="16" t="s">
+        <v>328</v>
+      </c>
+      <c r="C52" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="D52" s="20" t="s">
-        <v>228</v>
-      </c>
-      <c r="E52" s="17" t="s">
-        <v>267</v>
-      </c>
-      <c r="F52" s="17" t="s">
-        <v>267</v>
-      </c>
-      <c r="G52" s="17" t="s">
-        <v>267</v>
+      <c r="D52" s="17" t="s">
+        <v>222</v>
+      </c>
+      <c r="E52" s="14" t="s">
+        <v>261</v>
+      </c>
+      <c r="F52" s="14" t="s">
+        <v>261</v>
+      </c>
+      <c r="G52" s="14" t="s">
+        <v>261</v>
       </c>
       <c r="H52" s="5"/>
       <c r="I52" s="5"/>
@@ -4052,26 +4029,26 @@
       <c r="L52" s="5"/>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A53" s="15" t="s">
+      <c r="A53" s="12" t="s">
         <v>111</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="C53" s="16" t="s">
+        <v>176</v>
+      </c>
+      <c r="C53" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="D53" s="20" t="s">
-        <v>229</v>
-      </c>
-      <c r="E53" s="19" t="s">
-        <v>232</v>
-      </c>
-      <c r="F53" s="19" t="s">
-        <v>232</v>
-      </c>
-      <c r="G53" s="19" t="s">
-        <v>232</v>
+      <c r="D53" s="17" t="s">
+        <v>223</v>
+      </c>
+      <c r="E53" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="F53" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="G53" s="16" t="s">
+        <v>226</v>
       </c>
       <c r="H53" s="5"/>
       <c r="I53" s="5"/>
@@ -4080,26 +4057,26 @@
       <c r="L53" s="5"/>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A54" s="15" t="s">
+      <c r="A54" s="12" t="s">
         <v>111</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="C54" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="C54" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="D54" s="20" t="s">
-        <v>230</v>
-      </c>
-      <c r="E54" s="19" t="s">
-        <v>233</v>
-      </c>
-      <c r="F54" s="19" t="s">
-        <v>233</v>
-      </c>
-      <c r="G54" s="19" t="s">
-        <v>233</v>
+      <c r="D54" s="17" t="s">
+        <v>224</v>
+      </c>
+      <c r="E54" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="F54" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="G54" s="16" t="s">
+        <v>227</v>
       </c>
       <c r="H54" s="5"/>
       <c r="I54" s="5"/>
@@ -4108,26 +4085,26 @@
       <c r="L54" s="5"/>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A55" s="18" t="s">
-        <v>343</v>
-      </c>
-      <c r="B55" s="19" t="s">
-        <v>344</v>
-      </c>
-      <c r="C55" s="16" t="s">
+      <c r="A55" s="15" t="s">
+        <v>334</v>
+      </c>
+      <c r="B55" s="16" t="s">
+        <v>335</v>
+      </c>
+      <c r="C55" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="D55" s="20" t="s">
-        <v>346</v>
-      </c>
-      <c r="E55" s="19" t="s">
-        <v>348</v>
-      </c>
-      <c r="F55" s="19" t="s">
-        <v>348</v>
-      </c>
-      <c r="G55" s="19" t="s">
-        <v>348</v>
+      <c r="D55" s="17" t="s">
+        <v>337</v>
+      </c>
+      <c r="E55" s="16" t="s">
+        <v>339</v>
+      </c>
+      <c r="F55" s="16" t="s">
+        <v>339</v>
+      </c>
+      <c r="G55" s="16" t="s">
+        <v>339</v>
       </c>
       <c r="H55" s="5"/>
       <c r="I55" s="5"/>
@@ -4136,26 +4113,26 @@
       <c r="L55" s="5"/>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A56" s="18" t="s">
-        <v>343</v>
-      </c>
-      <c r="B56" s="19" t="s">
-        <v>345</v>
-      </c>
-      <c r="C56" s="16" t="s">
+      <c r="A56" s="15" t="s">
+        <v>334</v>
+      </c>
+      <c r="B56" s="16" t="s">
+        <v>336</v>
+      </c>
+      <c r="C56" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="D56" s="20" t="s">
-        <v>347</v>
-      </c>
-      <c r="E56" s="19" t="s">
-        <v>349</v>
-      </c>
-      <c r="F56" s="19" t="s">
-        <v>349</v>
-      </c>
-      <c r="G56" s="19" t="s">
-        <v>349</v>
+      <c r="D56" s="17" t="s">
+        <v>338</v>
+      </c>
+      <c r="E56" s="16" t="s">
+        <v>340</v>
+      </c>
+      <c r="F56" s="16" t="s">
+        <v>340</v>
+      </c>
+      <c r="G56" s="16" t="s">
+        <v>340</v>
       </c>
       <c r="H56" s="5"/>
       <c r="I56" s="5"/>
@@ -4165,10 +4142,10 @@
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" s="5"/>
-      <c r="B57" s="19"/>
-      <c r="C57" s="16"/>
-      <c r="D57" s="17"/>
-      <c r="E57" s="19"/>
+      <c r="B57" s="16"/>
+      <c r="C57" s="13"/>
+      <c r="D57" s="14"/>
+      <c r="E57" s="16"/>
       <c r="F57" s="5"/>
       <c r="G57" s="5"/>
       <c r="H57" s="5"/>
@@ -4179,10 +4156,10 @@
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" s="5"/>
-      <c r="B58" s="19"/>
-      <c r="C58" s="16"/>
-      <c r="D58" s="17"/>
-      <c r="E58" s="19"/>
+      <c r="B58" s="16"/>
+      <c r="C58" s="13"/>
+      <c r="D58" s="14"/>
+      <c r="E58" s="16"/>
       <c r="F58" s="5"/>
       <c r="G58" s="5"/>
       <c r="H58" s="5"/>
@@ -4193,10 +4170,10 @@
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" s="5"/>
-      <c r="B59" s="19"/>
-      <c r="C59" s="16"/>
-      <c r="D59" s="17"/>
-      <c r="E59" s="19"/>
+      <c r="B59" s="16"/>
+      <c r="C59" s="13"/>
+      <c r="D59" s="14"/>
+      <c r="E59" s="16"/>
       <c r="F59" s="5"/>
       <c r="G59" s="5"/>
       <c r="H59" s="5"/>
@@ -4207,10 +4184,10 @@
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" s="5"/>
-      <c r="B60" s="19"/>
-      <c r="C60" s="16"/>
-      <c r="D60" s="17"/>
-      <c r="E60" s="19"/>
+      <c r="B60" s="16"/>
+      <c r="C60" s="13"/>
+      <c r="D60" s="14"/>
+      <c r="E60" s="16"/>
       <c r="F60" s="5"/>
       <c r="G60" s="5"/>
       <c r="H60" s="5"/>
@@ -4221,10 +4198,10 @@
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" s="5"/>
-      <c r="B61" s="19"/>
-      <c r="C61" s="16"/>
-      <c r="D61" s="17"/>
-      <c r="E61" s="19"/>
+      <c r="B61" s="16"/>
+      <c r="C61" s="13"/>
+      <c r="D61" s="14"/>
+      <c r="E61" s="16"/>
       <c r="F61" s="5"/>
       <c r="G61" s="5"/>
       <c r="H61" s="5"/>
@@ -4235,10 +4212,10 @@
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" s="5"/>
-      <c r="B62" s="19"/>
-      <c r="C62" s="16"/>
-      <c r="D62" s="17"/>
-      <c r="E62" s="19"/>
+      <c r="B62" s="16"/>
+      <c r="C62" s="13"/>
+      <c r="D62" s="14"/>
+      <c r="E62" s="16"/>
       <c r="F62" s="5"/>
       <c r="G62" s="5"/>
       <c r="H62" s="5"/>
@@ -4249,10 +4226,10 @@
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" s="5"/>
-      <c r="B63" s="19"/>
-      <c r="C63" s="16"/>
-      <c r="D63" s="17"/>
-      <c r="E63" s="19"/>
+      <c r="B63" s="16"/>
+      <c r="C63" s="13"/>
+      <c r="D63" s="14"/>
+      <c r="E63" s="16"/>
       <c r="F63" s="5"/>
       <c r="G63" s="5"/>
       <c r="H63" s="5"/>
@@ -4263,10 +4240,10 @@
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" s="5"/>
-      <c r="B64" s="19"/>
-      <c r="C64" s="16"/>
-      <c r="D64" s="17"/>
-      <c r="E64" s="19"/>
+      <c r="B64" s="16"/>
+      <c r="C64" s="13"/>
+      <c r="D64" s="14"/>
+      <c r="E64" s="16"/>
       <c r="F64" s="5"/>
       <c r="G64" s="5"/>
       <c r="H64" s="5"/>
@@ -4277,10 +4254,10 @@
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" s="5"/>
-      <c r="B65" s="19"/>
-      <c r="C65" s="16"/>
-      <c r="D65" s="17"/>
-      <c r="E65" s="19"/>
+      <c r="B65" s="16"/>
+      <c r="C65" s="13"/>
+      <c r="D65" s="14"/>
+      <c r="E65" s="16"/>
       <c r="F65" s="5"/>
       <c r="G65" s="5"/>
       <c r="H65" s="5"/>
@@ -4291,10 +4268,10 @@
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" s="5"/>
-      <c r="B66" s="19"/>
-      <c r="C66" s="16"/>
-      <c r="D66" s="17"/>
-      <c r="E66" s="19"/>
+      <c r="B66" s="16"/>
+      <c r="C66" s="13"/>
+      <c r="D66" s="14"/>
+      <c r="E66" s="16"/>
       <c r="F66" s="5"/>
       <c r="G66" s="5"/>
       <c r="H66" s="5"/>
@@ -4305,10 +4282,10 @@
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" s="5"/>
-      <c r="B67" s="19"/>
-      <c r="C67" s="16"/>
-      <c r="D67" s="17"/>
-      <c r="E67" s="19"/>
+      <c r="B67" s="16"/>
+      <c r="C67" s="13"/>
+      <c r="D67" s="14"/>
+      <c r="E67" s="16"/>
       <c r="F67" s="5"/>
       <c r="G67" s="5"/>
       <c r="H67" s="5"/>
@@ -4319,10 +4296,10 @@
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" s="5"/>
-      <c r="B68" s="19"/>
-      <c r="C68" s="16"/>
-      <c r="D68" s="17"/>
-      <c r="E68" s="19"/>
+      <c r="B68" s="16"/>
+      <c r="C68" s="13"/>
+      <c r="D68" s="14"/>
+      <c r="E68" s="16"/>
       <c r="F68" s="5"/>
       <c r="G68" s="5"/>
       <c r="H68" s="5"/>
@@ -4333,10 +4310,10 @@
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" s="5"/>
-      <c r="B69" s="19"/>
-      <c r="C69" s="16"/>
-      <c r="D69" s="17"/>
-      <c r="E69" s="19"/>
+      <c r="B69" s="16"/>
+      <c r="C69" s="13"/>
+      <c r="D69" s="14"/>
+      <c r="E69" s="16"/>
       <c r="F69" s="5"/>
       <c r="G69" s="5"/>
       <c r="H69" s="5"/>
@@ -4347,10 +4324,10 @@
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A70" s="5"/>
-      <c r="B70" s="19"/>
-      <c r="C70" s="16"/>
-      <c r="D70" s="17"/>
-      <c r="E70" s="19"/>
+      <c r="B70" s="16"/>
+      <c r="C70" s="13"/>
+      <c r="D70" s="14"/>
+      <c r="E70" s="16"/>
       <c r="F70" s="5"/>
       <c r="G70" s="5"/>
       <c r="H70" s="5"/>
@@ -4361,10 +4338,10 @@
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A71" s="5"/>
-      <c r="B71" s="19"/>
-      <c r="C71" s="16"/>
-      <c r="D71" s="17"/>
-      <c r="E71" s="19"/>
+      <c r="B71" s="16"/>
+      <c r="C71" s="13"/>
+      <c r="D71" s="14"/>
+      <c r="E71" s="16"/>
       <c r="F71" s="5"/>
       <c r="G71" s="5"/>
       <c r="H71" s="5"/>
@@ -4375,10 +4352,10 @@
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A72" s="5"/>
-      <c r="B72" s="19"/>
-      <c r="C72" s="16"/>
-      <c r="D72" s="17"/>
-      <c r="E72" s="19"/>
+      <c r="B72" s="16"/>
+      <c r="C72" s="13"/>
+      <c r="D72" s="14"/>
+      <c r="E72" s="16"/>
       <c r="F72" s="5"/>
       <c r="G72" s="5"/>
       <c r="H72" s="5"/>
@@ -4389,10 +4366,10 @@
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" s="5"/>
-      <c r="B73" s="19"/>
-      <c r="C73" s="16"/>
-      <c r="D73" s="17"/>
-      <c r="E73" s="19"/>
+      <c r="B73" s="16"/>
+      <c r="C73" s="13"/>
+      <c r="D73" s="14"/>
+      <c r="E73" s="16"/>
       <c r="F73" s="5"/>
       <c r="G73" s="5"/>
       <c r="H73" s="5"/>
@@ -4403,10 +4380,10 @@
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A74" s="5"/>
-      <c r="B74" s="19"/>
-      <c r="C74" s="16"/>
-      <c r="D74" s="17"/>
-      <c r="E74" s="19"/>
+      <c r="B74" s="16"/>
+      <c r="C74" s="13"/>
+      <c r="D74" s="14"/>
+      <c r="E74" s="16"/>
       <c r="F74" s="5"/>
       <c r="G74" s="5"/>
       <c r="H74" s="5"/>
@@ -4417,10 +4394,10 @@
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75" s="5"/>
-      <c r="B75" s="19"/>
-      <c r="C75" s="16"/>
-      <c r="D75" s="17"/>
-      <c r="E75" s="19"/>
+      <c r="B75" s="16"/>
+      <c r="C75" s="13"/>
+      <c r="D75" s="14"/>
+      <c r="E75" s="16"/>
       <c r="F75" s="5"/>
       <c r="G75" s="5"/>
       <c r="H75" s="5"/>
@@ -4431,10 +4408,10 @@
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76" s="5"/>
-      <c r="B76" s="19"/>
-      <c r="C76" s="16"/>
-      <c r="D76" s="17"/>
-      <c r="E76" s="19"/>
+      <c r="B76" s="16"/>
+      <c r="C76" s="13"/>
+      <c r="D76" s="14"/>
+      <c r="E76" s="16"/>
       <c r="F76" s="5"/>
       <c r="G76" s="5"/>
       <c r="H76" s="5"/>
@@ -4445,10 +4422,10 @@
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A77" s="5"/>
-      <c r="B77" s="19"/>
-      <c r="C77" s="16"/>
-      <c r="D77" s="17"/>
-      <c r="E77" s="19"/>
+      <c r="B77" s="16"/>
+      <c r="C77" s="13"/>
+      <c r="D77" s="14"/>
+      <c r="E77" s="16"/>
       <c r="F77" s="5"/>
       <c r="G77" s="5"/>
       <c r="H77" s="5"/>
@@ -4459,10 +4436,10 @@
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A78" s="5"/>
-      <c r="B78" s="19"/>
-      <c r="C78" s="16"/>
-      <c r="D78" s="17"/>
-      <c r="E78" s="19"/>
+      <c r="B78" s="16"/>
+      <c r="C78" s="13"/>
+      <c r="D78" s="14"/>
+      <c r="E78" s="16"/>
       <c r="F78" s="5"/>
       <c r="G78" s="5"/>
       <c r="H78" s="5"/>
@@ -4473,10 +4450,10 @@
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A79" s="5"/>
-      <c r="B79" s="19"/>
-      <c r="C79" s="16"/>
-      <c r="D79" s="17"/>
-      <c r="E79" s="19"/>
+      <c r="B79" s="16"/>
+      <c r="C79" s="13"/>
+      <c r="D79" s="14"/>
+      <c r="E79" s="16"/>
       <c r="F79" s="5"/>
       <c r="G79" s="5"/>
       <c r="H79" s="5"/>
@@ -4487,10 +4464,10 @@
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A80" s="5"/>
-      <c r="B80" s="19"/>
-      <c r="C80" s="16"/>
-      <c r="D80" s="17"/>
-      <c r="E80" s="19"/>
+      <c r="B80" s="16"/>
+      <c r="C80" s="13"/>
+      <c r="D80" s="14"/>
+      <c r="E80" s="16"/>
       <c r="F80" s="5"/>
       <c r="G80" s="5"/>
       <c r="H80" s="5"/>
@@ -4501,10 +4478,10 @@
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A81" s="5"/>
-      <c r="B81" s="19"/>
-      <c r="C81" s="16"/>
-      <c r="D81" s="17"/>
-      <c r="E81" s="19"/>
+      <c r="B81" s="16"/>
+      <c r="C81" s="13"/>
+      <c r="D81" s="14"/>
+      <c r="E81" s="16"/>
       <c r="F81" s="5"/>
       <c r="G81" s="5"/>
       <c r="H81" s="5"/>
@@ -4515,10 +4492,10 @@
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A82" s="5"/>
-      <c r="B82" s="19"/>
-      <c r="C82" s="16"/>
-      <c r="D82" s="17"/>
-      <c r="E82" s="19"/>
+      <c r="B82" s="16"/>
+      <c r="C82" s="13"/>
+      <c r="D82" s="14"/>
+      <c r="E82" s="16"/>
       <c r="F82" s="5"/>
       <c r="G82" s="5"/>
       <c r="H82" s="5"/>
@@ -4529,10 +4506,10 @@
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A83" s="5"/>
-      <c r="B83" s="19"/>
-      <c r="C83" s="16"/>
-      <c r="D83" s="17"/>
-      <c r="E83" s="19"/>
+      <c r="B83" s="16"/>
+      <c r="C83" s="13"/>
+      <c r="D83" s="14"/>
+      <c r="E83" s="16"/>
       <c r="F83" s="5"/>
       <c r="G83" s="5"/>
       <c r="H83" s="5"/>
@@ -4543,10 +4520,10 @@
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A84" s="5"/>
-      <c r="B84" s="19"/>
-      <c r="C84" s="16"/>
-      <c r="D84" s="17"/>
-      <c r="E84" s="19"/>
+      <c r="B84" s="16"/>
+      <c r="C84" s="13"/>
+      <c r="D84" s="14"/>
+      <c r="E84" s="16"/>
       <c r="F84" s="5"/>
       <c r="G84" s="5"/>
       <c r="H84" s="5"/>
@@ -4557,10 +4534,10 @@
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A85" s="5"/>
-      <c r="B85" s="19"/>
-      <c r="C85" s="16"/>
-      <c r="D85" s="17"/>
-      <c r="E85" s="19"/>
+      <c r="B85" s="16"/>
+      <c r="C85" s="13"/>
+      <c r="D85" s="14"/>
+      <c r="E85" s="16"/>
       <c r="F85" s="5"/>
       <c r="G85" s="5"/>
       <c r="H85" s="5"/>
@@ -4571,10 +4548,10 @@
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A86" s="5"/>
-      <c r="B86" s="19"/>
-      <c r="C86" s="16"/>
-      <c r="D86" s="17"/>
-      <c r="E86" s="19"/>
+      <c r="B86" s="16"/>
+      <c r="C86" s="13"/>
+      <c r="D86" s="14"/>
+      <c r="E86" s="16"/>
       <c r="F86" s="5"/>
       <c r="G86" s="5"/>
       <c r="H86" s="5"/>
@@ -4585,10 +4562,10 @@
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A87" s="5"/>
-      <c r="B87" s="19"/>
-      <c r="C87" s="16"/>
-      <c r="D87" s="17"/>
-      <c r="E87" s="19"/>
+      <c r="B87" s="16"/>
+      <c r="C87" s="13"/>
+      <c r="D87" s="14"/>
+      <c r="E87" s="16"/>
       <c r="F87" s="5"/>
       <c r="G87" s="5"/>
       <c r="H87" s="5"/>
@@ -4599,10 +4576,10 @@
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A88" s="5"/>
-      <c r="B88" s="19"/>
-      <c r="C88" s="16"/>
-      <c r="D88" s="17"/>
-      <c r="E88" s="19"/>
+      <c r="B88" s="16"/>
+      <c r="C88" s="13"/>
+      <c r="D88" s="14"/>
+      <c r="E88" s="16"/>
       <c r="F88" s="5"/>
       <c r="G88" s="5"/>
       <c r="H88" s="5"/>
@@ -4613,10 +4590,10 @@
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A89" s="5"/>
-      <c r="B89" s="19"/>
-      <c r="C89" s="16"/>
-      <c r="D89" s="17"/>
-      <c r="E89" s="19"/>
+      <c r="B89" s="16"/>
+      <c r="C89" s="13"/>
+      <c r="D89" s="14"/>
+      <c r="E89" s="16"/>
       <c r="F89" s="5"/>
       <c r="G89" s="5"/>
       <c r="H89" s="5"/>
@@ -4627,10 +4604,10 @@
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A90" s="5"/>
-      <c r="B90" s="19"/>
-      <c r="C90" s="16"/>
-      <c r="D90" s="17"/>
-      <c r="E90" s="19"/>
+      <c r="B90" s="16"/>
+      <c r="C90" s="13"/>
+      <c r="D90" s="14"/>
+      <c r="E90" s="16"/>
       <c r="F90" s="5"/>
       <c r="G90" s="5"/>
       <c r="H90" s="5"/>
@@ -4641,10 +4618,10 @@
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A91" s="5"/>
-      <c r="B91" s="19"/>
-      <c r="C91" s="16"/>
-      <c r="D91" s="17"/>
-      <c r="E91" s="19"/>
+      <c r="B91" s="16"/>
+      <c r="C91" s="13"/>
+      <c r="D91" s="14"/>
+      <c r="E91" s="16"/>
       <c r="F91" s="5"/>
       <c r="G91" s="5"/>
       <c r="H91" s="5"/>
@@ -4655,10 +4632,10 @@
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A92" s="5"/>
-      <c r="B92" s="19"/>
-      <c r="C92" s="16"/>
-      <c r="D92" s="17"/>
-      <c r="E92" s="19"/>
+      <c r="B92" s="16"/>
+      <c r="C92" s="13"/>
+      <c r="D92" s="14"/>
+      <c r="E92" s="16"/>
       <c r="F92" s="5"/>
       <c r="G92" s="5"/>
       <c r="H92" s="5"/>
@@ -4669,10 +4646,10 @@
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A93" s="5"/>
-      <c r="B93" s="19"/>
-      <c r="C93" s="16"/>
-      <c r="D93" s="17"/>
-      <c r="E93" s="19"/>
+      <c r="B93" s="16"/>
+      <c r="C93" s="13"/>
+      <c r="D93" s="14"/>
+      <c r="E93" s="16"/>
       <c r="F93" s="5"/>
       <c r="G93" s="5"/>
       <c r="H93" s="5"/>
@@ -4683,10 +4660,10 @@
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A94" s="5"/>
-      <c r="B94" s="19"/>
-      <c r="C94" s="16"/>
-      <c r="D94" s="17"/>
-      <c r="E94" s="19"/>
+      <c r="B94" s="16"/>
+      <c r="C94" s="13"/>
+      <c r="D94" s="14"/>
+      <c r="E94" s="16"/>
       <c r="F94" s="5"/>
       <c r="G94" s="5"/>
       <c r="H94" s="5"/>
@@ -4697,10 +4674,10 @@
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A95" s="5"/>
-      <c r="B95" s="19"/>
-      <c r="C95" s="16"/>
-      <c r="D95" s="17"/>
-      <c r="E95" s="19"/>
+      <c r="B95" s="16"/>
+      <c r="C95" s="13"/>
+      <c r="D95" s="14"/>
+      <c r="E95" s="16"/>
       <c r="F95" s="5"/>
       <c r="G95" s="5"/>
       <c r="H95" s="5"/>
@@ -4711,10 +4688,10 @@
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A96" s="5"/>
-      <c r="B96" s="19"/>
-      <c r="C96" s="16"/>
-      <c r="D96" s="17"/>
-      <c r="E96" s="19"/>
+      <c r="B96" s="16"/>
+      <c r="C96" s="13"/>
+      <c r="D96" s="14"/>
+      <c r="E96" s="16"/>
       <c r="F96" s="5"/>
       <c r="G96" s="5"/>
       <c r="H96" s="5"/>
@@ -4725,10 +4702,10 @@
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A97" s="5"/>
-      <c r="B97" s="19"/>
-      <c r="C97" s="16"/>
-      <c r="D97" s="17"/>
-      <c r="E97" s="19"/>
+      <c r="B97" s="16"/>
+      <c r="C97" s="13"/>
+      <c r="D97" s="14"/>
+      <c r="E97" s="16"/>
       <c r="F97" s="5"/>
       <c r="G97" s="5"/>
       <c r="H97" s="5"/>
@@ -4739,10 +4716,10 @@
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A98" s="5"/>
-      <c r="B98" s="19"/>
-      <c r="C98" s="16"/>
-      <c r="D98" s="17"/>
-      <c r="E98" s="19"/>
+      <c r="B98" s="16"/>
+      <c r="C98" s="13"/>
+      <c r="D98" s="14"/>
+      <c r="E98" s="16"/>
       <c r="F98" s="5"/>
       <c r="G98" s="5"/>
       <c r="H98" s="5"/>
@@ -4753,10 +4730,10 @@
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A99" s="5"/>
-      <c r="B99" s="19"/>
-      <c r="C99" s="16"/>
-      <c r="D99" s="17"/>
-      <c r="E99" s="19"/>
+      <c r="B99" s="16"/>
+      <c r="C99" s="13"/>
+      <c r="D99" s="14"/>
+      <c r="E99" s="16"/>
       <c r="F99" s="5"/>
       <c r="G99" s="5"/>
       <c r="H99" s="5"/>
@@ -4767,10 +4744,10 @@
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A100" s="5"/>
-      <c r="B100" s="19"/>
-      <c r="C100" s="16"/>
-      <c r="D100" s="17"/>
-      <c r="E100" s="19"/>
+      <c r="B100" s="16"/>
+      <c r="C100" s="13"/>
+      <c r="D100" s="14"/>
+      <c r="E100" s="16"/>
       <c r="F100" s="5"/>
       <c r="G100" s="5"/>
       <c r="H100" s="5"/>
@@ -4781,10 +4758,10 @@
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A101" s="5"/>
-      <c r="B101" s="19"/>
-      <c r="C101" s="16"/>
-      <c r="D101" s="17"/>
-      <c r="E101" s="19"/>
+      <c r="B101" s="16"/>
+      <c r="C101" s="13"/>
+      <c r="D101" s="14"/>
+      <c r="E101" s="16"/>
       <c r="F101" s="5"/>
       <c r="G101" s="5"/>
       <c r="H101" s="5"/>
@@ -4795,10 +4772,10 @@
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A102" s="5"/>
-      <c r="B102" s="19"/>
-      <c r="C102" s="16"/>
-      <c r="D102" s="17"/>
-      <c r="E102" s="19"/>
+      <c r="B102" s="16"/>
+      <c r="C102" s="13"/>
+      <c r="D102" s="14"/>
+      <c r="E102" s="16"/>
       <c r="F102" s="5"/>
       <c r="G102" s="5"/>
       <c r="H102" s="5"/>
@@ -4809,10 +4786,10 @@
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A103" s="5"/>
-      <c r="B103" s="19"/>
-      <c r="C103" s="16"/>
-      <c r="D103" s="17"/>
-      <c r="E103" s="19"/>
+      <c r="B103" s="16"/>
+      <c r="C103" s="13"/>
+      <c r="D103" s="14"/>
+      <c r="E103" s="16"/>
       <c r="F103" s="5"/>
       <c r="G103" s="5"/>
       <c r="H103" s="5"/>
@@ -4823,10 +4800,10 @@
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A104" s="5"/>
-      <c r="B104" s="19"/>
-      <c r="C104" s="16"/>
-      <c r="D104" s="17"/>
-      <c r="E104" s="19"/>
+      <c r="B104" s="16"/>
+      <c r="C104" s="13"/>
+      <c r="D104" s="14"/>
+      <c r="E104" s="16"/>
       <c r="F104" s="5"/>
       <c r="G104" s="5"/>
       <c r="H104" s="5"/>
@@ -4837,10 +4814,10 @@
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A105" s="5"/>
-      <c r="B105" s="19"/>
-      <c r="C105" s="16"/>
-      <c r="D105" s="17"/>
-      <c r="E105" s="19"/>
+      <c r="B105" s="16"/>
+      <c r="C105" s="13"/>
+      <c r="D105" s="14"/>
+      <c r="E105" s="16"/>
       <c r="F105" s="5"/>
       <c r="G105" s="5"/>
       <c r="H105" s="5"/>
@@ -4851,10 +4828,10 @@
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A106" s="5"/>
-      <c r="B106" s="19"/>
-      <c r="C106" s="16"/>
-      <c r="D106" s="17"/>
-      <c r="E106" s="19"/>
+      <c r="B106" s="16"/>
+      <c r="C106" s="13"/>
+      <c r="D106" s="14"/>
+      <c r="E106" s="16"/>
       <c r="F106" s="5"/>
       <c r="G106" s="5"/>
       <c r="H106" s="5"/>
@@ -4865,10 +4842,10 @@
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A107" s="5"/>
-      <c r="B107" s="19"/>
-      <c r="C107" s="16"/>
-      <c r="D107" s="17"/>
-      <c r="E107" s="19"/>
+      <c r="B107" s="16"/>
+      <c r="C107" s="13"/>
+      <c r="D107" s="14"/>
+      <c r="E107" s="16"/>
       <c r="F107" s="5"/>
       <c r="G107" s="5"/>
       <c r="H107" s="5"/>
@@ -4941,12 +4918,12 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="12" t="s">
         <v>89</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="6"/>
-      <c r="D2" s="21"/>
+      <c r="D2" s="18"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
@@ -4954,12 +4931,12 @@
       <c r="I2" s="5"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="15" t="s">
         <v>96</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="6"/>
-      <c r="D3" s="21"/>
+      <c r="D3" s="18"/>
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
@@ -4967,12 +4944,12 @@
       <c r="I3" s="5"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="12" t="s">
         <v>97</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="6"/>
-      <c r="D4" s="21"/>
+      <c r="D4" s="18"/>
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
       <c r="G4" s="5"/>
@@ -4980,42 +4957,42 @@
       <c r="I4" s="5"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="15" t="s">
         <v>95</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="21" t="s">
-        <v>242</v>
+      <c r="D5" s="18" t="s">
+        <v>236</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="15" t="s">
         <v>95</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="21" t="s">
-        <v>243</v>
+      <c r="D6" s="18" t="s">
+        <v>237</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>112</v>
@@ -5030,7 +5007,7 @@
       <c r="I6" s="5"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="15" t="s">
         <v>95</v>
       </c>
       <c r="B7" s="4" t="s">
@@ -5039,253 +5016,253 @@
       <c r="C7" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="21" t="s">
-        <v>244</v>
+      <c r="D7" s="18" t="s">
+        <v>238</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="H7" s="5"/>
       <c r="I7" s="5"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="15" t="s">
         <v>95</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="21" t="s">
-        <v>245</v>
+      <c r="D8" s="18" t="s">
+        <v>239</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="H8" s="5"/>
       <c r="I8" s="5"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="15" t="s">
         <v>95</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="D9" s="21" t="s">
-        <v>246</v>
+      <c r="D9" s="18" t="s">
+        <v>240</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="H9" s="5"/>
       <c r="I9" s="5"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="15" t="s">
         <v>95</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D10" s="21" t="s">
-        <v>247</v>
+      <c r="D10" s="18" t="s">
+        <v>241</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="15" t="s">
         <v>95</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="D11" s="21" t="s">
-        <v>248</v>
+      <c r="D11" s="18" t="s">
+        <v>242</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="H11" s="5"/>
       <c r="I11" s="5"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="18" t="s">
+      <c r="A12" s="15" t="s">
         <v>95</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="D12" s="21" t="s">
-        <v>249</v>
+      <c r="D12" s="18" t="s">
+        <v>243</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="18" t="s">
+      <c r="A13" s="15" t="s">
         <v>95</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D13" s="21" t="s">
-        <v>250</v>
+      <c r="D13" s="18" t="s">
+        <v>244</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="18" t="s">
+      <c r="A14" s="15" t="s">
         <v>95</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="D14" s="21" t="s">
-        <v>251</v>
+      <c r="D14" s="18" t="s">
+        <v>245</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="H14" s="5"/>
       <c r="I14" s="5"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="18" t="s">
+      <c r="A15" s="15" t="s">
         <v>95</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="D15" s="21" t="s">
-        <v>249</v>
+      <c r="D15" s="18" t="s">
+        <v>243</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" s="18" t="s">
+      <c r="A16" s="15" t="s">
         <v>95</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D16" s="21" t="s">
-        <v>252</v>
+      <c r="D16" s="18" t="s">
+        <v>246</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="H16" s="5"/>
       <c r="I16" s="5"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" s="15" t="s">
+      <c r="A17" s="12" t="s">
         <v>94</v>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="6"/>
-      <c r="D17" s="21"/>
+      <c r="D17" s="18"/>
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
@@ -5293,35 +5270,35 @@
       <c r="I17" s="5"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="18" t="s">
+      <c r="A18" s="15" t="s">
         <v>99</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>116</v>
       </c>
       <c r="C18" s="6"/>
-      <c r="D18" s="21" t="s">
-        <v>253</v>
+      <c r="D18" s="18" t="s">
+        <v>247</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="15" t="s">
+      <c r="A19" s="12" t="s">
         <v>93</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="6"/>
-      <c r="D19" s="21"/>
+      <c r="D19" s="18"/>
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
@@ -5329,393 +5306,393 @@
       <c r="I19" s="5"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="18" t="s">
+      <c r="A20" s="15" t="s">
         <v>92</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="C20" s="6"/>
-      <c r="D20" s="21" t="s">
-        <v>276</v>
+      <c r="D20" s="18" t="s">
+        <v>270</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="H20" s="5"/>
       <c r="I20" s="5"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="18" t="s">
+      <c r="A21" s="15" t="s">
         <v>92</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="C21" s="6"/>
-      <c r="D21" s="21" t="s">
-        <v>277</v>
+      <c r="D21" s="18" t="s">
+        <v>271</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="H21" s="5"/>
       <c r="I21" s="5"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="18" t="s">
+      <c r="A22" s="15" t="s">
         <v>92</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>115</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>317</v>
-      </c>
-      <c r="D22" s="21" t="s">
-        <v>278</v>
+        <v>308</v>
+      </c>
+      <c r="D22" s="18" t="s">
+        <v>272</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="18" t="s">
+      <c r="A23" s="15" t="s">
         <v>92</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C23" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D23" s="18" t="s">
+        <v>273</v>
+      </c>
+      <c r="E23" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="D23" s="21" t="s">
-        <v>279</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>147</v>
-      </c>
       <c r="F23" s="5" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="H23" s="5"/>
       <c r="I23" s="5"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="15" t="s">
+      <c r="A24" s="12" t="s">
         <v>90</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C24" s="6"/>
-      <c r="D24" s="21" t="s">
-        <v>262</v>
+      <c r="D24" s="18" t="s">
+        <v>256</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="H24" s="5"/>
       <c r="I24" s="5"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="15" t="s">
+      <c r="A25" s="12" t="s">
         <v>90</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="D25" s="21" t="s">
-        <v>263</v>
+      <c r="D25" s="18" t="s">
+        <v>257</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="H25" s="5"/>
       <c r="I25" s="5"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A26" s="15" t="s">
+      <c r="A26" s="12" t="s">
         <v>90</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="D26" s="21" t="s">
-        <v>272</v>
+        <v>121</v>
+      </c>
+      <c r="D26" s="18" t="s">
+        <v>266</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="H26" s="5"/>
       <c r="I26" s="5"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A27" s="15" t="s">
+      <c r="A27" s="12" t="s">
         <v>90</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="D27" s="21" t="s">
-        <v>264</v>
+      <c r="D27" s="18" t="s">
+        <v>258</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="H27" s="5"/>
       <c r="I27" s="5"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" s="18" t="s">
+      <c r="A28" s="15" t="s">
         <v>91</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="D28" s="21" t="s">
-        <v>254</v>
+      <c r="D28" s="18" t="s">
+        <v>248</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="H28" s="5"/>
       <c r="I28" s="5"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A29" s="18" t="s">
+      <c r="A29" s="15" t="s">
         <v>91</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="D29" s="21" t="s">
-        <v>255</v>
+      <c r="D29" s="18" t="s">
+        <v>249</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="H29" s="5"/>
       <c r="I29" s="5"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A30" s="18" t="s">
+      <c r="A30" s="15" t="s">
         <v>91</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="D30" s="21" t="s">
-        <v>256</v>
+      <c r="D30" s="18" t="s">
+        <v>250</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="H30" s="5"/>
       <c r="I30" s="5"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A31" s="18" t="s">
+      <c r="A31" s="15" t="s">
         <v>91</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D31" s="21" t="s">
-        <v>257</v>
+      <c r="D31" s="18" t="s">
+        <v>251</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="H31" s="5"/>
       <c r="I31" s="5"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A32" s="18" t="s">
+      <c r="A32" s="15" t="s">
         <v>91</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="D32" s="21" t="s">
-        <v>258</v>
+      <c r="D32" s="18" t="s">
+        <v>252</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="H32" s="5"/>
       <c r="I32" s="5"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A33" s="18" t="s">
+      <c r="A33" s="15" t="s">
         <v>91</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="D33" s="21" t="s">
-        <v>259</v>
+      <c r="D33" s="18" t="s">
+        <v>253</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="H33" s="5"/>
       <c r="I33" s="5"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A34" s="18" t="s">
+      <c r="A34" s="15" t="s">
         <v>91</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="D34" s="21" t="s">
-        <v>260</v>
+      <c r="D34" s="18" t="s">
+        <v>254</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A35" s="18" t="s">
+      <c r="A35" s="15" t="s">
         <v>91</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D35" s="21" t="s">
-        <v>261</v>
+      <c r="D35" s="18" t="s">
+        <v>255</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
@@ -5729,89 +5706,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6C1B83A-C39F-40B8-8309-44C0020910F4}">
-  <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" s="21" t="s">
-        <v>280</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="D3" s="21" t="s">
-        <v>282</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/eBus_Functions/Post_Processing/Root_Cause_Analysis_Work/info/eBus_Model_Info.xlsx
+++ b/eBus_Functions/Post_Processing/Root_Cause_Analysis_Work/info/eBus_Model_Info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\TempData\Github\eBus_Tool\eBus_Functions\Post_Processing\Root_Cause_Analysis_Work\info\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF227378-3B1D-4275-BAFD-D07C7631569C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCF1F810-C04D-4BFA-B43E-40A72C0038C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Block_Diagram" sheetId="1" r:id="rId1"/>
